--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -1862,13 +1862,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46122.38452245371</v>
+        <v>46122.55118912037</v>
       </c>
       <c r="C4" s="5">
-        <v>46128.426341053244</v>
+        <v>46128.59300771991</v>
       </c>
       <c r="D4" s="5">
-        <v>46157.93633454861</v>
+        <v>46158.10300121528</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1911,13 +1911,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46122.38467905093</v>
+        <v>46122.55134571759</v>
       </c>
       <c r="C5" s="8">
-        <v>46128.42632796297</v>
+        <v>46128.59299462963</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.70935505787</v>
+        <v>46133.876021724536</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1974,13 +1974,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46122.384682812495</v>
+        <v>46122.55134947917</v>
       </c>
       <c r="C6" s="5">
-        <v>46128.42601201389</v>
+        <v>46128.59267868055</v>
       </c>
       <c r="D6" s="5">
-        <v>46128.43715965278</v>
+        <v>46128.60382631945</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2037,13 +2037,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46122.38468587963</v>
+        <v>46122.551352546296</v>
       </c>
       <c r="C7" s="8">
-        <v>46128.42603200232</v>
+        <v>46128.59269866898</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.460593807875</v>
+        <v>46161.62726047453</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2100,13 +2100,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46122.38468890046</v>
+        <v>46122.551355567135</v>
       </c>
       <c r="C8" s="5">
-        <v>46128.42605055556</v>
+        <v>46128.59271722222</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.43733940972</v>
+        <v>46128.60400607639</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2163,13 +2163,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46122.384692719905</v>
+        <v>46122.551359386576</v>
       </c>
       <c r="C9" s="8">
-        <v>46128.4261833912</v>
+        <v>46128.592850057874</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.66910643518</v>
+        <v>46156.83577310185</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2226,11 +2226,11 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46122.3845274537</v>
+        <v>46122.55119412037</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46132.404066296294</v>
+        <v>46132.570732962966</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2273,13 +2273,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46122.384696504625</v>
+        <v>46122.5513631713</v>
       </c>
       <c r="C11" s="8">
-        <v>46128.43768854167</v>
+        <v>46128.60435520833</v>
       </c>
       <c r="D11" s="8">
-        <v>46129.000499456015</v>
+        <v>46129.16716612269</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2338,13 +2338,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46122.38470238426</v>
+        <v>46122.551369050925</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.43976447917</v>
+        <v>46128.60643114583</v>
       </c>
       <c r="D12" s="5">
-        <v>46136.039352175925</v>
+        <v>46136.2060188426</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2403,13 +2403,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46122.384708020836</v>
+        <v>46122.5513746875</v>
       </c>
       <c r="C13" s="8">
-        <v>46132.40405894676</v>
+        <v>46132.57072561343</v>
       </c>
       <c r="D13" s="8">
-        <v>46136.03935219908</v>
+        <v>46136.20601886574</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2468,13 +2468,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46122.38692751157</v>
+        <v>46122.553594178244</v>
       </c>
       <c r="C14" s="5">
-        <v>46128.44274908565</v>
+        <v>46128.60941575232</v>
       </c>
       <c r="D14" s="5">
-        <v>46136.03935251157</v>
+        <v>46136.20601917824</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2533,11 +2533,11 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46122.38471399306</v>
+        <v>46122.55138065972</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46136.03935212963</v>
+        <v>46136.20601879629</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2596,11 +2596,11 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46122.38453280093</v>
+        <v>46122.55119946759</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46181.49973898148</v>
+        <v>46181.66640564815</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2643,13 +2643,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46122.38472188657</v>
+        <v>46122.55138855324</v>
       </c>
       <c r="C17" s="8">
-        <v>46128.44033724537</v>
+        <v>46128.60700391204</v>
       </c>
       <c r="D17" s="8">
-        <v>46133.0133283912</v>
+        <v>46133.17999505787</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2708,13 +2708,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46122.38472815973</v>
+        <v>46122.55139482639</v>
       </c>
       <c r="C18" s="5">
-        <v>46128.44034490741</v>
+        <v>46128.60701157407</v>
       </c>
       <c r="D18" s="5">
-        <v>46132.01554025463</v>
+        <v>46132.182206921294</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2773,11 +2773,11 @@
         <v>80</v>
       </c>
       <c r="B19" s="8">
-        <v>46122.38473373842</v>
+        <v>46122.55140040509</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46139.00426390047</v>
+        <v>46139.170930567125</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>81</v>
@@ -2836,13 +2836,13 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46122.384739375004</v>
+        <v>46122.55140604167</v>
       </c>
       <c r="C20" s="5">
-        <v>46181.499732384254</v>
+        <v>46181.666399050926</v>
       </c>
       <c r="D20" s="5">
-        <v>46181.499747650465</v>
+        <v>46181.66641431713</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2901,13 +2901,13 @@
         <v>91</v>
       </c>
       <c r="B21" s="8">
-        <v>46122.3847449537</v>
+        <v>46122.55141162037</v>
       </c>
       <c r="C21" s="8">
-        <v>46128.442831215274</v>
+        <v>46128.609497881946</v>
       </c>
       <c r="D21" s="8">
-        <v>46132.01553989583</v>
+        <v>46132.1822065625</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>64</v>
@@ -2966,13 +2966,13 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46122.39987912037</v>
+        <v>46122.566545787035</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.49969386574</v>
+        <v>46181.66636053241</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.49971099537</v>
+        <v>46181.66637766204</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -3031,13 +3031,13 @@
         <v>97</v>
       </c>
       <c r="B23" s="8">
-        <v>46122.39994855324</v>
+        <v>46122.56661521991</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.499709641204</v>
+        <v>46181.66637630787</v>
       </c>
       <c r="D23" s="8">
-        <v>46181.499723877314</v>
+        <v>46181.66639054398</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>98</v>
@@ -3096,13 +3096,13 @@
         <v>100</v>
       </c>
       <c r="B24" s="5">
-        <v>46122.40619606481</v>
+        <v>46122.57286273148</v>
       </c>
       <c r="C24" s="5">
-        <v>46181.4997655787</v>
+        <v>46181.66643224537</v>
       </c>
       <c r="D24" s="5">
-        <v>46181.4998697338</v>
+        <v>46181.66653640046</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>101</v>
@@ -3161,11 +3161,11 @@
         <v>103</v>
       </c>
       <c r="B25" s="8">
-        <v>46122.38453728009</v>
+        <v>46122.55120394676</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46181.50021655092</v>
+        <v>46181.66688321759</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>104</v>
@@ -3208,13 +3208,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46122.38475027778</v>
+        <v>46122.55141694444</v>
       </c>
       <c r="C26" s="5">
-        <v>46174.45950203703</v>
+        <v>46174.626168703704</v>
       </c>
       <c r="D26" s="5">
-        <v>46174.45951446759</v>
+        <v>46174.626181134256</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3273,13 +3273,13 @@
         <v>111</v>
       </c>
       <c r="B27" s="8">
-        <v>46122.38475541667</v>
+        <v>46122.55142208333</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.45658625</v>
+        <v>46174.62325291667</v>
       </c>
       <c r="D27" s="8">
-        <v>46174.456587824076</v>
+        <v>46174.62325449074</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>112</v>
@@ -3334,13 +3334,13 @@
         <v>115</v>
       </c>
       <c r="B28" s="5">
-        <v>46122.38476032407</v>
+        <v>46122.55142699074</v>
       </c>
       <c r="C28" s="5">
-        <v>46174.45948622686</v>
+        <v>46174.626152893514</v>
       </c>
       <c r="D28" s="5">
-        <v>46174.45948762732</v>
+        <v>46174.62615429398</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>116</v>
@@ -3395,11 +3395,11 @@
         <v>118</v>
       </c>
       <c r="B29" s="8">
-        <v>46122.38476556713</v>
+        <v>46122.5514322338</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46183.01826041666</v>
+        <v>46183.18492708333</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>119</v>
@@ -3458,11 +3458,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46122.38477087963</v>
+        <v>46122.551437546295</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46141.0031746875</v>
+        <v>46141.16984135417</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3517,11 +3517,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="8">
-        <v>46122.3847758912</v>
+        <v>46122.55144255787</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46125.424820879634</v>
+        <v>46125.59148754629</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>125</v>
@@ -3576,13 +3576,13 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46122.38478104166</v>
+        <v>46122.551447708334</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.661133263886</v>
+        <v>46133.82779993056</v>
       </c>
       <c r="D32" s="5">
-        <v>46133.66114655093</v>
+        <v>46133.82781321759</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3641,13 +3641,13 @@
         <v>130</v>
       </c>
       <c r="B33" s="8">
-        <v>46122.38478609954</v>
+        <v>46122.5514527662</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.66106445601</v>
+        <v>46133.827731122685</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.6610659375</v>
+        <v>46133.82773260417</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>131</v>
@@ -3702,13 +3702,13 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46122.384791296296</v>
+        <v>46122.55145796297</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.66112020833</v>
+        <v>46133.827786875</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.661121412035</v>
+        <v>46133.82778807871</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3763,13 +3763,13 @@
         <v>136</v>
       </c>
       <c r="B35" s="8">
-        <v>46122.38479633102</v>
+        <v>46122.55146299768</v>
       </c>
       <c r="C35" s="8">
-        <v>46133.6611012963</v>
+        <v>46133.82776796297</v>
       </c>
       <c r="D35" s="8">
-        <v>46133.66110246528</v>
+        <v>46133.827769131945</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>137</v>
@@ -3824,13 +3824,13 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46122.38480128472</v>
+        <v>46122.55146795139</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.50020540509</v>
+        <v>46181.66687207176</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.5002191088</v>
+        <v>46181.66688577546</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3889,13 +3889,13 @@
         <v>144</v>
       </c>
       <c r="B37" s="8">
-        <v>46122.38480630787</v>
+        <v>46122.551472974534</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.50015100694</v>
+        <v>46181.66681767361</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.50015280093</v>
+        <v>46181.66681946759</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>145</v>
@@ -3950,13 +3950,13 @@
         <v>147</v>
       </c>
       <c r="B38" s="5">
-        <v>46122.384855868055</v>
+        <v>46122.55152253472</v>
       </c>
       <c r="C38" s="5">
-        <v>46181.50019012731</v>
+        <v>46181.66685679398</v>
       </c>
       <c r="D38" s="5">
-        <v>46181.5001915162</v>
+        <v>46181.66685818287</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>148</v>
@@ -4011,13 +4011,13 @@
         <v>150</v>
       </c>
       <c r="B39" s="8">
-        <v>46122.384862245366</v>
+        <v>46122.55152891204</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.70100114583</v>
+        <v>46154.867667812505</v>
       </c>
       <c r="D39" s="8">
-        <v>46181.03818855324</v>
+        <v>46181.20485521991</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -4076,13 +4076,13 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46122.384867395835</v>
+        <v>46122.5515340625</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.70085026621</v>
+        <v>46154.86751693287</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.70085260417</v>
+        <v>46154.86751927083</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>93</v>
@@ -4131,13 +4131,13 @@
         <v>155</v>
       </c>
       <c r="B41" s="8">
-        <v>46122.38487178241</v>
+        <v>46122.55153844907</v>
       </c>
       <c r="C41" s="8">
-        <v>46154.70090960649</v>
+        <v>46154.867576273144</v>
       </c>
       <c r="D41" s="8">
-        <v>46154.70091078704</v>
+        <v>46154.867577453704</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>156</v>
@@ -4186,13 +4186,13 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46122.40826678241</v>
+        <v>46122.574933449076</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.500100335645</v>
+        <v>46181.666767002316</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.50011658565</v>
+        <v>46181.666783252316</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4251,13 +4251,13 @@
         <v>161</v>
       </c>
       <c r="B43" s="8">
-        <v>46122.40925430556</v>
+        <v>46122.575920972224</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.500040729166</v>
+        <v>46181.66670739584</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.500041886575</v>
+        <v>46181.66670855324</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>96</v>
@@ -4306,13 +4306,13 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46122.409418090276</v>
+        <v>46122.57608475695</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.50008614583</v>
+        <v>46181.666752812496</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.500087685185</v>
+        <v>46181.666754351856</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>164</v>
@@ -4361,13 +4361,13 @@
         <v>166</v>
       </c>
       <c r="B45" s="8">
-        <v>46122.40834771991</v>
+        <v>46122.57501438657</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.500291805554</v>
+        <v>46181.666958472226</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.500401990736</v>
+        <v>46181.66706865741</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>167</v>
@@ -4426,13 +4426,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46122.41255444444</v>
+        <v>46122.57922111111</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.50023484953</v>
+        <v>46181.666901516204</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.50023640046</v>
+        <v>46181.66690306713</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>102</v>
@@ -4481,13 +4481,13 @@
         <v>173</v>
       </c>
       <c r="B47" s="8">
-        <v>46122.4128253588</v>
+        <v>46122.57949202546</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.500276562496</v>
+        <v>46181.66694322917</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.50027793982</v>
+        <v>46181.66694460648</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>174</v>
@@ -4536,13 +4536,13 @@
         <v>176</v>
       </c>
       <c r="B48" s="5">
-        <v>46125.362951550924</v>
+        <v>46125.529618217595</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.50055453704</v>
+        <v>46181.66722120371</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.500568449075</v>
+        <v>46181.66723511574</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4601,13 +4601,13 @@
         <v>179</v>
       </c>
       <c r="B49" s="8">
-        <v>46125.36311331019</v>
+        <v>46125.52977997685</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.50049065972</v>
+        <v>46181.66715732639</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.500492453706</v>
+        <v>46181.66715912037</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>99</v>
@@ -4656,13 +4656,13 @@
         <v>181</v>
       </c>
       <c r="B50" s="5">
-        <v>46125.36325149305</v>
+        <v>46125.52991815972</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.5005374537</v>
+        <v>46181.66720412037</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.50053896991</v>
+        <v>46181.66720563658</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>182</v>
@@ -4711,11 +4711,11 @@
         <v>184</v>
       </c>
       <c r="B51" s="8">
-        <v>46122.384541886575</v>
+        <v>46122.55120855324</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46181.50123415509</v>
+        <v>46181.66790082176</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -4758,13 +4758,13 @@
         <v>187</v>
       </c>
       <c r="B52" s="5">
-        <v>46122.38487678241</v>
+        <v>46122.55154344907</v>
       </c>
       <c r="C52" s="5">
-        <v>46133.62917814815</v>
+        <v>46133.79584481481</v>
       </c>
       <c r="D52" s="5">
-        <v>46143.00447921296</v>
+        <v>46143.171145879634</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4823,13 +4823,13 @@
         <v>192</v>
       </c>
       <c r="B53" s="8">
-        <v>46122.38488232639</v>
+        <v>46122.551548993055</v>
       </c>
       <c r="C53" s="8">
-        <v>46134.62573756944</v>
+        <v>46134.79240423611</v>
       </c>
       <c r="D53" s="8">
-        <v>46134.62575309028</v>
+        <v>46134.792419756945</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>193</v>
@@ -4888,13 +4888,13 @@
         <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46122.38489054398</v>
+        <v>46122.55155721065</v>
       </c>
       <c r="C54" s="5">
-        <v>46134.62578480324</v>
+        <v>46134.79245146991</v>
       </c>
       <c r="D54" s="5">
-        <v>46134.62580515046</v>
+        <v>46134.79247181713</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>88</v>
@@ -4951,11 +4951,11 @@
         <v>198</v>
       </c>
       <c r="B55" s="8">
-        <v>46122.38489901621</v>
+        <v>46122.55156568287</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46125.49400097222</v>
+        <v>46125.66066763889</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>199</v>
@@ -5012,11 +5012,11 @@
         <v>203</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.43695545139</v>
+        <v>46125.603622118055</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46125.493128587965</v>
+        <v>46125.65979525463</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>
@@ -5063,11 +5063,11 @@
         <v>206</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.43700428241</v>
+        <v>46125.60367094907</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46125.49319310185</v>
+        <v>46125.65985976852</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>204</v>
@@ -5114,11 +5114,11 @@
         <v>207</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.43705284722</v>
+        <v>46125.60371951389</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46125.49316949074</v>
+        <v>46125.65983615741</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>204</v>
@@ -5165,11 +5165,11 @@
         <v>208</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.43709796296</v>
+        <v>46125.60376462963</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46125.49320902777</v>
+        <v>46125.659875694444</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>204</v>
@@ -5216,11 +5216,11 @@
         <v>209</v>
       </c>
       <c r="B60" s="5">
-        <v>46125.437150729165</v>
+        <v>46125.60381739584</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46125.49323032408</v>
+        <v>46125.659896990735</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>204</v>
@@ -5267,13 +5267,13 @@
         <v>210</v>
       </c>
       <c r="B61" s="8">
-        <v>46122.38490304398</v>
+        <v>46122.551569710646</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.501105787036</v>
+        <v>46181.6677724537</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.501186574074</v>
+        <v>46181.66785324074</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>211</v>
@@ -5316,13 +5316,13 @@
         <v>213</v>
       </c>
       <c r="B62" s="5">
-        <v>46122.38490655093</v>
+        <v>46122.55157321759</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.50071136574</v>
+        <v>46181.667378032405</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.500728576386</v>
+        <v>46181.66739524306</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>214</v>
@@ -5381,13 +5381,13 @@
         <v>218</v>
       </c>
       <c r="B63" s="8">
-        <v>46122.41824972222</v>
+        <v>46122.58491638889</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.50074653935</v>
+        <v>46181.667413206014</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.50076234953</v>
+        <v>46181.667429016205</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>219</v>
@@ -5446,13 +5446,13 @@
         <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46125.36435991898</v>
+        <v>46125.53102658565</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.500763460645</v>
+        <v>46181.667430127316</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.50078259259</v>
+        <v>46181.66744925926</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>222</v>
@@ -5511,13 +5511,13 @@
         <v>224</v>
       </c>
       <c r="B65" s="8">
-        <v>46122.38491179398</v>
+        <v>46122.55157846065</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.501089212965</v>
+        <v>46181.66775587963</v>
       </c>
       <c r="D65" s="8">
-        <v>46181.501105752315</v>
+        <v>46181.66777241898</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>220</v>
@@ -5576,13 +5576,13 @@
         <v>229</v>
       </c>
       <c r="B66" s="5">
-        <v>46122.38491716435</v>
+        <v>46122.551583831024</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.50212802083</v>
+        <v>46181.6687946875</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.50224104167</v>
+        <v>46181.66890770833</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>230</v>
@@ -5625,13 +5625,13 @@
         <v>232</v>
       </c>
       <c r="B67" s="8">
-        <v>46122.384920219905</v>
+        <v>46122.55158688658</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.49942690972</v>
+        <v>46181.666093576394</v>
       </c>
       <c r="D67" s="8">
-        <v>46181.50214266204</v>
+        <v>46181.66880932871</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>233</v>
@@ -5690,13 +5690,13 @@
         <v>237</v>
       </c>
       <c r="B68" s="5">
-        <v>46122.384925185186</v>
+        <v>46122.55159185185</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.49953199074</v>
+        <v>46181.6661986574</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.50217939814</v>
+        <v>46181.668846064815</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>238</v>
@@ -5755,13 +5755,13 @@
         <v>240</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.42914525463</v>
+        <v>46125.595811921296</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.501410324076</v>
+        <v>46181.66807699074</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.50141217593</v>
+        <v>46181.66807884259</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>241</v>
@@ -5810,13 +5810,13 @@
         <v>244</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.42943380787</v>
+        <v>46125.59610047453</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.50141914352</v>
+        <v>46181.66808581019</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.50142061342</v>
+        <v>46181.66808728009</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>204</v>
@@ -5865,13 +5865,13 @@
         <v>245</v>
       </c>
       <c r="B71" s="8">
-        <v>46125.429543715276</v>
+        <v>46125.59621038195</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.501487326386</v>
+        <v>46181.66815399306</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.501488842594</v>
+        <v>46181.66815550926</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>204</v>
@@ -5920,13 +5920,13 @@
         <v>246</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.42958805556</v>
+        <v>46125.59625472222</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.50150002315</v>
+        <v>46181.668166689815</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.501501527775</v>
+        <v>46181.66816819445</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>204</v>
@@ -5975,13 +5975,13 @@
         <v>247</v>
       </c>
       <c r="B73" s="8">
-        <v>46125.42963248843</v>
+        <v>46125.59629915509</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.50151289352</v>
+        <v>46181.66817956018</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.50151412037</v>
+        <v>46181.66818078703</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>204</v>
@@ -6030,13 +6030,13 @@
         <v>248</v>
       </c>
       <c r="B74" s="5">
-        <v>46122.384930844906</v>
+        <v>46122.55159751157</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.50211394676</v>
+        <v>46181.66878061343</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.50211555556</v>
+        <v>46181.66878222222</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>249</v>
@@ -6095,13 +6095,13 @@
         <v>250</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.4298218287</v>
+        <v>46125.59648849537</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.501985254625</v>
+        <v>46181.668651921296</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.501986724536</v>
+        <v>46181.6686533912</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>204</v>
@@ -6150,13 +6150,13 @@
         <v>253</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.429951875005</v>
+        <v>46125.59661854166</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.50199983796</v>
+        <v>46181.66866650463</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.50200115741</v>
+        <v>46181.66866782407</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>204</v>
@@ -6205,13 +6205,13 @@
         <v>255</v>
       </c>
       <c r="B77" s="8">
-        <v>46125.43000208333</v>
+        <v>46125.596668750004</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.50200921296</v>
+        <v>46181.66867587963</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.50201078704</v>
+        <v>46181.66867745371</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>204</v>
@@ -6260,13 +6260,13 @@
         <v>256</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.430048842594</v>
+        <v>46125.59671550926</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.50201895833</v>
+        <v>46181.668685625</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.50202039352</v>
+        <v>46181.668687060184</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>204</v>
@@ -6315,13 +6315,13 @@
         <v>258</v>
       </c>
       <c r="B79" s="8">
-        <v>46125.430088796296</v>
+        <v>46125.59675546296</v>
       </c>
       <c r="C79" s="8">
-        <v>46181.5020371875</v>
+        <v>46181.66870385417</v>
       </c>
       <c r="D79" s="8">
-        <v>46181.502038356484</v>
+        <v>46181.66870502315</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>204</v>
@@ -6370,11 +6370,11 @@
         <v>259</v>
       </c>
       <c r="B80" s="5">
-        <v>46122.38493690972</v>
+        <v>46122.55160357639</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46125.520105069445</v>
+        <v>46125.68677173612</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>211</v>
@@ -6417,11 +6417,11 @@
         <v>261</v>
       </c>
       <c r="B81" s="8">
-        <v>46122.38494012732</v>
+        <v>46122.55160679398</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46185.021272060185</v>
+        <v>46185.18793872686</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>262</v>
@@ -6480,11 +6480,11 @@
         <v>264</v>
       </c>
       <c r="B82" s="5">
-        <v>46122.38494559028</v>
+        <v>46122.551612256946</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46174.45950489583</v>
+        <v>46174.6261715625</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>265</v>
@@ -6543,11 +6543,11 @@
         <v>266</v>
       </c>
       <c r="B83" s="8">
-        <v>46122.38495090278</v>
+        <v>46122.55161756944</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46133.66113695602</v>
+        <v>46133.827803622684</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>267</v>
@@ -6606,11 +6606,11 @@
         <v>268</v>
       </c>
       <c r="B84" s="5">
-        <v>46122.384956215275</v>
+        <v>46122.55162288195</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46183.018260069446</v>
+        <v>46183.18492673611</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>269</v>
@@ -6669,11 +6669,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="8">
-        <v>46122.427324965276</v>
+        <v>46122.59399163195</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46181.50029684028</v>
+        <v>46181.66696350694</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>271</v>
@@ -6732,11 +6732,11 @@
         <v>273</v>
       </c>
       <c r="B86" s="5">
-        <v>46122.3849615162</v>
+        <v>46122.551628182875</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46125.46585777777</v>
+        <v>46125.632524444445</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>274</v>
@@ -6779,11 +6779,11 @@
         <v>276</v>
       </c>
       <c r="B87" s="8">
-        <v>46122.38496491898</v>
+        <v>46122.55163158565</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46181.50204561342</v>
+        <v>46181.668712280094</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>277</v>
@@ -6842,11 +6842,11 @@
         <v>279</v>
       </c>
       <c r="B88" s="5">
-        <v>46125.43083025463</v>
+        <v>46125.5974969213</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46181.501990358796</v>
+        <v>46181.66865702547</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>204</v>
@@ -6895,11 +6895,11 @@
         <v>281</v>
       </c>
       <c r="B89" s="8">
-        <v>46125.430879039355</v>
+        <v>46125.59754570602</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46181.50200619213</v>
+        <v>46181.668672858796</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>204</v>
@@ -6948,11 +6948,11 @@
         <v>282</v>
       </c>
       <c r="B90" s="5">
-        <v>46125.430940439815</v>
+        <v>46125.59760710648</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46181.50201631944</v>
+        <v>46181.668682986114</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>204</v>
@@ -7001,11 +7001,11 @@
         <v>283</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.43099224537</v>
+        <v>46125.59765891204</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46181.50202730324</v>
+        <v>46181.66869396991</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>204</v>
@@ -7054,11 +7054,11 @@
         <v>284</v>
       </c>
       <c r="B92" s="5">
-        <v>46125.431036724534</v>
+        <v>46125.597703391206</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46181.50204620371</v>
+        <v>46181.66871287037</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>204</v>
@@ -7107,11 +7107,11 @@
         <v>285</v>
       </c>
       <c r="B93" s="8">
-        <v>46122.38503993055</v>
+        <v>46122.55170659722</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46125.49038394676</v>
+        <v>46125.65705061343</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>286</v>
@@ -7170,11 +7170,11 @@
         <v>287</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.43316075232</v>
+        <v>46125.59982741898</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46134.62581221065</v>
+        <v>46134.792478877316</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>204</v>
@@ -7223,11 +7223,11 @@
         <v>290</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.43322416667</v>
+        <v>46125.599890833335</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46134.62580530092</v>
+        <v>46134.792471967594</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>204</v>
@@ -7276,11 +7276,11 @@
         <v>292</v>
       </c>
       <c r="B96" s="5">
-        <v>46125.43326467593</v>
+        <v>46125.59993134259</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46134.625812812505</v>
+        <v>46134.79247947916</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>204</v>
@@ -7329,11 +7329,11 @@
         <v>293</v>
       </c>
       <c r="B97" s="8">
-        <v>46125.433302627316</v>
+        <v>46125.59996929398</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46134.625810405094</v>
+        <v>46134.79247707176</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>204</v>
@@ -7382,11 +7382,11 @@
         <v>294</v>
       </c>
       <c r="B98" s="5">
-        <v>46125.43334484954</v>
+        <v>46125.6000115162</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46134.62582099537</v>
+        <v>46134.79248766204</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>204</v>
@@ -7435,11 +7435,11 @@
         <v>295</v>
       </c>
       <c r="B99" s="8">
-        <v>46122.38497746528</v>
+        <v>46122.55164413195</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46125.490387997685</v>
+        <v>46125.65705466435</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>296</v>
@@ -7498,11 +7498,11 @@
         <v>298</v>
       </c>
       <c r="B100" s="5">
-        <v>46125.43249607639</v>
+        <v>46125.599162743056</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46134.62582064814</v>
+        <v>46134.792487314815</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>204</v>
@@ -7551,11 +7551,11 @@
         <v>301</v>
       </c>
       <c r="B101" s="8">
-        <v>46125.4326358449</v>
+        <v>46125.599302511575</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46134.62580262731</v>
+        <v>46134.792469293985</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>204</v>
@@ -7604,11 +7604,11 @@
         <v>302</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.43267978009</v>
+        <v>46125.59934644676</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46134.625807557866</v>
+        <v>46134.79247422454</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>204</v>
@@ -7657,11 +7657,11 @@
         <v>303</v>
       </c>
       <c r="B103" s="8">
-        <v>46125.43272190972</v>
+        <v>46125.59938857639</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46134.62580707176</v>
+        <v>46134.79247373843</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>204</v>
@@ -7710,11 +7710,11 @@
         <v>304</v>
       </c>
       <c r="B104" s="5">
-        <v>46125.43276428241</v>
+        <v>46125.59943094908</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46134.62581978009</v>
+        <v>46134.792486446764</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>204</v>
@@ -7763,11 +7763,11 @@
         <v>305</v>
       </c>
       <c r="B105" s="8">
-        <v>46122.3849843287</v>
+        <v>46122.551650995374</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46125.49039208333</v>
+        <v>46125.65705875</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>306</v>
@@ -7826,11 +7826,11 @@
         <v>307</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.43286347222</v>
+        <v>46125.59953013889</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46134.625813900464</v>
+        <v>46134.79248056713</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>204</v>
@@ -7879,11 +7879,11 @@
         <v>309</v>
       </c>
       <c r="B107" s="8">
-        <v>46125.43294756944</v>
+        <v>46125.59961423611</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46134.62580652778</v>
+        <v>46134.792473194444</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>204</v>
@@ -7932,11 +7932,11 @@
         <v>310</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.43298765046</v>
+        <v>46125.599654317135</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46134.62580417824</v>
+        <v>46134.792470844906</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>204</v>
@@ -7985,11 +7985,11 @@
         <v>311</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.43290399306</v>
+        <v>46125.59957065972</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46134.62581003472</v>
+        <v>46134.79247670139</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>204</v>
@@ -8038,11 +8038,11 @@
         <v>312</v>
       </c>
       <c r="B110" s="5">
-        <v>46125.433030451386</v>
+        <v>46125.59969711806</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46134.62580940972</v>
+        <v>46134.792476076385</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>204</v>
@@ -8091,11 +8091,11 @@
         <v>313</v>
       </c>
       <c r="B111" s="8">
-        <v>46122.38497059028</v>
+        <v>46122.55163725694</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46125.49039508102</v>
+        <v>46125.65706174768</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>314</v>
@@ -8154,11 +8154,11 @@
         <v>315</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.431135439816</v>
+        <v>46125.59780210648</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46134.625819050925</v>
+        <v>46134.7924857176</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>204</v>
@@ -8207,11 +8207,11 @@
         <v>318</v>
       </c>
       <c r="B113" s="8">
-        <v>46125.43117026621</v>
+        <v>46125.597836932866</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46134.625811122685</v>
+        <v>46134.79247778935</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>204</v>
@@ -8260,11 +8260,11 @@
         <v>319</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.43125422453</v>
+        <v>46125.5979208912</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46134.62581167824</v>
+        <v>46134.79247834491</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>204</v>
@@ -8313,11 +8313,11 @@
         <v>320</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.431214212964</v>
+        <v>46125.59788087963</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46134.6258049537</v>
+        <v>46134.79247162037</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>204</v>
@@ -8366,11 +8366,11 @@
         <v>321</v>
       </c>
       <c r="B116" s="5">
-        <v>46125.43129835648</v>
+        <v>46125.597965023146</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46134.625803310184</v>
+        <v>46134.79246997685</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>204</v>
@@ -8419,11 +8419,11 @@
         <v>322</v>
       </c>
       <c r="B117" s="8">
-        <v>46122.38505377315</v>
+        <v>46122.55172043982</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46125.4922274537</v>
+        <v>46125.658894120366</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>323</v>
@@ -8482,11 +8482,11 @@
         <v>324</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.43371586806</v>
+        <v>46125.60038253472</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46125.4916552662</v>
+        <v>46125.658321932875</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>204</v>
@@ -8533,11 +8533,11 @@
         <v>326</v>
       </c>
       <c r="B119" s="8">
-        <v>46125.43376346065</v>
+        <v>46125.60043012731</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46125.491677569444</v>
+        <v>46125.658344236115</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>204</v>
@@ -8584,11 +8584,11 @@
         <v>327</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.43380623843</v>
+        <v>46125.60047290509</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46125.491704942135</v>
+        <v>46125.65837160879</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>204</v>
@@ -8635,11 +8635,11 @@
         <v>328</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.4338474074</v>
+        <v>46125.600514074074</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46125.49173302083</v>
+        <v>46125.6583996875</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>204</v>
@@ -8686,11 +8686,11 @@
         <v>329</v>
       </c>
       <c r="B122" s="5">
-        <v>46125.43389193287</v>
+        <v>46125.60055859954</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46125.49177476852</v>
+        <v>46125.65844143518</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>204</v>
@@ -8737,11 +8737,11 @@
         <v>330</v>
       </c>
       <c r="B123" s="8">
-        <v>46122.385063194444</v>
+        <v>46122.55172986111</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46125.49400050926</v>
+        <v>46125.66066717592</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>331</v>
@@ -8800,11 +8800,11 @@
         <v>333</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.4339775</v>
+        <v>46125.60064416667</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46125.49535254629</v>
+        <v>46125.66201921296</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>204</v>
@@ -8851,11 +8851,11 @@
         <v>335</v>
       </c>
       <c r="B125" s="8">
-        <v>46125.43402074074</v>
+        <v>46125.60068740741</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46125.49538491898</v>
+        <v>46125.66205158565</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>204</v>
@@ -8902,11 +8902,11 @@
         <v>336</v>
       </c>
       <c r="B126" s="5">
-        <v>46125.43407178241</v>
+        <v>46125.60073844907</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46125.49540674769</v>
+        <v>46125.66207341435</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>204</v>
@@ -8953,11 +8953,11 @@
         <v>337</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.434109560185</v>
+        <v>46125.60077622686</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46125.49542936342</v>
+        <v>46125.66209603009</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>204</v>
@@ -9004,11 +9004,11 @@
         <v>338</v>
       </c>
       <c r="B128" s="5">
-        <v>46125.43416247686</v>
+        <v>46125.600829143514</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46125.495473726856</v>
+        <v>46125.66214039351</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>204</v>
@@ -9055,11 +9055,11 @@
         <v>339</v>
       </c>
       <c r="B129" s="8">
-        <v>46122.38506837963</v>
+        <v>46122.5517350463</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46125.422394988425</v>
+        <v>46125.58906165509</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>340</v>
@@ -9102,11 +9102,11 @@
         <v>342</v>
       </c>
       <c r="B130" s="5">
-        <v>46122.38507239583</v>
+        <v>46122.5517390625</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46125.498291365744</v>
+        <v>46125.66495803241</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>343</v>
@@ -9165,11 +9165,11 @@
         <v>347</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.43427064815</v>
+        <v>46125.60093731481</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46125.4975104051</v>
+        <v>46125.664177071754</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>204</v>
@@ -9216,11 +9216,11 @@
         <v>349</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.4347141551</v>
+        <v>46125.601380821754</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46125.497530023145</v>
+        <v>46125.66419668982</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>204</v>
@@ -9267,11 +9267,11 @@
         <v>350</v>
       </c>
       <c r="B133" s="8">
-        <v>46125.43475814815</v>
+        <v>46125.60142481481</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46125.497552534725</v>
+        <v>46125.66421920139</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>204</v>
@@ -9318,11 +9318,11 @@
         <v>351</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.434794189816</v>
+        <v>46125.60146085648</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46125.49757475694</v>
+        <v>46125.66424142361</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>204</v>
@@ -9369,11 +9369,11 @@
         <v>352</v>
       </c>
       <c r="B135" s="8">
-        <v>46125.434835416665</v>
+        <v>46125.60150208333</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46125.497614305554</v>
+        <v>46125.664280972225</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>204</v>
@@ -9420,11 +9420,11 @@
         <v>353</v>
       </c>
       <c r="B136" s="5">
-        <v>46122.38507716435</v>
+        <v>46122.55174383102</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46185.47987476852</v>
+        <v>46185.646541435184</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>354</v>
@@ -9481,11 +9481,11 @@
         <v>355</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.4344203125</v>
+        <v>46125.601086979164</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46125.50094561343</v>
+        <v>46125.66761228009</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>204</v>
@@ -9532,11 +9532,11 @@
         <v>357</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.4344865162</v>
+        <v>46125.60115318287</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46125.500989548615</v>
+        <v>46125.66765621528</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>204</v>
@@ -9583,11 +9583,11 @@
         <v>358</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.43453724537</v>
+        <v>46125.60120391204</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46125.501024363424</v>
+        <v>46125.66769103009</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>204</v>
@@ -9634,11 +9634,11 @@
         <v>359</v>
       </c>
       <c r="B140" s="5">
-        <v>46125.434591296296</v>
+        <v>46125.60125796296</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46125.50104548611</v>
+        <v>46125.667712152775</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>204</v>
@@ -9685,11 +9685,11 @@
         <v>360</v>
       </c>
       <c r="B141" s="8">
-        <v>46125.43463761574</v>
+        <v>46125.601304282405</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46125.50106056713</v>
+        <v>46125.6677272338</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>204</v>
@@ -9736,11 +9736,11 @@
         <v>361</v>
       </c>
       <c r="B142" s="5">
-        <v>46122.38508202546</v>
+        <v>46122.55174869213</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46185.47698734954</v>
+        <v>46185.6436540162</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>362</v>
@@ -9797,11 +9797,11 @@
         <v>363</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.434919837964</v>
+        <v>46125.60158650463</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46125.59907921296</v>
+        <v>46125.76574587963</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>204</v>
@@ -9848,11 +9848,11 @@
         <v>365</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.43496466435</v>
+        <v>46125.60163133102</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46125.596421504626</v>
+        <v>46125.7630881713</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>204</v>
@@ -9899,11 +9899,11 @@
         <v>366</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.43500349537</v>
+        <v>46125.60167016204</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46125.59718804398</v>
+        <v>46125.76385471065</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>204</v>
@@ -9950,11 +9950,11 @@
         <v>368</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.43503768518</v>
+        <v>46125.60170435185</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46125.59647042824</v>
+        <v>46125.76313709491</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>204</v>
@@ -10001,11 +10001,11 @@
         <v>369</v>
       </c>
       <c r="B147" s="8">
-        <v>46125.4350728125</v>
+        <v>46125.60173947917</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46125.59650554398</v>
+        <v>46125.763172210645</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>204</v>
@@ -10052,11 +10052,11 @@
         <v>370</v>
       </c>
       <c r="B148" s="5">
-        <v>46122.38508680556</v>
+        <v>46122.551753472224</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46125.59811322916</v>
+        <v>46125.764779895835</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>371</v>
@@ -10113,11 +10113,11 @@
         <v>373</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.43514888889</v>
+        <v>46125.60181555555</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46125.59746821759</v>
+        <v>46125.76413488426</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>204</v>
@@ -10164,11 +10164,11 @@
         <v>374</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.43519024306</v>
+        <v>46125.60185690972</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46125.59749013888</v>
+        <v>46125.764156805555</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>204</v>
@@ -10215,11 +10215,11 @@
         <v>375</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.43523282408</v>
+        <v>46125.601899490735</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46125.59751504629</v>
+        <v>46125.76418171296</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>204</v>
@@ -10266,11 +10266,11 @@
         <v>376</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.43527268519</v>
+        <v>46125.60193935185</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46125.59754094908</v>
+        <v>46125.764207615735</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>204</v>
@@ -10317,11 +10317,11 @@
         <v>377</v>
       </c>
       <c r="B153" s="8">
-        <v>46125.43531043982</v>
+        <v>46125.60197710648</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46125.59757878473</v>
+        <v>46125.764245451384</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>204</v>
@@ -10368,11 +10368,11 @@
         <v>378</v>
       </c>
       <c r="B154" s="5">
-        <v>46122.38509195602</v>
+        <v>46122.551758622685</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46125.422702118056</v>
+        <v>46125.58936878473</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>379</v>
@@ -10415,11 +10415,11 @@
         <v>381</v>
       </c>
       <c r="B155" s="8">
-        <v>46122.38509467593</v>
+        <v>46122.55176134259</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46125.427344791664</v>
+        <v>46125.594011458335</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>382</v>
@@ -10478,11 +10478,11 @@
         <v>385</v>
       </c>
       <c r="B156" s="5">
-        <v>46122.38509943287</v>
+        <v>46122.55176609954</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46125.42734174768</v>
+        <v>46125.59400841435</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>386</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -9106,7 +9106,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46125.66495803241</v>
+        <v>46188.534497569446</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>343</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4017,7 +4017,7 @@
         <v>46154.867667812505</v>
       </c>
       <c r="D39" s="8">
-        <v>46181.20485521991</v>
+        <v>46189.172213136575</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -4061,8 +4061,8 @@
       <c r="R39" s="8">
         <v>46188</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>79</v>
+      <c r="S39" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46188.534497569446</v>
+        <v>46189.53573824074</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>343</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46183.18492708333</v>
+        <v>46190.16826327547</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>119</v>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46125.59148754629</v>
+        <v>46190.16825996528</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>125</v>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46183.18492673611</v>
+        <v>46190.16826148148</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>269</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4829,7 +4829,7 @@
         <v>46134.79240423611</v>
       </c>
       <c r="D53" s="8">
-        <v>46134.792419756945</v>
+        <v>46190.18859494213</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>193</v>
@@ -4873,8 +4873,8 @@
       <c r="R53" s="8">
         <v>46197</v>
       </c>
-      <c r="S53" s="11" t="s">
-        <v>90</v>
+      <c r="S53" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="T53" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46190.16826327547</v>
+        <v>46191.16761827546</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>119</v>
@@ -3443,8 +3443,8 @@
       <c r="R29" s="8">
         <v>46190</v>
       </c>
-      <c r="S29" s="12" t="s">
-        <v>79</v>
+      <c r="S29" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
@@ -4894,7 +4894,7 @@
         <v>46134.79245146991</v>
       </c>
       <c r="D54" s="5">
-        <v>46134.79247181713</v>
+        <v>46191.18981792824</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>88</v>
@@ -4936,8 +4936,8 @@
       <c r="R54" s="5">
         <v>46198</v>
       </c>
-      <c r="S54" s="11" t="s">
-        <v>90</v>
+      <c r="S54" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46190.16826148148</v>
+        <v>46191.167618402775</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>269</v>
@@ -6654,8 +6654,8 @@
       <c r="R84" s="5">
         <v>46190</v>
       </c>
-      <c r="S84" s="12" t="s">
-        <v>79</v>
+      <c r="S84" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -9059,7 +9059,7 @@
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46125.58906165509</v>
+        <v>46191.706051354166</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>340</v>
@@ -9738,9 +9738,11 @@
       <c r="B142" s="5">
         <v>46122.55174869213</v>
       </c>
-      <c r="C142" s="6"/>
+      <c r="C142" s="5">
+        <v>46191.70598530093</v>
+      </c>
       <c r="D142" s="5">
-        <v>46185.6436540162</v>
+        <v>46191.706001886574</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>362</v>
@@ -9786,10 +9788,10 @@
         <v>90</v>
       </c>
       <c r="T142" s="6">
-        <v>0</v>
-      </c>
-      <c r="U142" s="10" t="s">
-        <v>114</v>
+        <v>1</v>
+      </c>
+      <c r="U142" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
@@ -10054,9 +10056,11 @@
       <c r="B148" s="5">
         <v>46122.551753472224</v>
       </c>
-      <c r="C148" s="6"/>
+      <c r="C148" s="5">
+        <v>46191.70604009259</v>
+      </c>
       <c r="D148" s="5">
-        <v>46125.764779895835</v>
+        <v>46191.706057812495</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>371</v>
@@ -10102,10 +10106,10 @@
         <v>90</v>
       </c>
       <c r="T148" s="6">
-        <v>0</v>
-      </c>
-      <c r="U148" s="10" t="s">
-        <v>114</v>
+        <v>1</v>
+      </c>
+      <c r="U148" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
@@ -10419,7 +10423,7 @@
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46125.594011458335</v>
+        <v>46191.70605767361</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>382</v>
@@ -10469,8 +10473,8 @@
       <c r="T155" s="9">
         <v>0</v>
       </c>
-      <c r="U155" s="10" t="s">
-        <v>114</v>
+      <c r="U155" s="12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
@@ -10482,7 +10486,7 @@
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46125.59400841435</v>
+        <v>46191.70605090278</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>386</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46191.16761827546</v>
+        <v>46191.83435208333</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>119</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -6421,7 +6421,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46185.18793872686</v>
+        <v>46192.1695193287</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>262</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46191.83435208333</v>
+        <v>46192.84300386574</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>119</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -217,9 +217,6 @@
     <t>Ingenieria Basica Motor,Ingenieria basica Rodete,Ingenieria Detalle</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1214004989966429</t>
   </si>
   <si>
@@ -312,6 +309,9 @@
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214005097392408</t>
@@ -2213,9 +2213,11 @@
       <c r="B10" s="5">
         <v>46122.55119412037</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46193.93280347223</v>
+      </c>
       <c r="D10" s="5">
-        <v>46192.97384186342</v>
+        <v>46193.9328209838</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2250,14 +2252,16 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="12" t="s">
-        <v>50</v>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="8">
         <v>46122.5513631713</v>
@@ -2269,7 +2273,7 @@
         <v>46192.97382803241</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
@@ -2290,7 +2294,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>26</v>
@@ -2302,7 +2306,7 @@
         <v>41</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q11" s="8">
         <v>46127</v>
@@ -2322,7 +2326,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46122.551369050925</v>
@@ -2334,7 +2338,7 @@
         <v>46192.97382813657</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2355,7 +2359,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2367,7 +2371,7 @@
         <v>41</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q12" s="5">
         <v>46127</v>
@@ -2387,7 +2391,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="8">
         <v>46122.5513746875</v>
@@ -2399,7 +2403,7 @@
         <v>46192.97382800926</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
@@ -2432,7 +2436,7 @@
         <v>41</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="8">
         <v>46127</v>
@@ -2452,7 +2456,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14" s="5">
         <v>46122.553594178244</v>
@@ -2464,7 +2468,7 @@
         <v>46136.20601917824</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2485,7 +2489,7 @@
         <v>26</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>26</v>
@@ -2497,7 +2501,7 @@
         <v>41</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q14" s="5">
         <v>46127</v>
@@ -2517,7 +2521,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8">
         <v>46122.55119946759</v>
@@ -2527,7 +2531,7 @@
         <v>46181.66640564815</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>25</v>
@@ -2551,7 +2555,7 @@
         <v>26</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P15" s="9" t="s">
         <v>26</v>
@@ -2564,7 +2568,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46122.55138855324</v>
@@ -2576,7 +2580,7 @@
         <v>46133.17999505787</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2603,13 +2607,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46129</v>
@@ -2629,7 +2633,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="8">
         <v>46122.55139482639</v>
@@ -2641,7 +2645,7 @@
         <v>46132.182206921294</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2668,13 +2672,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="8">
         <v>46136</v>
@@ -2683,7 +2687,7 @@
         <v>46139</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T17" s="9">
         <v>1</v>
@@ -2694,7 +2698,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46122.55140040509</v>
@@ -2704,16 +2708,16 @@
         <v>46139.170930567125</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="H18" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I18" s="5">
         <v>46136</v>
@@ -2731,13 +2735,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="5">
         <v>46136</v>
@@ -2746,13 +2750,13 @@
         <v>46139</v>
       </c>
       <c r="S18" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -2796,7 +2800,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>84</v>
@@ -2834,7 +2838,7 @@
         <v>46132.1822065625</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2861,10 +2865,10 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>89</v>
@@ -2876,7 +2880,7 @@
         <v>46139</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2926,7 +2930,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>84</v>
@@ -2991,7 +2995,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>84</v>
@@ -3056,7 +3060,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>84</v>
@@ -3236,7 +3240,7 @@
         <v>103</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>109</v>
@@ -3419,7 +3423,7 @@
         <v>115</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>119</v>
@@ -3604,7 +3608,7 @@
         <v>124</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>128</v>
@@ -4039,7 +4043,7 @@
         <v>147</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>150</v>
@@ -4721,7 +4725,7 @@
         <v>181</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>187</v>
@@ -4798,7 +4802,7 @@
         <v>46197</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T52" s="6">
         <v>1</v>
@@ -4861,7 +4865,7 @@
         <v>46198</v>
       </c>
       <c r="S53" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T53" s="9">
         <v>1</v>
@@ -6459,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="12" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6522,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="U82" s="12" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6585,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="12" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6595,9 +6599,11 @@
       <c r="B84" s="5">
         <v>46122.59399163195</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46193.93315311342</v>
+      </c>
       <c r="D84" s="5">
-        <v>46181.66696350694</v>
+        <v>46193.9332800463</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>267</v>
@@ -6645,10 +6651,10 @@
         <v>86</v>
       </c>
       <c r="T84" s="6">
-        <v>0</v>
-      </c>
-      <c r="U84" s="12" t="s">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="U84" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6707,7 +6713,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46181.668712280094</v>
+        <v>46193.93317614583</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>273</v>
@@ -6716,10 +6722,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I86" s="5">
         <v>46260</v>
@@ -6757,8 +6763,8 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="10" t="s">
-        <v>110</v>
+      <c r="U86" s="12" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6770,7 +6776,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46181.66865702547</v>
+        <v>46193.933163194444</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>200</v>
@@ -6779,10 +6785,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I87" s="8">
         <v>46260</v>
@@ -6823,7 +6829,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46181.668672858796</v>
+        <v>46193.93316084491</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>200</v>
@@ -6832,10 +6838,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I88" s="5">
         <v>46260</v>
@@ -6876,7 +6882,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46181.668682986114</v>
+        <v>46193.93316216435</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>200</v>
@@ -6885,10 +6891,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I89" s="8">
         <v>46260</v>
@@ -6929,7 +6935,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46181.66869396991</v>
+        <v>46193.933167083334</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>200</v>
@@ -6938,10 +6944,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I90" s="5">
         <v>46260</v>
@@ -6982,7 +6988,7 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46181.66871287037</v>
+        <v>46193.93316814815</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>200</v>
@@ -6991,10 +6997,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I91" s="8">
         <v>46260</v>
@@ -7044,10 +7050,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I92" s="5">
         <v>46280</v>
@@ -7107,10 +7113,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I93" s="8">
         <v>46280</v>
@@ -7160,10 +7166,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I94" s="5">
         <v>46280</v>
@@ -7213,10 +7219,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I95" s="8">
         <v>46280</v>
@@ -7266,10 +7272,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I96" s="5">
         <v>46280</v>
@@ -7319,10 +7325,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I97" s="8">
         <v>46280</v>
@@ -7372,10 +7378,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I98" s="5">
         <v>46286</v>
@@ -7435,10 +7441,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I99" s="8">
         <v>46286</v>
@@ -7488,10 +7494,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I100" s="5">
         <v>46286</v>
@@ -7541,10 +7547,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I101" s="8">
         <v>46286</v>
@@ -7594,10 +7600,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I102" s="5">
         <v>46286</v>
@@ -7647,10 +7653,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I103" s="8">
         <v>46286</v>
@@ -7700,10 +7706,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I104" s="5">
         <v>46289</v>
@@ -7763,10 +7769,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I105" s="8">
         <v>46289</v>
@@ -7816,10 +7822,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I106" s="5">
         <v>46289</v>
@@ -7869,10 +7875,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I107" s="8">
         <v>46289</v>
@@ -7922,10 +7928,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I108" s="5">
         <v>46289</v>
@@ -7975,10 +7981,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I109" s="8">
         <v>46289</v>
@@ -8028,10 +8034,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I110" s="5">
         <v>46311</v>
@@ -8091,10 +8097,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I111" s="8">
         <v>46311</v>
@@ -8144,10 +8150,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I112" s="5">
         <v>46311</v>
@@ -8197,10 +8203,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I113" s="8">
         <v>46311</v>
@@ -8250,10 +8256,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I114" s="5">
         <v>46311</v>
@@ -8303,10 +8309,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I115" s="8">
         <v>46311</v>
@@ -8356,10 +8362,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I116" s="5">
         <v>46315</v>
@@ -8419,10 +8425,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8470,10 +8476,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8521,10 +8527,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8572,10 +8578,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8623,10 +8629,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8674,10 +8680,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I122" s="5">
         <v>46317</v>
@@ -8737,10 +8743,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -8788,10 +8794,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -8839,10 +8845,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
@@ -8890,10 +8896,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -8941,10 +8947,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
@@ -9357,10 +9363,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9418,10 +9424,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9469,10 +9475,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9520,10 +9526,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9571,10 +9577,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9622,10 +9628,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -10398,7 +10404,7 @@
         <v>0</v>
       </c>
       <c r="U154" s="12" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
@@ -10461,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="U155" s="12" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="383">
   <si>
     <t xml:space="preserve"> 50001466 - ZITRON PERU (PODEROSA) </t>
   </si>
@@ -311,910 +311,910 @@
     <t>Propuesta compras:,Generación OC Rodete</t>
   </si>
   <si>
+    <t>1214005097392408</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser - OT 4302,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1214005097392428</t>
+  </si>
+  <si>
+    <t>SISTEMA DE MONITOREO WEG MOTORSCAN 100</t>
+  </si>
+  <si>
+    <t>Generación OC Sensor</t>
+  </si>
+  <si>
+    <t>1213997266064458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Corte plasma </t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  - OT 4302</t>
+  </si>
+  <si>
+    <t>1213997266064459</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado- OT 4302</t>
+  </si>
+  <si>
+    <t>1213997266064464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Fabricación externa </t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa- OT 4302</t>
+  </si>
+  <si>
+    <t>1213997266064444</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Motor,Materiales corte Laser - OT 4302,Alabe- OT 4302,Sensor,rodete-OT 4302</t>
+  </si>
+  <si>
+    <t>1214005097392556</t>
+  </si>
+  <si>
+    <t>Alabe- OT 4302</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe - OT 4302,Fabricación Alabe - OT 4302</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1214005097392571</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe - OT 4302</t>
+  </si>
+  <si>
+    <t>Alabe- OT 4302,Fabricación Alabe - OT 4302</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1214005226759171</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe - OT 4302</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Alabe- OT 4302</t>
+  </si>
+  <si>
+    <t>1214005226759189</t>
+  </si>
+  <si>
+    <t>rodete-OT 4302</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete,Fabricación Rodete</t>
+  </si>
+  <si>
+    <t>1214004989988431</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>rodete-OT 4302,Fabricación Rodete</t>
+  </si>
+  <si>
+    <t>1214004989988449</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete</t>
+  </si>
+  <si>
+    <t>rodete-OT 4302,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214004989993788</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1214004989993803</t>
+  </si>
+  <si>
+    <t>Generación OC motor</t>
+  </si>
+  <si>
+    <t>Motor,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1214005013706404</t>
+  </si>
+  <si>
+    <t>Fabricación motor</t>
+  </si>
+  <si>
+    <t>Motor,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214005013706422</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Motor,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214005013708760</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser - OT 4302</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser - OT 4302,Fabricacion Corte Laser - OT 4302</t>
+  </si>
+  <si>
+    <t>1214005013708775</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser - OT 4302</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser - OT 4302,Fabricacion Corte Laser - OT 4302</t>
+  </si>
+  <si>
+    <t>1214005226746426</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser - OT 4302</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser - OT 4302</t>
+  </si>
+  <si>
+    <t>1214005226746444</t>
+  </si>
+  <si>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>Generación OC Sensor,Fabricacion Sensor</t>
+  </si>
+  <si>
+    <t>1214005097427846</t>
+  </si>
+  <si>
+    <t>Sensor,Fabricacion Sensor</t>
+  </si>
+  <si>
+    <t>1214005097427861</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensor</t>
+  </si>
+  <si>
+    <t>Recepcion Sensor,Sensor</t>
+  </si>
+  <si>
+    <t>1213997266064470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma- OT 4302 </t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  - OT 4302,Fabricación Corte Plasma - OT 4302</t>
+  </si>
+  <si>
+    <t>1213997266064472</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma- OT 4302 ,Fabricación Corte Plasma - OT 4302</t>
+  </si>
+  <si>
+    <t>1213997266064473</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma - OT 4302</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma- OT 4302 ,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1213997266064471</t>
+  </si>
+  <si>
+    <t>Fabricación Externa - OT 4302</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa- OT 4302,Fabricación estructura proveedor externo- OT 4302</t>
+  </si>
+  <si>
+    <t>1213997266064478</t>
+  </si>
+  <si>
+    <t>Fabricación Externa - OT 4302,Fabricación estructura proveedor externo- OT 4302</t>
+  </si>
+  <si>
+    <t>1213997266064480</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo- OT 4302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa - OT 4302,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214051476709290</t>
+  </si>
+  <si>
+    <t>Mecanizado- OT 4302</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado- OT 4302,Fabricación Mecanizado- OT 4302</t>
+  </si>
+  <si>
+    <t>1214051476709292</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado- OT 4302,Mecanizado- OT 4302</t>
+  </si>
+  <si>
+    <t>1214051476709293</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado- OT 4302</t>
+  </si>
+  <si>
+    <t>Mecanizado- OT 4302,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1213997266064446</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1214005097430122</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214005097430142</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214005018307393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propuesta Corte Laser,Propuesta Corte plasma ,Propuesta Mecanizado,Propuesta Fabricación externa ,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2 </t>
+  </si>
+  <si>
+    <t>1214005013741367</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974064</t>
+  </si>
+  <si>
+    <t>OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974065</t>
+  </si>
+  <si>
+    <t>1214046914974066</t>
+  </si>
+  <si>
+    <t>1214046914974067</t>
+  </si>
+  <si>
+    <t>1214046914974068</t>
+  </si>
+  <si>
+    <t>1214005013741377</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1214005013741387</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213997266064483</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1214051476709298</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2 </t>
+  </si>
+  <si>
+    <t>1214005013741642</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Bodega:</t>
+  </si>
+  <si>
+    <t>1214005013741662</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214004990028314</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caldereria:,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2 </t>
+  </si>
+  <si>
+    <t>1214004990028334</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>OT 4302 -ZVN 1-10-26/2 ,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914973973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4302 -ZVN 1-10-26/2 </t>
+  </si>
+  <si>
+    <t>Preparación Materiales,check planos,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Armado,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914973976</t>
+  </si>
+  <si>
+    <t>1214046914973978</t>
+  </si>
+  <si>
+    <t>1214046914973979</t>
+  </si>
+  <si>
+    <t>1214046914973980</t>
+  </si>
+  <si>
+    <t>1214004990028435</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214046914973981</t>
+  </si>
+  <si>
+    <t>OT 4302 -ZVN 1-10-26/2 ,check planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4302 -ZVN 1-10-26/2,Revestimiento</t>
+  </si>
+  <si>
+    <t>1214046914973984</t>
+  </si>
+  <si>
+    <t>OT 4302 -ZVN 1-10-26/2,check planos</t>
+  </si>
+  <si>
+    <t>1214046914973985</t>
+  </si>
+  <si>
+    <t>1214046914973986</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Revestimiento,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914973987</t>
+  </si>
+  <si>
+    <t>1214005013744117</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor,Recepcion Sensor</t>
+  </si>
+  <si>
+    <t>1214005013744127</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214005013745271</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214005013745291</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214005013749480</t>
+  </si>
+  <si>
+    <t>Recepcion Sensor</t>
+  </si>
+  <si>
+    <t>1213997266064487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,Revestimiento,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214005018321934</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214005018321944</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214046914973998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4302 -ZVN 1-10-26/2,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214046914973999</t>
+  </si>
+  <si>
+    <t>1214046914974000</t>
+  </si>
+  <si>
+    <t>1214046914974001</t>
+  </si>
+  <si>
+    <t>1214046914974002</t>
+  </si>
+  <si>
+    <t>1214005226824264</t>
+  </si>
+  <si>
+    <t>Montaje Sensor</t>
+  </si>
+  <si>
+    <t>1214046914974021</t>
+  </si>
+  <si>
+    <t>OT 4302 -ZVN 1-10-26/2,Recepcion Sensor,check planos</t>
+  </si>
+  <si>
+    <t>Montaje Sensor,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974022</t>
+  </si>
+  <si>
+    <t>Montaje Sensor,Montaje Alabe,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974023</t>
+  </si>
+  <si>
+    <t>1214046914974024</t>
+  </si>
+  <si>
+    <t>1214046914974025</t>
+  </si>
+  <si>
+    <t>1214005018327326</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974008</t>
+  </si>
+  <si>
+    <t>OT 4302 -ZVN 1-10-26/2,Recepcion Alabe,check planos</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974011</t>
+  </si>
+  <si>
+    <t>1214046914974012</t>
+  </si>
+  <si>
+    <t>1214046914974013</t>
+  </si>
+  <si>
+    <t>1214046914974014</t>
+  </si>
+  <si>
+    <t>1214005097460453</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214046914974015</t>
+  </si>
+  <si>
+    <t>OT 4302 -ZVN 1-10-26/2,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>1214046914974017</t>
+  </si>
+  <si>
+    <t>1214046914974018</t>
+  </si>
+  <si>
+    <t>1214046914974016</t>
+  </si>
+  <si>
+    <t>1214046914974019</t>
+  </si>
+  <si>
+    <t>1214005018327197</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1214046914974003</t>
+  </si>
+  <si>
+    <t>Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>Montaje motor,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974004</t>
+  </si>
+  <si>
+    <t>1214046914974006</t>
+  </si>
+  <si>
+    <t>1214046914974005</t>
+  </si>
+  <si>
+    <t>1214046914974007</t>
+  </si>
+  <si>
+    <t>1214005238745312</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214046914974032</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974033</t>
+  </si>
+  <si>
+    <t>1214046914974034</t>
+  </si>
+  <si>
+    <t>1214046914974035</t>
+  </si>
+  <si>
+    <t>1214046914974036</t>
+  </si>
+  <si>
+    <t>1214005013774782</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1214046914974037</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974038</t>
+  </si>
+  <si>
+    <t>1214046914974039</t>
+  </si>
+  <si>
+    <t>1214046914974040</t>
+  </si>
+  <si>
+    <t>1214046914974041</t>
+  </si>
+  <si>
+    <t>1214005013774802</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Despacho,Embalaje,PACKING LIST</t>
+  </si>
+  <si>
+    <t>1214005013777033</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974042</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974050</t>
+  </si>
+  <si>
+    <t>1214046914974051</t>
+  </si>
+  <si>
+    <t>1214046914974052</t>
+  </si>
+  <si>
+    <t>1214046914974053</t>
+  </si>
+  <si>
+    <t>1214005013777053</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
+    <t>1214046914974045</t>
+  </si>
+  <si>
+    <t>Embalaje,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974046</t>
+  </si>
+  <si>
+    <t>1214046914974047</t>
+  </si>
+  <si>
+    <t>1214046914974048</t>
+  </si>
+  <si>
+    <t>1214046914974049</t>
+  </si>
+  <si>
+    <t>1214005238752846</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t>1214046914974054</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT 4302 -ZVN 1-10-26/2,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1214046914974055</t>
+  </si>
+  <si>
+    <t>1214046914974056</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT 4302 -ZVN 1-10-26/2</t>
+  </si>
+  <si>
+    <t>1214046914974057</t>
+  </si>
+  <si>
+    <t>1214046914974058</t>
+  </si>
+  <si>
+    <t>1214005226833662</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Gestion,Costos,Logistica:</t>
+  </si>
+  <si>
+    <t>1214046914974059</t>
+  </si>
+  <si>
+    <t>1214046914974060</t>
+  </si>
+  <si>
+    <t>1214046914974061</t>
+  </si>
+  <si>
+    <t>1214046914974062</t>
+  </si>
+  <si>
+    <t>1214046914974063</t>
+  </si>
+  <si>
+    <t>1214005226833682</t>
+  </si>
+  <si>
+    <t>Cierre proyecto:</t>
+  </si>
+  <si>
+    <t>Gestion,Costos</t>
+  </si>
+  <si>
+    <t>1214005018360978</t>
+  </si>
+  <si>
+    <t>Gestion</t>
+  </si>
+  <si>
+    <t>Nicolás</t>
+  </si>
+  <si>
+    <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214005097392408</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser - OT 4302,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1214005097392428</t>
-  </si>
-  <si>
-    <t>SISTEMA DE MONITOREO WEG MOTORSCAN 100</t>
-  </si>
-  <si>
-    <t>Generación OC Sensor</t>
-  </si>
-  <si>
-    <t>1213997266064458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Corte plasma </t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  - OT 4302</t>
-  </si>
-  <si>
-    <t>1213997266064459</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado- OT 4302</t>
-  </si>
-  <si>
-    <t>1213997266064464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Fabricación externa </t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa- OT 4302</t>
-  </si>
-  <si>
-    <t>1213997266064444</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Motor,Materiales corte Laser - OT 4302,Alabe- OT 4302,Sensor,rodete-OT 4302</t>
-  </si>
-  <si>
-    <t>1214005097392556</t>
-  </si>
-  <si>
-    <t>Alabe- OT 4302</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe - OT 4302,Fabricación Alabe - OT 4302</t>
-  </si>
-  <si>
-    <t>1214005097392571</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe - OT 4302</t>
-  </si>
-  <si>
-    <t>Alabe- OT 4302,Fabricación Alabe - OT 4302</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214005226759171</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe - OT 4302</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Alabe- OT 4302</t>
-  </si>
-  <si>
-    <t>1214005226759189</t>
-  </si>
-  <si>
-    <t>rodete-OT 4302</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete,Fabricación Rodete</t>
-  </si>
-  <si>
-    <t>1214004989988431</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete</t>
-  </si>
-  <si>
-    <t>rodete-OT 4302,Fabricación Rodete</t>
-  </si>
-  <si>
-    <t>1214004989988449</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete</t>
-  </si>
-  <si>
-    <t>rodete-OT 4302,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214004989993788</t>
-  </si>
-  <si>
-    <t>Motor</t>
-  </si>
-  <si>
-    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1214004989993803</t>
-  </si>
-  <si>
-    <t>Generación OC motor</t>
-  </si>
-  <si>
-    <t>Motor,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1214005013706404</t>
-  </si>
-  <si>
-    <t>Fabricación motor</t>
-  </si>
-  <si>
-    <t>Motor,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214005013706422</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Motor,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214005013708760</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser - OT 4302</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser - OT 4302,Fabricacion Corte Laser - OT 4302</t>
-  </si>
-  <si>
-    <t>1214005013708775</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser - OT 4302</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser - OT 4302,Fabricacion Corte Laser - OT 4302</t>
-  </si>
-  <si>
-    <t>1214005226746426</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser - OT 4302</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser - OT 4302</t>
-  </si>
-  <si>
-    <t>1214005226746444</t>
-  </si>
-  <si>
-    <t>Sensor</t>
-  </si>
-  <si>
-    <t>Generación OC Sensor,Fabricacion Sensor</t>
-  </si>
-  <si>
-    <t>1214005097427846</t>
-  </si>
-  <si>
-    <t>Sensor,Fabricacion Sensor</t>
-  </si>
-  <si>
-    <t>1214005097427861</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensor</t>
-  </si>
-  <si>
-    <t>Recepcion Sensor,Sensor</t>
-  </si>
-  <si>
-    <t>1213997266064470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma- OT 4302 </t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  - OT 4302,Fabricación Corte Plasma - OT 4302</t>
-  </si>
-  <si>
-    <t>1213997266064472</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma- OT 4302 ,Fabricación Corte Plasma - OT 4302</t>
-  </si>
-  <si>
-    <t>1213997266064473</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma - OT 4302</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma- OT 4302 ,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1213997266064471</t>
-  </si>
-  <si>
-    <t>Fabricación Externa - OT 4302</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa- OT 4302,Fabricación estructura proveedor externo- OT 4302</t>
-  </si>
-  <si>
-    <t>1213997266064478</t>
-  </si>
-  <si>
-    <t>Fabricación Externa - OT 4302,Fabricación estructura proveedor externo- OT 4302</t>
-  </si>
-  <si>
-    <t>1213997266064480</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo- OT 4302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa - OT 4302,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214051476709290</t>
-  </si>
-  <si>
-    <t>Mecanizado- OT 4302</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado- OT 4302,Fabricación Mecanizado- OT 4302</t>
-  </si>
-  <si>
-    <t>1214051476709292</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado- OT 4302,Mecanizado- OT 4302</t>
-  </si>
-  <si>
-    <t>1214051476709293</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado- OT 4302</t>
-  </si>
-  <si>
-    <t>Mecanizado- OT 4302,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1213997266064446</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1214005097430122</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214005097430142</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214005018307393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propuesta Corte Laser,Propuesta Corte plasma ,Propuesta Mecanizado,Propuesta Fabricación externa ,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2 </t>
-  </si>
-  <si>
-    <t>1214005013741367</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974064</t>
-  </si>
-  <si>
-    <t>OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974065</t>
-  </si>
-  <si>
-    <t>1214046914974066</t>
-  </si>
-  <si>
-    <t>1214046914974067</t>
-  </si>
-  <si>
-    <t>1214046914974068</t>
-  </si>
-  <si>
-    <t>1214005013741377</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1214005013741387</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213997266064483</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1214051476709298</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2 </t>
-  </si>
-  <si>
-    <t>1214005013741642</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Bodega:</t>
-  </si>
-  <si>
-    <t>1214005013741662</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214004990028314</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caldereria:,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2 </t>
-  </si>
-  <si>
-    <t>1214004990028334</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>OT 4302 -ZVN 1-10-26/2 ,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914973973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4302 -ZVN 1-10-26/2 </t>
-  </si>
-  <si>
-    <t>Preparación Materiales,check planos,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Armado,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914973976</t>
-  </si>
-  <si>
-    <t>1214046914973978</t>
-  </si>
-  <si>
-    <t>1214046914973979</t>
-  </si>
-  <si>
-    <t>1214046914973980</t>
-  </si>
-  <si>
-    <t>1214004990028435</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214046914973981</t>
-  </si>
-  <si>
-    <t>OT 4302 -ZVN 1-10-26/2 ,check planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4302 -ZVN 1-10-26/2,Revestimiento</t>
-  </si>
-  <si>
-    <t>1214046914973984</t>
-  </si>
-  <si>
-    <t>OT 4302 -ZVN 1-10-26/2,check planos</t>
-  </si>
-  <si>
-    <t>1214046914973985</t>
-  </si>
-  <si>
-    <t>1214046914973986</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Revestimiento,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914973987</t>
-  </si>
-  <si>
-    <t>1214005013744117</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor,Recepcion Sensor</t>
-  </si>
-  <si>
-    <t>1214005013744127</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214005013745271</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214005013745291</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214005013749480</t>
-  </si>
-  <si>
-    <t>Recepcion Sensor</t>
-  </si>
-  <si>
-    <t>1213997266064487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,Revestimiento,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214005018321934</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214005018321944</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214046914973998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4302 -ZVN 1-10-26/2,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214046914973999</t>
-  </si>
-  <si>
-    <t>1214046914974000</t>
-  </si>
-  <si>
-    <t>1214046914974001</t>
-  </si>
-  <si>
-    <t>1214046914974002</t>
-  </si>
-  <si>
-    <t>1214005226824264</t>
-  </si>
-  <si>
-    <t>Montaje Sensor</t>
-  </si>
-  <si>
-    <t>1214046914974021</t>
-  </si>
-  <si>
-    <t>OT 4302 -ZVN 1-10-26/2,Recepcion Sensor,check planos</t>
-  </si>
-  <si>
-    <t>Montaje Sensor,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974022</t>
-  </si>
-  <si>
-    <t>Montaje Sensor,Montaje Alabe,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974023</t>
-  </si>
-  <si>
-    <t>1214046914974024</t>
-  </si>
-  <si>
-    <t>1214046914974025</t>
-  </si>
-  <si>
-    <t>1214005018327326</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974008</t>
-  </si>
-  <si>
-    <t>OT 4302 -ZVN 1-10-26/2,Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974011</t>
-  </si>
-  <si>
-    <t>1214046914974012</t>
-  </si>
-  <si>
-    <t>1214046914974013</t>
-  </si>
-  <si>
-    <t>1214046914974014</t>
-  </si>
-  <si>
-    <t>1214005097460453</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214046914974015</t>
-  </si>
-  <si>
-    <t>OT 4302 -ZVN 1-10-26/2,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>1214046914974017</t>
-  </si>
-  <si>
-    <t>1214046914974018</t>
-  </si>
-  <si>
-    <t>1214046914974016</t>
-  </si>
-  <si>
-    <t>1214046914974019</t>
-  </si>
-  <si>
-    <t>1214005018327197</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1214046914974003</t>
-  </si>
-  <si>
-    <t>Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>Montaje motor,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974004</t>
-  </si>
-  <si>
-    <t>1214046914974006</t>
-  </si>
-  <si>
-    <t>1214046914974005</t>
-  </si>
-  <si>
-    <t>1214046914974007</t>
-  </si>
-  <si>
-    <t>1214005238745312</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214046914974032</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974033</t>
-  </si>
-  <si>
-    <t>1214046914974034</t>
-  </si>
-  <si>
-    <t>1214046914974035</t>
-  </si>
-  <si>
-    <t>1214046914974036</t>
-  </si>
-  <si>
-    <t>1214005013774782</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1214046914974037</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974038</t>
-  </si>
-  <si>
-    <t>1214046914974039</t>
-  </si>
-  <si>
-    <t>1214046914974040</t>
-  </si>
-  <si>
-    <t>1214046914974041</t>
-  </si>
-  <si>
-    <t>1214005013774802</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Despacho,Embalaje,PACKING LIST</t>
-  </si>
-  <si>
-    <t>1214005013777033</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974042</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974050</t>
-  </si>
-  <si>
-    <t>1214046914974051</t>
-  </si>
-  <si>
-    <t>1214046914974052</t>
-  </si>
-  <si>
-    <t>1214046914974053</t>
-  </si>
-  <si>
-    <t>1214005013777053</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
-  </si>
-  <si>
-    <t>1214046914974045</t>
-  </si>
-  <si>
-    <t>Embalaje,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974046</t>
-  </si>
-  <si>
-    <t>1214046914974047</t>
-  </si>
-  <si>
-    <t>1214046914974048</t>
-  </si>
-  <si>
-    <t>1214046914974049</t>
-  </si>
-  <si>
-    <t>1214005238752846</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
-  </si>
-  <si>
-    <t>1214046914974054</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT 4302 -ZVN 1-10-26/2,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1214046914974055</t>
-  </si>
-  <si>
-    <t>1214046914974056</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT 4302 -ZVN 1-10-26/2</t>
-  </si>
-  <si>
-    <t>1214046914974057</t>
-  </si>
-  <si>
-    <t>1214046914974058</t>
-  </si>
-  <si>
-    <t>1214005226833662</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Gestion,Costos,Logistica:</t>
-  </si>
-  <si>
-    <t>1214046914974059</t>
-  </si>
-  <si>
-    <t>1214046914974060</t>
-  </si>
-  <si>
-    <t>1214046914974061</t>
-  </si>
-  <si>
-    <t>1214046914974062</t>
-  </si>
-  <si>
-    <t>1214046914974063</t>
-  </si>
-  <si>
-    <t>1214005226833682</t>
-  </si>
-  <si>
-    <t>Cierre proyecto:</t>
-  </si>
-  <si>
-    <t>Gestion,Costos</t>
-  </si>
-  <si>
-    <t>1214005018360978</t>
-  </si>
-  <si>
-    <t>Gestion</t>
-  </si>
-  <si>
-    <t>Nicolás</t>
-  </si>
-  <si>
-    <t>nicolas.tello@zitron.com</t>
   </si>
   <si>
     <t>1214005018360998</t>
@@ -2526,9 +2526,11 @@
       <c r="B15" s="8">
         <v>46122.55119946759</v>
       </c>
-      <c r="C15" s="9"/>
+      <c r="C15" s="8">
+        <v>46195.50723163194</v>
+      </c>
       <c r="D15" s="8">
-        <v>46181.66640564815</v>
+        <v>46195.50724608796</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2563,8 +2565,12 @@
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
+      <c r="T15" s="9">
+        <v>1</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -2703,9 +2709,11 @@
       <c r="B18" s="5">
         <v>46122.55140040509</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46195.50721171296</v>
+      </c>
       <c r="D18" s="5">
-        <v>46139.170930567125</v>
+        <v>46195.50723229167</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2753,15 +2761,15 @@
         <v>74</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B19" s="8">
         <v>46122.55140604167</v>
@@ -2770,19 +2778,19 @@
         <v>46181.666399050926</v>
       </c>
       <c r="D19" s="8">
-        <v>46181.66641431713</v>
+        <v>46195.20558476852</v>
       </c>
       <c r="E19" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="I19" s="8">
         <v>46199</v>
@@ -2803,10 +2811,10 @@
         <v>66</v>
       </c>
       <c r="O19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="P19" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="Q19" s="8">
         <v>46199</v>
@@ -2814,8 +2822,8 @@
       <c r="R19" s="8">
         <v>46202</v>
       </c>
-      <c r="S19" s="11" t="s">
-        <v>86</v>
+      <c r="S19" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T19" s="9">
         <v>1</v>
@@ -2826,7 +2834,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46122.55141162037</v>
@@ -2859,7 +2867,7 @@
         <v>26</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>26</v>
@@ -2871,7 +2879,7 @@
         <v>62</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46136</v>
@@ -2891,7 +2899,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B21" s="8">
         <v>46122.566545787035</v>
@@ -2900,19 +2908,19 @@
         <v>46181.66636053241</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.66637766204</v>
+        <v>46195.20558446759</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="I21" s="8">
         <v>46199</v>
@@ -2933,10 +2941,10 @@
         <v>66</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="8">
         <v>46199</v>
@@ -2944,8 +2952,8 @@
       <c r="R21" s="8">
         <v>46202</v>
       </c>
-      <c r="S21" s="11" t="s">
-        <v>86</v>
+      <c r="S21" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T21" s="9">
         <v>1</v>
@@ -2956,7 +2964,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46122.56661521991</v>
@@ -2965,19 +2973,19 @@
         <v>46181.66637630787</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.66639054398</v>
+        <v>46195.20558434028</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="I22" s="5">
         <v>46199</v>
@@ -2998,10 +3006,10 @@
         <v>66</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Q22" s="5">
         <v>46199</v>
@@ -3009,8 +3017,8 @@
       <c r="R22" s="5">
         <v>46202</v>
       </c>
-      <c r="S22" s="11" t="s">
-        <v>86</v>
+      <c r="S22" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -3021,7 +3029,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B23" s="8">
         <v>46122.57286273148</v>
@@ -3030,19 +3038,19 @@
         <v>46181.66643224537</v>
       </c>
       <c r="D23" s="8">
-        <v>46181.66653640046</v>
+        <v>46195.205584386575</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="I23" s="8">
         <v>46199</v>
@@ -3063,10 +3071,10 @@
         <v>66</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q23" s="8">
         <v>46199</v>
@@ -3074,8 +3082,8 @@
       <c r="R23" s="8">
         <v>46202</v>
       </c>
-      <c r="S23" s="11" t="s">
-        <v>86</v>
+      <c r="S23" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T23" s="9">
         <v>1</v>
@@ -3086,17 +3094,19 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46122.55120394676</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46195.50733982639</v>
+      </c>
       <c r="D24" s="5">
-        <v>46181.66688321759</v>
+        <v>46195.50735353009</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>25</v>
@@ -3120,7 +3130,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -3128,12 +3138,16 @@
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
+      <c r="T24" s="6">
+        <v>1</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B25" s="8">
         <v>46122.55141694444</v>
@@ -3145,16 +3159,16 @@
         <v>46174.626181134256</v>
       </c>
       <c r="E25" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>103</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="I25" s="8">
         <v>46140</v>
@@ -3172,13 +3186,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q25" s="8">
         <v>46142</v>
@@ -3187,7 +3201,7 @@
         <v>46265</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T25" s="9">
         <v>1</v>
@@ -3198,7 +3212,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46122.55142208333</v>
@@ -3210,16 +3224,16 @@
         <v>46174.62325449074</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I26" s="5">
         <v>46140</v>
@@ -3237,29 +3251,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B27" s="8">
         <v>46122.55142699074</v>
@@ -3271,16 +3285,16 @@
         <v>46174.62615429398</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I27" s="8">
         <v>46142</v>
@@ -3298,48 +3312,50 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46122.5514322338</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46195.50732521991</v>
+      </c>
       <c r="D28" s="5">
-        <v>46192.84300386574</v>
+        <v>46195.5073399074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>46140</v>
@@ -3357,13 +3373,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q28" s="5">
         <v>46140</v>
@@ -3375,34 +3391,34 @@
         <v>32</v>
       </c>
       <c r="T28" s="6">
-        <v>0</v>
-      </c>
-      <c r="U28" s="10" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U28" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B29" s="8">
         <v>46122.551437546295</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46141.16984135417</v>
+        <v>46195.507223981476</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I29" s="8">
         <v>46140</v>
@@ -3420,29 +3436,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>76</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46122.55144255787</v>
@@ -3452,16 +3468,16 @@
         <v>46190.16825996528</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I30" s="5">
         <v>46142</v>
@@ -3479,29 +3495,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31" s="8">
         <v>46122.551447708334</v>
@@ -3513,16 +3529,16 @@
         <v>46133.82781321759</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I31" s="8">
         <v>46133</v>
@@ -3540,13 +3556,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q31" s="8">
         <v>46133</v>
@@ -3555,7 +3571,7 @@
         <v>46308</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T31" s="9">
         <v>1</v>
@@ -3566,7 +3582,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46122.5514527662</v>
@@ -3578,16 +3594,16 @@
         <v>46133.82773260417</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I32" s="5">
         <v>46133</v>
@@ -3605,29 +3621,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" s="8">
         <v>46122.55145796297</v>
@@ -3639,16 +3655,16 @@
         <v>46133.82778807871</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I33" s="8">
         <v>46153</v>
@@ -3666,29 +3682,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46122.55146299768</v>
@@ -3700,16 +3716,16 @@
         <v>46133.827769131945</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I34" s="5">
         <v>46153</v>
@@ -3727,29 +3743,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="8">
         <v>46122.55146795139</v>
@@ -3761,16 +3777,16 @@
         <v>46181.66688577546</v>
       </c>
       <c r="E35" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="9" t="s">
+      <c r="H35" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>138</v>
       </c>
       <c r="I35" s="8">
         <v>46203</v>
@@ -3788,13 +3804,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q35" s="8">
         <v>46203</v>
@@ -3803,7 +3819,7 @@
         <v>46213</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T35" s="9">
         <v>1</v>
@@ -3814,7 +3830,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46122.551472974534</v>
@@ -3826,16 +3842,16 @@
         <v>46181.66681946759</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I36" s="5">
         <v>46203</v>
@@ -3853,29 +3869,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B37" s="8">
         <v>46122.55152253472</v>
@@ -3887,16 +3903,16 @@
         <v>46181.66685818287</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>138</v>
       </c>
       <c r="I37" s="8">
         <v>46205</v>
@@ -3914,29 +3930,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46122.55152891204</v>
@@ -3948,16 +3964,16 @@
         <v>46189.172213136575</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I38" s="5">
         <v>46140</v>
@@ -3975,13 +3991,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q38" s="5">
         <v>46140</v>
@@ -4001,7 +4017,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B39" s="8">
         <v>46122.5515340625</v>
@@ -4013,16 +4029,16 @@
         <v>46154.86751927083</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>138</v>
       </c>
       <c r="I39" s="8">
         <v>46140</v>
@@ -4040,13 +4056,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4056,7 +4072,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46122.55153844907</v>
@@ -4068,16 +4084,16 @@
         <v>46154.867577453704</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I40" s="5">
         <v>46160</v>
@@ -4095,13 +4111,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4111,7 +4127,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46122.574933449076</v>
@@ -4123,16 +4139,16 @@
         <v>46181.666783252316</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>138</v>
       </c>
       <c r="I41" s="8">
         <v>46203</v>
@@ -4150,10 +4166,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4165,7 +4181,7 @@
         <v>46220</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -4176,7 +4192,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46122.575920972224</v>
@@ -4188,16 +4204,16 @@
         <v>46181.66670855324</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I42" s="5">
         <v>46203</v>
@@ -4215,13 +4231,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4231,7 +4247,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46122.57608475695</v>
@@ -4243,16 +4259,16 @@
         <v>46181.666754351856</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>138</v>
       </c>
       <c r="I43" s="8">
         <v>46212</v>
@@ -4270,13 +4286,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4286,7 +4302,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46122.57501438657</v>
@@ -4298,16 +4314,16 @@
         <v>46181.66706865741</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4325,10 +4341,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4340,7 +4356,7 @@
         <v>46238</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4351,7 +4367,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46122.57922111111</v>
@@ -4363,16 +4379,16 @@
         <v>46181.66690306713</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I45" s="8">
         <v>46203</v>
@@ -4390,13 +4406,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4406,7 +4422,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46122.57949202546</v>
@@ -4418,16 +4434,16 @@
         <v>46181.66694460648</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46210</v>
@@ -4445,13 +4461,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4461,7 +4477,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46125.529618217595</v>
@@ -4473,16 +4489,16 @@
         <v>46181.66723511574</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>138</v>
       </c>
       <c r="I47" s="8">
         <v>46203</v>
@@ -4500,10 +4516,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4515,7 +4531,7 @@
         <v>46218</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -4526,7 +4542,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46125.52977997685</v>
@@ -4538,16 +4554,16 @@
         <v>46181.66715912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I48" s="5">
         <v>46203</v>
@@ -4565,13 +4581,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4581,7 +4597,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46125.52991815972</v>
@@ -4593,16 +4609,16 @@
         <v>46181.66720563658</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>138</v>
       </c>
       <c r="I49" s="8">
         <v>46210</v>
@@ -4620,13 +4636,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4636,17 +4652,19 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B50" s="5">
         <v>46122.55120855324</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46195.5074512963</v>
+      </c>
       <c r="D50" s="5">
-        <v>46181.66790082176</v>
+        <v>46195.50756488426</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4670,7 +4688,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4678,12 +4696,16 @@
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
       <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
+      <c r="T50" s="6">
+        <v>1</v>
+      </c>
+      <c r="U50" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B51" s="8">
         <v>46122.55154344907</v>
@@ -4695,16 +4717,16 @@
         <v>46143.171145879634</v>
       </c>
       <c r="E51" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="9" t="s">
+      <c r="H51" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I51" s="8">
         <v>46136</v>
@@ -4722,13 +4744,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="8">
         <v>46136</v>
@@ -4748,7 +4770,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46122.551548993055</v>
@@ -4760,16 +4782,16 @@
         <v>46190.18859494213</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46191</v>
@@ -4787,13 +4809,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O52" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="Q52" s="5">
         <v>46191</v>
@@ -4813,7 +4835,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B53" s="8">
         <v>46122.55155721065</v>
@@ -4825,16 +4847,16 @@
         <v>46191.18981792824</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4850,13 +4872,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q53" s="8">
         <v>46198</v>
@@ -4876,26 +4898,28 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46122.55156568287</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46195.50761325231</v>
+      </c>
       <c r="D54" s="5">
-        <v>46125.66066763889</v>
+        <v>46195.50762895834</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4911,10 +4935,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4926,18 +4950,18 @@
         <v>46316</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T54" s="6">
-        <v>0</v>
-      </c>
-      <c r="U54" s="10" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U54" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B55" s="8">
         <v>46125.603622118055</v>
@@ -4947,16 +4971,16 @@
         <v>46125.65979525463</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4972,13 +4996,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4988,7 +5012,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46125.60367094907</v>
@@ -4998,16 +5022,16 @@
         <v>46125.65985976852</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5023,13 +5047,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5039,7 +5063,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B57" s="8">
         <v>46125.60371951389</v>
@@ -5049,16 +5073,16 @@
         <v>46125.65983615741</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -5074,13 +5098,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="P57" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5090,7 +5114,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
         <v>46125.60376462963</v>
@@ -5100,16 +5124,16 @@
         <v>46125.659875694444</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5125,13 +5149,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5141,7 +5165,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46125.60381739584</v>
@@ -5151,16 +5175,16 @@
         <v>46125.659896990735</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5176,13 +5200,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5192,7 +5216,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B60" s="5">
         <v>46122.551569710646</v>
@@ -5204,7 +5228,7 @@
         <v>46181.66785324074</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5228,7 +5252,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5241,7 +5265,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B61" s="8">
         <v>46122.55157321759</v>
@@ -5253,16 +5277,16 @@
         <v>46181.66739524306</v>
       </c>
       <c r="E61" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="9" t="s">
+      <c r="H61" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="I61" s="8">
         <v>46216</v>
@@ -5280,13 +5304,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q61" s="8">
         <v>46216</v>
@@ -5306,7 +5330,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B62" s="5">
         <v>46122.58491638889</v>
@@ -5318,16 +5342,16 @@
         <v>46181.667429016205</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I62" s="5">
         <v>46223</v>
@@ -5345,13 +5369,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46132</v>
@@ -5371,7 +5395,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B63" s="8">
         <v>46125.53102658565</v>
@@ -5383,16 +5407,16 @@
         <v>46181.66744925926</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="I63" s="8">
         <v>46219</v>
@@ -5410,13 +5434,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q63" s="8">
         <v>46219</v>
@@ -5425,7 +5449,7 @@
         <v>46220</v>
       </c>
       <c r="S63" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T63" s="9">
         <v>1</v>
@@ -5436,7 +5460,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B64" s="5">
         <v>46122.55157846065</v>
@@ -5448,16 +5472,16 @@
         <v>46181.66777241898</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="I64" s="5">
         <v>46225</v>
@@ -5475,13 +5499,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="Q64" s="5">
         <v>46225</v>
@@ -5490,7 +5514,7 @@
         <v>46226</v>
       </c>
       <c r="S64" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T64" s="6">
         <v>1</v>
@@ -5501,7 +5525,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B65" s="8">
         <v>46122.551583831024</v>
@@ -5513,7 +5537,7 @@
         <v>46181.66890770833</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5537,7 +5561,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5550,7 +5574,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46122.55158688658</v>
@@ -5562,16 +5586,16 @@
         <v>46181.66880932871</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I66" s="5">
         <v>46227</v>
@@ -5589,13 +5613,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q66" s="5">
         <v>46227</v>
@@ -5604,7 +5628,7 @@
         <v>46237</v>
       </c>
       <c r="S66" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -5615,7 +5639,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46122.55159185185</v>
@@ -5627,16 +5651,16 @@
         <v>46181.668846064815</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I67" s="8">
         <v>46238</v>
@@ -5654,13 +5678,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5669,7 +5693,7 @@
         <v>46255</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>
@@ -5680,7 +5704,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46125.595811921296</v>
@@ -5692,16 +5716,16 @@
         <v>46181.66807884259</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I68" s="5">
         <v>46238</v>
@@ -5719,13 +5743,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5735,7 +5759,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B69" s="8">
         <v>46125.59610047453</v>
@@ -5747,16 +5771,16 @@
         <v>46181.66808728009</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I69" s="8">
         <v>46238</v>
@@ -5774,13 +5798,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O69" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="P69" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5790,7 +5814,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46125.59621038195</v>
@@ -5802,16 +5826,16 @@
         <v>46181.66815550926</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I70" s="5">
         <v>46238</v>
@@ -5829,13 +5853,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5845,7 +5869,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B71" s="8">
         <v>46125.59625472222</v>
@@ -5857,16 +5881,16 @@
         <v>46181.66816819445</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I71" s="8">
         <v>46238</v>
@@ -5884,13 +5908,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O71" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5900,7 +5924,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46125.59629915509</v>
@@ -5912,16 +5936,16 @@
         <v>46181.66818078703</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I72" s="5">
         <v>46238</v>
@@ -5939,13 +5963,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5955,7 +5979,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46122.55159751157</v>
@@ -5967,16 +5991,16 @@
         <v>46181.66878222222</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I73" s="8">
         <v>46258</v>
@@ -5994,13 +6018,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q73" s="8">
         <v>46258</v>
@@ -6009,7 +6033,7 @@
         <v>46259</v>
       </c>
       <c r="S73" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T73" s="9">
         <v>1</v>
@@ -6020,7 +6044,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46125.59648849537</v>
@@ -6032,16 +6056,16 @@
         <v>46181.6686533912</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I74" s="5">
         <v>46258</v>
@@ -6059,13 +6083,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6075,7 +6099,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B75" s="8">
         <v>46125.59661854166</v>
@@ -6087,16 +6111,16 @@
         <v>46181.66866782407</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6114,13 +6138,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6130,7 +6154,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B76" s="5">
         <v>46125.596668750004</v>
@@ -6142,16 +6166,16 @@
         <v>46181.66867745371</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6169,13 +6193,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6185,7 +6209,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B77" s="8">
         <v>46125.59671550926</v>
@@ -6197,16 +6221,16 @@
         <v>46181.668687060184</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6224,13 +6248,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6240,7 +6264,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B78" s="5">
         <v>46125.59675546296</v>
@@ -6252,16 +6276,16 @@
         <v>46181.66870502315</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I78" s="5">
         <v>46258</v>
@@ -6279,13 +6303,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6295,17 +6319,17 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B79" s="8">
         <v>46122.55160357639</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46125.68677173612</v>
+        <v>46195.50752947917</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6329,7 +6353,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6342,7 +6366,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46122.55160679398</v>
@@ -6352,16 +6376,16 @@
         <v>46193.175859236115</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I80" s="5">
         <v>46191</v>
@@ -6379,13 +6403,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q80" s="5">
         <v>46191</v>
@@ -6400,31 +6424,33 @@
         <v>0</v>
       </c>
       <c r="U80" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B81" s="8">
         <v>46122.551612256946</v>
       </c>
-      <c r="C81" s="9"/>
+      <c r="C81" s="8">
+        <v>46195.50751318287</v>
+      </c>
       <c r="D81" s="8">
-        <v>46174.6261715625</v>
+        <v>46195.50753130787</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="I81" s="8">
         <v>46266</v>
@@ -6442,13 +6468,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q81" s="8">
         <v>46266</v>
@@ -6457,37 +6483,39 @@
         <v>46267</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T81" s="9">
-        <v>0</v>
-      </c>
-      <c r="U81" s="12" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+      <c r="U81" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46122.55161756944</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46195.50751851852</v>
+      </c>
       <c r="D82" s="5">
-        <v>46133.827803622684</v>
+        <v>46195.50753259259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I82" s="5">
         <v>46309</v>
@@ -6505,13 +6533,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q82" s="5">
         <v>46309</v>
@@ -6520,37 +6548,39 @@
         <v>46310</v>
       </c>
       <c r="S82" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T82" s="6">
-        <v>0</v>
-      </c>
-      <c r="U82" s="12" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+      <c r="U82" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B83" s="8">
         <v>46122.55162288195</v>
       </c>
-      <c r="C83" s="9"/>
+      <c r="C83" s="8">
+        <v>46195.507523437496</v>
+      </c>
       <c r="D83" s="8">
-        <v>46191.167618402775</v>
+        <v>46195.507539479164</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="I83" s="8">
         <v>46189</v>
@@ -6568,13 +6598,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q83" s="8">
         <v>46189</v>
@@ -6586,15 +6616,15 @@
         <v>32</v>
       </c>
       <c r="T83" s="9">
-        <v>0</v>
-      </c>
-      <c r="U83" s="12" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+      <c r="U83" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B84" s="5">
         <v>46122.59399163195</v>
@@ -6606,16 +6636,16 @@
         <v>46193.9332800463</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I84" s="5">
         <v>46239</v>
@@ -6633,13 +6663,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q84" s="5">
         <v>46239</v>
@@ -6648,7 +6678,7 @@
         <v>46240</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T84" s="6">
         <v>1</v>
@@ -6659,17 +6689,17 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B85" s="8">
         <v>46122.551628182875</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46125.632524444445</v>
+        <v>46195.507700347225</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6693,7 +6723,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6706,17 +6736,19 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B86" s="5">
         <v>46122.55163158565</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46195.50768850694</v>
+      </c>
       <c r="D86" s="5">
-        <v>46193.93317614583</v>
+        <v>46195.507707129625</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6743,13 +6775,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q86" s="5">
         <v>46260</v>
@@ -6758,18 +6790,18 @@
         <v>46279</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T86" s="6">
-        <v>0</v>
-      </c>
-      <c r="U86" s="12" t="s">
-        <v>79</v>
+        <v>1</v>
+      </c>
+      <c r="U86" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B87" s="8">
         <v>46125.5974969213</v>
@@ -6779,7 +6811,7 @@
         <v>46193.933163194444</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6806,13 +6838,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6822,7 +6854,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B88" s="5">
         <v>46125.59754570602</v>
@@ -6832,7 +6864,7 @@
         <v>46193.93316084491</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6859,13 +6891,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6875,7 +6907,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B89" s="8">
         <v>46125.59760710648</v>
@@ -6885,7 +6917,7 @@
         <v>46193.93316216435</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6912,13 +6944,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6928,7 +6960,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46125.59765891204</v>
@@ -6938,7 +6970,7 @@
         <v>46193.933167083334</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6965,13 +6997,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6981,7 +7013,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B91" s="8">
         <v>46125.597703391206</v>
@@ -6991,7 +7023,7 @@
         <v>46193.93316814815</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7018,13 +7050,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7034,7 +7066,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46122.55170659722</v>
@@ -7044,7 +7076,7 @@
         <v>46125.65705061343</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7071,13 +7103,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q92" s="5">
         <v>46280</v>
@@ -7086,28 +7118,28 @@
         <v>46282</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T92" s="6">
         <v>0</v>
       </c>
       <c r="U92" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" s="8">
         <v>46125.59982741898</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46134.792478877316</v>
+        <v>46195.50753101852</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7134,13 +7166,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O93" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="P93" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7150,17 +7182,17 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46125.599890833335</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46134.792471967594</v>
+        <v>46195.50752997685</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7187,13 +7219,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7203,17 +7235,17 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B95" s="8">
         <v>46125.59993134259</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46134.79247947916</v>
+        <v>46195.50753152778</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7240,13 +7272,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7256,17 +7288,17 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46125.59996929398</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46134.79247707176</v>
+        <v>46195.507530532406</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7293,13 +7325,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O96" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7309,17 +7341,17 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B97" s="8">
         <v>46125.6000115162</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46134.79248766204</v>
+        <v>46195.50753190972</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7346,13 +7378,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O97" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="P97" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7362,7 +7394,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B98" s="5">
         <v>46122.55164413195</v>
@@ -7372,7 +7404,7 @@
         <v>46125.65705466435</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7399,13 +7431,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q98" s="5">
         <v>46286</v>
@@ -7414,28 +7446,28 @@
         <v>46288</v>
       </c>
       <c r="S98" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
       <c r="U98" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B99" s="8">
         <v>46125.599162743056</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46134.792487314815</v>
+        <v>46195.50752082176</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7462,13 +7494,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O99" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="P99" s="9" t="s">
         <v>295</v>
-      </c>
-      <c r="P99" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7478,17 +7510,17 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B100" s="5">
         <v>46125.599302511575</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46134.792469293985</v>
+        <v>46195.507520127314</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7515,13 +7547,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7531,17 +7563,17 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B101" s="8">
         <v>46125.59934644676</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46134.79247422454</v>
+        <v>46195.507522314816</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7568,13 +7600,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>295</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7584,17 +7616,17 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B102" s="5">
         <v>46125.59938857639</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46134.79247373843</v>
+        <v>46195.50752153935</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7621,13 +7653,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O102" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="P102" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7637,17 +7669,17 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B103" s="8">
         <v>46125.59943094908</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46134.792486446764</v>
+        <v>46195.50752328704</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7674,13 +7706,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O103" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="P103" s="9" t="s">
         <v>295</v>
-      </c>
-      <c r="P103" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7690,7 +7722,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B104" s="5">
         <v>46122.551650995374</v>
@@ -7700,7 +7732,7 @@
         <v>46125.65705875</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7727,13 +7759,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q104" s="5">
         <v>46289</v>
@@ -7742,18 +7774,18 @@
         <v>46293</v>
       </c>
       <c r="S104" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B105" s="8">
         <v>46125.59953013889</v>
@@ -7763,7 +7795,7 @@
         <v>46134.79248056713</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7790,13 +7822,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7806,7 +7838,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B106" s="5">
         <v>46125.59961423611</v>
@@ -7816,7 +7848,7 @@
         <v>46134.792473194444</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7843,13 +7875,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7859,7 +7891,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B107" s="8">
         <v>46125.599654317135</v>
@@ -7869,7 +7901,7 @@
         <v>46134.792470844906</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7896,13 +7928,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7912,7 +7944,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B108" s="5">
         <v>46125.59957065972</v>
@@ -7922,7 +7954,7 @@
         <v>46134.79247670139</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7949,13 +7981,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7965,7 +7997,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B109" s="8">
         <v>46125.59969711806</v>
@@ -7975,7 +8007,7 @@
         <v>46134.792476076385</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8002,13 +8034,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8018,7 +8050,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B110" s="5">
         <v>46122.55163725694</v>
@@ -8028,7 +8060,7 @@
         <v>46125.65706174768</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8055,13 +8087,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q110" s="5">
         <v>46311</v>
@@ -8070,28 +8102,28 @@
         <v>46314</v>
       </c>
       <c r="S110" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>
       </c>
       <c r="U110" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B111" s="8">
         <v>46125.59780210648</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46134.7924857176</v>
+        <v>46195.50753145834</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8118,13 +8150,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O111" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="P111" s="9" t="s">
         <v>312</v>
-      </c>
-      <c r="P111" s="9" t="s">
-        <v>313</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8134,17 +8166,17 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B112" s="5">
         <v>46125.597836932866</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46134.79247778935</v>
+        <v>46195.50752924768</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8171,13 +8203,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O112" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="P112" s="6" t="s">
         <v>312</v>
-      </c>
-      <c r="P112" s="6" t="s">
-        <v>313</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8187,17 +8219,17 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B113" s="8">
         <v>46125.5979208912</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46134.79247834491</v>
+        <v>46195.507530347226</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8224,13 +8256,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O113" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="P113" s="9" t="s">
         <v>312</v>
-      </c>
-      <c r="P113" s="9" t="s">
-        <v>313</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8240,17 +8272,17 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B114" s="5">
         <v>46125.59788087963</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46134.79247162037</v>
+        <v>46195.507528125</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8277,13 +8309,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O114" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="P114" s="6" t="s">
         <v>312</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>313</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8293,17 +8325,17 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B115" s="8">
         <v>46125.597965023146</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46134.79246997685</v>
+        <v>46195.507526608795</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8330,13 +8362,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O115" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="P115" s="9" t="s">
         <v>312</v>
-      </c>
-      <c r="P115" s="9" t="s">
-        <v>313</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8346,7 +8378,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B116" s="5">
         <v>46122.55172043982</v>
@@ -8356,7 +8388,7 @@
         <v>46125.658894120366</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8383,13 +8415,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q116" s="5">
         <v>46315</v>
@@ -8398,18 +8430,18 @@
         <v>46315</v>
       </c>
       <c r="S116" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T116" s="6">
         <v>0</v>
       </c>
       <c r="U116" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B117" s="8">
         <v>46125.60038253472</v>
@@ -8419,7 +8451,7 @@
         <v>46125.658321932875</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8444,13 +8476,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8460,7 +8492,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B118" s="5">
         <v>46125.60043012731</v>
@@ -8470,7 +8502,7 @@
         <v>46125.658344236115</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8495,13 +8527,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8511,7 +8543,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B119" s="8">
         <v>46125.60047290509</v>
@@ -8521,7 +8553,7 @@
         <v>46125.65837160879</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8546,13 +8578,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8562,7 +8594,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B120" s="5">
         <v>46125.600514074074</v>
@@ -8572,7 +8604,7 @@
         <v>46125.6583996875</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8597,13 +8629,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8613,7 +8645,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B121" s="8">
         <v>46125.60055859954</v>
@@ -8623,7 +8655,7 @@
         <v>46125.65844143518</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8648,13 +8680,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8664,7 +8696,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B122" s="5">
         <v>46122.55172986111</v>
@@ -8674,7 +8706,7 @@
         <v>46125.66066717592</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8701,13 +8733,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q122" s="5">
         <v>46317</v>
@@ -8716,18 +8748,18 @@
         <v>46317</v>
       </c>
       <c r="S122" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T122" s="6">
         <v>0</v>
       </c>
       <c r="U122" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B123" s="8">
         <v>46125.60064416667</v>
@@ -8737,7 +8769,7 @@
         <v>46125.66201921296</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8762,13 +8794,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8778,7 +8810,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B124" s="5">
         <v>46125.60068740741</v>
@@ -8788,7 +8820,7 @@
         <v>46125.66205158565</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8813,13 +8845,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8829,7 +8861,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B125" s="8">
         <v>46125.60073844907</v>
@@ -8839,7 +8871,7 @@
         <v>46125.66207341435</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8864,13 +8896,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8880,7 +8912,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B126" s="5">
         <v>46125.60077622686</v>
@@ -8890,7 +8922,7 @@
         <v>46125.66209603009</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8915,13 +8947,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8931,7 +8963,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B127" s="8">
         <v>46125.600829143514</v>
@@ -8941,7 +8973,7 @@
         <v>46125.66214039351</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8966,13 +8998,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -8982,7 +9014,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B128" s="5">
         <v>46122.5517350463</v>
@@ -8992,7 +9024,7 @@
         <v>46191.706051354166</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>25</v>
@@ -9016,7 +9048,7 @@
         <v>26</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>26</v>
@@ -9029,7 +9061,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B129" s="8">
         <v>46122.5517390625</v>
@@ -9039,16 +9071,16 @@
         <v>46189.53573824074</v>
       </c>
       <c r="E129" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G129" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="F129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G129" s="9" t="s">
+      <c r="H129" s="9" t="s">
         <v>340</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>341</v>
       </c>
       <c r="I129" s="8">
         <v>46318</v>
@@ -9066,13 +9098,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q129" s="8">
         <v>46318</v>
@@ -9081,18 +9113,18 @@
         <v>46318</v>
       </c>
       <c r="S129" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T129" s="9">
         <v>0</v>
       </c>
       <c r="U129" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B130" s="5">
         <v>46125.60093731481</v>
@@ -9102,16 +9134,16 @@
         <v>46125.664177071754</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>341</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9127,13 +9159,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9143,7 +9175,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B131" s="8">
         <v>46125.601380821754</v>
@@ -9153,16 +9185,16 @@
         <v>46125.66419668982</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="H131" s="9" t="s">
         <v>340</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>341</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9178,13 +9210,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9194,7 +9226,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B132" s="5">
         <v>46125.60142481481</v>
@@ -9204,16 +9236,16 @@
         <v>46125.66421920139</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>341</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9229,13 +9261,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9245,7 +9277,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B133" s="8">
         <v>46125.60146085648</v>
@@ -9255,16 +9287,16 @@
         <v>46125.66424142361</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="H133" s="9" t="s">
         <v>340</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>341</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9280,13 +9312,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9296,7 +9328,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B134" s="5">
         <v>46125.60150208333</v>
@@ -9306,16 +9338,16 @@
         <v>46125.664280972225</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>341</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9331,13 +9363,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9347,7 +9379,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B135" s="8">
         <v>46122.55174383102</v>
@@ -9357,7 +9389,7 @@
         <v>46185.646541435184</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9382,13 +9414,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q135" s="8">
         <v>46321</v>
@@ -9397,18 +9429,18 @@
         <v>46321</v>
       </c>
       <c r="S135" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T135" s="9">
         <v>0</v>
       </c>
       <c r="U135" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B136" s="5">
         <v>46125.601086979164</v>
@@ -9418,7 +9450,7 @@
         <v>46125.66761228009</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9443,13 +9475,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9459,7 +9491,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B137" s="8">
         <v>46125.60115318287</v>
@@ -9469,7 +9501,7 @@
         <v>46125.66765621528</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9494,13 +9526,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9510,7 +9542,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B138" s="5">
         <v>46125.60120391204</v>
@@ -9520,7 +9552,7 @@
         <v>46125.66769103009</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9545,13 +9577,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9561,7 +9593,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B139" s="8">
         <v>46125.60125796296</v>
@@ -9571,7 +9603,7 @@
         <v>46125.667712152775</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9596,13 +9628,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9612,7 +9644,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B140" s="5">
         <v>46125.601304282405</v>
@@ -9622,7 +9654,7 @@
         <v>46125.6677272338</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9647,13 +9679,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9663,7 +9695,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B141" s="8">
         <v>46122.55174869213</v>
@@ -9675,16 +9707,16 @@
         <v>46191.706001886574</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9700,13 +9732,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q141" s="8">
         <v>46322</v>
@@ -9715,7 +9747,7 @@
         <v>46322</v>
       </c>
       <c r="S141" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T141" s="9">
         <v>1</v>
@@ -9726,7 +9758,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B142" s="5">
         <v>46125.60158650463</v>
@@ -9736,16 +9768,16 @@
         <v>46125.76574587963</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9761,13 +9793,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9777,7 +9809,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B143" s="8">
         <v>46125.60163133102</v>
@@ -9787,16 +9819,16 @@
         <v>46125.7630881713</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -9812,13 +9844,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9828,7 +9860,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B144" s="5">
         <v>46125.60167016204</v>
@@ -9838,16 +9870,16 @@
         <v>46125.76385471065</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9863,13 +9895,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9879,7 +9911,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B145" s="8">
         <v>46125.60170435185</v>
@@ -9889,16 +9921,16 @@
         <v>46125.76313709491</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9914,13 +9946,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -9930,7 +9962,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B146" s="5">
         <v>46125.60173947917</v>
@@ -9940,16 +9972,16 @@
         <v>46125.763172210645</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -9965,13 +9997,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9981,7 +10013,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B147" s="8">
         <v>46122.551753472224</v>
@@ -9993,16 +10025,16 @@
         <v>46191.706057812495</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -10018,13 +10050,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q147" s="8">
         <v>46323</v>
@@ -10033,7 +10065,7 @@
         <v>46323</v>
       </c>
       <c r="S147" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T147" s="9">
         <v>1</v>
@@ -10044,7 +10076,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B148" s="5">
         <v>46125.60181555555</v>
@@ -10054,16 +10086,16 @@
         <v>46125.76413488426</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10079,13 +10111,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10095,7 +10127,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B149" s="8">
         <v>46125.60185690972</v>
@@ -10105,16 +10137,16 @@
         <v>46125.764156805555</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10130,13 +10162,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10146,7 +10178,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B150" s="5">
         <v>46125.601899490735</v>
@@ -10156,16 +10188,16 @@
         <v>46125.76418171296</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10181,13 +10213,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10197,7 +10229,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B151" s="8">
         <v>46125.60193935185</v>
@@ -10207,16 +10239,16 @@
         <v>46125.764207615735</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H151" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10232,13 +10264,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10248,7 +10280,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B152" s="5">
         <v>46125.60197710648</v>
@@ -10258,16 +10290,16 @@
         <v>46125.764245451384</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10283,13 +10315,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10299,7 +10331,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B153" s="8">
         <v>46122.551758622685</v>
@@ -10309,7 +10341,7 @@
         <v>46125.58936878473</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>25</v>
@@ -10333,7 +10365,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>26</v>
@@ -10346,7 +10378,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B154" s="5">
         <v>46122.55176134259</v>
@@ -10356,16 +10388,16 @@
         <v>46191.70605767361</v>
       </c>
       <c r="E154" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G154" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="F154" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G154" s="6" t="s">
+      <c r="H154" s="6" t="s">
         <v>379</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>380</v>
       </c>
       <c r="I154" s="5">
         <v>46324</v>
@@ -10383,13 +10415,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q154" s="5">
         <v>46324</v>
@@ -10398,13 +10430,13 @@
         <v>46332</v>
       </c>
       <c r="S154" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T154" s="6">
         <v>0</v>
       </c>
       <c r="U154" s="12" t="s">
-        <v>79</v>
+        <v>380</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
@@ -10425,10 +10457,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="H155" s="9" t="s">
         <v>379</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>380</v>
       </c>
       <c r="I155" s="8">
         <v>46324</v>
@@ -10446,13 +10478,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q155" s="8">
         <v>46324</v>
@@ -10461,13 +10493,13 @@
         <v>46332</v>
       </c>
       <c r="S155" s="11" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="T155" s="9">
         <v>0</v>
       </c>
       <c r="U155" s="12" t="s">
-        <v>79</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="383">
   <si>
     <t xml:space="preserve"> 50001466 - ZITRON PERU (PODEROSA) </t>
   </si>
@@ -842,6 +842,9 @@
     <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor,Recepcion Sensor</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1214005013744127</t>
   </si>
   <si>
@@ -1212,9 +1215,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214005018360998</t>
@@ -6324,9 +6324,11 @@
       <c r="B79" s="8">
         <v>46122.55160357639</v>
       </c>
-      <c r="C79" s="9"/>
+      <c r="C79" s="8">
+        <v>46195.563125636574</v>
+      </c>
       <c r="D79" s="8">
-        <v>46195.50752947917</v>
+        <v>46195.563290335645</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>206</v>
@@ -6361,22 +6363,28 @@
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
       <c r="S79" s="9"/>
-      <c r="T79" s="9"/>
-      <c r="U79" s="9"/>
+      <c r="T79" s="9">
+        <v>1</v>
+      </c>
+      <c r="U79" s="12" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
         <v>46122.55160679398</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46195.563269363425</v>
+      </c>
       <c r="D80" s="5">
-        <v>46193.175859236115</v>
+        <v>46195.563288715275</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6409,7 +6417,7 @@
         <v>120</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q80" s="5">
         <v>46191</v>
@@ -6421,15 +6429,15 @@
         <v>32</v>
       </c>
       <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U80" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B81" s="8">
         <v>46122.551612256946</v>
@@ -6441,7 +6449,7 @@
         <v>46195.50753130787</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6474,7 +6482,7 @@
         <v>111</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q81" s="8">
         <v>46266</v>
@@ -6494,7 +6502,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B82" s="5">
         <v>46122.55161756944</v>
@@ -6506,7 +6514,7 @@
         <v>46195.50753259259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6539,7 +6547,7 @@
         <v>129</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q82" s="5">
         <v>46309</v>
@@ -6559,7 +6567,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B83" s="8">
         <v>46122.55162288195</v>
@@ -6571,7 +6579,7 @@
         <v>46195.507539479164</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6604,7 +6612,7 @@
         <v>151</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="8">
         <v>46189</v>
@@ -6624,7 +6632,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46122.59399163195</v>
@@ -6636,7 +6644,7 @@
         <v>46193.9332800463</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6669,7 +6677,7 @@
         <v>169</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q84" s="5">
         <v>46239</v>
@@ -6689,17 +6697,19 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B85" s="8">
         <v>46122.551628182875</v>
       </c>
-      <c r="C85" s="9"/>
+      <c r="C85" s="8">
+        <v>46195.5630599537</v>
+      </c>
       <c r="D85" s="8">
-        <v>46195.507700347225</v>
+        <v>46195.56307581019</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6723,7 +6733,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6731,12 +6741,16 @@
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
       <c r="S85" s="9"/>
-      <c r="T85" s="9"/>
-      <c r="U85" s="9"/>
+      <c r="T85" s="9">
+        <v>1</v>
+      </c>
+      <c r="U85" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B86" s="5">
         <v>46122.55163158565</v>
@@ -6748,7 +6762,7 @@
         <v>46195.507707129625</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6775,13 +6789,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q86" s="5">
         <v>46260</v>
@@ -6801,7 +6815,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B87" s="8">
         <v>46125.5974969213</v>
@@ -6838,10 +6852,10 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>199</v>
@@ -6854,7 +6868,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B88" s="5">
         <v>46125.59754570602</v>
@@ -6891,10 +6905,10 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>199</v>
@@ -6907,7 +6921,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B89" s="8">
         <v>46125.59760710648</v>
@@ -6944,10 +6958,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>199</v>
@@ -6960,7 +6974,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
         <v>46125.59765891204</v>
@@ -6997,10 +7011,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>199</v>
@@ -7013,7 +7027,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B91" s="8">
         <v>46125.597703391206</v>
@@ -7050,10 +7064,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>199</v>
@@ -7066,7 +7080,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46122.55170659722</v>
@@ -7076,7 +7090,7 @@
         <v>46125.65705061343</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7103,13 +7117,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q92" s="5">
         <v>46280</v>
@@ -7129,7 +7143,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="8">
         <v>46125.59982741898</v>
@@ -7166,13 +7180,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7182,7 +7196,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B94" s="5">
         <v>46125.599890833335</v>
@@ -7219,13 +7233,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7235,7 +7249,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B95" s="8">
         <v>46125.59993134259</v>
@@ -7272,13 +7286,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7288,7 +7302,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46125.59996929398</v>
@@ -7325,13 +7339,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7341,7 +7355,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B97" s="8">
         <v>46125.6000115162</v>
@@ -7378,13 +7392,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7394,7 +7408,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B98" s="5">
         <v>46122.55164413195</v>
@@ -7404,7 +7418,7 @@
         <v>46125.65705466435</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7431,13 +7445,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q98" s="5">
         <v>46286</v>
@@ -7457,7 +7471,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B99" s="8">
         <v>46125.599162743056</v>
@@ -7494,13 +7508,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7510,7 +7524,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B100" s="5">
         <v>46125.599302511575</v>
@@ -7547,13 +7561,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7563,7 +7577,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B101" s="8">
         <v>46125.59934644676</v>
@@ -7600,13 +7614,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7616,7 +7630,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B102" s="5">
         <v>46125.59938857639</v>
@@ -7653,13 +7667,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7669,7 +7683,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B103" s="8">
         <v>46125.59943094908</v>
@@ -7706,13 +7720,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7722,7 +7736,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B104" s="5">
         <v>46122.551650995374</v>
@@ -7732,7 +7746,7 @@
         <v>46125.65705875</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7759,13 +7773,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q104" s="5">
         <v>46289</v>
@@ -7785,14 +7799,14 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B105" s="8">
         <v>46125.59953013889</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46134.79248056713</v>
+        <v>46195.56328270833</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>199</v>
@@ -7822,13 +7836,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7838,14 +7852,14 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B106" s="5">
         <v>46125.59961423611</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46134.792473194444</v>
+        <v>46195.56328116899</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>199</v>
@@ -7875,13 +7889,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7891,14 +7905,14 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B107" s="8">
         <v>46125.599654317135</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46134.792470844906</v>
+        <v>46195.56328055555</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>199</v>
@@ -7928,13 +7942,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7944,14 +7958,14 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B108" s="5">
         <v>46125.59957065972</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46134.79247670139</v>
+        <v>46195.56328217592</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>199</v>
@@ -7981,13 +7995,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7997,14 +8011,14 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B109" s="8">
         <v>46125.59969711806</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46134.792476076385</v>
+        <v>46195.563281724535</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>199</v>
@@ -8034,13 +8048,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8050,7 +8064,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B110" s="5">
         <v>46122.55163725694</v>
@@ -8060,7 +8074,7 @@
         <v>46125.65706174768</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8087,13 +8101,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q110" s="5">
         <v>46311</v>
@@ -8113,7 +8127,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B111" s="8">
         <v>46125.59780210648</v>
@@ -8150,13 +8164,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8166,7 +8180,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B112" s="5">
         <v>46125.597836932866</v>
@@ -8203,13 +8217,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8219,7 +8233,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B113" s="8">
         <v>46125.5979208912</v>
@@ -8256,13 +8270,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8272,7 +8286,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B114" s="5">
         <v>46125.59788087963</v>
@@ -8309,13 +8323,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8325,7 +8339,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B115" s="8">
         <v>46125.597965023146</v>
@@ -8362,13 +8376,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8378,7 +8392,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B116" s="5">
         <v>46122.55172043982</v>
@@ -8388,7 +8402,7 @@
         <v>46125.658894120366</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8415,13 +8429,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q116" s="5">
         <v>46315</v>
@@ -8441,7 +8455,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B117" s="8">
         <v>46125.60038253472</v>
@@ -8476,13 +8490,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O117" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8492,7 +8506,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B118" s="5">
         <v>46125.60043012731</v>
@@ -8527,13 +8541,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8543,7 +8557,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B119" s="8">
         <v>46125.60047290509</v>
@@ -8578,13 +8592,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8594,7 +8608,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B120" s="5">
         <v>46125.600514074074</v>
@@ -8629,13 +8643,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8645,7 +8659,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B121" s="8">
         <v>46125.60055859954</v>
@@ -8680,13 +8694,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8696,7 +8710,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B122" s="5">
         <v>46122.55172986111</v>
@@ -8706,7 +8720,7 @@
         <v>46125.66066717592</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8733,13 +8747,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q122" s="5">
         <v>46317</v>
@@ -8759,7 +8773,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B123" s="8">
         <v>46125.60064416667</v>
@@ -8794,13 +8808,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O123" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8810,7 +8824,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B124" s="5">
         <v>46125.60068740741</v>
@@ -8845,13 +8859,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8861,7 +8875,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B125" s="8">
         <v>46125.60073844907</v>
@@ -8896,13 +8910,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O125" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8912,7 +8926,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B126" s="5">
         <v>46125.60077622686</v>
@@ -8947,13 +8961,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8963,7 +8977,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B127" s="8">
         <v>46125.600829143514</v>
@@ -8998,13 +9012,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9014,17 +9028,19 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B128" s="5">
         <v>46122.5517350463</v>
       </c>
-      <c r="C128" s="6"/>
+      <c r="C128" s="5">
+        <v>46195.56317517361</v>
+      </c>
       <c r="D128" s="5">
-        <v>46191.706051354166</v>
+        <v>46195.56318964121</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>25</v>
@@ -9048,7 +9064,7 @@
         <v>26</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>26</v>
@@ -9056,12 +9072,16 @@
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
       <c r="S128" s="6"/>
-      <c r="T128" s="6"/>
-      <c r="U128" s="6"/>
+      <c r="T128" s="6">
+        <v>1</v>
+      </c>
+      <c r="U128" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B129" s="8">
         <v>46122.5517390625</v>
@@ -9071,16 +9091,16 @@
         <v>46189.53573824074</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I129" s="8">
         <v>46318</v>
@@ -9098,13 +9118,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q129" s="8">
         <v>46318</v>
@@ -9124,7 +9144,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B130" s="5">
         <v>46125.60093731481</v>
@@ -9140,10 +9160,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9159,13 +9179,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9175,7 +9195,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B131" s="8">
         <v>46125.601380821754</v>
@@ -9191,10 +9211,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9210,13 +9230,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9226,7 +9246,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B132" s="5">
         <v>46125.60142481481</v>
@@ -9242,10 +9262,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9261,13 +9281,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9277,7 +9297,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B133" s="8">
         <v>46125.60146085648</v>
@@ -9293,10 +9313,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9312,13 +9332,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9328,7 +9348,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B134" s="5">
         <v>46125.60150208333</v>
@@ -9344,10 +9364,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9363,13 +9383,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9379,7 +9399,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B135" s="8">
         <v>46122.55174383102</v>
@@ -9389,7 +9409,7 @@
         <v>46185.646541435184</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9414,13 +9434,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>197</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q135" s="8">
         <v>46321</v>
@@ -9440,7 +9460,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B136" s="5">
         <v>46125.601086979164</v>
@@ -9475,13 +9495,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9491,7 +9511,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B137" s="8">
         <v>46125.60115318287</v>
@@ -9526,13 +9546,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9542,7 +9562,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B138" s="5">
         <v>46125.60120391204</v>
@@ -9577,13 +9597,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9593,7 +9613,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B139" s="8">
         <v>46125.60125796296</v>
@@ -9628,13 +9648,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O139" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9644,7 +9664,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B140" s="5">
         <v>46125.601304282405</v>
@@ -9679,13 +9699,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9695,7 +9715,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B141" s="8">
         <v>46122.55174869213</v>
@@ -9707,7 +9727,7 @@
         <v>46191.706001886574</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9732,13 +9752,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>197</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q141" s="8">
         <v>46322</v>
@@ -9758,7 +9778,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B142" s="5">
         <v>46125.60158650463</v>
@@ -9793,13 +9813,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9809,7 +9829,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B143" s="8">
         <v>46125.60163133102</v>
@@ -9844,13 +9864,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9860,7 +9880,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B144" s="5">
         <v>46125.60167016204</v>
@@ -9895,13 +9915,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9911,7 +9931,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B145" s="8">
         <v>46125.60170435185</v>
@@ -9946,13 +9966,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O145" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -9962,7 +9982,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B146" s="5">
         <v>46125.60173947917</v>
@@ -9997,13 +10017,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O146" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10013,7 +10033,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B147" s="8">
         <v>46122.551753472224</v>
@@ -10025,7 +10045,7 @@
         <v>46191.706057812495</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10050,13 +10070,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O147" s="9" t="s">
         <v>197</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q147" s="8">
         <v>46323</v>
@@ -10076,7 +10096,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B148" s="5">
         <v>46125.60181555555</v>
@@ -10111,13 +10131,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10127,7 +10147,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B149" s="8">
         <v>46125.60185690972</v>
@@ -10162,13 +10182,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O149" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10178,7 +10198,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B150" s="5">
         <v>46125.601899490735</v>
@@ -10213,13 +10233,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10229,7 +10249,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B151" s="8">
         <v>46125.60193935185</v>
@@ -10264,13 +10284,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>199</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10280,7 +10300,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B152" s="5">
         <v>46125.60197710648</v>
@@ -10315,13 +10335,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>199</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10331,7 +10351,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B153" s="8">
         <v>46122.551758622685</v>
@@ -10341,7 +10361,7 @@
         <v>46125.58936878473</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>25</v>
@@ -10365,7 +10385,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>26</v>
@@ -10378,7 +10398,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B154" s="5">
         <v>46122.55176134259</v>
@@ -10388,16 +10408,16 @@
         <v>46191.70605767361</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I154" s="5">
         <v>46324</v>
@@ -10415,13 +10435,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q154" s="5">
         <v>46324</v>
@@ -10436,7 +10456,7 @@
         <v>0</v>
       </c>
       <c r="U154" s="12" t="s">
-        <v>380</v>
+        <v>256</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
@@ -10457,10 +10477,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I155" s="8">
         <v>46324</v>
@@ -10478,13 +10498,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q155" s="8">
         <v>46324</v>
@@ -10499,7 +10519,7 @@
         <v>0</v>
       </c>
       <c r="U155" s="12" t="s">
-        <v>380</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -422,6 +422,9 @@
     <t>Generación OC Rodete,Fabricación Rodete</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1214004989988431</t>
   </si>
   <si>
@@ -840,9 +843,6 @@
   </si>
   <si>
     <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor,Recepcion Sensor</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214005013744127</t>
@@ -3343,7 +3343,7 @@
         <v>46195.50732521991</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.5073399074</v>
+        <v>46195.71184679398</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3393,23 +3393,25 @@
       <c r="T28" s="6">
         <v>1</v>
       </c>
-      <c r="U28" s="11" t="s">
-        <v>33</v>
+      <c r="U28" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="8">
         <v>46122.551437546295</v>
       </c>
-      <c r="C29" s="9"/>
+      <c r="C29" s="8">
+        <v>46195.71138274306</v>
+      </c>
       <c r="D29" s="8">
-        <v>46195.507223981476</v>
+        <v>46195.71138517361</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3442,7 +3444,7 @@
         <v>76</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3458,17 +3460,19 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46122.55144255787</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46195.711830960645</v>
+      </c>
       <c r="D30" s="5">
-        <v>46190.16825996528</v>
+        <v>46195.711832500005</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3498,10 +3502,10 @@
         <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3517,7 +3521,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="8">
         <v>46122.551447708334</v>
@@ -3529,7 +3533,7 @@
         <v>46133.82781321759</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3559,7 +3563,7 @@
         <v>98</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>98</v>
@@ -3582,7 +3586,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46122.5514527662</v>
@@ -3594,7 +3598,7 @@
         <v>46133.82773260417</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3621,13 +3625,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3643,7 +3647,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B33" s="8">
         <v>46122.55145796297</v>
@@ -3655,7 +3659,7 @@
         <v>46133.82778807871</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3682,13 +3686,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3704,7 +3708,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46122.55146299768</v>
@@ -3716,7 +3720,7 @@
         <v>46133.827769131945</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3743,13 +3747,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3765,7 +3769,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="8">
         <v>46122.55146795139</v>
@@ -3777,16 +3781,16 @@
         <v>46181.66688577546</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I35" s="8">
         <v>46203</v>
@@ -3807,7 +3811,7 @@
         <v>98</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>98</v>
@@ -3830,7 +3834,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46122.551472974534</v>
@@ -3842,16 +3846,16 @@
         <v>46181.66681946759</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I36" s="5">
         <v>46203</v>
@@ -3869,13 +3873,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>80</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3891,7 +3895,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="8">
         <v>46122.55152253472</v>
@@ -3903,16 +3907,16 @@
         <v>46181.66685818287</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I37" s="8">
         <v>46205</v>
@@ -3930,13 +3934,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3952,7 +3956,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46122.55152891204</v>
@@ -3964,16 +3968,16 @@
         <v>46189.172213136575</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I38" s="5">
         <v>46140</v>
@@ -3994,7 +3998,7 @@
         <v>98</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>98</v>
@@ -4017,7 +4021,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="8">
         <v>46122.5515340625</v>
@@ -4035,10 +4039,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I39" s="8">
         <v>46140</v>
@@ -4056,13 +4060,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4072,7 +4076,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46122.55153844907</v>
@@ -4084,16 +4088,16 @@
         <v>46154.867577453704</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I40" s="5">
         <v>46160</v>
@@ -4111,13 +4115,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4127,7 +4131,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="8">
         <v>46122.574933449076</v>
@@ -4139,16 +4143,16 @@
         <v>46181.666783252316</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I41" s="8">
         <v>46203</v>
@@ -4169,7 +4173,7 @@
         <v>98</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4192,7 +4196,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46122.575920972224</v>
@@ -4210,10 +4214,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I42" s="5">
         <v>46203</v>
@@ -4231,13 +4235,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4247,7 +4251,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46122.57608475695</v>
@@ -4259,16 +4263,16 @@
         <v>46181.666754351856</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I43" s="8">
         <v>46212</v>
@@ -4286,13 +4290,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4302,7 +4306,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46122.57501438657</v>
@@ -4314,16 +4318,16 @@
         <v>46181.66706865741</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4344,7 +4348,7 @@
         <v>98</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4367,7 +4371,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="8">
         <v>46122.57922111111</v>
@@ -4385,10 +4389,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I45" s="8">
         <v>46203</v>
@@ -4406,13 +4410,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>95</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4422,7 +4426,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46122.57949202546</v>
@@ -4434,16 +4438,16 @@
         <v>46181.66694460648</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46210</v>
@@ -4461,13 +4465,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4477,7 +4481,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46125.529618217595</v>
@@ -4489,16 +4493,16 @@
         <v>46181.66723511574</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I47" s="8">
         <v>46203</v>
@@ -4519,7 +4523,7 @@
         <v>98</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4542,7 +4546,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46125.52977997685</v>
@@ -4560,10 +4564,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I48" s="5">
         <v>46203</v>
@@ -4581,13 +4585,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>92</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4597,7 +4601,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B49" s="8">
         <v>46125.52991815972</v>
@@ -4609,16 +4613,16 @@
         <v>46181.66720563658</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I49" s="8">
         <v>46210</v>
@@ -4636,13 +4640,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>93</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4652,7 +4656,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
         <v>46122.55120855324</v>
@@ -4664,7 +4668,7 @@
         <v>46195.50756488426</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4688,7 +4692,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4705,7 +4709,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B51" s="8">
         <v>46122.55154344907</v>
@@ -4717,16 +4721,16 @@
         <v>46143.171145879634</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I51" s="8">
         <v>46136</v>
@@ -4744,13 +4748,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="8">
         <v>46136</v>
@@ -4770,7 +4774,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46122.551548993055</v>
@@ -4782,16 +4786,16 @@
         <v>46190.18859494213</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46191</v>
@@ -4809,13 +4813,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="5">
         <v>46191</v>
@@ -4835,7 +4839,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B53" s="8">
         <v>46122.55155721065</v>
@@ -4853,10 +4857,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4872,13 +4876,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q53" s="8">
         <v>46198</v>
@@ -4898,7 +4902,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46122.55156568287</v>
@@ -4910,16 +4914,16 @@
         <v>46195.50762895834</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4935,10 +4939,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4961,7 +4965,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B55" s="8">
         <v>46125.603622118055</v>
@@ -4971,16 +4975,16 @@
         <v>46125.65979525463</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4996,13 +5000,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -5012,7 +5016,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B56" s="5">
         <v>46125.60367094907</v>
@@ -5022,16 +5026,16 @@
         <v>46125.65985976852</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5047,13 +5051,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5063,7 +5067,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B57" s="8">
         <v>46125.60371951389</v>
@@ -5073,16 +5077,16 @@
         <v>46125.65983615741</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -5098,13 +5102,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5114,7 +5118,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B58" s="5">
         <v>46125.60376462963</v>
@@ -5124,16 +5128,16 @@
         <v>46125.659875694444</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5149,13 +5153,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5165,7 +5169,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B59" s="8">
         <v>46125.60381739584</v>
@@ -5175,16 +5179,16 @@
         <v>46125.659896990735</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5200,13 +5204,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5216,7 +5220,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B60" s="5">
         <v>46122.551569710646</v>
@@ -5228,7 +5232,7 @@
         <v>46181.66785324074</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5252,7 +5256,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5265,7 +5269,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B61" s="8">
         <v>46122.55157321759</v>
@@ -5277,16 +5281,16 @@
         <v>46181.66739524306</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I61" s="8">
         <v>46216</v>
@@ -5304,13 +5308,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q61" s="8">
         <v>46216</v>
@@ -5330,7 +5334,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46122.58491638889</v>
@@ -5342,16 +5346,16 @@
         <v>46181.667429016205</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I62" s="5">
         <v>46223</v>
@@ -5369,13 +5373,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q62" s="5">
         <v>46132</v>
@@ -5395,7 +5399,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46125.53102658565</v>
@@ -5407,16 +5411,16 @@
         <v>46181.66744925926</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I63" s="8">
         <v>46219</v>
@@ -5434,13 +5438,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q63" s="8">
         <v>46219</v>
@@ -5460,7 +5464,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
         <v>46122.55157846065</v>
@@ -5472,16 +5476,16 @@
         <v>46181.66777241898</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I64" s="5">
         <v>46225</v>
@@ -5499,13 +5503,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="5">
         <v>46225</v>
@@ -5525,7 +5529,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
         <v>46122.551583831024</v>
@@ -5537,7 +5541,7 @@
         <v>46181.66890770833</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5561,7 +5565,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5574,7 +5578,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46122.55158688658</v>
@@ -5586,16 +5590,16 @@
         <v>46181.66880932871</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I66" s="5">
         <v>46227</v>
@@ -5613,13 +5617,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q66" s="5">
         <v>46227</v>
@@ -5639,7 +5643,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="8">
         <v>46122.55159185185</v>
@@ -5651,16 +5655,16 @@
         <v>46181.668846064815</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I67" s="8">
         <v>46238</v>
@@ -5678,13 +5682,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5704,7 +5708,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B68" s="5">
         <v>46125.595811921296</v>
@@ -5716,16 +5720,16 @@
         <v>46181.66807884259</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I68" s="5">
         <v>46238</v>
@@ -5743,13 +5747,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5759,7 +5763,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B69" s="8">
         <v>46125.59610047453</v>
@@ -5771,16 +5775,16 @@
         <v>46181.66808728009</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I69" s="8">
         <v>46238</v>
@@ -5798,13 +5802,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5814,7 +5818,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B70" s="5">
         <v>46125.59621038195</v>
@@ -5826,16 +5830,16 @@
         <v>46181.66815550926</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I70" s="5">
         <v>46238</v>
@@ -5853,13 +5857,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5869,7 +5873,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B71" s="8">
         <v>46125.59625472222</v>
@@ -5881,16 +5885,16 @@
         <v>46181.66816819445</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I71" s="8">
         <v>46238</v>
@@ -5908,13 +5912,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5924,7 +5928,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B72" s="5">
         <v>46125.59629915509</v>
@@ -5936,16 +5940,16 @@
         <v>46181.66818078703</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I72" s="5">
         <v>46238</v>
@@ -5963,13 +5967,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5979,7 +5983,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46122.55159751157</v>
@@ -5991,16 +5995,16 @@
         <v>46181.66878222222</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I73" s="8">
         <v>46258</v>
@@ -6018,13 +6022,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q73" s="8">
         <v>46258</v>
@@ -6044,7 +6048,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46125.59648849537</v>
@@ -6056,16 +6060,16 @@
         <v>46181.6686533912</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I74" s="5">
         <v>46258</v>
@@ -6083,13 +6087,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6099,7 +6103,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B75" s="8">
         <v>46125.59661854166</v>
@@ -6111,16 +6115,16 @@
         <v>46181.66866782407</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6138,13 +6142,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6154,7 +6158,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B76" s="5">
         <v>46125.596668750004</v>
@@ -6166,16 +6170,16 @@
         <v>46181.66867745371</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6193,13 +6197,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6209,7 +6213,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B77" s="8">
         <v>46125.59671550926</v>
@@ -6221,16 +6225,16 @@
         <v>46181.668687060184</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6248,13 +6252,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6264,7 +6268,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B78" s="5">
         <v>46125.59675546296</v>
@@ -6276,16 +6280,16 @@
         <v>46181.66870502315</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I78" s="5">
         <v>46258</v>
@@ -6303,13 +6307,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6319,7 +6323,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B79" s="8">
         <v>46122.55160357639</v>
@@ -6331,7 +6335,7 @@
         <v>46195.563290335645</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6355,7 +6359,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6367,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>256</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6381,7 +6385,7 @@
         <v>46195.563269363425</v>
       </c>
       <c r="D80" s="5">
-        <v>46195.563288715275</v>
+        <v>46195.711846817125</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6390,10 +6394,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I80" s="5">
         <v>46191</v>
@@ -6411,10 +6415,10 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>259</v>
@@ -6431,8 +6435,8 @@
       <c r="T80" s="6">
         <v>1</v>
       </c>
-      <c r="U80" s="11" t="s">
-        <v>33</v>
+      <c r="U80" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6455,10 +6459,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I81" s="8">
         <v>46266</v>
@@ -6476,7 +6480,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>111</v>
@@ -6520,10 +6524,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I82" s="5">
         <v>46309</v>
@@ -6541,10 +6545,10 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>259</v>
@@ -6585,10 +6589,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I83" s="8">
         <v>46189</v>
@@ -6606,10 +6610,10 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>259</v>
@@ -6650,10 +6654,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I84" s="5">
         <v>46239</v>
@@ -6671,10 +6675,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>268</v>
@@ -6825,7 +6829,7 @@
         <v>46193.933163194444</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6858,7 +6862,7 @@
         <v>276</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6878,7 +6882,7 @@
         <v>46193.93316084491</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6911,7 +6915,7 @@
         <v>276</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6931,7 +6935,7 @@
         <v>46193.93316216435</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6964,7 +6968,7 @@
         <v>276</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6984,7 +6988,7 @@
         <v>46193.933167083334</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7017,7 +7021,7 @@
         <v>276</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7037,7 +7041,7 @@
         <v>46193.93316814815</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7070,7 +7074,7 @@
         <v>276</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7120,7 +7124,7 @@
         <v>270</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>270</v>
@@ -7153,7 +7157,7 @@
         <v>46195.50753101852</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7206,7 +7210,7 @@
         <v>46195.50752997685</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7259,7 +7263,7 @@
         <v>46195.50753152778</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7312,7 +7316,7 @@
         <v>46195.507530532406</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7365,7 +7369,7 @@
         <v>46195.50753190972</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7481,7 +7485,7 @@
         <v>46195.50752082176</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7534,7 +7538,7 @@
         <v>46195.507520127314</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7587,7 +7591,7 @@
         <v>46195.507522314816</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7640,7 +7644,7 @@
         <v>46195.50752153935</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7693,7 +7697,7 @@
         <v>46195.50752328704</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7776,7 +7780,7 @@
         <v>270</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>270</v>
@@ -7809,7 +7813,7 @@
         <v>46195.56328270833</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7862,7 +7866,7 @@
         <v>46195.56328116899</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7915,7 +7919,7 @@
         <v>46195.56328055555</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7968,7 +7972,7 @@
         <v>46195.56328217592</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8021,7 +8025,7 @@
         <v>46195.563281724535</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8104,7 +8108,7 @@
         <v>270</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>270</v>
@@ -8137,7 +8141,7 @@
         <v>46195.50753145834</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8190,7 +8194,7 @@
         <v>46195.50752924768</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8243,7 +8247,7 @@
         <v>46195.507530347226</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8296,7 +8300,7 @@
         <v>46195.507528125</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8349,7 +8353,7 @@
         <v>46195.507526608795</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8432,7 +8436,7 @@
         <v>270</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>270</v>
@@ -8465,7 +8469,7 @@
         <v>46125.658321932875</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8493,7 +8497,7 @@
         <v>319</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>321</v>
@@ -8516,7 +8520,7 @@
         <v>46125.658344236115</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8544,7 +8548,7 @@
         <v>319</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>321</v>
@@ -8567,7 +8571,7 @@
         <v>46125.65837160879</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8595,7 +8599,7 @@
         <v>319</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>321</v>
@@ -8618,7 +8622,7 @@
         <v>46125.6583996875</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8646,7 +8650,7 @@
         <v>319</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>321</v>
@@ -8669,7 +8673,7 @@
         <v>46125.65844143518</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8697,7 +8701,7 @@
         <v>319</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>321</v>
@@ -8750,7 +8754,7 @@
         <v>270</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>328</v>
@@ -8783,7 +8787,7 @@
         <v>46125.66201921296</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8811,7 +8815,7 @@
         <v>327</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>330</v>
@@ -8834,7 +8838,7 @@
         <v>46125.66205158565</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8862,7 +8866,7 @@
         <v>327</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>330</v>
@@ -8885,7 +8889,7 @@
         <v>46125.66207341435</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8913,7 +8917,7 @@
         <v>327</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>330</v>
@@ -8936,7 +8940,7 @@
         <v>46125.66209603009</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8964,7 +8968,7 @@
         <v>327</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>330</v>
@@ -8987,7 +8991,7 @@
         <v>46125.66214039351</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9015,7 +9019,7 @@
         <v>327</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>330</v>
@@ -9154,7 +9158,7 @@
         <v>46125.664177071754</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9182,7 +9186,7 @@
         <v>339</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>344</v>
@@ -9205,7 +9209,7 @@
         <v>46125.66419668982</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9233,7 +9237,7 @@
         <v>339</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P131" s="9" t="s">
         <v>344</v>
@@ -9256,7 +9260,7 @@
         <v>46125.66421920139</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9284,7 +9288,7 @@
         <v>339</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>344</v>
@@ -9307,7 +9311,7 @@
         <v>46125.66424142361</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9335,7 +9339,7 @@
         <v>339</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P133" s="9" t="s">
         <v>344</v>
@@ -9358,7 +9362,7 @@
         <v>46125.664280972225</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9386,7 +9390,7 @@
         <v>339</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>344</v>
@@ -9437,7 +9441,7 @@
         <v>336</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>336</v>
@@ -9470,7 +9474,7 @@
         <v>46125.66761228009</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9498,7 +9502,7 @@
         <v>350</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>352</v>
@@ -9521,7 +9525,7 @@
         <v>46125.66765621528</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9549,7 +9553,7 @@
         <v>350</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P137" s="9" t="s">
         <v>352</v>
@@ -9572,7 +9576,7 @@
         <v>46125.66769103009</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9600,7 +9604,7 @@
         <v>350</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>352</v>
@@ -9623,7 +9627,7 @@
         <v>46125.667712152775</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9651,7 +9655,7 @@
         <v>350</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>352</v>
@@ -9674,7 +9678,7 @@
         <v>46125.6677272338</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9702,7 +9706,7 @@
         <v>350</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>352</v>
@@ -9733,10 +9737,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9755,7 +9759,7 @@
         <v>336</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>336</v>
@@ -9788,16 +9792,16 @@
         <v>46125.76574587963</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9816,7 +9820,7 @@
         <v>358</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>360</v>
@@ -9839,16 +9843,16 @@
         <v>46125.7630881713</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -9867,7 +9871,7 @@
         <v>358</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P143" s="9" t="s">
         <v>360</v>
@@ -9890,16 +9894,16 @@
         <v>46125.76385471065</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9918,7 +9922,7 @@
         <v>358</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>363</v>
@@ -9941,16 +9945,16 @@
         <v>46125.76313709491</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9969,7 +9973,7 @@
         <v>358</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>363</v>
@@ -9992,16 +9996,16 @@
         <v>46125.763172210645</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10020,7 +10024,7 @@
         <v>358</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>363</v>
@@ -10051,10 +10055,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -10073,7 +10077,7 @@
         <v>336</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>368</v>
@@ -10106,16 +10110,16 @@
         <v>46125.76413488426</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10134,7 +10138,7 @@
         <v>367</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>367</v>
@@ -10157,16 +10161,16 @@
         <v>46125.764156805555</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10185,7 +10189,7 @@
         <v>367</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>367</v>
@@ -10208,16 +10212,16 @@
         <v>46125.76418171296</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10236,7 +10240,7 @@
         <v>367</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>367</v>
@@ -10259,16 +10263,16 @@
         <v>46125.764207615735</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10287,7 +10291,7 @@
         <v>367</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P151" s="9" t="s">
         <v>367</v>
@@ -10310,16 +10314,16 @@
         <v>46125.764245451384</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10338,7 +10342,7 @@
         <v>367</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>367</v>
@@ -10456,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="U154" s="12" t="s">
-        <v>256</v>
+        <v>116</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
@@ -10519,7 +10523,7 @@
         <v>0</v>
       </c>
       <c r="U155" s="12" t="s">
-        <v>256</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4911,7 +4911,7 @@
         <v>46195.50761325231</v>
       </c>
       <c r="D54" s="5">
-        <v>46195.50762895834</v>
+        <v>46196.76907818287</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -4959,8 +4959,8 @@
       <c r="T54" s="6">
         <v>1</v>
       </c>
-      <c r="U54" s="11" t="s">
-        <v>33</v>
+      <c r="U54" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4970,9 +4970,11 @@
       <c r="B55" s="8">
         <v>46125.603622118055</v>
       </c>
-      <c r="C55" s="9"/>
+      <c r="C55" s="8">
+        <v>46196.76904752315</v>
+      </c>
       <c r="D55" s="8">
-        <v>46125.65979525463</v>
+        <v>46196.7690521412</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>200</v>
@@ -5021,9 +5023,11 @@
       <c r="B56" s="5">
         <v>46125.60367094907</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46196.769048449074</v>
+      </c>
       <c r="D56" s="5">
-        <v>46125.65985976852</v>
+        <v>46196.769052523145</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -5072,9 +5076,11 @@
       <c r="B57" s="8">
         <v>46125.60371951389</v>
       </c>
-      <c r="C57" s="9"/>
+      <c r="C57" s="8">
+        <v>46196.76904929398</v>
+      </c>
       <c r="D57" s="8">
-        <v>46125.65983615741</v>
+        <v>46196.76905283565</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5123,9 +5129,11 @@
       <c r="B58" s="5">
         <v>46125.60376462963</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46196.769050069444</v>
+      </c>
       <c r="D58" s="5">
-        <v>46125.659875694444</v>
+        <v>46196.76905314815</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>200</v>
@@ -5174,9 +5182,11 @@
       <c r="B59" s="8">
         <v>46125.60381739584</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46196.76905077546</v>
+      </c>
       <c r="D59" s="8">
-        <v>46125.659896990735</v>
+        <v>46196.76905349537</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>200</v>
@@ -6710,7 +6720,7 @@
         <v>46195.5630599537</v>
       </c>
       <c r="D85" s="8">
-        <v>46195.56307581019</v>
+        <v>46196.769192685184</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>270</v>
@@ -6748,8 +6758,8 @@
       <c r="T85" s="9">
         <v>1</v>
       </c>
-      <c r="U85" s="11" t="s">
-        <v>33</v>
+      <c r="U85" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6824,9 +6834,11 @@
       <c r="B87" s="8">
         <v>46125.5974969213</v>
       </c>
-      <c r="C87" s="9"/>
+      <c r="C87" s="8">
+        <v>46196.76791707176</v>
+      </c>
       <c r="D87" s="8">
-        <v>46193.933163194444</v>
+        <v>46196.767918831014</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>200</v>
@@ -6877,9 +6889,11 @@
       <c r="B88" s="5">
         <v>46125.59754570602</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46196.76795405093</v>
+      </c>
       <c r="D88" s="5">
-        <v>46193.93316084491</v>
+        <v>46196.76795645834</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>200</v>
@@ -6930,9 +6944,11 @@
       <c r="B89" s="8">
         <v>46125.59760710648</v>
       </c>
-      <c r="C89" s="9"/>
+      <c r="C89" s="8">
+        <v>46196.767928217596</v>
+      </c>
       <c r="D89" s="8">
-        <v>46193.93316216435</v>
+        <v>46196.76793001157</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>200</v>
@@ -6983,9 +6999,11 @@
       <c r="B90" s="5">
         <v>46125.59765891204</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46196.76794651621</v>
+      </c>
       <c r="D90" s="5">
-        <v>46193.933167083334</v>
+        <v>46196.76794809027</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>200</v>
@@ -7036,9 +7054,11 @@
       <c r="B91" s="8">
         <v>46125.597703391206</v>
       </c>
-      <c r="C91" s="9"/>
+      <c r="C91" s="8">
+        <v>46196.76794100694</v>
+      </c>
       <c r="D91" s="8">
-        <v>46193.93316814815</v>
+        <v>46196.76794287037</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>200</v>
@@ -7089,9 +7109,11 @@
       <c r="B92" s="5">
         <v>46122.55170659722</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5">
+        <v>46196.76755512731</v>
+      </c>
       <c r="D92" s="5">
-        <v>46125.65705061343</v>
+        <v>46196.76807780092</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>282</v>
@@ -7139,10 +7161,10 @@
         <v>105</v>
       </c>
       <c r="T92" s="6">
-        <v>0</v>
-      </c>
-      <c r="U92" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U92" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7152,9 +7174,11 @@
       <c r="B93" s="8">
         <v>46125.59982741898</v>
       </c>
-      <c r="C93" s="9"/>
+      <c r="C93" s="8">
+        <v>46196.76800195602</v>
+      </c>
       <c r="D93" s="8">
-        <v>46195.50753101852</v>
+        <v>46196.76800386574</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>200</v>
@@ -7205,9 +7229,11 @@
       <c r="B94" s="5">
         <v>46125.599890833335</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46196.768023020835</v>
+      </c>
       <c r="D94" s="5">
-        <v>46195.50752997685</v>
+        <v>46196.768024687495</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>200</v>
@@ -7258,9 +7284,11 @@
       <c r="B95" s="8">
         <v>46125.59993134259</v>
       </c>
-      <c r="C95" s="9"/>
+      <c r="C95" s="8">
+        <v>46196.76801494213</v>
+      </c>
       <c r="D95" s="8">
-        <v>46195.50753152778</v>
+        <v>46196.76801675926</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>200</v>
@@ -7311,9 +7339,11 @@
       <c r="B96" s="5">
         <v>46125.59996929398</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46196.76805109954</v>
+      </c>
       <c r="D96" s="5">
-        <v>46195.507530532406</v>
+        <v>46196.76805278935</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>200</v>
@@ -7364,9 +7394,11 @@
       <c r="B97" s="8">
         <v>46125.6000115162</v>
       </c>
-      <c r="C97" s="9"/>
+      <c r="C97" s="8">
+        <v>46196.76805706018</v>
+      </c>
       <c r="D97" s="8">
-        <v>46195.50753190972</v>
+        <v>46196.76805907408</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>200</v>
@@ -7417,9 +7449,11 @@
       <c r="B98" s="5">
         <v>46122.55164413195</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46196.76839824074</v>
+      </c>
       <c r="D98" s="5">
-        <v>46125.65705466435</v>
+        <v>46196.76840872686</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>292</v>
@@ -7467,10 +7501,10 @@
         <v>105</v>
       </c>
       <c r="T98" s="6">
-        <v>0</v>
-      </c>
-      <c r="U98" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U98" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7480,9 +7514,11 @@
       <c r="B99" s="8">
         <v>46125.599162743056</v>
       </c>
-      <c r="C99" s="9"/>
+      <c r="C99" s="8">
+        <v>46196.76818966435</v>
+      </c>
       <c r="D99" s="8">
-        <v>46195.50752082176</v>
+        <v>46196.7681912963</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>200</v>
@@ -7533,9 +7569,11 @@
       <c r="B100" s="5">
         <v>46125.599302511575</v>
       </c>
-      <c r="C100" s="6"/>
+      <c r="C100" s="5">
+        <v>46196.76820421296</v>
+      </c>
       <c r="D100" s="5">
-        <v>46195.507520127314</v>
+        <v>46196.76820597222</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>200</v>
@@ -7586,9 +7624,11 @@
       <c r="B101" s="8">
         <v>46125.59934644676</v>
       </c>
-      <c r="C101" s="9"/>
+      <c r="C101" s="8">
+        <v>46196.768375949076</v>
+      </c>
       <c r="D101" s="8">
-        <v>46195.507522314816</v>
+        <v>46196.76837958333</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>200</v>
@@ -7639,9 +7679,11 @@
       <c r="B102" s="5">
         <v>46125.59938857639</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46196.76837696759</v>
+      </c>
       <c r="D102" s="5">
-        <v>46195.50752153935</v>
+        <v>46196.76838008102</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>200</v>
@@ -7692,9 +7734,11 @@
       <c r="B103" s="8">
         <v>46125.59943094908</v>
       </c>
-      <c r="C103" s="9"/>
+      <c r="C103" s="8">
+        <v>46196.76837790509</v>
+      </c>
       <c r="D103" s="8">
-        <v>46195.50752328704</v>
+        <v>46196.768380520836</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>200</v>
@@ -7745,9 +7789,11 @@
       <c r="B104" s="5">
         <v>46122.551650995374</v>
       </c>
-      <c r="C104" s="6"/>
+      <c r="C104" s="5">
+        <v>46196.76854788195</v>
+      </c>
       <c r="D104" s="5">
-        <v>46125.65705875</v>
+        <v>46196.76856074074</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>302</v>
@@ -7795,10 +7841,10 @@
         <v>105</v>
       </c>
       <c r="T104" s="6">
-        <v>0</v>
-      </c>
-      <c r="U104" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U104" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7808,9 +7854,11 @@
       <c r="B105" s="8">
         <v>46125.59953013889</v>
       </c>
-      <c r="C105" s="9"/>
+      <c r="C105" s="8">
+        <v>46196.76852783565</v>
+      </c>
       <c r="D105" s="8">
-        <v>46195.56328270833</v>
+        <v>46196.768531724534</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>200</v>
@@ -7861,9 +7909,11 @@
       <c r="B106" s="5">
         <v>46125.59961423611</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="5">
+        <v>46196.76846329861</v>
+      </c>
       <c r="D106" s="5">
-        <v>46195.56328116899</v>
+        <v>46196.76846496528</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>200</v>
@@ -7914,9 +7964,11 @@
       <c r="B107" s="8">
         <v>46125.599654317135</v>
       </c>
-      <c r="C107" s="9"/>
+      <c r="C107" s="8">
+        <v>46196.768528796296</v>
+      </c>
       <c r="D107" s="8">
-        <v>46195.56328055555</v>
+        <v>46196.76853203704</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>200</v>
@@ -7967,9 +8019,11 @@
       <c r="B108" s="5">
         <v>46125.59957065972</v>
       </c>
-      <c r="C108" s="6"/>
+      <c r="C108" s="5">
+        <v>46196.768529548615</v>
+      </c>
       <c r="D108" s="5">
-        <v>46195.56328217592</v>
+        <v>46196.76853233796</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>200</v>
@@ -8020,9 +8074,11 @@
       <c r="B109" s="8">
         <v>46125.59969711806</v>
       </c>
-      <c r="C109" s="9"/>
+      <c r="C109" s="8">
+        <v>46196.7685304051</v>
+      </c>
       <c r="D109" s="8">
-        <v>46195.563281724535</v>
+        <v>46196.76853265046</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>200</v>
@@ -8073,9 +8129,11 @@
       <c r="B110" s="5">
         <v>46122.55163725694</v>
       </c>
-      <c r="C110" s="6"/>
+      <c r="C110" s="5">
+        <v>46196.76866755787</v>
+      </c>
       <c r="D110" s="5">
-        <v>46125.65706174768</v>
+        <v>46196.76867908565</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>310</v>
@@ -8123,10 +8181,10 @@
         <v>105</v>
       </c>
       <c r="T110" s="6">
-        <v>0</v>
-      </c>
-      <c r="U110" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U110" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -8136,9 +8194,11 @@
       <c r="B111" s="8">
         <v>46125.59780210648</v>
       </c>
-      <c r="C111" s="9"/>
+      <c r="C111" s="8">
+        <v>46196.76864902778</v>
+      </c>
       <c r="D111" s="8">
-        <v>46195.50753145834</v>
+        <v>46196.76865387731</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>200</v>
@@ -8189,9 +8249,11 @@
       <c r="B112" s="5">
         <v>46125.597836932866</v>
       </c>
-      <c r="C112" s="6"/>
+      <c r="C112" s="5">
+        <v>46196.76865</v>
+      </c>
       <c r="D112" s="5">
-        <v>46195.50752924768</v>
+        <v>46196.76865427083</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>200</v>
@@ -8242,9 +8304,11 @@
       <c r="B113" s="8">
         <v>46125.5979208912</v>
       </c>
-      <c r="C113" s="9"/>
+      <c r="C113" s="8">
+        <v>46196.76865077546</v>
+      </c>
       <c r="D113" s="8">
-        <v>46195.507530347226</v>
+        <v>46196.76865460648</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>200</v>
@@ -8295,9 +8359,11 @@
       <c r="B114" s="5">
         <v>46125.59788087963</v>
       </c>
-      <c r="C114" s="6"/>
+      <c r="C114" s="5">
+        <v>46196.768651527775</v>
+      </c>
       <c r="D114" s="5">
-        <v>46195.507528125</v>
+        <v>46196.768654942134</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>200</v>
@@ -8348,9 +8414,11 @@
       <c r="B115" s="8">
         <v>46125.597965023146</v>
       </c>
-      <c r="C115" s="9"/>
+      <c r="C115" s="8">
+        <v>46196.768652314815</v>
+      </c>
       <c r="D115" s="8">
-        <v>46195.507526608795</v>
+        <v>46196.768655312495</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>200</v>
@@ -8401,9 +8469,11 @@
       <c r="B116" s="5">
         <v>46122.55172043982</v>
       </c>
-      <c r="C116" s="6"/>
+      <c r="C116" s="5">
+        <v>46196.76877224537</v>
+      </c>
       <c r="D116" s="5">
-        <v>46125.658894120366</v>
+        <v>46196.768798784724</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>319</v>
@@ -8451,10 +8521,10 @@
         <v>105</v>
       </c>
       <c r="T116" s="6">
-        <v>0</v>
-      </c>
-      <c r="U116" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U116" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -8464,9 +8534,11 @@
       <c r="B117" s="8">
         <v>46125.60038253472</v>
       </c>
-      <c r="C117" s="9"/>
+      <c r="C117" s="8">
+        <v>46196.76875258102</v>
+      </c>
       <c r="D117" s="8">
-        <v>46125.658321932875</v>
+        <v>46196.768757337966</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>200</v>
@@ -8515,9 +8587,11 @@
       <c r="B118" s="5">
         <v>46125.60043012731</v>
       </c>
-      <c r="C118" s="6"/>
+      <c r="C118" s="5">
+        <v>46196.7687534838</v>
+      </c>
       <c r="D118" s="5">
-        <v>46125.658344236115</v>
+        <v>46196.76875768519</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>200</v>
@@ -8566,9 +8640,11 @@
       <c r="B119" s="8">
         <v>46125.60047290509</v>
       </c>
-      <c r="C119" s="9"/>
+      <c r="C119" s="8">
+        <v>46196.768754178236</v>
+      </c>
       <c r="D119" s="8">
-        <v>46125.65837160879</v>
+        <v>46196.76875800926</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>200</v>
@@ -8617,9 +8693,11 @@
       <c r="B120" s="5">
         <v>46125.600514074074</v>
       </c>
-      <c r="C120" s="6"/>
+      <c r="C120" s="5">
+        <v>46196.768754930556</v>
+      </c>
       <c r="D120" s="5">
-        <v>46125.6583996875</v>
+        <v>46196.76875832176</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>200</v>
@@ -8668,9 +8746,11 @@
       <c r="B121" s="8">
         <v>46125.60055859954</v>
       </c>
-      <c r="C121" s="9"/>
+      <c r="C121" s="8">
+        <v>46196.7687558912</v>
+      </c>
       <c r="D121" s="8">
-        <v>46125.65844143518</v>
+        <v>46196.76875862268</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>200</v>
@@ -8719,9 +8799,11 @@
       <c r="B122" s="5">
         <v>46122.55172986111</v>
       </c>
-      <c r="C122" s="6"/>
+      <c r="C122" s="5">
+        <v>46196.76917457176</v>
+      </c>
       <c r="D122" s="5">
-        <v>46125.66066717592</v>
+        <v>46196.76918584491</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>327</v>
@@ -8769,10 +8851,10 @@
         <v>105</v>
       </c>
       <c r="T122" s="6">
-        <v>0</v>
-      </c>
-      <c r="U122" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U122" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
@@ -8782,9 +8864,11 @@
       <c r="B123" s="8">
         <v>46125.60064416667</v>
       </c>
-      <c r="C123" s="9"/>
+      <c r="C123" s="8">
+        <v>46196.76915099537</v>
+      </c>
       <c r="D123" s="8">
-        <v>46125.66201921296</v>
+        <v>46196.76915743056</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>200</v>
@@ -8833,9 +8917,11 @@
       <c r="B124" s="5">
         <v>46125.60068740741</v>
       </c>
-      <c r="C124" s="6"/>
+      <c r="C124" s="5">
+        <v>46196.76915237268</v>
+      </c>
       <c r="D124" s="5">
-        <v>46125.66205158565</v>
+        <v>46196.76915791667</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>200</v>
@@ -8884,9 +8970,11 @@
       <c r="B125" s="8">
         <v>46125.60073844907</v>
       </c>
-      <c r="C125" s="9"/>
+      <c r="C125" s="8">
+        <v>46196.76915341435</v>
+      </c>
       <c r="D125" s="8">
-        <v>46125.66207341435</v>
+        <v>46196.76915841435</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>200</v>
@@ -8935,9 +9023,11 @@
       <c r="B126" s="5">
         <v>46125.60077622686</v>
       </c>
-      <c r="C126" s="6"/>
+      <c r="C126" s="5">
+        <v>46196.76915438657</v>
+      </c>
       <c r="D126" s="5">
-        <v>46125.66209603009</v>
+        <v>46196.769158842595</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>200</v>
@@ -8986,9 +9076,11 @@
       <c r="B127" s="8">
         <v>46125.600829143514</v>
       </c>
-      <c r="C127" s="9"/>
+      <c r="C127" s="8">
+        <v>46196.769155358794</v>
+      </c>
       <c r="D127" s="8">
-        <v>46125.66214039351</v>
+        <v>46196.76915931713</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>200</v>
@@ -9041,7 +9133,7 @@
         <v>46195.56317517361</v>
       </c>
       <c r="D128" s="5">
-        <v>46195.56318964121</v>
+        <v>46196.76960409722</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>336</v>
@@ -9079,8 +9171,8 @@
       <c r="T128" s="6">
         <v>1</v>
       </c>
-      <c r="U128" s="11" t="s">
-        <v>33</v>
+      <c r="U128" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
@@ -9090,9 +9182,11 @@
       <c r="B129" s="8">
         <v>46122.5517390625</v>
       </c>
-      <c r="C129" s="9"/>
+      <c r="C129" s="8">
+        <v>46196.76936652778</v>
+      </c>
       <c r="D129" s="8">
-        <v>46189.53573824074</v>
+        <v>46196.76939736111</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>339</v>
@@ -9140,10 +9234,10 @@
         <v>105</v>
       </c>
       <c r="T129" s="9">
-        <v>0</v>
-      </c>
-      <c r="U129" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U129" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -9153,9 +9247,11 @@
       <c r="B130" s="5">
         <v>46125.60093731481</v>
       </c>
-      <c r="C130" s="6"/>
+      <c r="C130" s="5">
+        <v>46196.76934515046</v>
+      </c>
       <c r="D130" s="5">
-        <v>46125.664177071754</v>
+        <v>46196.769350682865</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>200</v>
@@ -9204,9 +9300,11 @@
       <c r="B131" s="8">
         <v>46125.601380821754</v>
       </c>
-      <c r="C131" s="9"/>
+      <c r="C131" s="8">
+        <v>46196.769346307876</v>
+      </c>
       <c r="D131" s="8">
-        <v>46125.66419668982</v>
+        <v>46196.769351145835</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>200</v>
@@ -9255,9 +9353,11 @@
       <c r="B132" s="5">
         <v>46125.60142481481</v>
       </c>
-      <c r="C132" s="6"/>
+      <c r="C132" s="5">
+        <v>46196.7693472338</v>
+      </c>
       <c r="D132" s="5">
-        <v>46125.66421920139</v>
+        <v>46196.76935155093</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>200</v>
@@ -9306,9 +9406,11 @@
       <c r="B133" s="8">
         <v>46125.60146085648</v>
       </c>
-      <c r="C133" s="9"/>
+      <c r="C133" s="8">
+        <v>46196.769348125</v>
+      </c>
       <c r="D133" s="8">
-        <v>46125.66424142361</v>
+        <v>46196.76935192129</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>200</v>
@@ -9357,9 +9459,11 @@
       <c r="B134" s="5">
         <v>46125.60150208333</v>
       </c>
-      <c r="C134" s="6"/>
+      <c r="C134" s="5">
+        <v>46196.769348981485</v>
+      </c>
       <c r="D134" s="5">
-        <v>46125.664280972225</v>
+        <v>46196.76935229167</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>200</v>
@@ -9408,9 +9512,11 @@
       <c r="B135" s="8">
         <v>46122.55174383102</v>
       </c>
-      <c r="C135" s="9"/>
+      <c r="C135" s="8">
+        <v>46196.769596921295</v>
+      </c>
       <c r="D135" s="8">
-        <v>46185.646541435184</v>
+        <v>46196.76961396991</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>350</v>
@@ -9456,10 +9562,10 @@
         <v>105</v>
       </c>
       <c r="T135" s="9">
-        <v>0</v>
-      </c>
-      <c r="U135" s="10" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="U135" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -9469,9 +9575,11 @@
       <c r="B136" s="5">
         <v>46125.601086979164</v>
       </c>
-      <c r="C136" s="6"/>
+      <c r="C136" s="5">
+        <v>46196.76947155093</v>
+      </c>
       <c r="D136" s="5">
-        <v>46125.66761228009</v>
+        <v>46196.76947347222</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>200</v>
@@ -9520,9 +9628,11 @@
       <c r="B137" s="8">
         <v>46125.60115318287</v>
       </c>
-      <c r="C137" s="9"/>
+      <c r="C137" s="8">
+        <v>46196.7695043287</v>
+      </c>
       <c r="D137" s="8">
-        <v>46125.66765621528</v>
+        <v>46196.76950902778</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>200</v>
@@ -9571,9 +9681,11 @@
       <c r="B138" s="5">
         <v>46125.60120391204</v>
       </c>
-      <c r="C138" s="6"/>
+      <c r="C138" s="5">
+        <v>46196.76950549769</v>
+      </c>
       <c r="D138" s="5">
-        <v>46125.66769103009</v>
+        <v>46196.76950944445</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>200</v>
@@ -9622,9 +9734,11 @@
       <c r="B139" s="8">
         <v>46125.60125796296</v>
       </c>
-      <c r="C139" s="9"/>
+      <c r="C139" s="8">
+        <v>46196.76950637731</v>
+      </c>
       <c r="D139" s="8">
-        <v>46125.667712152775</v>
+        <v>46196.76950987268</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>200</v>
@@ -9673,9 +9787,11 @@
       <c r="B140" s="5">
         <v>46125.601304282405</v>
       </c>
-      <c r="C140" s="6"/>
+      <c r="C140" s="5">
+        <v>46196.76950730324</v>
+      </c>
       <c r="D140" s="5">
-        <v>46125.6677272338</v>
+        <v>46196.769510266204</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>200</v>
@@ -9728,7 +9844,7 @@
         <v>46191.70598530093</v>
       </c>
       <c r="D141" s="8">
-        <v>46191.706001886574</v>
+        <v>46196.769715787035</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>358</v>
@@ -9776,8 +9892,8 @@
       <c r="T141" s="9">
         <v>1</v>
       </c>
-      <c r="U141" s="11" t="s">
-        <v>33</v>
+      <c r="U141" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
@@ -9787,9 +9903,11 @@
       <c r="B142" s="5">
         <v>46125.60158650463</v>
       </c>
-      <c r="C142" s="6"/>
+      <c r="C142" s="5">
+        <v>46196.76968462963</v>
+      </c>
       <c r="D142" s="5">
-        <v>46125.76574587963</v>
+        <v>46196.76968989584</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>200</v>
@@ -9838,9 +9956,11 @@
       <c r="B143" s="8">
         <v>46125.60163133102</v>
       </c>
-      <c r="C143" s="9"/>
+      <c r="C143" s="8">
+        <v>46196.76968585648</v>
+      </c>
       <c r="D143" s="8">
-        <v>46125.7630881713</v>
+        <v>46196.7696903125</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>200</v>
@@ -9889,9 +10009,11 @@
       <c r="B144" s="5">
         <v>46125.60167016204</v>
       </c>
-      <c r="C144" s="6"/>
+      <c r="C144" s="5">
+        <v>46196.7696866551</v>
+      </c>
       <c r="D144" s="5">
-        <v>46125.76385471065</v>
+        <v>46196.769690706016</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>200</v>
@@ -9940,9 +10062,11 @@
       <c r="B145" s="8">
         <v>46125.60170435185</v>
       </c>
-      <c r="C145" s="9"/>
+      <c r="C145" s="8">
+        <v>46196.769687395834</v>
+      </c>
       <c r="D145" s="8">
-        <v>46125.76313709491</v>
+        <v>46196.76969114583</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>200</v>
@@ -9991,9 +10115,11 @@
       <c r="B146" s="5">
         <v>46125.60173947917</v>
       </c>
-      <c r="C146" s="6"/>
+      <c r="C146" s="5">
+        <v>46196.769688113425</v>
+      </c>
       <c r="D146" s="5">
-        <v>46125.763172210645</v>
+        <v>46196.76969164352</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>200</v>
@@ -10046,7 +10172,7 @@
         <v>46191.70604009259</v>
       </c>
       <c r="D147" s="8">
-        <v>46191.706057812495</v>
+        <v>46196.76981105324</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>367</v>
@@ -10094,8 +10220,8 @@
       <c r="T147" s="9">
         <v>1</v>
       </c>
-      <c r="U147" s="11" t="s">
-        <v>33</v>
+      <c r="U147" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
@@ -10105,9 +10231,11 @@
       <c r="B148" s="5">
         <v>46125.60181555555</v>
       </c>
-      <c r="C148" s="6"/>
+      <c r="C148" s="5">
+        <v>46196.76979265046</v>
+      </c>
       <c r="D148" s="5">
-        <v>46125.76413488426</v>
+        <v>46196.76979569445</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>200</v>
@@ -10156,9 +10284,11 @@
       <c r="B149" s="8">
         <v>46125.60185690972</v>
       </c>
-      <c r="C149" s="9"/>
+      <c r="C149" s="8">
+        <v>46196.76979356482</v>
+      </c>
       <c r="D149" s="8">
-        <v>46125.764156805555</v>
+        <v>46196.76979614583</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>200</v>
@@ -10207,9 +10337,11 @@
       <c r="B150" s="5">
         <v>46125.601899490735</v>
       </c>
-      <c r="C150" s="6"/>
+      <c r="C150" s="5">
+        <v>46196.769794224536</v>
+      </c>
       <c r="D150" s="5">
-        <v>46125.76418171296</v>
+        <v>46196.76979648148</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>200</v>
@@ -10258,9 +10390,11 @@
       <c r="B151" s="8">
         <v>46125.60193935185</v>
       </c>
-      <c r="C151" s="9"/>
+      <c r="C151" s="8">
+        <v>46196.76976476852</v>
+      </c>
       <c r="D151" s="8">
-        <v>46125.764207615735</v>
+        <v>46196.769766875004</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>200</v>
@@ -10309,9 +10443,11 @@
       <c r="B152" s="5">
         <v>46125.60197710648</v>
       </c>
-      <c r="C152" s="6"/>
+      <c r="C152" s="5">
+        <v>46196.76977206019</v>
+      </c>
       <c r="D152" s="5">
-        <v>46125.764245451384</v>
+        <v>46196.76977370371</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>200</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -1847,13 +1847,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46122.55118912037</v>
+        <v>46122.38452245371</v>
       </c>
       <c r="C4" s="5">
-        <v>46128.59300771991</v>
+        <v>46128.426341053244</v>
       </c>
       <c r="D4" s="5">
-        <v>46158.10300121528</v>
+        <v>46157.93633454861</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1896,13 +1896,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46122.55134571759</v>
+        <v>46122.38467905093</v>
       </c>
       <c r="C5" s="8">
-        <v>46128.59299462963</v>
+        <v>46128.42632796297</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.876021724536</v>
+        <v>46133.70935505787</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1959,13 +1959,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46122.55134947917</v>
+        <v>46122.384682812495</v>
       </c>
       <c r="C6" s="5">
-        <v>46128.59267868055</v>
+        <v>46128.42601201389</v>
       </c>
       <c r="D6" s="5">
-        <v>46128.60382631945</v>
+        <v>46128.43715965278</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2022,13 +2022,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46122.551352546296</v>
+        <v>46122.38468587963</v>
       </c>
       <c r="C7" s="8">
-        <v>46128.59269866898</v>
+        <v>46128.42603200232</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.62726047453</v>
+        <v>46161.460593807875</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2085,13 +2085,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46122.551355567135</v>
+        <v>46122.38468890046</v>
       </c>
       <c r="C8" s="5">
-        <v>46128.59271722222</v>
+        <v>46128.42605055556</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.60400607639</v>
+        <v>46128.43733940972</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2148,13 +2148,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46122.551359386576</v>
+        <v>46122.384692719905</v>
       </c>
       <c r="C9" s="8">
-        <v>46128.592850057874</v>
+        <v>46128.4261833912</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.83577310185</v>
+        <v>46156.66910643518</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2211,13 +2211,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46122.55119412037</v>
+        <v>46122.3845274537</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.93280347223</v>
+        <v>46193.766136805556</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.9328209838</v>
+        <v>46193.76615431713</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2264,13 +2264,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46122.5513631713</v>
+        <v>46122.384696504625</v>
       </c>
       <c r="C11" s="8">
-        <v>46128.60435520833</v>
+        <v>46128.43768854167</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.97382803241</v>
+        <v>46192.80716136574</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2329,13 +2329,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46122.551369050925</v>
+        <v>46122.38470238426</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.60643114583</v>
+        <v>46128.43976447917</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.97382813657</v>
+        <v>46192.80716146991</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2394,13 +2394,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46122.5513746875</v>
+        <v>46122.384708020836</v>
       </c>
       <c r="C13" s="8">
-        <v>46132.57072561343</v>
+        <v>46132.40405894676</v>
       </c>
       <c r="D13" s="8">
-        <v>46192.97382800926</v>
+        <v>46192.80716134259</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2459,13 +2459,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46122.553594178244</v>
+        <v>46122.38692751157</v>
       </c>
       <c r="C14" s="5">
-        <v>46128.60941575232</v>
+        <v>46128.44274908565</v>
       </c>
       <c r="D14" s="5">
-        <v>46136.20601917824</v>
+        <v>46136.03935251157</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2524,13 +2524,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46122.55119946759</v>
+        <v>46122.38453280093</v>
       </c>
       <c r="C15" s="8">
-        <v>46195.50723163194</v>
+        <v>46195.34056496528</v>
       </c>
       <c r="D15" s="8">
-        <v>46195.50724608796</v>
+        <v>46195.340579421296</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2577,13 +2577,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46122.55138855324</v>
+        <v>46122.38472188657</v>
       </c>
       <c r="C16" s="5">
-        <v>46128.60700391204</v>
+        <v>46128.44033724537</v>
       </c>
       <c r="D16" s="5">
-        <v>46133.17999505787</v>
+        <v>46133.0133283912</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2642,13 +2642,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46122.55139482639</v>
+        <v>46122.38472815973</v>
       </c>
       <c r="C17" s="8">
-        <v>46128.60701157407</v>
+        <v>46128.44034490741</v>
       </c>
       <c r="D17" s="8">
-        <v>46132.182206921294</v>
+        <v>46132.01554025463</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2707,13 +2707,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46122.55140040509</v>
+        <v>46122.38473373842</v>
       </c>
       <c r="C18" s="5">
-        <v>46195.50721171296</v>
+        <v>46195.340545046296</v>
       </c>
       <c r="D18" s="5">
-        <v>46195.50723229167</v>
+        <v>46195.340565624996</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2772,13 +2772,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46122.55140604167</v>
+        <v>46122.384739375004</v>
       </c>
       <c r="C19" s="8">
-        <v>46181.666399050926</v>
+        <v>46181.499732384254</v>
       </c>
       <c r="D19" s="8">
-        <v>46195.20558476852</v>
+        <v>46195.038918101855</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2837,13 +2837,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46122.55141162037</v>
+        <v>46122.3847449537</v>
       </c>
       <c r="C20" s="5">
-        <v>46128.609497881946</v>
+        <v>46128.442831215274</v>
       </c>
       <c r="D20" s="5">
-        <v>46132.1822065625</v>
+        <v>46132.01553989583</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>64</v>
@@ -2902,13 +2902,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46122.566545787035</v>
+        <v>46122.39987912037</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.66636053241</v>
+        <v>46181.49969386574</v>
       </c>
       <c r="D21" s="8">
-        <v>46195.20558446759</v>
+        <v>46195.03891780092</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2967,13 +2967,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46122.56661521991</v>
+        <v>46122.39994855324</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.66637630787</v>
+        <v>46181.499709641204</v>
       </c>
       <c r="D22" s="5">
-        <v>46195.20558434028</v>
+        <v>46195.038917673606</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3032,13 +3032,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="8">
-        <v>46122.57286273148</v>
+        <v>46122.40619606481</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.66643224537</v>
+        <v>46181.4997655787</v>
       </c>
       <c r="D23" s="8">
-        <v>46195.205584386575</v>
+        <v>46195.03891771991</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -3097,13 +3097,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46122.55120394676</v>
+        <v>46122.38453728009</v>
       </c>
       <c r="C24" s="5">
-        <v>46195.50733982639</v>
+        <v>46195.34067315972</v>
       </c>
       <c r="D24" s="5">
-        <v>46195.50735353009</v>
+        <v>46195.34068686343</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -3150,13 +3150,13 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46122.55141694444</v>
+        <v>46122.38475027778</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.626168703704</v>
+        <v>46174.45950203703</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.626181134256</v>
+        <v>46174.45951446759</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -3215,13 +3215,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46122.55142208333</v>
+        <v>46122.38475541667</v>
       </c>
       <c r="C26" s="5">
-        <v>46174.62325291667</v>
+        <v>46174.45658625</v>
       </c>
       <c r="D26" s="5">
-        <v>46174.62325449074</v>
+        <v>46174.456587824076</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3276,13 +3276,13 @@
         <v>110</v>
       </c>
       <c r="B27" s="8">
-        <v>46122.55142699074</v>
+        <v>46122.38476032407</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.626152893514</v>
+        <v>46174.45948622686</v>
       </c>
       <c r="D27" s="8">
-        <v>46174.62615429398</v>
+        <v>46174.45948762732</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>111</v>
@@ -3337,13 +3337,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46122.5514322338</v>
+        <v>46122.38476556713</v>
       </c>
       <c r="C28" s="5">
-        <v>46195.50732521991</v>
+        <v>46195.340658553236</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.71184679398</v>
+        <v>46195.545180127316</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3402,13 +3402,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="8">
-        <v>46122.551437546295</v>
+        <v>46122.38477087963</v>
       </c>
       <c r="C29" s="8">
-        <v>46195.71138274306</v>
+        <v>46195.54471607639</v>
       </c>
       <c r="D29" s="8">
-        <v>46195.71138517361</v>
+        <v>46195.54471850695</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>118</v>
@@ -3463,13 +3463,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46122.55144255787</v>
+        <v>46122.3847758912</v>
       </c>
       <c r="C30" s="5">
-        <v>46195.711830960645</v>
+        <v>46195.54516429398</v>
       </c>
       <c r="D30" s="5">
-        <v>46195.711832500005</v>
+        <v>46195.54516583333</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3524,13 +3524,13 @@
         <v>123</v>
       </c>
       <c r="B31" s="8">
-        <v>46122.551447708334</v>
+        <v>46122.38478104166</v>
       </c>
       <c r="C31" s="8">
-        <v>46133.82779993056</v>
+        <v>46133.661133263886</v>
       </c>
       <c r="D31" s="8">
-        <v>46133.82781321759</v>
+        <v>46133.66114655093</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>124</v>
@@ -3589,13 +3589,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46122.5514527662</v>
+        <v>46122.38478609954</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.827731122685</v>
+        <v>46133.66106445601</v>
       </c>
       <c r="D32" s="5">
-        <v>46133.82773260417</v>
+        <v>46133.6610659375</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3650,13 +3650,13 @@
         <v>129</v>
       </c>
       <c r="B33" s="8">
-        <v>46122.55145796297</v>
+        <v>46122.384791296296</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.827786875</v>
+        <v>46133.66112020833</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.82778807871</v>
+        <v>46133.661121412035</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>130</v>
@@ -3711,13 +3711,13 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46122.55146299768</v>
+        <v>46122.38479633102</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.82776796297</v>
+        <v>46133.6611012963</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.827769131945</v>
+        <v>46133.66110246528</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3772,13 +3772,13 @@
         <v>135</v>
       </c>
       <c r="B35" s="8">
-        <v>46122.55146795139</v>
+        <v>46122.38480128472</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.66687207176</v>
+        <v>46181.50020540509</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.66688577546</v>
+        <v>46181.5002191088</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3837,13 +3837,13 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46122.551472974534</v>
+        <v>46122.38480630787</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.66681767361</v>
+        <v>46181.50015100694</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.66681946759</v>
+        <v>46181.50015280093</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3898,13 +3898,13 @@
         <v>143</v>
       </c>
       <c r="B37" s="8">
-        <v>46122.55152253472</v>
+        <v>46122.384855868055</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.66685679398</v>
+        <v>46181.50019012731</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.66685818287</v>
+        <v>46181.5001915162</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>144</v>
@@ -3959,13 +3959,13 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46122.55152891204</v>
+        <v>46122.384862245366</v>
       </c>
       <c r="C38" s="5">
-        <v>46154.867667812505</v>
+        <v>46154.70100114583</v>
       </c>
       <c r="D38" s="5">
-        <v>46189.172213136575</v>
+        <v>46189.00554646991</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -4024,13 +4024,13 @@
         <v>149</v>
       </c>
       <c r="B39" s="8">
-        <v>46122.5515340625</v>
+        <v>46122.384867395835</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.86751693287</v>
+        <v>46154.70085026621</v>
       </c>
       <c r="D39" s="8">
-        <v>46154.86751927083</v>
+        <v>46154.70085260417</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>87</v>
@@ -4079,13 +4079,13 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46122.55153844907</v>
+        <v>46122.38487178241</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.867576273144</v>
+        <v>46154.70090960649</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.867577453704</v>
+        <v>46154.70091078704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4134,13 +4134,13 @@
         <v>154</v>
       </c>
       <c r="B41" s="8">
-        <v>46122.574933449076</v>
+        <v>46122.40826678241</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.666767002316</v>
+        <v>46181.500100335645</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.666783252316</v>
+        <v>46181.50011658565</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>155</v>
@@ -4199,13 +4199,13 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46122.575920972224</v>
+        <v>46122.40925430556</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.66670739584</v>
+        <v>46181.500040729166</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.66670855324</v>
+        <v>46181.500041886575</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>90</v>
@@ -4254,13 +4254,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46122.57608475695</v>
+        <v>46122.409418090276</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.666752812496</v>
+        <v>46181.50008614583</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.666754351856</v>
+        <v>46181.500087685185</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4309,13 +4309,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46122.57501438657</v>
+        <v>46122.40834771991</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.666958472226</v>
+        <v>46181.500291805554</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.66706865741</v>
+        <v>46181.500401990736</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4374,13 +4374,13 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46122.57922111111</v>
+        <v>46122.41255444444</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.666901516204</v>
+        <v>46181.50023484953</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.66690306713</v>
+        <v>46181.50023640046</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>96</v>
@@ -4429,13 +4429,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46122.57949202546</v>
+        <v>46122.4128253588</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.66694322917</v>
+        <v>46181.500276562496</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.66694460648</v>
+        <v>46181.50027793982</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4484,13 +4484,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46125.529618217595</v>
+        <v>46125.362951550924</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.66722120371</v>
+        <v>46181.50055453704</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.66723511574</v>
+        <v>46181.500568449075</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4549,13 +4549,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46125.52977997685</v>
+        <v>46125.36311331019</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.66715732639</v>
+        <v>46181.50049065972</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.66715912037</v>
+        <v>46181.500492453706</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>93</v>
@@ -4604,13 +4604,13 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46125.52991815972</v>
+        <v>46125.36325149305</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.66720412037</v>
+        <v>46181.5005374537</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.66720563658</v>
+        <v>46181.50053896991</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4659,13 +4659,13 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46122.55120855324</v>
+        <v>46122.384541886575</v>
       </c>
       <c r="C50" s="5">
-        <v>46195.5074512963</v>
+        <v>46195.34078462963</v>
       </c>
       <c r="D50" s="5">
-        <v>46195.50756488426</v>
+        <v>46195.34089821759</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4712,13 +4712,13 @@
         <v>183</v>
       </c>
       <c r="B51" s="8">
-        <v>46122.55154344907</v>
+        <v>46122.38487678241</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.79584481481</v>
+        <v>46133.62917814815</v>
       </c>
       <c r="D51" s="8">
-        <v>46143.171145879634</v>
+        <v>46143.00447921296</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>184</v>
@@ -4777,13 +4777,13 @@
         <v>188</v>
       </c>
       <c r="B52" s="5">
-        <v>46122.551548993055</v>
+        <v>46122.38488232639</v>
       </c>
       <c r="C52" s="5">
-        <v>46134.79240423611</v>
+        <v>46134.62573756944</v>
       </c>
       <c r="D52" s="5">
-        <v>46190.18859494213</v>
+        <v>46190.02192827546</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4842,13 +4842,13 @@
         <v>192</v>
       </c>
       <c r="B53" s="8">
-        <v>46122.55155721065</v>
+        <v>46122.38489054398</v>
       </c>
       <c r="C53" s="8">
-        <v>46134.79245146991</v>
+        <v>46134.62578480324</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.18981792824</v>
+        <v>46191.02315126157</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>83</v>
@@ -4905,13 +4905,13 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46122.55156568287</v>
+        <v>46122.38489901621</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.50761325231</v>
+        <v>46195.34094658565</v>
       </c>
       <c r="D54" s="5">
-        <v>46196.76907818287</v>
+        <v>46196.6024115162</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -4968,13 +4968,13 @@
         <v>199</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.603622118055</v>
+        <v>46125.43695545139</v>
       </c>
       <c r="C55" s="8">
-        <v>46196.76904752315</v>
+        <v>46196.60238085648</v>
       </c>
       <c r="D55" s="8">
-        <v>46196.7690521412</v>
+        <v>46196.602385474536</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>200</v>
@@ -5021,13 +5021,13 @@
         <v>202</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.60367094907</v>
+        <v>46125.43700428241</v>
       </c>
       <c r="C56" s="5">
-        <v>46196.769048449074</v>
+        <v>46196.6023817824</v>
       </c>
       <c r="D56" s="5">
-        <v>46196.769052523145</v>
+        <v>46196.60238585648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -5074,13 +5074,13 @@
         <v>203</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.60371951389</v>
+        <v>46125.43705284722</v>
       </c>
       <c r="C57" s="8">
-        <v>46196.76904929398</v>
+        <v>46196.602382627316</v>
       </c>
       <c r="D57" s="8">
-        <v>46196.76905283565</v>
+        <v>46196.60238616898</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5127,13 +5127,13 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.60376462963</v>
+        <v>46125.43709796296</v>
       </c>
       <c r="C58" s="5">
-        <v>46196.769050069444</v>
+        <v>46196.60238340277</v>
       </c>
       <c r="D58" s="5">
-        <v>46196.76905314815</v>
+        <v>46196.60238648148</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>200</v>
@@ -5180,13 +5180,13 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.60381739584</v>
+        <v>46125.437150729165</v>
       </c>
       <c r="C59" s="8">
-        <v>46196.76905077546</v>
+        <v>46196.602384108795</v>
       </c>
       <c r="D59" s="8">
-        <v>46196.76905349537</v>
+        <v>46196.6023868287</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>200</v>
@@ -5233,13 +5233,13 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46122.551569710646</v>
+        <v>46122.38490304398</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.6677724537</v>
+        <v>46181.501105787036</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.66785324074</v>
+        <v>46181.501186574074</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5282,13 +5282,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46122.55157321759</v>
+        <v>46122.38490655093</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.667378032405</v>
+        <v>46181.50071136574</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.66739524306</v>
+        <v>46181.500728576386</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5347,13 +5347,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46122.58491638889</v>
+        <v>46122.41824972222</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.667413206014</v>
+        <v>46181.50074653935</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.667429016205</v>
+        <v>46181.50076234953</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5412,13 +5412,13 @@
         <v>217</v>
       </c>
       <c r="B63" s="8">
-        <v>46125.53102658565</v>
+        <v>46125.36435991898</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.667430127316</v>
+        <v>46181.500763460645</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.66744925926</v>
+        <v>46181.50078259259</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -5477,13 +5477,13 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46122.55157846065</v>
+        <v>46122.38491179398</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.66775587963</v>
+        <v>46181.501089212965</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.66777241898</v>
+        <v>46181.501105752315</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5542,13 +5542,13 @@
         <v>225</v>
       </c>
       <c r="B65" s="8">
-        <v>46122.551583831024</v>
+        <v>46122.38491716435</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.6687946875</v>
+        <v>46181.50212802083</v>
       </c>
       <c r="D65" s="8">
-        <v>46181.66890770833</v>
+        <v>46181.50224104167</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>226</v>
@@ -5591,13 +5591,13 @@
         <v>228</v>
       </c>
       <c r="B66" s="5">
-        <v>46122.55158688658</v>
+        <v>46122.384920219905</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.666093576394</v>
+        <v>46181.49942690972</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.66880932871</v>
+        <v>46181.50214266204</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>229</v>
@@ -5656,13 +5656,13 @@
         <v>233</v>
       </c>
       <c r="B67" s="8">
-        <v>46122.55159185185</v>
+        <v>46122.384925185186</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.6661986574</v>
+        <v>46181.49953199074</v>
       </c>
       <c r="D67" s="8">
-        <v>46181.668846064815</v>
+        <v>46181.50217939814</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>234</v>
@@ -5721,13 +5721,13 @@
         <v>236</v>
       </c>
       <c r="B68" s="5">
-        <v>46125.595811921296</v>
+        <v>46125.42914525463</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.66807699074</v>
+        <v>46181.501410324076</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.66807884259</v>
+        <v>46181.50141217593</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>237</v>
@@ -5776,13 +5776,13 @@
         <v>240</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.59610047453</v>
+        <v>46125.42943380787</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.66808581019</v>
+        <v>46181.50141914352</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.66808728009</v>
+        <v>46181.50142061342</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>200</v>
@@ -5831,13 +5831,13 @@
         <v>241</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.59621038195</v>
+        <v>46125.429543715276</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.66815399306</v>
+        <v>46181.501487326386</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.66815550926</v>
+        <v>46181.501488842594</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>200</v>
@@ -5886,13 +5886,13 @@
         <v>242</v>
       </c>
       <c r="B71" s="8">
-        <v>46125.59625472222</v>
+        <v>46125.42958805556</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.668166689815</v>
+        <v>46181.50150002315</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.66816819445</v>
+        <v>46181.501501527775</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>200</v>
@@ -5941,13 +5941,13 @@
         <v>243</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.59629915509</v>
+        <v>46125.42963248843</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.66817956018</v>
+        <v>46181.50151289352</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.66818078703</v>
+        <v>46181.50151412037</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>200</v>
@@ -5996,13 +5996,13 @@
         <v>244</v>
       </c>
       <c r="B73" s="8">
-        <v>46122.55159751157</v>
+        <v>46122.384930844906</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.66878061343</v>
+        <v>46181.50211394676</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.66878222222</v>
+        <v>46181.50211555556</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>245</v>
@@ -6061,13 +6061,13 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46125.59648849537</v>
+        <v>46125.4298218287</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.668651921296</v>
+        <v>46181.501985254625</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.6686533912</v>
+        <v>46181.501986724536</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>200</v>
@@ -6116,13 +6116,13 @@
         <v>249</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.59661854166</v>
+        <v>46125.429951875005</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.66866650463</v>
+        <v>46181.50199983796</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.66866782407</v>
+        <v>46181.50200115741</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>200</v>
@@ -6171,13 +6171,13 @@
         <v>251</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.596668750004</v>
+        <v>46125.43000208333</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.66867587963</v>
+        <v>46181.50200921296</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.66867745371</v>
+        <v>46181.50201078704</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>200</v>
@@ -6226,13 +6226,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="8">
-        <v>46125.59671550926</v>
+        <v>46125.430048842594</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.668685625</v>
+        <v>46181.50201895833</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.668687060184</v>
+        <v>46181.50202039352</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>200</v>
@@ -6281,13 +6281,13 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.59675546296</v>
+        <v>46125.430088796296</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.66870385417</v>
+        <v>46181.5020371875</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.66870502315</v>
+        <v>46181.502038356484</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>200</v>
@@ -6336,13 +6336,13 @@
         <v>255</v>
       </c>
       <c r="B79" s="8">
-        <v>46122.55160357639</v>
+        <v>46122.38493690972</v>
       </c>
       <c r="C79" s="8">
-        <v>46195.563125636574</v>
+        <v>46195.3964589699</v>
       </c>
       <c r="D79" s="8">
-        <v>46195.563290335645</v>
+        <v>46195.39662366898</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>207</v>
@@ -6389,13 +6389,13 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46122.55160679398</v>
+        <v>46122.38494012732</v>
       </c>
       <c r="C80" s="5">
-        <v>46195.563269363425</v>
+        <v>46195.39660269676</v>
       </c>
       <c r="D80" s="5">
-        <v>46195.711846817125</v>
+        <v>46195.54518015047</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6454,13 +6454,13 @@
         <v>260</v>
       </c>
       <c r="B81" s="8">
-        <v>46122.551612256946</v>
+        <v>46122.38494559028</v>
       </c>
       <c r="C81" s="8">
-        <v>46195.50751318287</v>
+        <v>46195.34084651621</v>
       </c>
       <c r="D81" s="8">
-        <v>46195.50753130787</v>
+        <v>46195.3408646412</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>261</v>
@@ -6519,13 +6519,13 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46122.55161756944</v>
+        <v>46122.38495090278</v>
       </c>
       <c r="C82" s="5">
-        <v>46195.50751851852</v>
+        <v>46195.340851851855</v>
       </c>
       <c r="D82" s="5">
-        <v>46195.50753259259</v>
+        <v>46195.34086592593</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6584,13 +6584,13 @@
         <v>264</v>
       </c>
       <c r="B83" s="8">
-        <v>46122.55162288195</v>
+        <v>46122.384956215275</v>
       </c>
       <c r="C83" s="8">
-        <v>46195.507523437496</v>
+        <v>46195.34085677083</v>
       </c>
       <c r="D83" s="8">
-        <v>46195.507539479164</v>
+        <v>46195.3408728125</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>265</v>
@@ -6649,13 +6649,13 @@
         <v>266</v>
       </c>
       <c r="B84" s="5">
-        <v>46122.59399163195</v>
+        <v>46122.427324965276</v>
       </c>
       <c r="C84" s="5">
-        <v>46193.93315311342</v>
+        <v>46193.76648644676</v>
       </c>
       <c r="D84" s="5">
-        <v>46193.9332800463</v>
+        <v>46193.76661337963</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>267</v>
@@ -6714,13 +6714,13 @@
         <v>269</v>
       </c>
       <c r="B85" s="8">
-        <v>46122.551628182875</v>
+        <v>46122.3849615162</v>
       </c>
       <c r="C85" s="8">
-        <v>46195.5630599537</v>
+        <v>46195.39639328704</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.769192685184</v>
+        <v>46196.60252601852</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>270</v>
@@ -6767,13 +6767,13 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46122.55163158565</v>
+        <v>46122.38496491898</v>
       </c>
       <c r="C86" s="5">
-        <v>46195.50768850694</v>
+        <v>46195.34102184028</v>
       </c>
       <c r="D86" s="5">
-        <v>46195.507707129625</v>
+        <v>46195.34104046296</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>273</v>
@@ -6832,13 +6832,13 @@
         <v>275</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.5974969213</v>
+        <v>46125.43083025463</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.76791707176</v>
+        <v>46196.60125040509</v>
       </c>
       <c r="D87" s="8">
-        <v>46196.767918831014</v>
+        <v>46196.60125216436</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>200</v>
@@ -6887,13 +6887,13 @@
         <v>277</v>
       </c>
       <c r="B88" s="5">
-        <v>46125.59754570602</v>
+        <v>46125.430879039355</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.76795405093</v>
+        <v>46196.601287384256</v>
       </c>
       <c r="D88" s="5">
-        <v>46196.76795645834</v>
+        <v>46196.601289791666</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>200</v>
@@ -6942,13 +6942,13 @@
         <v>278</v>
       </c>
       <c r="B89" s="8">
-        <v>46125.59760710648</v>
+        <v>46125.430940439815</v>
       </c>
       <c r="C89" s="8">
-        <v>46196.767928217596</v>
+        <v>46196.601261550924</v>
       </c>
       <c r="D89" s="8">
-        <v>46196.76793001157</v>
+        <v>46196.601263344906</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>200</v>
@@ -6997,13 +6997,13 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46125.59765891204</v>
+        <v>46125.43099224537</v>
       </c>
       <c r="C90" s="5">
-        <v>46196.76794651621</v>
+        <v>46196.601279849536</v>
       </c>
       <c r="D90" s="5">
-        <v>46196.76794809027</v>
+        <v>46196.60128142362</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>200</v>
@@ -7052,13 +7052,13 @@
         <v>280</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.597703391206</v>
+        <v>46125.431036724534</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.76794100694</v>
+        <v>46196.60127434028</v>
       </c>
       <c r="D91" s="8">
-        <v>46196.76794287037</v>
+        <v>46196.6012762037</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>200</v>
@@ -7107,13 +7107,13 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46122.55170659722</v>
+        <v>46122.38503993055</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.76755512731</v>
+        <v>46196.60088846065</v>
       </c>
       <c r="D92" s="5">
-        <v>46196.76807780092</v>
+        <v>46196.60141113426</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>282</v>
@@ -7172,13 +7172,13 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46125.59982741898</v>
+        <v>46125.43316075232</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.76800195602</v>
+        <v>46196.60133528935</v>
       </c>
       <c r="D93" s="8">
-        <v>46196.76800386574</v>
+        <v>46196.60133719907</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>200</v>
@@ -7227,13 +7227,13 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.599890833335</v>
+        <v>46125.43322416667</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.768023020835</v>
+        <v>46196.601356354164</v>
       </c>
       <c r="D94" s="5">
-        <v>46196.768024687495</v>
+        <v>46196.60135802084</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>200</v>
@@ -7282,13 +7282,13 @@
         <v>288</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.59993134259</v>
+        <v>46125.43326467593</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.76801494213</v>
+        <v>46196.601348275464</v>
       </c>
       <c r="D95" s="8">
-        <v>46196.76801675926</v>
+        <v>46196.60135009259</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>200</v>
@@ -7337,13 +7337,13 @@
         <v>289</v>
       </c>
       <c r="B96" s="5">
-        <v>46125.59996929398</v>
+        <v>46125.433302627316</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.76805109954</v>
+        <v>46196.60138443287</v>
       </c>
       <c r="D96" s="5">
-        <v>46196.76805278935</v>
+        <v>46196.60138612268</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>200</v>
@@ -7392,13 +7392,13 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46125.6000115162</v>
+        <v>46125.43334484954</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.76805706018</v>
+        <v>46196.60139039352</v>
       </c>
       <c r="D97" s="8">
-        <v>46196.76805907408</v>
+        <v>46196.60139240741</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>200</v>
@@ -7447,13 +7447,13 @@
         <v>291</v>
       </c>
       <c r="B98" s="5">
-        <v>46122.55164413195</v>
+        <v>46122.38497746528</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.76839824074</v>
+        <v>46196.601731574076</v>
       </c>
       <c r="D98" s="5">
-        <v>46196.76840872686</v>
+        <v>46196.601742060186</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>292</v>
@@ -7512,13 +7512,13 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46125.599162743056</v>
+        <v>46125.43249607639</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.76818966435</v>
+        <v>46196.601522997684</v>
       </c>
       <c r="D99" s="8">
-        <v>46196.7681912963</v>
+        <v>46196.60152462963</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>200</v>
@@ -7567,13 +7567,13 @@
         <v>297</v>
       </c>
       <c r="B100" s="5">
-        <v>46125.599302511575</v>
+        <v>46125.4326358449</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.76820421296</v>
+        <v>46196.601537546296</v>
       </c>
       <c r="D100" s="5">
-        <v>46196.76820597222</v>
+        <v>46196.60153930556</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>200</v>
@@ -7622,13 +7622,13 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46125.59934644676</v>
+        <v>46125.43267978009</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.768375949076</v>
+        <v>46196.601709282404</v>
       </c>
       <c r="D101" s="8">
-        <v>46196.76837958333</v>
+        <v>46196.60171291667</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>200</v>
@@ -7677,13 +7677,13 @@
         <v>299</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.59938857639</v>
+        <v>46125.43272190972</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.76837696759</v>
+        <v>46196.60171030092</v>
       </c>
       <c r="D102" s="5">
-        <v>46196.76838008102</v>
+        <v>46196.60171341435</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>200</v>
@@ -7732,13 +7732,13 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46125.59943094908</v>
+        <v>46125.43276428241</v>
       </c>
       <c r="C103" s="8">
-        <v>46196.76837790509</v>
+        <v>46196.60171123843</v>
       </c>
       <c r="D103" s="8">
-        <v>46196.768380520836</v>
+        <v>46196.601713854165</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>200</v>
@@ -7787,13 +7787,13 @@
         <v>301</v>
       </c>
       <c r="B104" s="5">
-        <v>46122.551650995374</v>
+        <v>46122.3849843287</v>
       </c>
       <c r="C104" s="5">
-        <v>46196.76854788195</v>
+        <v>46196.601881215276</v>
       </c>
       <c r="D104" s="5">
-        <v>46196.76856074074</v>
+        <v>46196.601894074076</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>302</v>
@@ -7852,13 +7852,13 @@
         <v>303</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.59953013889</v>
+        <v>46125.43286347222</v>
       </c>
       <c r="C105" s="8">
-        <v>46196.76852783565</v>
+        <v>46196.60186116898</v>
       </c>
       <c r="D105" s="8">
-        <v>46196.768531724534</v>
+        <v>46196.60186505787</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>200</v>
@@ -7907,13 +7907,13 @@
         <v>305</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.59961423611</v>
+        <v>46125.43294756944</v>
       </c>
       <c r="C106" s="5">
-        <v>46196.76846329861</v>
+        <v>46196.60179663195</v>
       </c>
       <c r="D106" s="5">
-        <v>46196.76846496528</v>
+        <v>46196.60179829861</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>200</v>
@@ -7962,13 +7962,13 @@
         <v>306</v>
       </c>
       <c r="B107" s="8">
-        <v>46125.599654317135</v>
+        <v>46125.43298765046</v>
       </c>
       <c r="C107" s="8">
-        <v>46196.768528796296</v>
+        <v>46196.601862129624</v>
       </c>
       <c r="D107" s="8">
-        <v>46196.76853203704</v>
+        <v>46196.601865370365</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>200</v>
@@ -8017,13 +8017,13 @@
         <v>307</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.59957065972</v>
+        <v>46125.43290399306</v>
       </c>
       <c r="C108" s="5">
-        <v>46196.768529548615</v>
+        <v>46196.601862881944</v>
       </c>
       <c r="D108" s="5">
-        <v>46196.76853233796</v>
+        <v>46196.6018656713</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>200</v>
@@ -8072,13 +8072,13 @@
         <v>308</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.59969711806</v>
+        <v>46125.433030451386</v>
       </c>
       <c r="C109" s="8">
-        <v>46196.7685304051</v>
+        <v>46196.601863738426</v>
       </c>
       <c r="D109" s="8">
-        <v>46196.76853265046</v>
+        <v>46196.6018659838</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>200</v>
@@ -8127,13 +8127,13 @@
         <v>309</v>
       </c>
       <c r="B110" s="5">
-        <v>46122.55163725694</v>
+        <v>46122.38497059028</v>
       </c>
       <c r="C110" s="5">
-        <v>46196.76866755787</v>
+        <v>46196.6020008912</v>
       </c>
       <c r="D110" s="5">
-        <v>46196.76867908565</v>
+        <v>46196.60201241898</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>310</v>
@@ -8192,13 +8192,13 @@
         <v>311</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.59780210648</v>
+        <v>46125.431135439816</v>
       </c>
       <c r="C111" s="8">
-        <v>46196.76864902778</v>
+        <v>46196.60198236111</v>
       </c>
       <c r="D111" s="8">
-        <v>46196.76865387731</v>
+        <v>46196.60198721065</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>200</v>
@@ -8247,13 +8247,13 @@
         <v>314</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.597836932866</v>
+        <v>46125.43117026621</v>
       </c>
       <c r="C112" s="5">
-        <v>46196.76865</v>
+        <v>46196.601983333334</v>
       </c>
       <c r="D112" s="5">
-        <v>46196.76865427083</v>
+        <v>46196.60198760417</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>200</v>
@@ -8302,13 +8302,13 @@
         <v>315</v>
       </c>
       <c r="B113" s="8">
-        <v>46125.5979208912</v>
+        <v>46125.43125422453</v>
       </c>
       <c r="C113" s="8">
-        <v>46196.76865077546</v>
+        <v>46196.6019841088</v>
       </c>
       <c r="D113" s="8">
-        <v>46196.76865460648</v>
+        <v>46196.601987939815</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>200</v>
@@ -8357,13 +8357,13 @@
         <v>316</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.59788087963</v>
+        <v>46125.431214212964</v>
       </c>
       <c r="C114" s="5">
-        <v>46196.768651527775</v>
+        <v>46196.60198486111</v>
       </c>
       <c r="D114" s="5">
-        <v>46196.768654942134</v>
+        <v>46196.60198827546</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>200</v>
@@ -8412,13 +8412,13 @@
         <v>317</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.597965023146</v>
+        <v>46125.43129835648</v>
       </c>
       <c r="C115" s="8">
-        <v>46196.768652314815</v>
+        <v>46196.60198564814</v>
       </c>
       <c r="D115" s="8">
-        <v>46196.768655312495</v>
+        <v>46196.60198864584</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>200</v>
@@ -8467,13 +8467,13 @@
         <v>318</v>
       </c>
       <c r="B116" s="5">
-        <v>46122.55172043982</v>
+        <v>46122.38505377315</v>
       </c>
       <c r="C116" s="5">
-        <v>46196.76877224537</v>
+        <v>46196.6021055787</v>
       </c>
       <c r="D116" s="5">
-        <v>46196.768798784724</v>
+        <v>46196.60213211806</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>319</v>
@@ -8532,13 +8532,13 @@
         <v>320</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.60038253472</v>
+        <v>46125.43371586806</v>
       </c>
       <c r="C117" s="8">
-        <v>46196.76875258102</v>
+        <v>46196.602085914354</v>
       </c>
       <c r="D117" s="8">
-        <v>46196.768757337966</v>
+        <v>46196.602090671295</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>200</v>
@@ -8585,13 +8585,13 @@
         <v>322</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.60043012731</v>
+        <v>46125.43376346065</v>
       </c>
       <c r="C118" s="5">
-        <v>46196.7687534838</v>
+        <v>46196.60208681713</v>
       </c>
       <c r="D118" s="5">
-        <v>46196.76875768519</v>
+        <v>46196.60209101852</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>200</v>
@@ -8638,13 +8638,13 @@
         <v>323</v>
       </c>
       <c r="B119" s="8">
-        <v>46125.60047290509</v>
+        <v>46125.43380623843</v>
       </c>
       <c r="C119" s="8">
-        <v>46196.768754178236</v>
+        <v>46196.60208751158</v>
       </c>
       <c r="D119" s="8">
-        <v>46196.76875800926</v>
+        <v>46196.60209134259</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>200</v>
@@ -8691,13 +8691,13 @@
         <v>324</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.600514074074</v>
+        <v>46125.4338474074</v>
       </c>
       <c r="C120" s="5">
-        <v>46196.768754930556</v>
+        <v>46196.602088263884</v>
       </c>
       <c r="D120" s="5">
-        <v>46196.76875832176</v>
+        <v>46196.60209165509</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>200</v>
@@ -8744,13 +8744,13 @@
         <v>325</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.60055859954</v>
+        <v>46125.43389193287</v>
       </c>
       <c r="C121" s="8">
-        <v>46196.7687558912</v>
+        <v>46196.602089224536</v>
       </c>
       <c r="D121" s="8">
-        <v>46196.76875862268</v>
+        <v>46196.60209195602</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>200</v>
@@ -8797,13 +8797,13 @@
         <v>326</v>
       </c>
       <c r="B122" s="5">
-        <v>46122.55172986111</v>
+        <v>46122.385063194444</v>
       </c>
       <c r="C122" s="5">
-        <v>46196.76917457176</v>
+        <v>46196.60250790509</v>
       </c>
       <c r="D122" s="5">
-        <v>46196.76918584491</v>
+        <v>46196.60251917824</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>327</v>
@@ -8862,13 +8862,13 @@
         <v>329</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.60064416667</v>
+        <v>46125.4339775</v>
       </c>
       <c r="C123" s="8">
-        <v>46196.76915099537</v>
+        <v>46196.6024843287</v>
       </c>
       <c r="D123" s="8">
-        <v>46196.76915743056</v>
+        <v>46196.60249076389</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>200</v>
@@ -8915,13 +8915,13 @@
         <v>331</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.60068740741</v>
+        <v>46125.43402074074</v>
       </c>
       <c r="C124" s="5">
-        <v>46196.76915237268</v>
+        <v>46196.60248570602</v>
       </c>
       <c r="D124" s="5">
-        <v>46196.76915791667</v>
+        <v>46196.60249125</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>200</v>
@@ -8968,13 +8968,13 @@
         <v>332</v>
       </c>
       <c r="B125" s="8">
-        <v>46125.60073844907</v>
+        <v>46125.43407178241</v>
       </c>
       <c r="C125" s="8">
-        <v>46196.76915341435</v>
+        <v>46196.60248674768</v>
       </c>
       <c r="D125" s="8">
-        <v>46196.76915841435</v>
+        <v>46196.60249174769</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>200</v>
@@ -9021,13 +9021,13 @@
         <v>333</v>
       </c>
       <c r="B126" s="5">
-        <v>46125.60077622686</v>
+        <v>46125.434109560185</v>
       </c>
       <c r="C126" s="5">
-        <v>46196.76915438657</v>
+        <v>46196.60248771991</v>
       </c>
       <c r="D126" s="5">
-        <v>46196.769158842595</v>
+        <v>46196.60249217592</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>200</v>
@@ -9074,13 +9074,13 @@
         <v>334</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.600829143514</v>
+        <v>46125.43416247686</v>
       </c>
       <c r="C127" s="8">
-        <v>46196.769155358794</v>
+        <v>46196.60248869213</v>
       </c>
       <c r="D127" s="8">
-        <v>46196.76915931713</v>
+        <v>46196.60249265046</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>200</v>
@@ -9127,13 +9127,13 @@
         <v>335</v>
       </c>
       <c r="B128" s="5">
-        <v>46122.5517350463</v>
+        <v>46122.38506837963</v>
       </c>
       <c r="C128" s="5">
-        <v>46195.56317517361</v>
+        <v>46195.39650850694</v>
       </c>
       <c r="D128" s="5">
-        <v>46196.76960409722</v>
+        <v>46196.60293743055</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>336</v>
@@ -9180,13 +9180,13 @@
         <v>338</v>
       </c>
       <c r="B129" s="8">
-        <v>46122.5517390625</v>
+        <v>46122.38507239583</v>
       </c>
       <c r="C129" s="8">
-        <v>46196.76936652778</v>
+        <v>46196.60269986111</v>
       </c>
       <c r="D129" s="8">
-        <v>46196.76939736111</v>
+        <v>46196.602730694445</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>339</v>
@@ -9245,13 +9245,13 @@
         <v>343</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.60093731481</v>
+        <v>46125.43427064815</v>
       </c>
       <c r="C130" s="5">
-        <v>46196.76934515046</v>
+        <v>46196.602678483796</v>
       </c>
       <c r="D130" s="5">
-        <v>46196.769350682865</v>
+        <v>46196.60268401621</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>200</v>
@@ -9298,13 +9298,13 @@
         <v>345</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.601380821754</v>
+        <v>46125.4347141551</v>
       </c>
       <c r="C131" s="8">
-        <v>46196.769346307876</v>
+        <v>46196.602679641204</v>
       </c>
       <c r="D131" s="8">
-        <v>46196.769351145835</v>
+        <v>46196.60268447916</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>200</v>
@@ -9351,13 +9351,13 @@
         <v>346</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.60142481481</v>
+        <v>46125.43475814815</v>
       </c>
       <c r="C132" s="5">
-        <v>46196.7693472338</v>
+        <v>46196.60268056713</v>
       </c>
       <c r="D132" s="5">
-        <v>46196.76935155093</v>
+        <v>46196.60268488426</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>200</v>
@@ -9404,13 +9404,13 @@
         <v>347</v>
       </c>
       <c r="B133" s="8">
-        <v>46125.60146085648</v>
+        <v>46125.434794189816</v>
       </c>
       <c r="C133" s="8">
-        <v>46196.769348125</v>
+        <v>46196.60268145833</v>
       </c>
       <c r="D133" s="8">
-        <v>46196.76935192129</v>
+        <v>46196.602685254635</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>200</v>
@@ -9457,13 +9457,13 @@
         <v>348</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.60150208333</v>
+        <v>46125.434835416665</v>
       </c>
       <c r="C134" s="5">
-        <v>46196.769348981485</v>
+        <v>46196.60268231481</v>
       </c>
       <c r="D134" s="5">
-        <v>46196.76935229167</v>
+        <v>46196.602685624996</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>200</v>
@@ -9510,13 +9510,13 @@
         <v>349</v>
       </c>
       <c r="B135" s="8">
-        <v>46122.55174383102</v>
+        <v>46122.38507716435</v>
       </c>
       <c r="C135" s="8">
-        <v>46196.769596921295</v>
+        <v>46196.60293025463</v>
       </c>
       <c r="D135" s="8">
-        <v>46196.76961396991</v>
+        <v>46196.60294730324</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>350</v>
@@ -9573,13 +9573,13 @@
         <v>351</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.601086979164</v>
+        <v>46125.4344203125</v>
       </c>
       <c r="C136" s="5">
-        <v>46196.76947155093</v>
+        <v>46196.602804884256</v>
       </c>
       <c r="D136" s="5">
-        <v>46196.76947347222</v>
+        <v>46196.60280680556</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>200</v>
@@ -9626,13 +9626,13 @@
         <v>353</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.60115318287</v>
+        <v>46125.4344865162</v>
       </c>
       <c r="C137" s="8">
-        <v>46196.7695043287</v>
+        <v>46196.60283766204</v>
       </c>
       <c r="D137" s="8">
-        <v>46196.76950902778</v>
+        <v>46196.60284236111</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>200</v>
@@ -9679,13 +9679,13 @@
         <v>354</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.60120391204</v>
+        <v>46125.43453724537</v>
       </c>
       <c r="C138" s="5">
-        <v>46196.76950549769</v>
+        <v>46196.60283883102</v>
       </c>
       <c r="D138" s="5">
-        <v>46196.76950944445</v>
+        <v>46196.60284277778</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>200</v>
@@ -9732,13 +9732,13 @@
         <v>355</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.60125796296</v>
+        <v>46125.434591296296</v>
       </c>
       <c r="C139" s="8">
-        <v>46196.76950637731</v>
+        <v>46196.60283971065</v>
       </c>
       <c r="D139" s="8">
-        <v>46196.76950987268</v>
+        <v>46196.60284320602</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>200</v>
@@ -9785,13 +9785,13 @@
         <v>356</v>
       </c>
       <c r="B140" s="5">
-        <v>46125.601304282405</v>
+        <v>46125.43463761574</v>
       </c>
       <c r="C140" s="5">
-        <v>46196.76950730324</v>
+        <v>46196.60284063657</v>
       </c>
       <c r="D140" s="5">
-        <v>46196.769510266204</v>
+        <v>46196.60284359954</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>200</v>
@@ -9838,13 +9838,13 @@
         <v>357</v>
       </c>
       <c r="B141" s="8">
-        <v>46122.55174869213</v>
+        <v>46122.38508202546</v>
       </c>
       <c r="C141" s="8">
-        <v>46191.70598530093</v>
+        <v>46191.539318634255</v>
       </c>
       <c r="D141" s="8">
-        <v>46196.769715787035</v>
+        <v>46196.60304912037</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>358</v>
@@ -9901,13 +9901,13 @@
         <v>359</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.60158650463</v>
+        <v>46125.434919837964</v>
       </c>
       <c r="C142" s="5">
-        <v>46196.76968462963</v>
+        <v>46196.60301796296</v>
       </c>
       <c r="D142" s="5">
-        <v>46196.76968989584</v>
+        <v>46196.60302322917</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>200</v>
@@ -9954,13 +9954,13 @@
         <v>361</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.60163133102</v>
+        <v>46125.43496466435</v>
       </c>
       <c r="C143" s="8">
-        <v>46196.76968585648</v>
+        <v>46196.60301918982</v>
       </c>
       <c r="D143" s="8">
-        <v>46196.7696903125</v>
+        <v>46196.60302364583</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>200</v>
@@ -10007,13 +10007,13 @@
         <v>362</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.60167016204</v>
+        <v>46125.43500349537</v>
       </c>
       <c r="C144" s="5">
-        <v>46196.7696866551</v>
+        <v>46196.603019988426</v>
       </c>
       <c r="D144" s="5">
-        <v>46196.769690706016</v>
+        <v>46196.60302403935</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>200</v>
@@ -10060,13 +10060,13 @@
         <v>364</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.60170435185</v>
+        <v>46125.43503768518</v>
       </c>
       <c r="C145" s="8">
-        <v>46196.769687395834</v>
+        <v>46196.60302072916</v>
       </c>
       <c r="D145" s="8">
-        <v>46196.76969114583</v>
+        <v>46196.60302447916</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>200</v>
@@ -10113,13 +10113,13 @@
         <v>365</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.60173947917</v>
+        <v>46125.4350728125</v>
       </c>
       <c r="C146" s="5">
-        <v>46196.769688113425</v>
+        <v>46196.60302144676</v>
       </c>
       <c r="D146" s="5">
-        <v>46196.76969164352</v>
+        <v>46196.60302497685</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>200</v>
@@ -10166,13 +10166,13 @@
         <v>366</v>
       </c>
       <c r="B147" s="8">
-        <v>46122.551753472224</v>
+        <v>46122.38508680556</v>
       </c>
       <c r="C147" s="8">
-        <v>46191.70604009259</v>
+        <v>46191.53937342593</v>
       </c>
       <c r="D147" s="8">
-        <v>46196.76981105324</v>
+        <v>46196.60314438658</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>367</v>
@@ -10229,13 +10229,13 @@
         <v>369</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.60181555555</v>
+        <v>46125.43514888889</v>
       </c>
       <c r="C148" s="5">
-        <v>46196.76979265046</v>
+        <v>46196.60312598379</v>
       </c>
       <c r="D148" s="5">
-        <v>46196.76979569445</v>
+        <v>46196.603129027775</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>200</v>
@@ -10282,13 +10282,13 @@
         <v>370</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.60185690972</v>
+        <v>46125.43519024306</v>
       </c>
       <c r="C149" s="8">
-        <v>46196.76979356482</v>
+        <v>46196.603126898146</v>
       </c>
       <c r="D149" s="8">
-        <v>46196.76979614583</v>
+        <v>46196.60312947917</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>200</v>
@@ -10335,13 +10335,13 @@
         <v>371</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.601899490735</v>
+        <v>46125.43523282408</v>
       </c>
       <c r="C150" s="5">
-        <v>46196.769794224536</v>
+        <v>46196.60312755787</v>
       </c>
       <c r="D150" s="5">
-        <v>46196.76979648148</v>
+        <v>46196.603129814815</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>200</v>
@@ -10388,13 +10388,13 @@
         <v>372</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.60193935185</v>
+        <v>46125.43527268519</v>
       </c>
       <c r="C151" s="8">
-        <v>46196.76976476852</v>
+        <v>46196.603098101856</v>
       </c>
       <c r="D151" s="8">
-        <v>46196.769766875004</v>
+        <v>46196.60310020833</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>200</v>
@@ -10441,13 +10441,13 @@
         <v>373</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.60197710648</v>
+        <v>46125.43531043982</v>
       </c>
       <c r="C152" s="5">
-        <v>46196.76977206019</v>
+        <v>46196.603105393515</v>
       </c>
       <c r="D152" s="5">
-        <v>46196.76977370371</v>
+        <v>46196.60310703704</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>200</v>
@@ -10494,11 +10494,11 @@
         <v>374</v>
       </c>
       <c r="B153" s="8">
-        <v>46122.551758622685</v>
+        <v>46122.38509195602</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46125.58936878473</v>
+        <v>46125.422702118056</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>375</v>
@@ -10541,11 +10541,11 @@
         <v>377</v>
       </c>
       <c r="B154" s="5">
-        <v>46122.55176134259</v>
+        <v>46122.38509467593</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46191.70605767361</v>
+        <v>46191.53939100694</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>378</v>
@@ -10604,11 +10604,11 @@
         <v>381</v>
       </c>
       <c r="B155" s="8">
-        <v>46122.55176609954</v>
+        <v>46122.38509943287</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46192.97384414352</v>
+        <v>46192.80717747685</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>382</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -1847,13 +1847,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46122.38452245371</v>
+        <v>46122.55118912037</v>
       </c>
       <c r="C4" s="5">
-        <v>46128.426341053244</v>
+        <v>46128.59300771991</v>
       </c>
       <c r="D4" s="5">
-        <v>46157.93633454861</v>
+        <v>46158.10300121528</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1896,13 +1896,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46122.38467905093</v>
+        <v>46122.55134571759</v>
       </c>
       <c r="C5" s="8">
-        <v>46128.42632796297</v>
+        <v>46128.59299462963</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.70935505787</v>
+        <v>46133.876021724536</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1959,13 +1959,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46122.384682812495</v>
+        <v>46122.55134947917</v>
       </c>
       <c r="C6" s="5">
-        <v>46128.42601201389</v>
+        <v>46128.59267868055</v>
       </c>
       <c r="D6" s="5">
-        <v>46128.43715965278</v>
+        <v>46128.60382631945</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2022,13 +2022,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46122.38468587963</v>
+        <v>46122.551352546296</v>
       </c>
       <c r="C7" s="8">
-        <v>46128.42603200232</v>
+        <v>46128.59269866898</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.460593807875</v>
+        <v>46161.62726047453</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2085,13 +2085,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46122.38468890046</v>
+        <v>46122.551355567135</v>
       </c>
       <c r="C8" s="5">
-        <v>46128.42605055556</v>
+        <v>46128.59271722222</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.43733940972</v>
+        <v>46128.60400607639</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2148,13 +2148,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46122.384692719905</v>
+        <v>46122.551359386576</v>
       </c>
       <c r="C9" s="8">
-        <v>46128.4261833912</v>
+        <v>46128.592850057874</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.66910643518</v>
+        <v>46156.83577310185</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2211,13 +2211,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46122.3845274537</v>
+        <v>46122.55119412037</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.766136805556</v>
+        <v>46193.93280347223</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.76615431713</v>
+        <v>46193.9328209838</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2264,13 +2264,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46122.384696504625</v>
+        <v>46122.5513631713</v>
       </c>
       <c r="C11" s="8">
-        <v>46128.43768854167</v>
+        <v>46128.60435520833</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.80716136574</v>
+        <v>46192.97382803241</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2329,13 +2329,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46122.38470238426</v>
+        <v>46122.551369050925</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.43976447917</v>
+        <v>46128.60643114583</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.80716146991</v>
+        <v>46192.97382813657</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2394,13 +2394,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46122.384708020836</v>
+        <v>46122.5513746875</v>
       </c>
       <c r="C13" s="8">
-        <v>46132.40405894676</v>
+        <v>46132.57072561343</v>
       </c>
       <c r="D13" s="8">
-        <v>46192.80716134259</v>
+        <v>46192.97382800926</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2459,13 +2459,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46122.38692751157</v>
+        <v>46122.553594178244</v>
       </c>
       <c r="C14" s="5">
-        <v>46128.44274908565</v>
+        <v>46128.60941575232</v>
       </c>
       <c r="D14" s="5">
-        <v>46136.03935251157</v>
+        <v>46136.20601917824</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2524,13 +2524,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46122.38453280093</v>
+        <v>46122.55119946759</v>
       </c>
       <c r="C15" s="8">
-        <v>46195.34056496528</v>
+        <v>46195.50723163194</v>
       </c>
       <c r="D15" s="8">
-        <v>46195.340579421296</v>
+        <v>46195.50724608796</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2577,13 +2577,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46122.38472188657</v>
+        <v>46122.55138855324</v>
       </c>
       <c r="C16" s="5">
-        <v>46128.44033724537</v>
+        <v>46128.60700391204</v>
       </c>
       <c r="D16" s="5">
-        <v>46133.0133283912</v>
+        <v>46133.17999505787</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2642,13 +2642,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46122.38472815973</v>
+        <v>46122.55139482639</v>
       </c>
       <c r="C17" s="8">
-        <v>46128.44034490741</v>
+        <v>46128.60701157407</v>
       </c>
       <c r="D17" s="8">
-        <v>46132.01554025463</v>
+        <v>46132.182206921294</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2707,13 +2707,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46122.38473373842</v>
+        <v>46122.55140040509</v>
       </c>
       <c r="C18" s="5">
-        <v>46195.340545046296</v>
+        <v>46195.50721171296</v>
       </c>
       <c r="D18" s="5">
-        <v>46195.340565624996</v>
+        <v>46195.50723229167</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2772,13 +2772,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46122.384739375004</v>
+        <v>46122.55140604167</v>
       </c>
       <c r="C19" s="8">
-        <v>46181.499732384254</v>
+        <v>46181.666399050926</v>
       </c>
       <c r="D19" s="8">
-        <v>46195.038918101855</v>
+        <v>46195.20558476852</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2837,13 +2837,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46122.3847449537</v>
+        <v>46122.55141162037</v>
       </c>
       <c r="C20" s="5">
-        <v>46128.442831215274</v>
+        <v>46128.609497881946</v>
       </c>
       <c r="D20" s="5">
-        <v>46132.01553989583</v>
+        <v>46132.1822065625</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>64</v>
@@ -2902,13 +2902,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46122.39987912037</v>
+        <v>46122.566545787035</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.49969386574</v>
+        <v>46181.66636053241</v>
       </c>
       <c r="D21" s="8">
-        <v>46195.03891780092</v>
+        <v>46195.20558446759</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2967,13 +2967,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46122.39994855324</v>
+        <v>46122.56661521991</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.499709641204</v>
+        <v>46181.66637630787</v>
       </c>
       <c r="D22" s="5">
-        <v>46195.038917673606</v>
+        <v>46195.20558434028</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3032,13 +3032,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="8">
-        <v>46122.40619606481</v>
+        <v>46122.57286273148</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.4997655787</v>
+        <v>46181.66643224537</v>
       </c>
       <c r="D23" s="8">
-        <v>46195.03891771991</v>
+        <v>46195.205584386575</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -3097,13 +3097,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46122.38453728009</v>
+        <v>46122.55120394676</v>
       </c>
       <c r="C24" s="5">
-        <v>46195.34067315972</v>
+        <v>46195.50733982639</v>
       </c>
       <c r="D24" s="5">
-        <v>46195.34068686343</v>
+        <v>46195.50735353009</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -3150,13 +3150,13 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46122.38475027778</v>
+        <v>46122.55141694444</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.45950203703</v>
+        <v>46174.626168703704</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.45951446759</v>
+        <v>46174.626181134256</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -3215,13 +3215,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46122.38475541667</v>
+        <v>46122.55142208333</v>
       </c>
       <c r="C26" s="5">
-        <v>46174.45658625</v>
+        <v>46174.62325291667</v>
       </c>
       <c r="D26" s="5">
-        <v>46174.456587824076</v>
+        <v>46174.62325449074</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3276,13 +3276,13 @@
         <v>110</v>
       </c>
       <c r="B27" s="8">
-        <v>46122.38476032407</v>
+        <v>46122.55142699074</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.45948622686</v>
+        <v>46174.626152893514</v>
       </c>
       <c r="D27" s="8">
-        <v>46174.45948762732</v>
+        <v>46174.62615429398</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>111</v>
@@ -3337,13 +3337,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46122.38476556713</v>
+        <v>46122.5514322338</v>
       </c>
       <c r="C28" s="5">
-        <v>46195.340658553236</v>
+        <v>46195.50732521991</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.545180127316</v>
+        <v>46195.71184679398</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3402,13 +3402,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="8">
-        <v>46122.38477087963</v>
+        <v>46122.551437546295</v>
       </c>
       <c r="C29" s="8">
-        <v>46195.54471607639</v>
+        <v>46195.71138274306</v>
       </c>
       <c r="D29" s="8">
-        <v>46195.54471850695</v>
+        <v>46195.71138517361</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>118</v>
@@ -3463,13 +3463,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46122.3847758912</v>
+        <v>46122.55144255787</v>
       </c>
       <c r="C30" s="5">
-        <v>46195.54516429398</v>
+        <v>46195.711830960645</v>
       </c>
       <c r="D30" s="5">
-        <v>46195.54516583333</v>
+        <v>46195.711832500005</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3524,13 +3524,13 @@
         <v>123</v>
       </c>
       <c r="B31" s="8">
-        <v>46122.38478104166</v>
+        <v>46122.551447708334</v>
       </c>
       <c r="C31" s="8">
-        <v>46133.661133263886</v>
+        <v>46133.82779993056</v>
       </c>
       <c r="D31" s="8">
-        <v>46133.66114655093</v>
+        <v>46133.82781321759</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>124</v>
@@ -3589,13 +3589,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46122.38478609954</v>
+        <v>46122.5514527662</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.66106445601</v>
+        <v>46133.827731122685</v>
       </c>
       <c r="D32" s="5">
-        <v>46133.6610659375</v>
+        <v>46133.82773260417</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3650,13 +3650,13 @@
         <v>129</v>
       </c>
       <c r="B33" s="8">
-        <v>46122.384791296296</v>
+        <v>46122.55145796297</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.66112020833</v>
+        <v>46133.827786875</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.661121412035</v>
+        <v>46133.82778807871</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>130</v>
@@ -3711,13 +3711,13 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46122.38479633102</v>
+        <v>46122.55146299768</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.6611012963</v>
+        <v>46133.82776796297</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.66110246528</v>
+        <v>46133.827769131945</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3772,13 +3772,13 @@
         <v>135</v>
       </c>
       <c r="B35" s="8">
-        <v>46122.38480128472</v>
+        <v>46122.55146795139</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.50020540509</v>
+        <v>46181.66687207176</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.5002191088</v>
+        <v>46181.66688577546</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3837,13 +3837,13 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46122.38480630787</v>
+        <v>46122.551472974534</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.50015100694</v>
+        <v>46181.66681767361</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.50015280093</v>
+        <v>46181.66681946759</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3898,13 +3898,13 @@
         <v>143</v>
       </c>
       <c r="B37" s="8">
-        <v>46122.384855868055</v>
+        <v>46122.55152253472</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.50019012731</v>
+        <v>46181.66685679398</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.5001915162</v>
+        <v>46181.66685818287</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>144</v>
@@ -3959,13 +3959,13 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46122.384862245366</v>
+        <v>46122.55152891204</v>
       </c>
       <c r="C38" s="5">
-        <v>46154.70100114583</v>
+        <v>46154.867667812505</v>
       </c>
       <c r="D38" s="5">
-        <v>46189.00554646991</v>
+        <v>46189.172213136575</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -4024,13 +4024,13 @@
         <v>149</v>
       </c>
       <c r="B39" s="8">
-        <v>46122.384867395835</v>
+        <v>46122.5515340625</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.70085026621</v>
+        <v>46154.86751693287</v>
       </c>
       <c r="D39" s="8">
-        <v>46154.70085260417</v>
+        <v>46154.86751927083</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>87</v>
@@ -4079,13 +4079,13 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46122.38487178241</v>
+        <v>46122.55153844907</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.70090960649</v>
+        <v>46154.867576273144</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.70091078704</v>
+        <v>46154.867577453704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4134,13 +4134,13 @@
         <v>154</v>
       </c>
       <c r="B41" s="8">
-        <v>46122.40826678241</v>
+        <v>46122.574933449076</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.500100335645</v>
+        <v>46181.666767002316</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.50011658565</v>
+        <v>46181.666783252316</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>155</v>
@@ -4199,13 +4199,13 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46122.40925430556</v>
+        <v>46122.575920972224</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.500040729166</v>
+        <v>46181.66670739584</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.500041886575</v>
+        <v>46181.66670855324</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>90</v>
@@ -4254,13 +4254,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46122.409418090276</v>
+        <v>46122.57608475695</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.50008614583</v>
+        <v>46181.666752812496</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.500087685185</v>
+        <v>46181.666754351856</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4309,13 +4309,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46122.40834771991</v>
+        <v>46122.57501438657</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.500291805554</v>
+        <v>46181.666958472226</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.500401990736</v>
+        <v>46181.66706865741</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4374,13 +4374,13 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46122.41255444444</v>
+        <v>46122.57922111111</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.50023484953</v>
+        <v>46181.666901516204</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.50023640046</v>
+        <v>46181.66690306713</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>96</v>
@@ -4429,13 +4429,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46122.4128253588</v>
+        <v>46122.57949202546</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.500276562496</v>
+        <v>46181.66694322917</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.50027793982</v>
+        <v>46181.66694460648</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4484,13 +4484,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46125.362951550924</v>
+        <v>46125.529618217595</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.50055453704</v>
+        <v>46181.66722120371</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.500568449075</v>
+        <v>46181.66723511574</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4549,13 +4549,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46125.36311331019</v>
+        <v>46125.52977997685</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.50049065972</v>
+        <v>46181.66715732639</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.500492453706</v>
+        <v>46181.66715912037</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>93</v>
@@ -4604,13 +4604,13 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46125.36325149305</v>
+        <v>46125.52991815972</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.5005374537</v>
+        <v>46181.66720412037</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.50053896991</v>
+        <v>46181.66720563658</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4659,13 +4659,13 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46122.384541886575</v>
+        <v>46122.55120855324</v>
       </c>
       <c r="C50" s="5">
-        <v>46195.34078462963</v>
+        <v>46195.5074512963</v>
       </c>
       <c r="D50" s="5">
-        <v>46195.34089821759</v>
+        <v>46195.50756488426</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4712,13 +4712,13 @@
         <v>183</v>
       </c>
       <c r="B51" s="8">
-        <v>46122.38487678241</v>
+        <v>46122.55154344907</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.62917814815</v>
+        <v>46133.79584481481</v>
       </c>
       <c r="D51" s="8">
-        <v>46143.00447921296</v>
+        <v>46143.171145879634</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>184</v>
@@ -4777,13 +4777,13 @@
         <v>188</v>
       </c>
       <c r="B52" s="5">
-        <v>46122.38488232639</v>
+        <v>46122.551548993055</v>
       </c>
       <c r="C52" s="5">
-        <v>46134.62573756944</v>
+        <v>46134.79240423611</v>
       </c>
       <c r="D52" s="5">
-        <v>46190.02192827546</v>
+        <v>46190.18859494213</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4842,13 +4842,13 @@
         <v>192</v>
       </c>
       <c r="B53" s="8">
-        <v>46122.38489054398</v>
+        <v>46122.55155721065</v>
       </c>
       <c r="C53" s="8">
-        <v>46134.62578480324</v>
+        <v>46134.79245146991</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.02315126157</v>
+        <v>46191.18981792824</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>83</v>
@@ -4905,13 +4905,13 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46122.38489901621</v>
+        <v>46122.55156568287</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.34094658565</v>
+        <v>46195.50761325231</v>
       </c>
       <c r="D54" s="5">
-        <v>46196.6024115162</v>
+        <v>46196.76907818287</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -4968,13 +4968,13 @@
         <v>199</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.43695545139</v>
+        <v>46125.603622118055</v>
       </c>
       <c r="C55" s="8">
-        <v>46196.60238085648</v>
+        <v>46196.76904752315</v>
       </c>
       <c r="D55" s="8">
-        <v>46196.602385474536</v>
+        <v>46196.7690521412</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>200</v>
@@ -5021,13 +5021,13 @@
         <v>202</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.43700428241</v>
+        <v>46125.60367094907</v>
       </c>
       <c r="C56" s="5">
-        <v>46196.6023817824</v>
+        <v>46196.769048449074</v>
       </c>
       <c r="D56" s="5">
-        <v>46196.60238585648</v>
+        <v>46196.769052523145</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -5074,13 +5074,13 @@
         <v>203</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.43705284722</v>
+        <v>46125.60371951389</v>
       </c>
       <c r="C57" s="8">
-        <v>46196.602382627316</v>
+        <v>46196.76904929398</v>
       </c>
       <c r="D57" s="8">
-        <v>46196.60238616898</v>
+        <v>46196.76905283565</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5127,13 +5127,13 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.43709796296</v>
+        <v>46125.60376462963</v>
       </c>
       <c r="C58" s="5">
-        <v>46196.60238340277</v>
+        <v>46196.769050069444</v>
       </c>
       <c r="D58" s="5">
-        <v>46196.60238648148</v>
+        <v>46196.76905314815</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>200</v>
@@ -5180,13 +5180,13 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.437150729165</v>
+        <v>46125.60381739584</v>
       </c>
       <c r="C59" s="8">
-        <v>46196.602384108795</v>
+        <v>46196.76905077546</v>
       </c>
       <c r="D59" s="8">
-        <v>46196.6023868287</v>
+        <v>46196.76905349537</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>200</v>
@@ -5233,13 +5233,13 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46122.38490304398</v>
+        <v>46122.551569710646</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.501105787036</v>
+        <v>46181.6677724537</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.501186574074</v>
+        <v>46181.66785324074</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5282,13 +5282,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46122.38490655093</v>
+        <v>46122.55157321759</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.50071136574</v>
+        <v>46181.667378032405</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.500728576386</v>
+        <v>46181.66739524306</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5347,13 +5347,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46122.41824972222</v>
+        <v>46122.58491638889</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.50074653935</v>
+        <v>46181.667413206014</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.50076234953</v>
+        <v>46181.667429016205</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5412,13 +5412,13 @@
         <v>217</v>
       </c>
       <c r="B63" s="8">
-        <v>46125.36435991898</v>
+        <v>46125.53102658565</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.500763460645</v>
+        <v>46181.667430127316</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.50078259259</v>
+        <v>46181.66744925926</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -5477,13 +5477,13 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46122.38491179398</v>
+        <v>46122.55157846065</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.501089212965</v>
+        <v>46181.66775587963</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.501105752315</v>
+        <v>46181.66777241898</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5542,13 +5542,13 @@
         <v>225</v>
       </c>
       <c r="B65" s="8">
-        <v>46122.38491716435</v>
+        <v>46122.551583831024</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.50212802083</v>
+        <v>46181.6687946875</v>
       </c>
       <c r="D65" s="8">
-        <v>46181.50224104167</v>
+        <v>46181.66890770833</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>226</v>
@@ -5591,13 +5591,13 @@
         <v>228</v>
       </c>
       <c r="B66" s="5">
-        <v>46122.384920219905</v>
+        <v>46122.55158688658</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.49942690972</v>
+        <v>46181.666093576394</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.50214266204</v>
+        <v>46181.66880932871</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>229</v>
@@ -5656,13 +5656,13 @@
         <v>233</v>
       </c>
       <c r="B67" s="8">
-        <v>46122.384925185186</v>
+        <v>46122.55159185185</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.49953199074</v>
+        <v>46181.6661986574</v>
       </c>
       <c r="D67" s="8">
-        <v>46181.50217939814</v>
+        <v>46181.668846064815</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>234</v>
@@ -5721,13 +5721,13 @@
         <v>236</v>
       </c>
       <c r="B68" s="5">
-        <v>46125.42914525463</v>
+        <v>46125.595811921296</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.501410324076</v>
+        <v>46181.66807699074</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.50141217593</v>
+        <v>46181.66807884259</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>237</v>
@@ -5776,13 +5776,13 @@
         <v>240</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.42943380787</v>
+        <v>46125.59610047453</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.50141914352</v>
+        <v>46181.66808581019</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.50142061342</v>
+        <v>46181.66808728009</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>200</v>
@@ -5831,13 +5831,13 @@
         <v>241</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.429543715276</v>
+        <v>46125.59621038195</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.501487326386</v>
+        <v>46181.66815399306</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.501488842594</v>
+        <v>46181.66815550926</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>200</v>
@@ -5886,13 +5886,13 @@
         <v>242</v>
       </c>
       <c r="B71" s="8">
-        <v>46125.42958805556</v>
+        <v>46125.59625472222</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.50150002315</v>
+        <v>46181.668166689815</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.501501527775</v>
+        <v>46181.66816819445</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>200</v>
@@ -5941,13 +5941,13 @@
         <v>243</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.42963248843</v>
+        <v>46125.59629915509</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.50151289352</v>
+        <v>46181.66817956018</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.50151412037</v>
+        <v>46181.66818078703</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>200</v>
@@ -5996,13 +5996,13 @@
         <v>244</v>
       </c>
       <c r="B73" s="8">
-        <v>46122.384930844906</v>
+        <v>46122.55159751157</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.50211394676</v>
+        <v>46181.66878061343</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.50211555556</v>
+        <v>46181.66878222222</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>245</v>
@@ -6061,13 +6061,13 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46125.4298218287</v>
+        <v>46125.59648849537</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.501985254625</v>
+        <v>46181.668651921296</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.501986724536</v>
+        <v>46181.6686533912</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>200</v>
@@ -6116,13 +6116,13 @@
         <v>249</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.429951875005</v>
+        <v>46125.59661854166</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.50199983796</v>
+        <v>46181.66866650463</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.50200115741</v>
+        <v>46181.66866782407</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>200</v>
@@ -6171,13 +6171,13 @@
         <v>251</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.43000208333</v>
+        <v>46125.596668750004</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.50200921296</v>
+        <v>46181.66867587963</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.50201078704</v>
+        <v>46181.66867745371</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>200</v>
@@ -6226,13 +6226,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="8">
-        <v>46125.430048842594</v>
+        <v>46125.59671550926</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.50201895833</v>
+        <v>46181.668685625</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.50202039352</v>
+        <v>46181.668687060184</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>200</v>
@@ -6281,13 +6281,13 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.430088796296</v>
+        <v>46125.59675546296</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.5020371875</v>
+        <v>46181.66870385417</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.502038356484</v>
+        <v>46181.66870502315</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>200</v>
@@ -6336,13 +6336,13 @@
         <v>255</v>
       </c>
       <c r="B79" s="8">
-        <v>46122.38493690972</v>
+        <v>46122.55160357639</v>
       </c>
       <c r="C79" s="8">
-        <v>46195.3964589699</v>
+        <v>46195.563125636574</v>
       </c>
       <c r="D79" s="8">
-        <v>46195.39662366898</v>
+        <v>46195.563290335645</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>207</v>
@@ -6389,13 +6389,13 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46122.38494012732</v>
+        <v>46122.55160679398</v>
       </c>
       <c r="C80" s="5">
-        <v>46195.39660269676</v>
+        <v>46195.563269363425</v>
       </c>
       <c r="D80" s="5">
-        <v>46195.54518015047</v>
+        <v>46195.711846817125</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6454,13 +6454,13 @@
         <v>260</v>
       </c>
       <c r="B81" s="8">
-        <v>46122.38494559028</v>
+        <v>46122.551612256946</v>
       </c>
       <c r="C81" s="8">
-        <v>46195.34084651621</v>
+        <v>46195.50751318287</v>
       </c>
       <c r="D81" s="8">
-        <v>46195.3408646412</v>
+        <v>46195.50753130787</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>261</v>
@@ -6519,13 +6519,13 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46122.38495090278</v>
+        <v>46122.55161756944</v>
       </c>
       <c r="C82" s="5">
-        <v>46195.340851851855</v>
+        <v>46195.50751851852</v>
       </c>
       <c r="D82" s="5">
-        <v>46195.34086592593</v>
+        <v>46195.50753259259</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6584,13 +6584,13 @@
         <v>264</v>
       </c>
       <c r="B83" s="8">
-        <v>46122.384956215275</v>
+        <v>46122.55162288195</v>
       </c>
       <c r="C83" s="8">
-        <v>46195.34085677083</v>
+        <v>46195.507523437496</v>
       </c>
       <c r="D83" s="8">
-        <v>46195.3408728125</v>
+        <v>46195.507539479164</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>265</v>
@@ -6649,13 +6649,13 @@
         <v>266</v>
       </c>
       <c r="B84" s="5">
-        <v>46122.427324965276</v>
+        <v>46122.59399163195</v>
       </c>
       <c r="C84" s="5">
-        <v>46193.76648644676</v>
+        <v>46193.93315311342</v>
       </c>
       <c r="D84" s="5">
-        <v>46193.76661337963</v>
+        <v>46193.9332800463</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>267</v>
@@ -6714,13 +6714,13 @@
         <v>269</v>
       </c>
       <c r="B85" s="8">
-        <v>46122.3849615162</v>
+        <v>46122.551628182875</v>
       </c>
       <c r="C85" s="8">
-        <v>46195.39639328704</v>
+        <v>46195.5630599537</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.60252601852</v>
+        <v>46196.769192685184</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>270</v>
@@ -6767,13 +6767,13 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46122.38496491898</v>
+        <v>46122.55163158565</v>
       </c>
       <c r="C86" s="5">
-        <v>46195.34102184028</v>
+        <v>46195.50768850694</v>
       </c>
       <c r="D86" s="5">
-        <v>46195.34104046296</v>
+        <v>46195.507707129625</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>273</v>
@@ -6832,13 +6832,13 @@
         <v>275</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.43083025463</v>
+        <v>46125.5974969213</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.60125040509</v>
+        <v>46196.76791707176</v>
       </c>
       <c r="D87" s="8">
-        <v>46196.60125216436</v>
+        <v>46196.767918831014</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>200</v>
@@ -6887,13 +6887,13 @@
         <v>277</v>
       </c>
       <c r="B88" s="5">
-        <v>46125.430879039355</v>
+        <v>46125.59754570602</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.601287384256</v>
+        <v>46196.76795405093</v>
       </c>
       <c r="D88" s="5">
-        <v>46196.601289791666</v>
+        <v>46196.76795645834</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>200</v>
@@ -6942,13 +6942,13 @@
         <v>278</v>
       </c>
       <c r="B89" s="8">
-        <v>46125.430940439815</v>
+        <v>46125.59760710648</v>
       </c>
       <c r="C89" s="8">
-        <v>46196.601261550924</v>
+        <v>46196.767928217596</v>
       </c>
       <c r="D89" s="8">
-        <v>46196.601263344906</v>
+        <v>46196.76793001157</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>200</v>
@@ -6997,13 +6997,13 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46125.43099224537</v>
+        <v>46125.59765891204</v>
       </c>
       <c r="C90" s="5">
-        <v>46196.601279849536</v>
+        <v>46196.76794651621</v>
       </c>
       <c r="D90" s="5">
-        <v>46196.60128142362</v>
+        <v>46196.76794809027</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>200</v>
@@ -7052,13 +7052,13 @@
         <v>280</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.431036724534</v>
+        <v>46125.597703391206</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.60127434028</v>
+        <v>46196.76794100694</v>
       </c>
       <c r="D91" s="8">
-        <v>46196.6012762037</v>
+        <v>46196.76794287037</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>200</v>
@@ -7107,13 +7107,13 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46122.38503993055</v>
+        <v>46122.55170659722</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.60088846065</v>
+        <v>46196.76755512731</v>
       </c>
       <c r="D92" s="5">
-        <v>46196.60141113426</v>
+        <v>46196.76807780092</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>282</v>
@@ -7172,13 +7172,13 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46125.43316075232</v>
+        <v>46125.59982741898</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.60133528935</v>
+        <v>46196.76800195602</v>
       </c>
       <c r="D93" s="8">
-        <v>46196.60133719907</v>
+        <v>46196.76800386574</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>200</v>
@@ -7227,13 +7227,13 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.43322416667</v>
+        <v>46125.599890833335</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.601356354164</v>
+        <v>46196.768023020835</v>
       </c>
       <c r="D94" s="5">
-        <v>46196.60135802084</v>
+        <v>46196.768024687495</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>200</v>
@@ -7282,13 +7282,13 @@
         <v>288</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.43326467593</v>
+        <v>46125.59993134259</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.601348275464</v>
+        <v>46196.76801494213</v>
       </c>
       <c r="D95" s="8">
-        <v>46196.60135009259</v>
+        <v>46196.76801675926</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>200</v>
@@ -7337,13 +7337,13 @@
         <v>289</v>
       </c>
       <c r="B96" s="5">
-        <v>46125.433302627316</v>
+        <v>46125.59996929398</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.60138443287</v>
+        <v>46196.76805109954</v>
       </c>
       <c r="D96" s="5">
-        <v>46196.60138612268</v>
+        <v>46196.76805278935</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>200</v>
@@ -7392,13 +7392,13 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46125.43334484954</v>
+        <v>46125.6000115162</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.60139039352</v>
+        <v>46196.76805706018</v>
       </c>
       <c r="D97" s="8">
-        <v>46196.60139240741</v>
+        <v>46196.76805907408</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>200</v>
@@ -7447,13 +7447,13 @@
         <v>291</v>
       </c>
       <c r="B98" s="5">
-        <v>46122.38497746528</v>
+        <v>46122.55164413195</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.601731574076</v>
+        <v>46196.76839824074</v>
       </c>
       <c r="D98" s="5">
-        <v>46196.601742060186</v>
+        <v>46196.76840872686</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>292</v>
@@ -7512,13 +7512,13 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46125.43249607639</v>
+        <v>46125.599162743056</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.601522997684</v>
+        <v>46196.76818966435</v>
       </c>
       <c r="D99" s="8">
-        <v>46196.60152462963</v>
+        <v>46196.7681912963</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>200</v>
@@ -7567,13 +7567,13 @@
         <v>297</v>
       </c>
       <c r="B100" s="5">
-        <v>46125.4326358449</v>
+        <v>46125.599302511575</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.601537546296</v>
+        <v>46196.76820421296</v>
       </c>
       <c r="D100" s="5">
-        <v>46196.60153930556</v>
+        <v>46196.76820597222</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>200</v>
@@ -7622,13 +7622,13 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46125.43267978009</v>
+        <v>46125.59934644676</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.601709282404</v>
+        <v>46196.768375949076</v>
       </c>
       <c r="D101" s="8">
-        <v>46196.60171291667</v>
+        <v>46196.76837958333</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>200</v>
@@ -7677,13 +7677,13 @@
         <v>299</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.43272190972</v>
+        <v>46125.59938857639</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.60171030092</v>
+        <v>46196.76837696759</v>
       </c>
       <c r="D102" s="5">
-        <v>46196.60171341435</v>
+        <v>46196.76838008102</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>200</v>
@@ -7732,13 +7732,13 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46125.43276428241</v>
+        <v>46125.59943094908</v>
       </c>
       <c r="C103" s="8">
-        <v>46196.60171123843</v>
+        <v>46196.76837790509</v>
       </c>
       <c r="D103" s="8">
-        <v>46196.601713854165</v>
+        <v>46196.768380520836</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>200</v>
@@ -7787,13 +7787,13 @@
         <v>301</v>
       </c>
       <c r="B104" s="5">
-        <v>46122.3849843287</v>
+        <v>46122.551650995374</v>
       </c>
       <c r="C104" s="5">
-        <v>46196.601881215276</v>
+        <v>46196.76854788195</v>
       </c>
       <c r="D104" s="5">
-        <v>46196.601894074076</v>
+        <v>46196.76856074074</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>302</v>
@@ -7852,13 +7852,13 @@
         <v>303</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.43286347222</v>
+        <v>46125.59953013889</v>
       </c>
       <c r="C105" s="8">
-        <v>46196.60186116898</v>
+        <v>46196.76852783565</v>
       </c>
       <c r="D105" s="8">
-        <v>46196.60186505787</v>
+        <v>46196.768531724534</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>200</v>
@@ -7907,13 +7907,13 @@
         <v>305</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.43294756944</v>
+        <v>46125.59961423611</v>
       </c>
       <c r="C106" s="5">
-        <v>46196.60179663195</v>
+        <v>46196.76846329861</v>
       </c>
       <c r="D106" s="5">
-        <v>46196.60179829861</v>
+        <v>46196.76846496528</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>200</v>
@@ -7962,13 +7962,13 @@
         <v>306</v>
       </c>
       <c r="B107" s="8">
-        <v>46125.43298765046</v>
+        <v>46125.599654317135</v>
       </c>
       <c r="C107" s="8">
-        <v>46196.601862129624</v>
+        <v>46196.768528796296</v>
       </c>
       <c r="D107" s="8">
-        <v>46196.601865370365</v>
+        <v>46196.76853203704</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>200</v>
@@ -8017,13 +8017,13 @@
         <v>307</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.43290399306</v>
+        <v>46125.59957065972</v>
       </c>
       <c r="C108" s="5">
-        <v>46196.601862881944</v>
+        <v>46196.768529548615</v>
       </c>
       <c r="D108" s="5">
-        <v>46196.6018656713</v>
+        <v>46196.76853233796</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>200</v>
@@ -8072,13 +8072,13 @@
         <v>308</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.433030451386</v>
+        <v>46125.59969711806</v>
       </c>
       <c r="C109" s="8">
-        <v>46196.601863738426</v>
+        <v>46196.7685304051</v>
       </c>
       <c r="D109" s="8">
-        <v>46196.6018659838</v>
+        <v>46196.76853265046</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>200</v>
@@ -8127,13 +8127,13 @@
         <v>309</v>
       </c>
       <c r="B110" s="5">
-        <v>46122.38497059028</v>
+        <v>46122.55163725694</v>
       </c>
       <c r="C110" s="5">
-        <v>46196.6020008912</v>
+        <v>46196.76866755787</v>
       </c>
       <c r="D110" s="5">
-        <v>46196.60201241898</v>
+        <v>46196.76867908565</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>310</v>
@@ -8192,13 +8192,13 @@
         <v>311</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.431135439816</v>
+        <v>46125.59780210648</v>
       </c>
       <c r="C111" s="8">
-        <v>46196.60198236111</v>
+        <v>46196.76864902778</v>
       </c>
       <c r="D111" s="8">
-        <v>46196.60198721065</v>
+        <v>46196.76865387731</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>200</v>
@@ -8247,13 +8247,13 @@
         <v>314</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.43117026621</v>
+        <v>46125.597836932866</v>
       </c>
       <c r="C112" s="5">
-        <v>46196.601983333334</v>
+        <v>46196.76865</v>
       </c>
       <c r="D112" s="5">
-        <v>46196.60198760417</v>
+        <v>46196.76865427083</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>200</v>
@@ -8302,13 +8302,13 @@
         <v>315</v>
       </c>
       <c r="B113" s="8">
-        <v>46125.43125422453</v>
+        <v>46125.5979208912</v>
       </c>
       <c r="C113" s="8">
-        <v>46196.6019841088</v>
+        <v>46196.76865077546</v>
       </c>
       <c r="D113" s="8">
-        <v>46196.601987939815</v>
+        <v>46196.76865460648</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>200</v>
@@ -8357,13 +8357,13 @@
         <v>316</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.431214212964</v>
+        <v>46125.59788087963</v>
       </c>
       <c r="C114" s="5">
-        <v>46196.60198486111</v>
+        <v>46196.768651527775</v>
       </c>
       <c r="D114" s="5">
-        <v>46196.60198827546</v>
+        <v>46196.768654942134</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>200</v>
@@ -8412,13 +8412,13 @@
         <v>317</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.43129835648</v>
+        <v>46125.597965023146</v>
       </c>
       <c r="C115" s="8">
-        <v>46196.60198564814</v>
+        <v>46196.768652314815</v>
       </c>
       <c r="D115" s="8">
-        <v>46196.60198864584</v>
+        <v>46196.768655312495</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>200</v>
@@ -8467,13 +8467,13 @@
         <v>318</v>
       </c>
       <c r="B116" s="5">
-        <v>46122.38505377315</v>
+        <v>46122.55172043982</v>
       </c>
       <c r="C116" s="5">
-        <v>46196.6021055787</v>
+        <v>46196.76877224537</v>
       </c>
       <c r="D116" s="5">
-        <v>46196.60213211806</v>
+        <v>46196.768798784724</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>319</v>
@@ -8532,13 +8532,13 @@
         <v>320</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.43371586806</v>
+        <v>46125.60038253472</v>
       </c>
       <c r="C117" s="8">
-        <v>46196.602085914354</v>
+        <v>46196.76875258102</v>
       </c>
       <c r="D117" s="8">
-        <v>46196.602090671295</v>
+        <v>46196.768757337966</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>200</v>
@@ -8585,13 +8585,13 @@
         <v>322</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.43376346065</v>
+        <v>46125.60043012731</v>
       </c>
       <c r="C118" s="5">
-        <v>46196.60208681713</v>
+        <v>46196.7687534838</v>
       </c>
       <c r="D118" s="5">
-        <v>46196.60209101852</v>
+        <v>46196.76875768519</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>200</v>
@@ -8638,13 +8638,13 @@
         <v>323</v>
       </c>
       <c r="B119" s="8">
-        <v>46125.43380623843</v>
+        <v>46125.60047290509</v>
       </c>
       <c r="C119" s="8">
-        <v>46196.60208751158</v>
+        <v>46196.768754178236</v>
       </c>
       <c r="D119" s="8">
-        <v>46196.60209134259</v>
+        <v>46196.76875800926</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>200</v>
@@ -8691,13 +8691,13 @@
         <v>324</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.4338474074</v>
+        <v>46125.600514074074</v>
       </c>
       <c r="C120" s="5">
-        <v>46196.602088263884</v>
+        <v>46196.768754930556</v>
       </c>
       <c r="D120" s="5">
-        <v>46196.60209165509</v>
+        <v>46196.76875832176</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>200</v>
@@ -8744,13 +8744,13 @@
         <v>325</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.43389193287</v>
+        <v>46125.60055859954</v>
       </c>
       <c r="C121" s="8">
-        <v>46196.602089224536</v>
+        <v>46196.7687558912</v>
       </c>
       <c r="D121" s="8">
-        <v>46196.60209195602</v>
+        <v>46196.76875862268</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>200</v>
@@ -8797,13 +8797,13 @@
         <v>326</v>
       </c>
       <c r="B122" s="5">
-        <v>46122.385063194444</v>
+        <v>46122.55172986111</v>
       </c>
       <c r="C122" s="5">
-        <v>46196.60250790509</v>
+        <v>46196.76917457176</v>
       </c>
       <c r="D122" s="5">
-        <v>46196.60251917824</v>
+        <v>46196.76918584491</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>327</v>
@@ -8862,13 +8862,13 @@
         <v>329</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.4339775</v>
+        <v>46125.60064416667</v>
       </c>
       <c r="C123" s="8">
-        <v>46196.6024843287</v>
+        <v>46196.76915099537</v>
       </c>
       <c r="D123" s="8">
-        <v>46196.60249076389</v>
+        <v>46196.76915743056</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>200</v>
@@ -8915,13 +8915,13 @@
         <v>331</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.43402074074</v>
+        <v>46125.60068740741</v>
       </c>
       <c r="C124" s="5">
-        <v>46196.60248570602</v>
+        <v>46196.76915237268</v>
       </c>
       <c r="D124" s="5">
-        <v>46196.60249125</v>
+        <v>46196.76915791667</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>200</v>
@@ -8968,13 +8968,13 @@
         <v>332</v>
       </c>
       <c r="B125" s="8">
-        <v>46125.43407178241</v>
+        <v>46125.60073844907</v>
       </c>
       <c r="C125" s="8">
-        <v>46196.60248674768</v>
+        <v>46196.76915341435</v>
       </c>
       <c r="D125" s="8">
-        <v>46196.60249174769</v>
+        <v>46196.76915841435</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>200</v>
@@ -9021,13 +9021,13 @@
         <v>333</v>
       </c>
       <c r="B126" s="5">
-        <v>46125.434109560185</v>
+        <v>46125.60077622686</v>
       </c>
       <c r="C126" s="5">
-        <v>46196.60248771991</v>
+        <v>46196.76915438657</v>
       </c>
       <c r="D126" s="5">
-        <v>46196.60249217592</v>
+        <v>46196.769158842595</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>200</v>
@@ -9074,13 +9074,13 @@
         <v>334</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.43416247686</v>
+        <v>46125.600829143514</v>
       </c>
       <c r="C127" s="8">
-        <v>46196.60248869213</v>
+        <v>46196.769155358794</v>
       </c>
       <c r="D127" s="8">
-        <v>46196.60249265046</v>
+        <v>46196.76915931713</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>200</v>
@@ -9127,13 +9127,13 @@
         <v>335</v>
       </c>
       <c r="B128" s="5">
-        <v>46122.38506837963</v>
+        <v>46122.5517350463</v>
       </c>
       <c r="C128" s="5">
-        <v>46195.39650850694</v>
+        <v>46195.56317517361</v>
       </c>
       <c r="D128" s="5">
-        <v>46196.60293743055</v>
+        <v>46196.76960409722</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>336</v>
@@ -9180,13 +9180,13 @@
         <v>338</v>
       </c>
       <c r="B129" s="8">
-        <v>46122.38507239583</v>
+        <v>46122.5517390625</v>
       </c>
       <c r="C129" s="8">
-        <v>46196.60269986111</v>
+        <v>46196.76936652778</v>
       </c>
       <c r="D129" s="8">
-        <v>46196.602730694445</v>
+        <v>46196.76939736111</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>339</v>
@@ -9245,13 +9245,13 @@
         <v>343</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.43427064815</v>
+        <v>46125.60093731481</v>
       </c>
       <c r="C130" s="5">
-        <v>46196.602678483796</v>
+        <v>46196.76934515046</v>
       </c>
       <c r="D130" s="5">
-        <v>46196.60268401621</v>
+        <v>46196.769350682865</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>200</v>
@@ -9298,13 +9298,13 @@
         <v>345</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.4347141551</v>
+        <v>46125.601380821754</v>
       </c>
       <c r="C131" s="8">
-        <v>46196.602679641204</v>
+        <v>46196.769346307876</v>
       </c>
       <c r="D131" s="8">
-        <v>46196.60268447916</v>
+        <v>46196.769351145835</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>200</v>
@@ -9351,13 +9351,13 @@
         <v>346</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.43475814815</v>
+        <v>46125.60142481481</v>
       </c>
       <c r="C132" s="5">
-        <v>46196.60268056713</v>
+        <v>46196.7693472338</v>
       </c>
       <c r="D132" s="5">
-        <v>46196.60268488426</v>
+        <v>46196.76935155093</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>200</v>
@@ -9404,13 +9404,13 @@
         <v>347</v>
       </c>
       <c r="B133" s="8">
-        <v>46125.434794189816</v>
+        <v>46125.60146085648</v>
       </c>
       <c r="C133" s="8">
-        <v>46196.60268145833</v>
+        <v>46196.769348125</v>
       </c>
       <c r="D133" s="8">
-        <v>46196.602685254635</v>
+        <v>46196.76935192129</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>200</v>
@@ -9457,13 +9457,13 @@
         <v>348</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.434835416665</v>
+        <v>46125.60150208333</v>
       </c>
       <c r="C134" s="5">
-        <v>46196.60268231481</v>
+        <v>46196.769348981485</v>
       </c>
       <c r="D134" s="5">
-        <v>46196.602685624996</v>
+        <v>46196.76935229167</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>200</v>
@@ -9510,13 +9510,13 @@
         <v>349</v>
       </c>
       <c r="B135" s="8">
-        <v>46122.38507716435</v>
+        <v>46122.55174383102</v>
       </c>
       <c r="C135" s="8">
-        <v>46196.60293025463</v>
+        <v>46196.769596921295</v>
       </c>
       <c r="D135" s="8">
-        <v>46196.60294730324</v>
+        <v>46196.76961396991</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>350</v>
@@ -9573,13 +9573,13 @@
         <v>351</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.4344203125</v>
+        <v>46125.601086979164</v>
       </c>
       <c r="C136" s="5">
-        <v>46196.602804884256</v>
+        <v>46196.76947155093</v>
       </c>
       <c r="D136" s="5">
-        <v>46196.60280680556</v>
+        <v>46196.76947347222</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>200</v>
@@ -9626,13 +9626,13 @@
         <v>353</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.4344865162</v>
+        <v>46125.60115318287</v>
       </c>
       <c r="C137" s="8">
-        <v>46196.60283766204</v>
+        <v>46196.7695043287</v>
       </c>
       <c r="D137" s="8">
-        <v>46196.60284236111</v>
+        <v>46196.76950902778</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>200</v>
@@ -9679,13 +9679,13 @@
         <v>354</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.43453724537</v>
+        <v>46125.60120391204</v>
       </c>
       <c r="C138" s="5">
-        <v>46196.60283883102</v>
+        <v>46196.76950549769</v>
       </c>
       <c r="D138" s="5">
-        <v>46196.60284277778</v>
+        <v>46196.76950944445</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>200</v>
@@ -9732,13 +9732,13 @@
         <v>355</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.434591296296</v>
+        <v>46125.60125796296</v>
       </c>
       <c r="C139" s="8">
-        <v>46196.60283971065</v>
+        <v>46196.76950637731</v>
       </c>
       <c r="D139" s="8">
-        <v>46196.60284320602</v>
+        <v>46196.76950987268</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>200</v>
@@ -9785,13 +9785,13 @@
         <v>356</v>
       </c>
       <c r="B140" s="5">
-        <v>46125.43463761574</v>
+        <v>46125.601304282405</v>
       </c>
       <c r="C140" s="5">
-        <v>46196.60284063657</v>
+        <v>46196.76950730324</v>
       </c>
       <c r="D140" s="5">
-        <v>46196.60284359954</v>
+        <v>46196.769510266204</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>200</v>
@@ -9838,13 +9838,13 @@
         <v>357</v>
       </c>
       <c r="B141" s="8">
-        <v>46122.38508202546</v>
+        <v>46122.55174869213</v>
       </c>
       <c r="C141" s="8">
-        <v>46191.539318634255</v>
+        <v>46191.70598530093</v>
       </c>
       <c r="D141" s="8">
-        <v>46196.60304912037</v>
+        <v>46196.769715787035</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>358</v>
@@ -9901,13 +9901,13 @@
         <v>359</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.434919837964</v>
+        <v>46125.60158650463</v>
       </c>
       <c r="C142" s="5">
-        <v>46196.60301796296</v>
+        <v>46196.76968462963</v>
       </c>
       <c r="D142" s="5">
-        <v>46196.60302322917</v>
+        <v>46196.76968989584</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>200</v>
@@ -9954,13 +9954,13 @@
         <v>361</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.43496466435</v>
+        <v>46125.60163133102</v>
       </c>
       <c r="C143" s="8">
-        <v>46196.60301918982</v>
+        <v>46196.76968585648</v>
       </c>
       <c r="D143" s="8">
-        <v>46196.60302364583</v>
+        <v>46196.7696903125</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>200</v>
@@ -10007,13 +10007,13 @@
         <v>362</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.43500349537</v>
+        <v>46125.60167016204</v>
       </c>
       <c r="C144" s="5">
-        <v>46196.603019988426</v>
+        <v>46196.7696866551</v>
       </c>
       <c r="D144" s="5">
-        <v>46196.60302403935</v>
+        <v>46196.769690706016</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>200</v>
@@ -10060,13 +10060,13 @@
         <v>364</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.43503768518</v>
+        <v>46125.60170435185</v>
       </c>
       <c r="C145" s="8">
-        <v>46196.60302072916</v>
+        <v>46196.769687395834</v>
       </c>
       <c r="D145" s="8">
-        <v>46196.60302447916</v>
+        <v>46196.76969114583</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>200</v>
@@ -10113,13 +10113,13 @@
         <v>365</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.4350728125</v>
+        <v>46125.60173947917</v>
       </c>
       <c r="C146" s="5">
-        <v>46196.60302144676</v>
+        <v>46196.769688113425</v>
       </c>
       <c r="D146" s="5">
-        <v>46196.60302497685</v>
+        <v>46196.76969164352</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>200</v>
@@ -10166,13 +10166,13 @@
         <v>366</v>
       </c>
       <c r="B147" s="8">
-        <v>46122.38508680556</v>
+        <v>46122.551753472224</v>
       </c>
       <c r="C147" s="8">
-        <v>46191.53937342593</v>
+        <v>46191.70604009259</v>
       </c>
       <c r="D147" s="8">
-        <v>46196.60314438658</v>
+        <v>46196.76981105324</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>367</v>
@@ -10229,13 +10229,13 @@
         <v>369</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.43514888889</v>
+        <v>46125.60181555555</v>
       </c>
       <c r="C148" s="5">
-        <v>46196.60312598379</v>
+        <v>46196.76979265046</v>
       </c>
       <c r="D148" s="5">
-        <v>46196.603129027775</v>
+        <v>46196.76979569445</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>200</v>
@@ -10282,13 +10282,13 @@
         <v>370</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.43519024306</v>
+        <v>46125.60185690972</v>
       </c>
       <c r="C149" s="8">
-        <v>46196.603126898146</v>
+        <v>46196.76979356482</v>
       </c>
       <c r="D149" s="8">
-        <v>46196.60312947917</v>
+        <v>46196.76979614583</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>200</v>
@@ -10335,13 +10335,13 @@
         <v>371</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.43523282408</v>
+        <v>46125.601899490735</v>
       </c>
       <c r="C150" s="5">
-        <v>46196.60312755787</v>
+        <v>46196.769794224536</v>
       </c>
       <c r="D150" s="5">
-        <v>46196.603129814815</v>
+        <v>46196.76979648148</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>200</v>
@@ -10388,13 +10388,13 @@
         <v>372</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.43527268519</v>
+        <v>46125.60193935185</v>
       </c>
       <c r="C151" s="8">
-        <v>46196.603098101856</v>
+        <v>46196.76976476852</v>
       </c>
       <c r="D151" s="8">
-        <v>46196.60310020833</v>
+        <v>46196.769766875004</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>200</v>
@@ -10441,13 +10441,13 @@
         <v>373</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.43531043982</v>
+        <v>46125.60197710648</v>
       </c>
       <c r="C152" s="5">
-        <v>46196.603105393515</v>
+        <v>46196.76977206019</v>
       </c>
       <c r="D152" s="5">
-        <v>46196.60310703704</v>
+        <v>46196.76977370371</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>200</v>
@@ -10494,11 +10494,11 @@
         <v>374</v>
       </c>
       <c r="B153" s="8">
-        <v>46122.38509195602</v>
+        <v>46122.551758622685</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46125.422702118056</v>
+        <v>46125.58936878473</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>375</v>
@@ -10541,11 +10541,11 @@
         <v>377</v>
       </c>
       <c r="B154" s="5">
-        <v>46122.38509467593</v>
+        <v>46122.55176134259</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46191.53939100694</v>
+        <v>46191.70605767361</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>378</v>
@@ -10604,11 +10604,11 @@
         <v>381</v>
       </c>
       <c r="B155" s="8">
-        <v>46122.38509943287</v>
+        <v>46122.55176609954</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46192.80717747685</v>
+        <v>46192.97384414352</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>382</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4783,7 +4783,7 @@
         <v>46134.79240423611</v>
       </c>
       <c r="D52" s="5">
-        <v>46190.18859494213</v>
+        <v>46198.18781711806</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4827,8 +4827,8 @@
       <c r="R52" s="5">
         <v>46197</v>
       </c>
-      <c r="S52" s="12" t="s">
-        <v>74</v>
+      <c r="S52" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T52" s="6">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -1847,13 +1847,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46122.55118912037</v>
+        <v>46122.38452245371</v>
       </c>
       <c r="C4" s="5">
-        <v>46128.59300771991</v>
+        <v>46128.426341053244</v>
       </c>
       <c r="D4" s="5">
-        <v>46158.10300121528</v>
+        <v>46157.93633454861</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1896,13 +1896,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46122.55134571759</v>
+        <v>46122.38467905093</v>
       </c>
       <c r="C5" s="8">
-        <v>46128.59299462963</v>
+        <v>46128.42632796297</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.876021724536</v>
+        <v>46133.70935505787</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1959,13 +1959,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46122.55134947917</v>
+        <v>46122.384682812495</v>
       </c>
       <c r="C6" s="5">
-        <v>46128.59267868055</v>
+        <v>46128.42601201389</v>
       </c>
       <c r="D6" s="5">
-        <v>46128.60382631945</v>
+        <v>46128.43715965278</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2022,13 +2022,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46122.551352546296</v>
+        <v>46122.38468587963</v>
       </c>
       <c r="C7" s="8">
-        <v>46128.59269866898</v>
+        <v>46128.42603200232</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.62726047453</v>
+        <v>46161.460593807875</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2085,13 +2085,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46122.551355567135</v>
+        <v>46122.38468890046</v>
       </c>
       <c r="C8" s="5">
-        <v>46128.59271722222</v>
+        <v>46128.42605055556</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.60400607639</v>
+        <v>46128.43733940972</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2148,13 +2148,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46122.551359386576</v>
+        <v>46122.384692719905</v>
       </c>
       <c r="C9" s="8">
-        <v>46128.592850057874</v>
+        <v>46128.4261833912</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.83577310185</v>
+        <v>46156.66910643518</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2211,13 +2211,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46122.55119412037</v>
+        <v>46122.3845274537</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.93280347223</v>
+        <v>46193.766136805556</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.9328209838</v>
+        <v>46193.76615431713</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2264,13 +2264,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46122.5513631713</v>
+        <v>46122.384696504625</v>
       </c>
       <c r="C11" s="8">
-        <v>46128.60435520833</v>
+        <v>46128.43768854167</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.97382803241</v>
+        <v>46192.80716136574</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2329,13 +2329,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46122.551369050925</v>
+        <v>46122.38470238426</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.60643114583</v>
+        <v>46128.43976447917</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.97382813657</v>
+        <v>46192.80716146991</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2394,13 +2394,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46122.5513746875</v>
+        <v>46122.384708020836</v>
       </c>
       <c r="C13" s="8">
-        <v>46132.57072561343</v>
+        <v>46132.40405894676</v>
       </c>
       <c r="D13" s="8">
-        <v>46192.97382800926</v>
+        <v>46192.80716134259</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2459,13 +2459,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46122.553594178244</v>
+        <v>46122.38692751157</v>
       </c>
       <c r="C14" s="5">
-        <v>46128.60941575232</v>
+        <v>46128.44274908565</v>
       </c>
       <c r="D14" s="5">
-        <v>46136.20601917824</v>
+        <v>46136.03935251157</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2524,13 +2524,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46122.55119946759</v>
+        <v>46122.38453280093</v>
       </c>
       <c r="C15" s="8">
-        <v>46195.50723163194</v>
+        <v>46195.34056496528</v>
       </c>
       <c r="D15" s="8">
-        <v>46195.50724608796</v>
+        <v>46195.340579421296</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2577,13 +2577,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46122.55138855324</v>
+        <v>46122.38472188657</v>
       </c>
       <c r="C16" s="5">
-        <v>46128.60700391204</v>
+        <v>46128.44033724537</v>
       </c>
       <c r="D16" s="5">
-        <v>46133.17999505787</v>
+        <v>46133.0133283912</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2642,13 +2642,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46122.55139482639</v>
+        <v>46122.38472815973</v>
       </c>
       <c r="C17" s="8">
-        <v>46128.60701157407</v>
+        <v>46128.44034490741</v>
       </c>
       <c r="D17" s="8">
-        <v>46132.182206921294</v>
+        <v>46132.01554025463</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2707,13 +2707,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46122.55140040509</v>
+        <v>46122.38473373842</v>
       </c>
       <c r="C18" s="5">
-        <v>46195.50721171296</v>
+        <v>46195.340545046296</v>
       </c>
       <c r="D18" s="5">
-        <v>46195.50723229167</v>
+        <v>46195.340565624996</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2772,13 +2772,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46122.55140604167</v>
+        <v>46122.384739375004</v>
       </c>
       <c r="C19" s="8">
-        <v>46181.666399050926</v>
+        <v>46181.499732384254</v>
       </c>
       <c r="D19" s="8">
-        <v>46195.20558476852</v>
+        <v>46195.038918101855</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2837,13 +2837,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46122.55141162037</v>
+        <v>46122.3847449537</v>
       </c>
       <c r="C20" s="5">
-        <v>46128.609497881946</v>
+        <v>46128.442831215274</v>
       </c>
       <c r="D20" s="5">
-        <v>46132.1822065625</v>
+        <v>46132.01553989583</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>64</v>
@@ -2902,13 +2902,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46122.566545787035</v>
+        <v>46122.39987912037</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.66636053241</v>
+        <v>46181.49969386574</v>
       </c>
       <c r="D21" s="8">
-        <v>46195.20558446759</v>
+        <v>46195.03891780092</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2967,13 +2967,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46122.56661521991</v>
+        <v>46122.39994855324</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.66637630787</v>
+        <v>46181.499709641204</v>
       </c>
       <c r="D22" s="5">
-        <v>46195.20558434028</v>
+        <v>46195.038917673606</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3032,13 +3032,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="8">
-        <v>46122.57286273148</v>
+        <v>46122.40619606481</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.66643224537</v>
+        <v>46181.4997655787</v>
       </c>
       <c r="D23" s="8">
-        <v>46195.205584386575</v>
+        <v>46195.03891771991</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -3097,13 +3097,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46122.55120394676</v>
+        <v>46122.38453728009</v>
       </c>
       <c r="C24" s="5">
-        <v>46195.50733982639</v>
+        <v>46195.34067315972</v>
       </c>
       <c r="D24" s="5">
-        <v>46195.50735353009</v>
+        <v>46195.34068686343</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -3150,13 +3150,13 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46122.55141694444</v>
+        <v>46122.38475027778</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.626168703704</v>
+        <v>46174.45950203703</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.626181134256</v>
+        <v>46174.45951446759</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -3215,13 +3215,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46122.55142208333</v>
+        <v>46122.38475541667</v>
       </c>
       <c r="C26" s="5">
-        <v>46174.62325291667</v>
+        <v>46174.45658625</v>
       </c>
       <c r="D26" s="5">
-        <v>46174.62325449074</v>
+        <v>46174.456587824076</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3276,13 +3276,13 @@
         <v>110</v>
       </c>
       <c r="B27" s="8">
-        <v>46122.55142699074</v>
+        <v>46122.38476032407</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.626152893514</v>
+        <v>46174.45948622686</v>
       </c>
       <c r="D27" s="8">
-        <v>46174.62615429398</v>
+        <v>46174.45948762732</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>111</v>
@@ -3337,13 +3337,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46122.5514322338</v>
+        <v>46122.38476556713</v>
       </c>
       <c r="C28" s="5">
-        <v>46195.50732521991</v>
+        <v>46195.340658553236</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.71184679398</v>
+        <v>46195.545180127316</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3402,13 +3402,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="8">
-        <v>46122.551437546295</v>
+        <v>46122.38477087963</v>
       </c>
       <c r="C29" s="8">
-        <v>46195.71138274306</v>
+        <v>46195.54471607639</v>
       </c>
       <c r="D29" s="8">
-        <v>46195.71138517361</v>
+        <v>46195.54471850695</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>118</v>
@@ -3463,13 +3463,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46122.55144255787</v>
+        <v>46122.3847758912</v>
       </c>
       <c r="C30" s="5">
-        <v>46195.711830960645</v>
+        <v>46195.54516429398</v>
       </c>
       <c r="D30" s="5">
-        <v>46195.711832500005</v>
+        <v>46195.54516583333</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3524,13 +3524,13 @@
         <v>123</v>
       </c>
       <c r="B31" s="8">
-        <v>46122.551447708334</v>
+        <v>46122.38478104166</v>
       </c>
       <c r="C31" s="8">
-        <v>46133.82779993056</v>
+        <v>46133.661133263886</v>
       </c>
       <c r="D31" s="8">
-        <v>46133.82781321759</v>
+        <v>46133.66114655093</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>124</v>
@@ -3589,13 +3589,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46122.5514527662</v>
+        <v>46122.38478609954</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.827731122685</v>
+        <v>46133.66106445601</v>
       </c>
       <c r="D32" s="5">
-        <v>46133.82773260417</v>
+        <v>46133.6610659375</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3650,13 +3650,13 @@
         <v>129</v>
       </c>
       <c r="B33" s="8">
-        <v>46122.55145796297</v>
+        <v>46122.384791296296</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.827786875</v>
+        <v>46133.66112020833</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.82778807871</v>
+        <v>46133.661121412035</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>130</v>
@@ -3711,13 +3711,13 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46122.55146299768</v>
+        <v>46122.38479633102</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.82776796297</v>
+        <v>46133.6611012963</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.827769131945</v>
+        <v>46133.66110246528</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3772,13 +3772,13 @@
         <v>135</v>
       </c>
       <c r="B35" s="8">
-        <v>46122.55146795139</v>
+        <v>46122.38480128472</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.66687207176</v>
+        <v>46181.50020540509</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.66688577546</v>
+        <v>46181.5002191088</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3837,13 +3837,13 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46122.551472974534</v>
+        <v>46122.38480630787</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.66681767361</v>
+        <v>46181.50015100694</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.66681946759</v>
+        <v>46181.50015280093</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3898,13 +3898,13 @@
         <v>143</v>
       </c>
       <c r="B37" s="8">
-        <v>46122.55152253472</v>
+        <v>46122.384855868055</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.66685679398</v>
+        <v>46181.50019012731</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.66685818287</v>
+        <v>46181.5001915162</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>144</v>
@@ -3959,13 +3959,13 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46122.55152891204</v>
+        <v>46122.384862245366</v>
       </c>
       <c r="C38" s="5">
-        <v>46154.867667812505</v>
+        <v>46154.70100114583</v>
       </c>
       <c r="D38" s="5">
-        <v>46189.172213136575</v>
+        <v>46189.00554646991</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -4024,13 +4024,13 @@
         <v>149</v>
       </c>
       <c r="B39" s="8">
-        <v>46122.5515340625</v>
+        <v>46122.384867395835</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.86751693287</v>
+        <v>46154.70085026621</v>
       </c>
       <c r="D39" s="8">
-        <v>46154.86751927083</v>
+        <v>46154.70085260417</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>87</v>
@@ -4079,13 +4079,13 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46122.55153844907</v>
+        <v>46122.38487178241</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.867576273144</v>
+        <v>46154.70090960649</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.867577453704</v>
+        <v>46154.70091078704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4134,13 +4134,13 @@
         <v>154</v>
       </c>
       <c r="B41" s="8">
-        <v>46122.574933449076</v>
+        <v>46122.40826678241</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.666767002316</v>
+        <v>46181.500100335645</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.666783252316</v>
+        <v>46181.50011658565</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>155</v>
@@ -4199,13 +4199,13 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46122.575920972224</v>
+        <v>46122.40925430556</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.66670739584</v>
+        <v>46181.500040729166</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.66670855324</v>
+        <v>46181.500041886575</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>90</v>
@@ -4254,13 +4254,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46122.57608475695</v>
+        <v>46122.409418090276</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.666752812496</v>
+        <v>46181.50008614583</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.666754351856</v>
+        <v>46181.500087685185</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4309,13 +4309,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46122.57501438657</v>
+        <v>46122.40834771991</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.666958472226</v>
+        <v>46181.500291805554</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.66706865741</v>
+        <v>46181.500401990736</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4374,13 +4374,13 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46122.57922111111</v>
+        <v>46122.41255444444</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.666901516204</v>
+        <v>46181.50023484953</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.66690306713</v>
+        <v>46181.50023640046</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>96</v>
@@ -4429,13 +4429,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46122.57949202546</v>
+        <v>46122.4128253588</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.66694322917</v>
+        <v>46181.500276562496</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.66694460648</v>
+        <v>46181.50027793982</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4484,13 +4484,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46125.529618217595</v>
+        <v>46125.362951550924</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.66722120371</v>
+        <v>46181.50055453704</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.66723511574</v>
+        <v>46181.500568449075</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4549,13 +4549,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46125.52977997685</v>
+        <v>46125.36311331019</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.66715732639</v>
+        <v>46181.50049065972</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.66715912037</v>
+        <v>46181.500492453706</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>93</v>
@@ -4604,13 +4604,13 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46125.52991815972</v>
+        <v>46125.36325149305</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.66720412037</v>
+        <v>46181.5005374537</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.66720563658</v>
+        <v>46181.50053896991</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4659,13 +4659,13 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46122.55120855324</v>
+        <v>46122.384541886575</v>
       </c>
       <c r="C50" s="5">
-        <v>46195.5074512963</v>
+        <v>46195.34078462963</v>
       </c>
       <c r="D50" s="5">
-        <v>46195.50756488426</v>
+        <v>46195.34089821759</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4712,13 +4712,13 @@
         <v>183</v>
       </c>
       <c r="B51" s="8">
-        <v>46122.55154344907</v>
+        <v>46122.38487678241</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.79584481481</v>
+        <v>46133.62917814815</v>
       </c>
       <c r="D51" s="8">
-        <v>46143.171145879634</v>
+        <v>46143.00447921296</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>184</v>
@@ -4777,13 +4777,13 @@
         <v>188</v>
       </c>
       <c r="B52" s="5">
-        <v>46122.551548993055</v>
+        <v>46122.38488232639</v>
       </c>
       <c r="C52" s="5">
-        <v>46134.79240423611</v>
+        <v>46134.62573756944</v>
       </c>
       <c r="D52" s="5">
-        <v>46198.18781711806</v>
+        <v>46198.021150451386</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4842,13 +4842,13 @@
         <v>192</v>
       </c>
       <c r="B53" s="8">
-        <v>46122.55155721065</v>
+        <v>46122.38489054398</v>
       </c>
       <c r="C53" s="8">
-        <v>46134.79245146991</v>
+        <v>46134.62578480324</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.18981792824</v>
+        <v>46191.02315126157</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>83</v>
@@ -4905,13 +4905,13 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46122.55156568287</v>
+        <v>46122.38489901621</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.50761325231</v>
+        <v>46195.34094658565</v>
       </c>
       <c r="D54" s="5">
-        <v>46196.76907818287</v>
+        <v>46196.6024115162</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -4968,13 +4968,13 @@
         <v>199</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.603622118055</v>
+        <v>46125.43695545139</v>
       </c>
       <c r="C55" s="8">
-        <v>46196.76904752315</v>
+        <v>46196.60238085648</v>
       </c>
       <c r="D55" s="8">
-        <v>46196.7690521412</v>
+        <v>46196.602385474536</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>200</v>
@@ -5021,13 +5021,13 @@
         <v>202</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.60367094907</v>
+        <v>46125.43700428241</v>
       </c>
       <c r="C56" s="5">
-        <v>46196.769048449074</v>
+        <v>46196.6023817824</v>
       </c>
       <c r="D56" s="5">
-        <v>46196.769052523145</v>
+        <v>46196.60238585648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -5074,13 +5074,13 @@
         <v>203</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.60371951389</v>
+        <v>46125.43705284722</v>
       </c>
       <c r="C57" s="8">
-        <v>46196.76904929398</v>
+        <v>46196.602382627316</v>
       </c>
       <c r="D57" s="8">
-        <v>46196.76905283565</v>
+        <v>46196.60238616898</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5127,13 +5127,13 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.60376462963</v>
+        <v>46125.43709796296</v>
       </c>
       <c r="C58" s="5">
-        <v>46196.769050069444</v>
+        <v>46196.60238340277</v>
       </c>
       <c r="D58" s="5">
-        <v>46196.76905314815</v>
+        <v>46196.60238648148</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>200</v>
@@ -5180,13 +5180,13 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.60381739584</v>
+        <v>46125.437150729165</v>
       </c>
       <c r="C59" s="8">
-        <v>46196.76905077546</v>
+        <v>46196.602384108795</v>
       </c>
       <c r="D59" s="8">
-        <v>46196.76905349537</v>
+        <v>46196.6023868287</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>200</v>
@@ -5233,13 +5233,13 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46122.551569710646</v>
+        <v>46122.38490304398</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.6677724537</v>
+        <v>46181.501105787036</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.66785324074</v>
+        <v>46181.501186574074</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5282,13 +5282,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46122.55157321759</v>
+        <v>46122.38490655093</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.667378032405</v>
+        <v>46181.50071136574</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.66739524306</v>
+        <v>46181.500728576386</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5347,13 +5347,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46122.58491638889</v>
+        <v>46122.41824972222</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.667413206014</v>
+        <v>46181.50074653935</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.667429016205</v>
+        <v>46181.50076234953</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5412,13 +5412,13 @@
         <v>217</v>
       </c>
       <c r="B63" s="8">
-        <v>46125.53102658565</v>
+        <v>46125.36435991898</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.667430127316</v>
+        <v>46181.500763460645</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.66744925926</v>
+        <v>46181.50078259259</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -5477,13 +5477,13 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46122.55157846065</v>
+        <v>46122.38491179398</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.66775587963</v>
+        <v>46181.501089212965</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.66777241898</v>
+        <v>46181.501105752315</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5542,13 +5542,13 @@
         <v>225</v>
       </c>
       <c r="B65" s="8">
-        <v>46122.551583831024</v>
+        <v>46122.38491716435</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.6687946875</v>
+        <v>46181.50212802083</v>
       </c>
       <c r="D65" s="8">
-        <v>46181.66890770833</v>
+        <v>46181.50224104167</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>226</v>
@@ -5591,13 +5591,13 @@
         <v>228</v>
       </c>
       <c r="B66" s="5">
-        <v>46122.55158688658</v>
+        <v>46122.384920219905</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.666093576394</v>
+        <v>46181.49942690972</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.66880932871</v>
+        <v>46181.50214266204</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>229</v>
@@ -5656,13 +5656,13 @@
         <v>233</v>
       </c>
       <c r="B67" s="8">
-        <v>46122.55159185185</v>
+        <v>46122.384925185186</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.6661986574</v>
+        <v>46181.49953199074</v>
       </c>
       <c r="D67" s="8">
-        <v>46181.668846064815</v>
+        <v>46181.50217939814</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>234</v>
@@ -5721,13 +5721,13 @@
         <v>236</v>
       </c>
       <c r="B68" s="5">
-        <v>46125.595811921296</v>
+        <v>46125.42914525463</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.66807699074</v>
+        <v>46181.501410324076</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.66807884259</v>
+        <v>46181.50141217593</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>237</v>
@@ -5776,13 +5776,13 @@
         <v>240</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.59610047453</v>
+        <v>46125.42943380787</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.66808581019</v>
+        <v>46181.50141914352</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.66808728009</v>
+        <v>46181.50142061342</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>200</v>
@@ -5831,13 +5831,13 @@
         <v>241</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.59621038195</v>
+        <v>46125.429543715276</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.66815399306</v>
+        <v>46181.501487326386</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.66815550926</v>
+        <v>46181.501488842594</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>200</v>
@@ -5886,13 +5886,13 @@
         <v>242</v>
       </c>
       <c r="B71" s="8">
-        <v>46125.59625472222</v>
+        <v>46125.42958805556</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.668166689815</v>
+        <v>46181.50150002315</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.66816819445</v>
+        <v>46181.501501527775</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>200</v>
@@ -5941,13 +5941,13 @@
         <v>243</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.59629915509</v>
+        <v>46125.42963248843</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.66817956018</v>
+        <v>46181.50151289352</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.66818078703</v>
+        <v>46181.50151412037</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>200</v>
@@ -5996,13 +5996,13 @@
         <v>244</v>
       </c>
       <c r="B73" s="8">
-        <v>46122.55159751157</v>
+        <v>46122.384930844906</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.66878061343</v>
+        <v>46181.50211394676</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.66878222222</v>
+        <v>46181.50211555556</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>245</v>
@@ -6061,13 +6061,13 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46125.59648849537</v>
+        <v>46125.4298218287</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.668651921296</v>
+        <v>46181.501985254625</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.6686533912</v>
+        <v>46181.501986724536</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>200</v>
@@ -6116,13 +6116,13 @@
         <v>249</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.59661854166</v>
+        <v>46125.429951875005</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.66866650463</v>
+        <v>46181.50199983796</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.66866782407</v>
+        <v>46181.50200115741</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>200</v>
@@ -6171,13 +6171,13 @@
         <v>251</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.596668750004</v>
+        <v>46125.43000208333</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.66867587963</v>
+        <v>46181.50200921296</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.66867745371</v>
+        <v>46181.50201078704</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>200</v>
@@ -6226,13 +6226,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="8">
-        <v>46125.59671550926</v>
+        <v>46125.430048842594</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.668685625</v>
+        <v>46181.50201895833</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.668687060184</v>
+        <v>46181.50202039352</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>200</v>
@@ -6281,13 +6281,13 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.59675546296</v>
+        <v>46125.430088796296</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.66870385417</v>
+        <v>46181.5020371875</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.66870502315</v>
+        <v>46181.502038356484</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>200</v>
@@ -6336,13 +6336,13 @@
         <v>255</v>
       </c>
       <c r="B79" s="8">
-        <v>46122.55160357639</v>
+        <v>46122.38493690972</v>
       </c>
       <c r="C79" s="8">
-        <v>46195.563125636574</v>
+        <v>46195.3964589699</v>
       </c>
       <c r="D79" s="8">
-        <v>46195.563290335645</v>
+        <v>46195.39662366898</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>207</v>
@@ -6389,13 +6389,13 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46122.55160679398</v>
+        <v>46122.38494012732</v>
       </c>
       <c r="C80" s="5">
-        <v>46195.563269363425</v>
+        <v>46195.39660269676</v>
       </c>
       <c r="D80" s="5">
-        <v>46195.711846817125</v>
+        <v>46195.54518015047</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6454,13 +6454,13 @@
         <v>260</v>
       </c>
       <c r="B81" s="8">
-        <v>46122.551612256946</v>
+        <v>46122.38494559028</v>
       </c>
       <c r="C81" s="8">
-        <v>46195.50751318287</v>
+        <v>46195.34084651621</v>
       </c>
       <c r="D81" s="8">
-        <v>46195.50753130787</v>
+        <v>46195.3408646412</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>261</v>
@@ -6519,13 +6519,13 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46122.55161756944</v>
+        <v>46122.38495090278</v>
       </c>
       <c r="C82" s="5">
-        <v>46195.50751851852</v>
+        <v>46195.340851851855</v>
       </c>
       <c r="D82" s="5">
-        <v>46195.50753259259</v>
+        <v>46195.34086592593</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6584,13 +6584,13 @@
         <v>264</v>
       </c>
       <c r="B83" s="8">
-        <v>46122.55162288195</v>
+        <v>46122.384956215275</v>
       </c>
       <c r="C83" s="8">
-        <v>46195.507523437496</v>
+        <v>46195.34085677083</v>
       </c>
       <c r="D83" s="8">
-        <v>46195.507539479164</v>
+        <v>46195.3408728125</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>265</v>
@@ -6649,13 +6649,13 @@
         <v>266</v>
       </c>
       <c r="B84" s="5">
-        <v>46122.59399163195</v>
+        <v>46122.427324965276</v>
       </c>
       <c r="C84" s="5">
-        <v>46193.93315311342</v>
+        <v>46193.76648644676</v>
       </c>
       <c r="D84" s="5">
-        <v>46193.9332800463</v>
+        <v>46193.76661337963</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>267</v>
@@ -6714,13 +6714,13 @@
         <v>269</v>
       </c>
       <c r="B85" s="8">
-        <v>46122.551628182875</v>
+        <v>46122.3849615162</v>
       </c>
       <c r="C85" s="8">
-        <v>46195.5630599537</v>
+        <v>46195.39639328704</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.769192685184</v>
+        <v>46196.60252601852</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>270</v>
@@ -6767,13 +6767,13 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46122.55163158565</v>
+        <v>46122.38496491898</v>
       </c>
       <c r="C86" s="5">
-        <v>46195.50768850694</v>
+        <v>46195.34102184028</v>
       </c>
       <c r="D86" s="5">
-        <v>46195.507707129625</v>
+        <v>46195.34104046296</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>273</v>
@@ -6832,13 +6832,13 @@
         <v>275</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.5974969213</v>
+        <v>46125.43083025463</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.76791707176</v>
+        <v>46196.60125040509</v>
       </c>
       <c r="D87" s="8">
-        <v>46196.767918831014</v>
+        <v>46196.60125216436</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>200</v>
@@ -6887,13 +6887,13 @@
         <v>277</v>
       </c>
       <c r="B88" s="5">
-        <v>46125.59754570602</v>
+        <v>46125.430879039355</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.76795405093</v>
+        <v>46196.601287384256</v>
       </c>
       <c r="D88" s="5">
-        <v>46196.76795645834</v>
+        <v>46196.601289791666</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>200</v>
@@ -6942,13 +6942,13 @@
         <v>278</v>
       </c>
       <c r="B89" s="8">
-        <v>46125.59760710648</v>
+        <v>46125.430940439815</v>
       </c>
       <c r="C89" s="8">
-        <v>46196.767928217596</v>
+        <v>46196.601261550924</v>
       </c>
       <c r="D89" s="8">
-        <v>46196.76793001157</v>
+        <v>46196.601263344906</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>200</v>
@@ -6997,13 +6997,13 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46125.59765891204</v>
+        <v>46125.43099224537</v>
       </c>
       <c r="C90" s="5">
-        <v>46196.76794651621</v>
+        <v>46196.601279849536</v>
       </c>
       <c r="D90" s="5">
-        <v>46196.76794809027</v>
+        <v>46196.60128142362</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>200</v>
@@ -7052,13 +7052,13 @@
         <v>280</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.597703391206</v>
+        <v>46125.431036724534</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.76794100694</v>
+        <v>46196.60127434028</v>
       </c>
       <c r="D91" s="8">
-        <v>46196.76794287037</v>
+        <v>46196.6012762037</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>200</v>
@@ -7107,13 +7107,13 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46122.55170659722</v>
+        <v>46122.38503993055</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.76755512731</v>
+        <v>46196.60088846065</v>
       </c>
       <c r="D92" s="5">
-        <v>46196.76807780092</v>
+        <v>46196.60141113426</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>282</v>
@@ -7172,13 +7172,13 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46125.59982741898</v>
+        <v>46125.43316075232</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.76800195602</v>
+        <v>46196.60133528935</v>
       </c>
       <c r="D93" s="8">
-        <v>46196.76800386574</v>
+        <v>46196.60133719907</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>200</v>
@@ -7227,13 +7227,13 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.599890833335</v>
+        <v>46125.43322416667</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.768023020835</v>
+        <v>46196.601356354164</v>
       </c>
       <c r="D94" s="5">
-        <v>46196.768024687495</v>
+        <v>46196.60135802084</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>200</v>
@@ -7282,13 +7282,13 @@
         <v>288</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.59993134259</v>
+        <v>46125.43326467593</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.76801494213</v>
+        <v>46196.601348275464</v>
       </c>
       <c r="D95" s="8">
-        <v>46196.76801675926</v>
+        <v>46196.60135009259</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>200</v>
@@ -7337,13 +7337,13 @@
         <v>289</v>
       </c>
       <c r="B96" s="5">
-        <v>46125.59996929398</v>
+        <v>46125.433302627316</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.76805109954</v>
+        <v>46196.60138443287</v>
       </c>
       <c r="D96" s="5">
-        <v>46196.76805278935</v>
+        <v>46196.60138612268</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>200</v>
@@ -7392,13 +7392,13 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46125.6000115162</v>
+        <v>46125.43334484954</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.76805706018</v>
+        <v>46196.60139039352</v>
       </c>
       <c r="D97" s="8">
-        <v>46196.76805907408</v>
+        <v>46196.60139240741</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>200</v>
@@ -7447,13 +7447,13 @@
         <v>291</v>
       </c>
       <c r="B98" s="5">
-        <v>46122.55164413195</v>
+        <v>46122.38497746528</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.76839824074</v>
+        <v>46196.601731574076</v>
       </c>
       <c r="D98" s="5">
-        <v>46196.76840872686</v>
+        <v>46196.601742060186</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>292</v>
@@ -7512,13 +7512,13 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46125.599162743056</v>
+        <v>46125.43249607639</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.76818966435</v>
+        <v>46196.601522997684</v>
       </c>
       <c r="D99" s="8">
-        <v>46196.7681912963</v>
+        <v>46196.60152462963</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>200</v>
@@ -7567,13 +7567,13 @@
         <v>297</v>
       </c>
       <c r="B100" s="5">
-        <v>46125.599302511575</v>
+        <v>46125.4326358449</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.76820421296</v>
+        <v>46196.601537546296</v>
       </c>
       <c r="D100" s="5">
-        <v>46196.76820597222</v>
+        <v>46196.60153930556</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>200</v>
@@ -7622,13 +7622,13 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46125.59934644676</v>
+        <v>46125.43267978009</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.768375949076</v>
+        <v>46196.601709282404</v>
       </c>
       <c r="D101" s="8">
-        <v>46196.76837958333</v>
+        <v>46196.60171291667</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>200</v>
@@ -7677,13 +7677,13 @@
         <v>299</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.59938857639</v>
+        <v>46125.43272190972</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.76837696759</v>
+        <v>46196.60171030092</v>
       </c>
       <c r="D102" s="5">
-        <v>46196.76838008102</v>
+        <v>46196.60171341435</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>200</v>
@@ -7732,13 +7732,13 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46125.59943094908</v>
+        <v>46125.43276428241</v>
       </c>
       <c r="C103" s="8">
-        <v>46196.76837790509</v>
+        <v>46196.60171123843</v>
       </c>
       <c r="D103" s="8">
-        <v>46196.768380520836</v>
+        <v>46196.601713854165</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>200</v>
@@ -7787,13 +7787,13 @@
         <v>301</v>
       </c>
       <c r="B104" s="5">
-        <v>46122.551650995374</v>
+        <v>46122.3849843287</v>
       </c>
       <c r="C104" s="5">
-        <v>46196.76854788195</v>
+        <v>46196.601881215276</v>
       </c>
       <c r="D104" s="5">
-        <v>46196.76856074074</v>
+        <v>46196.601894074076</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>302</v>
@@ -7852,13 +7852,13 @@
         <v>303</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.59953013889</v>
+        <v>46125.43286347222</v>
       </c>
       <c r="C105" s="8">
-        <v>46196.76852783565</v>
+        <v>46196.60186116898</v>
       </c>
       <c r="D105" s="8">
-        <v>46196.768531724534</v>
+        <v>46196.60186505787</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>200</v>
@@ -7907,13 +7907,13 @@
         <v>305</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.59961423611</v>
+        <v>46125.43294756944</v>
       </c>
       <c r="C106" s="5">
-        <v>46196.76846329861</v>
+        <v>46196.60179663195</v>
       </c>
       <c r="D106" s="5">
-        <v>46196.76846496528</v>
+        <v>46196.60179829861</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>200</v>
@@ -7962,13 +7962,13 @@
         <v>306</v>
       </c>
       <c r="B107" s="8">
-        <v>46125.599654317135</v>
+        <v>46125.43298765046</v>
       </c>
       <c r="C107" s="8">
-        <v>46196.768528796296</v>
+        <v>46196.601862129624</v>
       </c>
       <c r="D107" s="8">
-        <v>46196.76853203704</v>
+        <v>46196.601865370365</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>200</v>
@@ -8017,13 +8017,13 @@
         <v>307</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.59957065972</v>
+        <v>46125.43290399306</v>
       </c>
       <c r="C108" s="5">
-        <v>46196.768529548615</v>
+        <v>46196.601862881944</v>
       </c>
       <c r="D108" s="5">
-        <v>46196.76853233796</v>
+        <v>46196.6018656713</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>200</v>
@@ -8072,13 +8072,13 @@
         <v>308</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.59969711806</v>
+        <v>46125.433030451386</v>
       </c>
       <c r="C109" s="8">
-        <v>46196.7685304051</v>
+        <v>46196.601863738426</v>
       </c>
       <c r="D109" s="8">
-        <v>46196.76853265046</v>
+        <v>46196.6018659838</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>200</v>
@@ -8127,13 +8127,13 @@
         <v>309</v>
       </c>
       <c r="B110" s="5">
-        <v>46122.55163725694</v>
+        <v>46122.38497059028</v>
       </c>
       <c r="C110" s="5">
-        <v>46196.76866755787</v>
+        <v>46196.6020008912</v>
       </c>
       <c r="D110" s="5">
-        <v>46196.76867908565</v>
+        <v>46196.60201241898</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>310</v>
@@ -8192,13 +8192,13 @@
         <v>311</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.59780210648</v>
+        <v>46125.431135439816</v>
       </c>
       <c r="C111" s="8">
-        <v>46196.76864902778</v>
+        <v>46196.60198236111</v>
       </c>
       <c r="D111" s="8">
-        <v>46196.76865387731</v>
+        <v>46196.60198721065</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>200</v>
@@ -8247,13 +8247,13 @@
         <v>314</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.597836932866</v>
+        <v>46125.43117026621</v>
       </c>
       <c r="C112" s="5">
-        <v>46196.76865</v>
+        <v>46196.601983333334</v>
       </c>
       <c r="D112" s="5">
-        <v>46196.76865427083</v>
+        <v>46196.60198760417</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>200</v>
@@ -8302,13 +8302,13 @@
         <v>315</v>
       </c>
       <c r="B113" s="8">
-        <v>46125.5979208912</v>
+        <v>46125.43125422453</v>
       </c>
       <c r="C113" s="8">
-        <v>46196.76865077546</v>
+        <v>46196.6019841088</v>
       </c>
       <c r="D113" s="8">
-        <v>46196.76865460648</v>
+        <v>46196.601987939815</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>200</v>
@@ -8357,13 +8357,13 @@
         <v>316</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.59788087963</v>
+        <v>46125.431214212964</v>
       </c>
       <c r="C114" s="5">
-        <v>46196.768651527775</v>
+        <v>46196.60198486111</v>
       </c>
       <c r="D114" s="5">
-        <v>46196.768654942134</v>
+        <v>46196.60198827546</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>200</v>
@@ -8412,13 +8412,13 @@
         <v>317</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.597965023146</v>
+        <v>46125.43129835648</v>
       </c>
       <c r="C115" s="8">
-        <v>46196.768652314815</v>
+        <v>46196.60198564814</v>
       </c>
       <c r="D115" s="8">
-        <v>46196.768655312495</v>
+        <v>46196.60198864584</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>200</v>
@@ -8467,13 +8467,13 @@
         <v>318</v>
       </c>
       <c r="B116" s="5">
-        <v>46122.55172043982</v>
+        <v>46122.38505377315</v>
       </c>
       <c r="C116" s="5">
-        <v>46196.76877224537</v>
+        <v>46196.6021055787</v>
       </c>
       <c r="D116" s="5">
-        <v>46196.768798784724</v>
+        <v>46196.60213211806</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>319</v>
@@ -8532,13 +8532,13 @@
         <v>320</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.60038253472</v>
+        <v>46125.43371586806</v>
       </c>
       <c r="C117" s="8">
-        <v>46196.76875258102</v>
+        <v>46196.602085914354</v>
       </c>
       <c r="D117" s="8">
-        <v>46196.768757337966</v>
+        <v>46196.602090671295</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>200</v>
@@ -8585,13 +8585,13 @@
         <v>322</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.60043012731</v>
+        <v>46125.43376346065</v>
       </c>
       <c r="C118" s="5">
-        <v>46196.7687534838</v>
+        <v>46196.60208681713</v>
       </c>
       <c r="D118" s="5">
-        <v>46196.76875768519</v>
+        <v>46196.60209101852</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>200</v>
@@ -8638,13 +8638,13 @@
         <v>323</v>
       </c>
       <c r="B119" s="8">
-        <v>46125.60047290509</v>
+        <v>46125.43380623843</v>
       </c>
       <c r="C119" s="8">
-        <v>46196.768754178236</v>
+        <v>46196.60208751158</v>
       </c>
       <c r="D119" s="8">
-        <v>46196.76875800926</v>
+        <v>46196.60209134259</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>200</v>
@@ -8691,13 +8691,13 @@
         <v>324</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.600514074074</v>
+        <v>46125.4338474074</v>
       </c>
       <c r="C120" s="5">
-        <v>46196.768754930556</v>
+        <v>46196.602088263884</v>
       </c>
       <c r="D120" s="5">
-        <v>46196.76875832176</v>
+        <v>46196.60209165509</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>200</v>
@@ -8744,13 +8744,13 @@
         <v>325</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.60055859954</v>
+        <v>46125.43389193287</v>
       </c>
       <c r="C121" s="8">
-        <v>46196.7687558912</v>
+        <v>46196.602089224536</v>
       </c>
       <c r="D121" s="8">
-        <v>46196.76875862268</v>
+        <v>46196.60209195602</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>200</v>
@@ -8797,13 +8797,13 @@
         <v>326</v>
       </c>
       <c r="B122" s="5">
-        <v>46122.55172986111</v>
+        <v>46122.385063194444</v>
       </c>
       <c r="C122" s="5">
-        <v>46196.76917457176</v>
+        <v>46196.60250790509</v>
       </c>
       <c r="D122" s="5">
-        <v>46196.76918584491</v>
+        <v>46196.60251917824</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>327</v>
@@ -8862,13 +8862,13 @@
         <v>329</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.60064416667</v>
+        <v>46125.4339775</v>
       </c>
       <c r="C123" s="8">
-        <v>46196.76915099537</v>
+        <v>46196.6024843287</v>
       </c>
       <c r="D123" s="8">
-        <v>46196.76915743056</v>
+        <v>46196.60249076389</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>200</v>
@@ -8915,13 +8915,13 @@
         <v>331</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.60068740741</v>
+        <v>46125.43402074074</v>
       </c>
       <c r="C124" s="5">
-        <v>46196.76915237268</v>
+        <v>46196.60248570602</v>
       </c>
       <c r="D124" s="5">
-        <v>46196.76915791667</v>
+        <v>46196.60249125</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>200</v>
@@ -8968,13 +8968,13 @@
         <v>332</v>
       </c>
       <c r="B125" s="8">
-        <v>46125.60073844907</v>
+        <v>46125.43407178241</v>
       </c>
       <c r="C125" s="8">
-        <v>46196.76915341435</v>
+        <v>46196.60248674768</v>
       </c>
       <c r="D125" s="8">
-        <v>46196.76915841435</v>
+        <v>46196.60249174769</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>200</v>
@@ -9021,13 +9021,13 @@
         <v>333</v>
       </c>
       <c r="B126" s="5">
-        <v>46125.60077622686</v>
+        <v>46125.434109560185</v>
       </c>
       <c r="C126" s="5">
-        <v>46196.76915438657</v>
+        <v>46196.60248771991</v>
       </c>
       <c r="D126" s="5">
-        <v>46196.769158842595</v>
+        <v>46196.60249217592</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>200</v>
@@ -9074,13 +9074,13 @@
         <v>334</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.600829143514</v>
+        <v>46125.43416247686</v>
       </c>
       <c r="C127" s="8">
-        <v>46196.769155358794</v>
+        <v>46196.60248869213</v>
       </c>
       <c r="D127" s="8">
-        <v>46196.76915931713</v>
+        <v>46196.60249265046</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>200</v>
@@ -9127,13 +9127,13 @@
         <v>335</v>
       </c>
       <c r="B128" s="5">
-        <v>46122.5517350463</v>
+        <v>46122.38506837963</v>
       </c>
       <c r="C128" s="5">
-        <v>46195.56317517361</v>
+        <v>46195.39650850694</v>
       </c>
       <c r="D128" s="5">
-        <v>46196.76960409722</v>
+        <v>46196.60293743055</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>336</v>
@@ -9180,13 +9180,13 @@
         <v>338</v>
       </c>
       <c r="B129" s="8">
-        <v>46122.5517390625</v>
+        <v>46122.38507239583</v>
       </c>
       <c r="C129" s="8">
-        <v>46196.76936652778</v>
+        <v>46196.60269986111</v>
       </c>
       <c r="D129" s="8">
-        <v>46196.76939736111</v>
+        <v>46196.602730694445</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>339</v>
@@ -9245,13 +9245,13 @@
         <v>343</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.60093731481</v>
+        <v>46125.43427064815</v>
       </c>
       <c r="C130" s="5">
-        <v>46196.76934515046</v>
+        <v>46196.602678483796</v>
       </c>
       <c r="D130" s="5">
-        <v>46196.769350682865</v>
+        <v>46196.60268401621</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>200</v>
@@ -9298,13 +9298,13 @@
         <v>345</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.601380821754</v>
+        <v>46125.4347141551</v>
       </c>
       <c r="C131" s="8">
-        <v>46196.769346307876</v>
+        <v>46196.602679641204</v>
       </c>
       <c r="D131" s="8">
-        <v>46196.769351145835</v>
+        <v>46196.60268447916</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>200</v>
@@ -9351,13 +9351,13 @@
         <v>346</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.60142481481</v>
+        <v>46125.43475814815</v>
       </c>
       <c r="C132" s="5">
-        <v>46196.7693472338</v>
+        <v>46196.60268056713</v>
       </c>
       <c r="D132" s="5">
-        <v>46196.76935155093</v>
+        <v>46196.60268488426</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>200</v>
@@ -9404,13 +9404,13 @@
         <v>347</v>
       </c>
       <c r="B133" s="8">
-        <v>46125.60146085648</v>
+        <v>46125.434794189816</v>
       </c>
       <c r="C133" s="8">
-        <v>46196.769348125</v>
+        <v>46196.60268145833</v>
       </c>
       <c r="D133" s="8">
-        <v>46196.76935192129</v>
+        <v>46196.602685254635</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>200</v>
@@ -9457,13 +9457,13 @@
         <v>348</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.60150208333</v>
+        <v>46125.434835416665</v>
       </c>
       <c r="C134" s="5">
-        <v>46196.769348981485</v>
+        <v>46196.60268231481</v>
       </c>
       <c r="D134" s="5">
-        <v>46196.76935229167</v>
+        <v>46196.602685624996</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>200</v>
@@ -9510,13 +9510,13 @@
         <v>349</v>
       </c>
       <c r="B135" s="8">
-        <v>46122.55174383102</v>
+        <v>46122.38507716435</v>
       </c>
       <c r="C135" s="8">
-        <v>46196.769596921295</v>
+        <v>46196.60293025463</v>
       </c>
       <c r="D135" s="8">
-        <v>46196.76961396991</v>
+        <v>46196.60294730324</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>350</v>
@@ -9573,13 +9573,13 @@
         <v>351</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.601086979164</v>
+        <v>46125.4344203125</v>
       </c>
       <c r="C136" s="5">
-        <v>46196.76947155093</v>
+        <v>46196.602804884256</v>
       </c>
       <c r="D136" s="5">
-        <v>46196.76947347222</v>
+        <v>46196.60280680556</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>200</v>
@@ -9626,13 +9626,13 @@
         <v>353</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.60115318287</v>
+        <v>46125.4344865162</v>
       </c>
       <c r="C137" s="8">
-        <v>46196.7695043287</v>
+        <v>46196.60283766204</v>
       </c>
       <c r="D137" s="8">
-        <v>46196.76950902778</v>
+        <v>46196.60284236111</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>200</v>
@@ -9679,13 +9679,13 @@
         <v>354</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.60120391204</v>
+        <v>46125.43453724537</v>
       </c>
       <c r="C138" s="5">
-        <v>46196.76950549769</v>
+        <v>46196.60283883102</v>
       </c>
       <c r="D138" s="5">
-        <v>46196.76950944445</v>
+        <v>46196.60284277778</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>200</v>
@@ -9732,13 +9732,13 @@
         <v>355</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.60125796296</v>
+        <v>46125.434591296296</v>
       </c>
       <c r="C139" s="8">
-        <v>46196.76950637731</v>
+        <v>46196.60283971065</v>
       </c>
       <c r="D139" s="8">
-        <v>46196.76950987268</v>
+        <v>46196.60284320602</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>200</v>
@@ -9785,13 +9785,13 @@
         <v>356</v>
       </c>
       <c r="B140" s="5">
-        <v>46125.601304282405</v>
+        <v>46125.43463761574</v>
       </c>
       <c r="C140" s="5">
-        <v>46196.76950730324</v>
+        <v>46196.60284063657</v>
       </c>
       <c r="D140" s="5">
-        <v>46196.769510266204</v>
+        <v>46196.60284359954</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>200</v>
@@ -9838,13 +9838,13 @@
         <v>357</v>
       </c>
       <c r="B141" s="8">
-        <v>46122.55174869213</v>
+        <v>46122.38508202546</v>
       </c>
       <c r="C141" s="8">
-        <v>46191.70598530093</v>
+        <v>46191.539318634255</v>
       </c>
       <c r="D141" s="8">
-        <v>46196.769715787035</v>
+        <v>46196.60304912037</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>358</v>
@@ -9901,13 +9901,13 @@
         <v>359</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.60158650463</v>
+        <v>46125.434919837964</v>
       </c>
       <c r="C142" s="5">
-        <v>46196.76968462963</v>
+        <v>46196.60301796296</v>
       </c>
       <c r="D142" s="5">
-        <v>46196.76968989584</v>
+        <v>46196.60302322917</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>200</v>
@@ -9954,13 +9954,13 @@
         <v>361</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.60163133102</v>
+        <v>46125.43496466435</v>
       </c>
       <c r="C143" s="8">
-        <v>46196.76968585648</v>
+        <v>46196.60301918982</v>
       </c>
       <c r="D143" s="8">
-        <v>46196.7696903125</v>
+        <v>46196.60302364583</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>200</v>
@@ -10007,13 +10007,13 @@
         <v>362</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.60167016204</v>
+        <v>46125.43500349537</v>
       </c>
       <c r="C144" s="5">
-        <v>46196.7696866551</v>
+        <v>46196.603019988426</v>
       </c>
       <c r="D144" s="5">
-        <v>46196.769690706016</v>
+        <v>46196.60302403935</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>200</v>
@@ -10060,13 +10060,13 @@
         <v>364</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.60170435185</v>
+        <v>46125.43503768518</v>
       </c>
       <c r="C145" s="8">
-        <v>46196.769687395834</v>
+        <v>46196.60302072916</v>
       </c>
       <c r="D145" s="8">
-        <v>46196.76969114583</v>
+        <v>46196.60302447916</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>200</v>
@@ -10113,13 +10113,13 @@
         <v>365</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.60173947917</v>
+        <v>46125.4350728125</v>
       </c>
       <c r="C146" s="5">
-        <v>46196.769688113425</v>
+        <v>46196.60302144676</v>
       </c>
       <c r="D146" s="5">
-        <v>46196.76969164352</v>
+        <v>46196.60302497685</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>200</v>
@@ -10166,13 +10166,13 @@
         <v>366</v>
       </c>
       <c r="B147" s="8">
-        <v>46122.551753472224</v>
+        <v>46122.38508680556</v>
       </c>
       <c r="C147" s="8">
-        <v>46191.70604009259</v>
+        <v>46191.53937342593</v>
       </c>
       <c r="D147" s="8">
-        <v>46196.76981105324</v>
+        <v>46196.60314438658</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>367</v>
@@ -10229,13 +10229,13 @@
         <v>369</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.60181555555</v>
+        <v>46125.43514888889</v>
       </c>
       <c r="C148" s="5">
-        <v>46196.76979265046</v>
+        <v>46196.60312598379</v>
       </c>
       <c r="D148" s="5">
-        <v>46196.76979569445</v>
+        <v>46196.603129027775</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>200</v>
@@ -10282,13 +10282,13 @@
         <v>370</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.60185690972</v>
+        <v>46125.43519024306</v>
       </c>
       <c r="C149" s="8">
-        <v>46196.76979356482</v>
+        <v>46196.603126898146</v>
       </c>
       <c r="D149" s="8">
-        <v>46196.76979614583</v>
+        <v>46196.60312947917</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>200</v>
@@ -10335,13 +10335,13 @@
         <v>371</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.601899490735</v>
+        <v>46125.43523282408</v>
       </c>
       <c r="C150" s="5">
-        <v>46196.769794224536</v>
+        <v>46196.60312755787</v>
       </c>
       <c r="D150" s="5">
-        <v>46196.76979648148</v>
+        <v>46196.603129814815</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>200</v>
@@ -10388,13 +10388,13 @@
         <v>372</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.60193935185</v>
+        <v>46125.43527268519</v>
       </c>
       <c r="C151" s="8">
-        <v>46196.76976476852</v>
+        <v>46196.603098101856</v>
       </c>
       <c r="D151" s="8">
-        <v>46196.769766875004</v>
+        <v>46196.60310020833</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>200</v>
@@ -10441,13 +10441,13 @@
         <v>373</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.60197710648</v>
+        <v>46125.43531043982</v>
       </c>
       <c r="C152" s="5">
-        <v>46196.76977206019</v>
+        <v>46196.603105393515</v>
       </c>
       <c r="D152" s="5">
-        <v>46196.76977370371</v>
+        <v>46196.60310703704</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>200</v>
@@ -10494,11 +10494,11 @@
         <v>374</v>
       </c>
       <c r="B153" s="8">
-        <v>46122.551758622685</v>
+        <v>46122.38509195602</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46125.58936878473</v>
+        <v>46125.422702118056</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>375</v>
@@ -10541,11 +10541,11 @@
         <v>377</v>
       </c>
       <c r="B154" s="5">
-        <v>46122.55176134259</v>
+        <v>46122.38509467593</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46191.70605767361</v>
+        <v>46191.53939100694</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>378</v>
@@ -10604,11 +10604,11 @@
         <v>381</v>
       </c>
       <c r="B155" s="8">
-        <v>46122.55176609954</v>
+        <v>46122.38509943287</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46192.97384414352</v>
+        <v>46192.80717747685</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>382</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -1847,13 +1847,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46122.38452245371</v>
+        <v>46122.55118912037</v>
       </c>
       <c r="C4" s="5">
-        <v>46128.426341053244</v>
+        <v>46128.59300771991</v>
       </c>
       <c r="D4" s="5">
-        <v>46157.93633454861</v>
+        <v>46158.10300121528</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1896,13 +1896,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46122.38467905093</v>
+        <v>46122.55134571759</v>
       </c>
       <c r="C5" s="8">
-        <v>46128.42632796297</v>
+        <v>46128.59299462963</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.70935505787</v>
+        <v>46133.876021724536</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1959,13 +1959,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46122.384682812495</v>
+        <v>46122.55134947917</v>
       </c>
       <c r="C6" s="5">
-        <v>46128.42601201389</v>
+        <v>46128.59267868055</v>
       </c>
       <c r="D6" s="5">
-        <v>46128.43715965278</v>
+        <v>46128.60382631945</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2022,13 +2022,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46122.38468587963</v>
+        <v>46122.551352546296</v>
       </c>
       <c r="C7" s="8">
-        <v>46128.42603200232</v>
+        <v>46128.59269866898</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.460593807875</v>
+        <v>46161.62726047453</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2085,13 +2085,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46122.38468890046</v>
+        <v>46122.551355567135</v>
       </c>
       <c r="C8" s="5">
-        <v>46128.42605055556</v>
+        <v>46128.59271722222</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.43733940972</v>
+        <v>46128.60400607639</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2148,13 +2148,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46122.384692719905</v>
+        <v>46122.551359386576</v>
       </c>
       <c r="C9" s="8">
-        <v>46128.4261833912</v>
+        <v>46128.592850057874</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.66910643518</v>
+        <v>46156.83577310185</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2211,13 +2211,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46122.3845274537</v>
+        <v>46122.55119412037</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.766136805556</v>
+        <v>46193.93280347223</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.76615431713</v>
+        <v>46193.9328209838</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2264,13 +2264,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46122.384696504625</v>
+        <v>46122.5513631713</v>
       </c>
       <c r="C11" s="8">
-        <v>46128.43768854167</v>
+        <v>46128.60435520833</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.80716136574</v>
+        <v>46192.97382803241</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2329,13 +2329,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46122.38470238426</v>
+        <v>46122.551369050925</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.43976447917</v>
+        <v>46128.60643114583</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.80716146991</v>
+        <v>46192.97382813657</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2394,13 +2394,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46122.384708020836</v>
+        <v>46122.5513746875</v>
       </c>
       <c r="C13" s="8">
-        <v>46132.40405894676</v>
+        <v>46132.57072561343</v>
       </c>
       <c r="D13" s="8">
-        <v>46192.80716134259</v>
+        <v>46192.97382800926</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2459,13 +2459,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46122.38692751157</v>
+        <v>46122.553594178244</v>
       </c>
       <c r="C14" s="5">
-        <v>46128.44274908565</v>
+        <v>46128.60941575232</v>
       </c>
       <c r="D14" s="5">
-        <v>46136.03935251157</v>
+        <v>46136.20601917824</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2524,13 +2524,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46122.38453280093</v>
+        <v>46122.55119946759</v>
       </c>
       <c r="C15" s="8">
-        <v>46195.34056496528</v>
+        <v>46195.50723163194</v>
       </c>
       <c r="D15" s="8">
-        <v>46195.340579421296</v>
+        <v>46195.50724608796</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2577,13 +2577,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46122.38472188657</v>
+        <v>46122.55138855324</v>
       </c>
       <c r="C16" s="5">
-        <v>46128.44033724537</v>
+        <v>46128.60700391204</v>
       </c>
       <c r="D16" s="5">
-        <v>46133.0133283912</v>
+        <v>46133.17999505787</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2642,13 +2642,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46122.38472815973</v>
+        <v>46122.55139482639</v>
       </c>
       <c r="C17" s="8">
-        <v>46128.44034490741</v>
+        <v>46128.60701157407</v>
       </c>
       <c r="D17" s="8">
-        <v>46132.01554025463</v>
+        <v>46132.182206921294</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2707,13 +2707,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46122.38473373842</v>
+        <v>46122.55140040509</v>
       </c>
       <c r="C18" s="5">
-        <v>46195.340545046296</v>
+        <v>46195.50721171296</v>
       </c>
       <c r="D18" s="5">
-        <v>46195.340565624996</v>
+        <v>46195.50723229167</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2772,13 +2772,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46122.384739375004</v>
+        <v>46122.55140604167</v>
       </c>
       <c r="C19" s="8">
-        <v>46181.499732384254</v>
+        <v>46181.666399050926</v>
       </c>
       <c r="D19" s="8">
-        <v>46195.038918101855</v>
+        <v>46195.20558476852</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2837,13 +2837,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46122.3847449537</v>
+        <v>46122.55141162037</v>
       </c>
       <c r="C20" s="5">
-        <v>46128.442831215274</v>
+        <v>46128.609497881946</v>
       </c>
       <c r="D20" s="5">
-        <v>46132.01553989583</v>
+        <v>46132.1822065625</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>64</v>
@@ -2902,13 +2902,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46122.39987912037</v>
+        <v>46122.566545787035</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.49969386574</v>
+        <v>46181.66636053241</v>
       </c>
       <c r="D21" s="8">
-        <v>46195.03891780092</v>
+        <v>46195.20558446759</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2967,13 +2967,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46122.39994855324</v>
+        <v>46122.56661521991</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.499709641204</v>
+        <v>46181.66637630787</v>
       </c>
       <c r="D22" s="5">
-        <v>46195.038917673606</v>
+        <v>46195.20558434028</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3032,13 +3032,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="8">
-        <v>46122.40619606481</v>
+        <v>46122.57286273148</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.4997655787</v>
+        <v>46181.66643224537</v>
       </c>
       <c r="D23" s="8">
-        <v>46195.03891771991</v>
+        <v>46195.205584386575</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -3097,13 +3097,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46122.38453728009</v>
+        <v>46122.55120394676</v>
       </c>
       <c r="C24" s="5">
-        <v>46195.34067315972</v>
+        <v>46195.50733982639</v>
       </c>
       <c r="D24" s="5">
-        <v>46195.34068686343</v>
+        <v>46195.50735353009</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -3150,13 +3150,13 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46122.38475027778</v>
+        <v>46122.55141694444</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.45950203703</v>
+        <v>46174.626168703704</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.45951446759</v>
+        <v>46174.626181134256</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -3215,13 +3215,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46122.38475541667</v>
+        <v>46122.55142208333</v>
       </c>
       <c r="C26" s="5">
-        <v>46174.45658625</v>
+        <v>46174.62325291667</v>
       </c>
       <c r="D26" s="5">
-        <v>46174.456587824076</v>
+        <v>46174.62325449074</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3276,13 +3276,13 @@
         <v>110</v>
       </c>
       <c r="B27" s="8">
-        <v>46122.38476032407</v>
+        <v>46122.55142699074</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.45948622686</v>
+        <v>46174.626152893514</v>
       </c>
       <c r="D27" s="8">
-        <v>46174.45948762732</v>
+        <v>46174.62615429398</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>111</v>
@@ -3337,13 +3337,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46122.38476556713</v>
+        <v>46122.5514322338</v>
       </c>
       <c r="C28" s="5">
-        <v>46195.340658553236</v>
+        <v>46195.50732521991</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.545180127316</v>
+        <v>46195.71184679398</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3402,13 +3402,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="8">
-        <v>46122.38477087963</v>
+        <v>46122.551437546295</v>
       </c>
       <c r="C29" s="8">
-        <v>46195.54471607639</v>
+        <v>46195.71138274306</v>
       </c>
       <c r="D29" s="8">
-        <v>46195.54471850695</v>
+        <v>46195.71138517361</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>118</v>
@@ -3463,13 +3463,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46122.3847758912</v>
+        <v>46122.55144255787</v>
       </c>
       <c r="C30" s="5">
-        <v>46195.54516429398</v>
+        <v>46195.711830960645</v>
       </c>
       <c r="D30" s="5">
-        <v>46195.54516583333</v>
+        <v>46195.711832500005</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3524,13 +3524,13 @@
         <v>123</v>
       </c>
       <c r="B31" s="8">
-        <v>46122.38478104166</v>
+        <v>46122.551447708334</v>
       </c>
       <c r="C31" s="8">
-        <v>46133.661133263886</v>
+        <v>46133.82779993056</v>
       </c>
       <c r="D31" s="8">
-        <v>46133.66114655093</v>
+        <v>46133.82781321759</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>124</v>
@@ -3589,13 +3589,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46122.38478609954</v>
+        <v>46122.5514527662</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.66106445601</v>
+        <v>46133.827731122685</v>
       </c>
       <c r="D32" s="5">
-        <v>46133.6610659375</v>
+        <v>46133.82773260417</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3650,13 +3650,13 @@
         <v>129</v>
       </c>
       <c r="B33" s="8">
-        <v>46122.384791296296</v>
+        <v>46122.55145796297</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.66112020833</v>
+        <v>46133.827786875</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.661121412035</v>
+        <v>46133.82778807871</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>130</v>
@@ -3711,13 +3711,13 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46122.38479633102</v>
+        <v>46122.55146299768</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.6611012963</v>
+        <v>46133.82776796297</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.66110246528</v>
+        <v>46133.827769131945</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3772,13 +3772,13 @@
         <v>135</v>
       </c>
       <c r="B35" s="8">
-        <v>46122.38480128472</v>
+        <v>46122.55146795139</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.50020540509</v>
+        <v>46181.66687207176</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.5002191088</v>
+        <v>46181.66688577546</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3837,13 +3837,13 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46122.38480630787</v>
+        <v>46122.551472974534</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.50015100694</v>
+        <v>46181.66681767361</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.50015280093</v>
+        <v>46181.66681946759</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3898,13 +3898,13 @@
         <v>143</v>
       </c>
       <c r="B37" s="8">
-        <v>46122.384855868055</v>
+        <v>46122.55152253472</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.50019012731</v>
+        <v>46181.66685679398</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.5001915162</v>
+        <v>46181.66685818287</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>144</v>
@@ -3959,13 +3959,13 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46122.384862245366</v>
+        <v>46122.55152891204</v>
       </c>
       <c r="C38" s="5">
-        <v>46154.70100114583</v>
+        <v>46154.867667812505</v>
       </c>
       <c r="D38" s="5">
-        <v>46189.00554646991</v>
+        <v>46189.172213136575</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -4024,13 +4024,13 @@
         <v>149</v>
       </c>
       <c r="B39" s="8">
-        <v>46122.384867395835</v>
+        <v>46122.5515340625</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.70085026621</v>
+        <v>46154.86751693287</v>
       </c>
       <c r="D39" s="8">
-        <v>46154.70085260417</v>
+        <v>46154.86751927083</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>87</v>
@@ -4079,13 +4079,13 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46122.38487178241</v>
+        <v>46122.55153844907</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.70090960649</v>
+        <v>46154.867576273144</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.70091078704</v>
+        <v>46154.867577453704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4134,13 +4134,13 @@
         <v>154</v>
       </c>
       <c r="B41" s="8">
-        <v>46122.40826678241</v>
+        <v>46122.574933449076</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.500100335645</v>
+        <v>46181.666767002316</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.50011658565</v>
+        <v>46181.666783252316</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>155</v>
@@ -4199,13 +4199,13 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46122.40925430556</v>
+        <v>46122.575920972224</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.500040729166</v>
+        <v>46181.66670739584</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.500041886575</v>
+        <v>46181.66670855324</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>90</v>
@@ -4254,13 +4254,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46122.409418090276</v>
+        <v>46122.57608475695</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.50008614583</v>
+        <v>46181.666752812496</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.500087685185</v>
+        <v>46181.666754351856</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4309,13 +4309,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46122.40834771991</v>
+        <v>46122.57501438657</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.500291805554</v>
+        <v>46181.666958472226</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.500401990736</v>
+        <v>46181.66706865741</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4374,13 +4374,13 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46122.41255444444</v>
+        <v>46122.57922111111</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.50023484953</v>
+        <v>46181.666901516204</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.50023640046</v>
+        <v>46181.66690306713</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>96</v>
@@ -4429,13 +4429,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46122.4128253588</v>
+        <v>46122.57949202546</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.500276562496</v>
+        <v>46181.66694322917</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.50027793982</v>
+        <v>46181.66694460648</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4484,13 +4484,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46125.362951550924</v>
+        <v>46125.529618217595</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.50055453704</v>
+        <v>46181.66722120371</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.500568449075</v>
+        <v>46181.66723511574</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4549,13 +4549,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46125.36311331019</v>
+        <v>46125.52977997685</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.50049065972</v>
+        <v>46181.66715732639</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.500492453706</v>
+        <v>46181.66715912037</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>93</v>
@@ -4604,13 +4604,13 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46125.36325149305</v>
+        <v>46125.52991815972</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.5005374537</v>
+        <v>46181.66720412037</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.50053896991</v>
+        <v>46181.66720563658</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4659,13 +4659,13 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46122.384541886575</v>
+        <v>46122.55120855324</v>
       </c>
       <c r="C50" s="5">
-        <v>46195.34078462963</v>
+        <v>46195.5074512963</v>
       </c>
       <c r="D50" s="5">
-        <v>46195.34089821759</v>
+        <v>46195.50756488426</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4712,13 +4712,13 @@
         <v>183</v>
       </c>
       <c r="B51" s="8">
-        <v>46122.38487678241</v>
+        <v>46122.55154344907</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.62917814815</v>
+        <v>46133.79584481481</v>
       </c>
       <c r="D51" s="8">
-        <v>46143.00447921296</v>
+        <v>46143.171145879634</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>184</v>
@@ -4777,13 +4777,13 @@
         <v>188</v>
       </c>
       <c r="B52" s="5">
-        <v>46122.38488232639</v>
+        <v>46122.551548993055</v>
       </c>
       <c r="C52" s="5">
-        <v>46134.62573756944</v>
+        <v>46134.79240423611</v>
       </c>
       <c r="D52" s="5">
-        <v>46198.021150451386</v>
+        <v>46198.18781711806</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4842,13 +4842,13 @@
         <v>192</v>
       </c>
       <c r="B53" s="8">
-        <v>46122.38489054398</v>
+        <v>46122.55155721065</v>
       </c>
       <c r="C53" s="8">
-        <v>46134.62578480324</v>
+        <v>46134.79245146991</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.02315126157</v>
+        <v>46191.18981792824</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>83</v>
@@ -4905,13 +4905,13 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46122.38489901621</v>
+        <v>46122.55156568287</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.34094658565</v>
+        <v>46195.50761325231</v>
       </c>
       <c r="D54" s="5">
-        <v>46196.6024115162</v>
+        <v>46196.76907818287</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -4968,13 +4968,13 @@
         <v>199</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.43695545139</v>
+        <v>46125.603622118055</v>
       </c>
       <c r="C55" s="8">
-        <v>46196.60238085648</v>
+        <v>46196.76904752315</v>
       </c>
       <c r="D55" s="8">
-        <v>46196.602385474536</v>
+        <v>46196.7690521412</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>200</v>
@@ -5021,13 +5021,13 @@
         <v>202</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.43700428241</v>
+        <v>46125.60367094907</v>
       </c>
       <c r="C56" s="5">
-        <v>46196.6023817824</v>
+        <v>46196.769048449074</v>
       </c>
       <c r="D56" s="5">
-        <v>46196.60238585648</v>
+        <v>46196.769052523145</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -5074,13 +5074,13 @@
         <v>203</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.43705284722</v>
+        <v>46125.60371951389</v>
       </c>
       <c r="C57" s="8">
-        <v>46196.602382627316</v>
+        <v>46196.76904929398</v>
       </c>
       <c r="D57" s="8">
-        <v>46196.60238616898</v>
+        <v>46196.76905283565</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5127,13 +5127,13 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.43709796296</v>
+        <v>46125.60376462963</v>
       </c>
       <c r="C58" s="5">
-        <v>46196.60238340277</v>
+        <v>46196.769050069444</v>
       </c>
       <c r="D58" s="5">
-        <v>46196.60238648148</v>
+        <v>46196.76905314815</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>200</v>
@@ -5180,13 +5180,13 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.437150729165</v>
+        <v>46125.60381739584</v>
       </c>
       <c r="C59" s="8">
-        <v>46196.602384108795</v>
+        <v>46196.76905077546</v>
       </c>
       <c r="D59" s="8">
-        <v>46196.6023868287</v>
+        <v>46196.76905349537</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>200</v>
@@ -5233,13 +5233,13 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46122.38490304398</v>
+        <v>46122.551569710646</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.501105787036</v>
+        <v>46181.6677724537</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.501186574074</v>
+        <v>46181.66785324074</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5282,13 +5282,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46122.38490655093</v>
+        <v>46122.55157321759</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.50071136574</v>
+        <v>46181.667378032405</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.500728576386</v>
+        <v>46181.66739524306</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5347,13 +5347,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46122.41824972222</v>
+        <v>46122.58491638889</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.50074653935</v>
+        <v>46181.667413206014</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.50076234953</v>
+        <v>46181.667429016205</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5412,13 +5412,13 @@
         <v>217</v>
       </c>
       <c r="B63" s="8">
-        <v>46125.36435991898</v>
+        <v>46125.53102658565</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.500763460645</v>
+        <v>46181.667430127316</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.50078259259</v>
+        <v>46181.66744925926</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -5477,13 +5477,13 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46122.38491179398</v>
+        <v>46122.55157846065</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.501089212965</v>
+        <v>46181.66775587963</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.501105752315</v>
+        <v>46181.66777241898</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5542,13 +5542,13 @@
         <v>225</v>
       </c>
       <c r="B65" s="8">
-        <v>46122.38491716435</v>
+        <v>46122.551583831024</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.50212802083</v>
+        <v>46181.6687946875</v>
       </c>
       <c r="D65" s="8">
-        <v>46181.50224104167</v>
+        <v>46181.66890770833</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>226</v>
@@ -5591,13 +5591,13 @@
         <v>228</v>
       </c>
       <c r="B66" s="5">
-        <v>46122.384920219905</v>
+        <v>46122.55158688658</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.49942690972</v>
+        <v>46181.666093576394</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.50214266204</v>
+        <v>46181.66880932871</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>229</v>
@@ -5656,13 +5656,13 @@
         <v>233</v>
       </c>
       <c r="B67" s="8">
-        <v>46122.384925185186</v>
+        <v>46122.55159185185</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.49953199074</v>
+        <v>46181.6661986574</v>
       </c>
       <c r="D67" s="8">
-        <v>46181.50217939814</v>
+        <v>46181.668846064815</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>234</v>
@@ -5721,13 +5721,13 @@
         <v>236</v>
       </c>
       <c r="B68" s="5">
-        <v>46125.42914525463</v>
+        <v>46125.595811921296</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.501410324076</v>
+        <v>46181.66807699074</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.50141217593</v>
+        <v>46181.66807884259</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>237</v>
@@ -5776,13 +5776,13 @@
         <v>240</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.42943380787</v>
+        <v>46125.59610047453</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.50141914352</v>
+        <v>46181.66808581019</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.50142061342</v>
+        <v>46181.66808728009</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>200</v>
@@ -5831,13 +5831,13 @@
         <v>241</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.429543715276</v>
+        <v>46125.59621038195</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.501487326386</v>
+        <v>46181.66815399306</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.501488842594</v>
+        <v>46181.66815550926</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>200</v>
@@ -5886,13 +5886,13 @@
         <v>242</v>
       </c>
       <c r="B71" s="8">
-        <v>46125.42958805556</v>
+        <v>46125.59625472222</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.50150002315</v>
+        <v>46181.668166689815</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.501501527775</v>
+        <v>46181.66816819445</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>200</v>
@@ -5941,13 +5941,13 @@
         <v>243</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.42963248843</v>
+        <v>46125.59629915509</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.50151289352</v>
+        <v>46181.66817956018</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.50151412037</v>
+        <v>46181.66818078703</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>200</v>
@@ -5996,13 +5996,13 @@
         <v>244</v>
       </c>
       <c r="B73" s="8">
-        <v>46122.384930844906</v>
+        <v>46122.55159751157</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.50211394676</v>
+        <v>46181.66878061343</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.50211555556</v>
+        <v>46181.66878222222</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>245</v>
@@ -6061,13 +6061,13 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46125.4298218287</v>
+        <v>46125.59648849537</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.501985254625</v>
+        <v>46181.668651921296</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.501986724536</v>
+        <v>46181.6686533912</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>200</v>
@@ -6116,13 +6116,13 @@
         <v>249</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.429951875005</v>
+        <v>46125.59661854166</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.50199983796</v>
+        <v>46181.66866650463</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.50200115741</v>
+        <v>46181.66866782407</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>200</v>
@@ -6171,13 +6171,13 @@
         <v>251</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.43000208333</v>
+        <v>46125.596668750004</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.50200921296</v>
+        <v>46181.66867587963</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.50201078704</v>
+        <v>46181.66867745371</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>200</v>
@@ -6226,13 +6226,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="8">
-        <v>46125.430048842594</v>
+        <v>46125.59671550926</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.50201895833</v>
+        <v>46181.668685625</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.50202039352</v>
+        <v>46181.668687060184</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>200</v>
@@ -6281,13 +6281,13 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.430088796296</v>
+        <v>46125.59675546296</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.5020371875</v>
+        <v>46181.66870385417</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.502038356484</v>
+        <v>46181.66870502315</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>200</v>
@@ -6336,13 +6336,13 @@
         <v>255</v>
       </c>
       <c r="B79" s="8">
-        <v>46122.38493690972</v>
+        <v>46122.55160357639</v>
       </c>
       <c r="C79" s="8">
-        <v>46195.3964589699</v>
+        <v>46195.563125636574</v>
       </c>
       <c r="D79" s="8">
-        <v>46195.39662366898</v>
+        <v>46195.563290335645</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>207</v>
@@ -6389,13 +6389,13 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46122.38494012732</v>
+        <v>46122.55160679398</v>
       </c>
       <c r="C80" s="5">
-        <v>46195.39660269676</v>
+        <v>46195.563269363425</v>
       </c>
       <c r="D80" s="5">
-        <v>46195.54518015047</v>
+        <v>46195.711846817125</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6454,13 +6454,13 @@
         <v>260</v>
       </c>
       <c r="B81" s="8">
-        <v>46122.38494559028</v>
+        <v>46122.551612256946</v>
       </c>
       <c r="C81" s="8">
-        <v>46195.34084651621</v>
+        <v>46195.50751318287</v>
       </c>
       <c r="D81" s="8">
-        <v>46195.3408646412</v>
+        <v>46195.50753130787</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>261</v>
@@ -6519,13 +6519,13 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46122.38495090278</v>
+        <v>46122.55161756944</v>
       </c>
       <c r="C82" s="5">
-        <v>46195.340851851855</v>
+        <v>46195.50751851852</v>
       </c>
       <c r="D82" s="5">
-        <v>46195.34086592593</v>
+        <v>46195.50753259259</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6584,13 +6584,13 @@
         <v>264</v>
       </c>
       <c r="B83" s="8">
-        <v>46122.384956215275</v>
+        <v>46122.55162288195</v>
       </c>
       <c r="C83" s="8">
-        <v>46195.34085677083</v>
+        <v>46195.507523437496</v>
       </c>
       <c r="D83" s="8">
-        <v>46195.3408728125</v>
+        <v>46195.507539479164</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>265</v>
@@ -6649,13 +6649,13 @@
         <v>266</v>
       </c>
       <c r="B84" s="5">
-        <v>46122.427324965276</v>
+        <v>46122.59399163195</v>
       </c>
       <c r="C84" s="5">
-        <v>46193.76648644676</v>
+        <v>46193.93315311342</v>
       </c>
       <c r="D84" s="5">
-        <v>46193.76661337963</v>
+        <v>46193.9332800463</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>267</v>
@@ -6714,13 +6714,13 @@
         <v>269</v>
       </c>
       <c r="B85" s="8">
-        <v>46122.3849615162</v>
+        <v>46122.551628182875</v>
       </c>
       <c r="C85" s="8">
-        <v>46195.39639328704</v>
+        <v>46195.5630599537</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.60252601852</v>
+        <v>46196.769192685184</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>270</v>
@@ -6767,13 +6767,13 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46122.38496491898</v>
+        <v>46122.55163158565</v>
       </c>
       <c r="C86" s="5">
-        <v>46195.34102184028</v>
+        <v>46195.50768850694</v>
       </c>
       <c r="D86" s="5">
-        <v>46195.34104046296</v>
+        <v>46195.507707129625</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>273</v>
@@ -6832,13 +6832,13 @@
         <v>275</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.43083025463</v>
+        <v>46125.5974969213</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.60125040509</v>
+        <v>46196.76791707176</v>
       </c>
       <c r="D87" s="8">
-        <v>46196.60125216436</v>
+        <v>46196.767918831014</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>200</v>
@@ -6887,13 +6887,13 @@
         <v>277</v>
       </c>
       <c r="B88" s="5">
-        <v>46125.430879039355</v>
+        <v>46125.59754570602</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.601287384256</v>
+        <v>46196.76795405093</v>
       </c>
       <c r="D88" s="5">
-        <v>46196.601289791666</v>
+        <v>46196.76795645834</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>200</v>
@@ -6942,13 +6942,13 @@
         <v>278</v>
       </c>
       <c r="B89" s="8">
-        <v>46125.430940439815</v>
+        <v>46125.59760710648</v>
       </c>
       <c r="C89" s="8">
-        <v>46196.601261550924</v>
+        <v>46196.767928217596</v>
       </c>
       <c r="D89" s="8">
-        <v>46196.601263344906</v>
+        <v>46196.76793001157</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>200</v>
@@ -6997,13 +6997,13 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46125.43099224537</v>
+        <v>46125.59765891204</v>
       </c>
       <c r="C90" s="5">
-        <v>46196.601279849536</v>
+        <v>46196.76794651621</v>
       </c>
       <c r="D90" s="5">
-        <v>46196.60128142362</v>
+        <v>46196.76794809027</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>200</v>
@@ -7052,13 +7052,13 @@
         <v>280</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.431036724534</v>
+        <v>46125.597703391206</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.60127434028</v>
+        <v>46196.76794100694</v>
       </c>
       <c r="D91" s="8">
-        <v>46196.6012762037</v>
+        <v>46196.76794287037</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>200</v>
@@ -7107,13 +7107,13 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46122.38503993055</v>
+        <v>46122.55170659722</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.60088846065</v>
+        <v>46196.76755512731</v>
       </c>
       <c r="D92" s="5">
-        <v>46196.60141113426</v>
+        <v>46196.76807780092</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>282</v>
@@ -7172,13 +7172,13 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46125.43316075232</v>
+        <v>46125.59982741898</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.60133528935</v>
+        <v>46196.76800195602</v>
       </c>
       <c r="D93" s="8">
-        <v>46196.60133719907</v>
+        <v>46196.76800386574</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>200</v>
@@ -7227,13 +7227,13 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.43322416667</v>
+        <v>46125.599890833335</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.601356354164</v>
+        <v>46196.768023020835</v>
       </c>
       <c r="D94" s="5">
-        <v>46196.60135802084</v>
+        <v>46196.768024687495</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>200</v>
@@ -7282,13 +7282,13 @@
         <v>288</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.43326467593</v>
+        <v>46125.59993134259</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.601348275464</v>
+        <v>46196.76801494213</v>
       </c>
       <c r="D95" s="8">
-        <v>46196.60135009259</v>
+        <v>46196.76801675926</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>200</v>
@@ -7337,13 +7337,13 @@
         <v>289</v>
       </c>
       <c r="B96" s="5">
-        <v>46125.433302627316</v>
+        <v>46125.59996929398</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.60138443287</v>
+        <v>46196.76805109954</v>
       </c>
       <c r="D96" s="5">
-        <v>46196.60138612268</v>
+        <v>46196.76805278935</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>200</v>
@@ -7392,13 +7392,13 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46125.43334484954</v>
+        <v>46125.6000115162</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.60139039352</v>
+        <v>46196.76805706018</v>
       </c>
       <c r="D97" s="8">
-        <v>46196.60139240741</v>
+        <v>46196.76805907408</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>200</v>
@@ -7447,13 +7447,13 @@
         <v>291</v>
       </c>
       <c r="B98" s="5">
-        <v>46122.38497746528</v>
+        <v>46122.55164413195</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.601731574076</v>
+        <v>46196.76839824074</v>
       </c>
       <c r="D98" s="5">
-        <v>46196.601742060186</v>
+        <v>46196.76840872686</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>292</v>
@@ -7512,13 +7512,13 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46125.43249607639</v>
+        <v>46125.599162743056</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.601522997684</v>
+        <v>46196.76818966435</v>
       </c>
       <c r="D99" s="8">
-        <v>46196.60152462963</v>
+        <v>46196.7681912963</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>200</v>
@@ -7567,13 +7567,13 @@
         <v>297</v>
       </c>
       <c r="B100" s="5">
-        <v>46125.4326358449</v>
+        <v>46125.599302511575</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.601537546296</v>
+        <v>46196.76820421296</v>
       </c>
       <c r="D100" s="5">
-        <v>46196.60153930556</v>
+        <v>46196.76820597222</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>200</v>
@@ -7622,13 +7622,13 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46125.43267978009</v>
+        <v>46125.59934644676</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.601709282404</v>
+        <v>46196.768375949076</v>
       </c>
       <c r="D101" s="8">
-        <v>46196.60171291667</v>
+        <v>46196.76837958333</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>200</v>
@@ -7677,13 +7677,13 @@
         <v>299</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.43272190972</v>
+        <v>46125.59938857639</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.60171030092</v>
+        <v>46196.76837696759</v>
       </c>
       <c r="D102" s="5">
-        <v>46196.60171341435</v>
+        <v>46196.76838008102</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>200</v>
@@ -7732,13 +7732,13 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46125.43276428241</v>
+        <v>46125.59943094908</v>
       </c>
       <c r="C103" s="8">
-        <v>46196.60171123843</v>
+        <v>46196.76837790509</v>
       </c>
       <c r="D103" s="8">
-        <v>46196.601713854165</v>
+        <v>46196.768380520836</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>200</v>
@@ -7787,13 +7787,13 @@
         <v>301</v>
       </c>
       <c r="B104" s="5">
-        <v>46122.3849843287</v>
+        <v>46122.551650995374</v>
       </c>
       <c r="C104" s="5">
-        <v>46196.601881215276</v>
+        <v>46196.76854788195</v>
       </c>
       <c r="D104" s="5">
-        <v>46196.601894074076</v>
+        <v>46196.76856074074</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>302</v>
@@ -7852,13 +7852,13 @@
         <v>303</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.43286347222</v>
+        <v>46125.59953013889</v>
       </c>
       <c r="C105" s="8">
-        <v>46196.60186116898</v>
+        <v>46196.76852783565</v>
       </c>
       <c r="D105" s="8">
-        <v>46196.60186505787</v>
+        <v>46196.768531724534</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>200</v>
@@ -7907,13 +7907,13 @@
         <v>305</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.43294756944</v>
+        <v>46125.59961423611</v>
       </c>
       <c r="C106" s="5">
-        <v>46196.60179663195</v>
+        <v>46196.76846329861</v>
       </c>
       <c r="D106" s="5">
-        <v>46196.60179829861</v>
+        <v>46196.76846496528</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>200</v>
@@ -7962,13 +7962,13 @@
         <v>306</v>
       </c>
       <c r="B107" s="8">
-        <v>46125.43298765046</v>
+        <v>46125.599654317135</v>
       </c>
       <c r="C107" s="8">
-        <v>46196.601862129624</v>
+        <v>46196.768528796296</v>
       </c>
       <c r="D107" s="8">
-        <v>46196.601865370365</v>
+        <v>46196.76853203704</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>200</v>
@@ -8017,13 +8017,13 @@
         <v>307</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.43290399306</v>
+        <v>46125.59957065972</v>
       </c>
       <c r="C108" s="5">
-        <v>46196.601862881944</v>
+        <v>46196.768529548615</v>
       </c>
       <c r="D108" s="5">
-        <v>46196.6018656713</v>
+        <v>46196.76853233796</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>200</v>
@@ -8072,13 +8072,13 @@
         <v>308</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.433030451386</v>
+        <v>46125.59969711806</v>
       </c>
       <c r="C109" s="8">
-        <v>46196.601863738426</v>
+        <v>46196.7685304051</v>
       </c>
       <c r="D109" s="8">
-        <v>46196.6018659838</v>
+        <v>46196.76853265046</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>200</v>
@@ -8127,13 +8127,13 @@
         <v>309</v>
       </c>
       <c r="B110" s="5">
-        <v>46122.38497059028</v>
+        <v>46122.55163725694</v>
       </c>
       <c r="C110" s="5">
-        <v>46196.6020008912</v>
+        <v>46196.76866755787</v>
       </c>
       <c r="D110" s="5">
-        <v>46196.60201241898</v>
+        <v>46196.76867908565</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>310</v>
@@ -8192,13 +8192,13 @@
         <v>311</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.431135439816</v>
+        <v>46125.59780210648</v>
       </c>
       <c r="C111" s="8">
-        <v>46196.60198236111</v>
+        <v>46196.76864902778</v>
       </c>
       <c r="D111" s="8">
-        <v>46196.60198721065</v>
+        <v>46196.76865387731</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>200</v>
@@ -8247,13 +8247,13 @@
         <v>314</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.43117026621</v>
+        <v>46125.597836932866</v>
       </c>
       <c r="C112" s="5">
-        <v>46196.601983333334</v>
+        <v>46196.76865</v>
       </c>
       <c r="D112" s="5">
-        <v>46196.60198760417</v>
+        <v>46196.76865427083</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>200</v>
@@ -8302,13 +8302,13 @@
         <v>315</v>
       </c>
       <c r="B113" s="8">
-        <v>46125.43125422453</v>
+        <v>46125.5979208912</v>
       </c>
       <c r="C113" s="8">
-        <v>46196.6019841088</v>
+        <v>46196.76865077546</v>
       </c>
       <c r="D113" s="8">
-        <v>46196.601987939815</v>
+        <v>46196.76865460648</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>200</v>
@@ -8357,13 +8357,13 @@
         <v>316</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.431214212964</v>
+        <v>46125.59788087963</v>
       </c>
       <c r="C114" s="5">
-        <v>46196.60198486111</v>
+        <v>46196.768651527775</v>
       </c>
       <c r="D114" s="5">
-        <v>46196.60198827546</v>
+        <v>46196.768654942134</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>200</v>
@@ -8412,13 +8412,13 @@
         <v>317</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.43129835648</v>
+        <v>46125.597965023146</v>
       </c>
       <c r="C115" s="8">
-        <v>46196.60198564814</v>
+        <v>46196.768652314815</v>
       </c>
       <c r="D115" s="8">
-        <v>46196.60198864584</v>
+        <v>46196.768655312495</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>200</v>
@@ -8467,13 +8467,13 @@
         <v>318</v>
       </c>
       <c r="B116" s="5">
-        <v>46122.38505377315</v>
+        <v>46122.55172043982</v>
       </c>
       <c r="C116" s="5">
-        <v>46196.6021055787</v>
+        <v>46196.76877224537</v>
       </c>
       <c r="D116" s="5">
-        <v>46196.60213211806</v>
+        <v>46196.768798784724</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>319</v>
@@ -8532,13 +8532,13 @@
         <v>320</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.43371586806</v>
+        <v>46125.60038253472</v>
       </c>
       <c r="C117" s="8">
-        <v>46196.602085914354</v>
+        <v>46196.76875258102</v>
       </c>
       <c r="D117" s="8">
-        <v>46196.602090671295</v>
+        <v>46196.768757337966</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>200</v>
@@ -8585,13 +8585,13 @@
         <v>322</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.43376346065</v>
+        <v>46125.60043012731</v>
       </c>
       <c r="C118" s="5">
-        <v>46196.60208681713</v>
+        <v>46196.7687534838</v>
       </c>
       <c r="D118" s="5">
-        <v>46196.60209101852</v>
+        <v>46196.76875768519</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>200</v>
@@ -8638,13 +8638,13 @@
         <v>323</v>
       </c>
       <c r="B119" s="8">
-        <v>46125.43380623843</v>
+        <v>46125.60047290509</v>
       </c>
       <c r="C119" s="8">
-        <v>46196.60208751158</v>
+        <v>46196.768754178236</v>
       </c>
       <c r="D119" s="8">
-        <v>46196.60209134259</v>
+        <v>46196.76875800926</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>200</v>
@@ -8691,13 +8691,13 @@
         <v>324</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.4338474074</v>
+        <v>46125.600514074074</v>
       </c>
       <c r="C120" s="5">
-        <v>46196.602088263884</v>
+        <v>46196.768754930556</v>
       </c>
       <c r="D120" s="5">
-        <v>46196.60209165509</v>
+        <v>46196.76875832176</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>200</v>
@@ -8744,13 +8744,13 @@
         <v>325</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.43389193287</v>
+        <v>46125.60055859954</v>
       </c>
       <c r="C121" s="8">
-        <v>46196.602089224536</v>
+        <v>46196.7687558912</v>
       </c>
       <c r="D121" s="8">
-        <v>46196.60209195602</v>
+        <v>46196.76875862268</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>200</v>
@@ -8797,13 +8797,13 @@
         <v>326</v>
       </c>
       <c r="B122" s="5">
-        <v>46122.385063194444</v>
+        <v>46122.55172986111</v>
       </c>
       <c r="C122" s="5">
-        <v>46196.60250790509</v>
+        <v>46196.76917457176</v>
       </c>
       <c r="D122" s="5">
-        <v>46196.60251917824</v>
+        <v>46196.76918584491</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>327</v>
@@ -8862,13 +8862,13 @@
         <v>329</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.4339775</v>
+        <v>46125.60064416667</v>
       </c>
       <c r="C123" s="8">
-        <v>46196.6024843287</v>
+        <v>46196.76915099537</v>
       </c>
       <c r="D123" s="8">
-        <v>46196.60249076389</v>
+        <v>46196.76915743056</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>200</v>
@@ -8915,13 +8915,13 @@
         <v>331</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.43402074074</v>
+        <v>46125.60068740741</v>
       </c>
       <c r="C124" s="5">
-        <v>46196.60248570602</v>
+        <v>46196.76915237268</v>
       </c>
       <c r="D124" s="5">
-        <v>46196.60249125</v>
+        <v>46196.76915791667</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>200</v>
@@ -8968,13 +8968,13 @@
         <v>332</v>
       </c>
       <c r="B125" s="8">
-        <v>46125.43407178241</v>
+        <v>46125.60073844907</v>
       </c>
       <c r="C125" s="8">
-        <v>46196.60248674768</v>
+        <v>46196.76915341435</v>
       </c>
       <c r="D125" s="8">
-        <v>46196.60249174769</v>
+        <v>46196.76915841435</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>200</v>
@@ -9021,13 +9021,13 @@
         <v>333</v>
       </c>
       <c r="B126" s="5">
-        <v>46125.434109560185</v>
+        <v>46125.60077622686</v>
       </c>
       <c r="C126" s="5">
-        <v>46196.60248771991</v>
+        <v>46196.76915438657</v>
       </c>
       <c r="D126" s="5">
-        <v>46196.60249217592</v>
+        <v>46196.769158842595</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>200</v>
@@ -9074,13 +9074,13 @@
         <v>334</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.43416247686</v>
+        <v>46125.600829143514</v>
       </c>
       <c r="C127" s="8">
-        <v>46196.60248869213</v>
+        <v>46196.769155358794</v>
       </c>
       <c r="D127" s="8">
-        <v>46196.60249265046</v>
+        <v>46196.76915931713</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>200</v>
@@ -9127,13 +9127,13 @@
         <v>335</v>
       </c>
       <c r="B128" s="5">
-        <v>46122.38506837963</v>
+        <v>46122.5517350463</v>
       </c>
       <c r="C128" s="5">
-        <v>46195.39650850694</v>
+        <v>46195.56317517361</v>
       </c>
       <c r="D128" s="5">
-        <v>46196.60293743055</v>
+        <v>46196.76960409722</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>336</v>
@@ -9180,13 +9180,13 @@
         <v>338</v>
       </c>
       <c r="B129" s="8">
-        <v>46122.38507239583</v>
+        <v>46122.5517390625</v>
       </c>
       <c r="C129" s="8">
-        <v>46196.60269986111</v>
+        <v>46196.76936652778</v>
       </c>
       <c r="D129" s="8">
-        <v>46196.602730694445</v>
+        <v>46196.76939736111</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>339</v>
@@ -9245,13 +9245,13 @@
         <v>343</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.43427064815</v>
+        <v>46125.60093731481</v>
       </c>
       <c r="C130" s="5">
-        <v>46196.602678483796</v>
+        <v>46196.76934515046</v>
       </c>
       <c r="D130" s="5">
-        <v>46196.60268401621</v>
+        <v>46196.769350682865</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>200</v>
@@ -9298,13 +9298,13 @@
         <v>345</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.4347141551</v>
+        <v>46125.601380821754</v>
       </c>
       <c r="C131" s="8">
-        <v>46196.602679641204</v>
+        <v>46196.769346307876</v>
       </c>
       <c r="D131" s="8">
-        <v>46196.60268447916</v>
+        <v>46196.769351145835</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>200</v>
@@ -9351,13 +9351,13 @@
         <v>346</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.43475814815</v>
+        <v>46125.60142481481</v>
       </c>
       <c r="C132" s="5">
-        <v>46196.60268056713</v>
+        <v>46196.7693472338</v>
       </c>
       <c r="D132" s="5">
-        <v>46196.60268488426</v>
+        <v>46196.76935155093</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>200</v>
@@ -9404,13 +9404,13 @@
         <v>347</v>
       </c>
       <c r="B133" s="8">
-        <v>46125.434794189816</v>
+        <v>46125.60146085648</v>
       </c>
       <c r="C133" s="8">
-        <v>46196.60268145833</v>
+        <v>46196.769348125</v>
       </c>
       <c r="D133" s="8">
-        <v>46196.602685254635</v>
+        <v>46196.76935192129</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>200</v>
@@ -9457,13 +9457,13 @@
         <v>348</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.434835416665</v>
+        <v>46125.60150208333</v>
       </c>
       <c r="C134" s="5">
-        <v>46196.60268231481</v>
+        <v>46196.769348981485</v>
       </c>
       <c r="D134" s="5">
-        <v>46196.602685624996</v>
+        <v>46196.76935229167</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>200</v>
@@ -9510,13 +9510,13 @@
         <v>349</v>
       </c>
       <c r="B135" s="8">
-        <v>46122.38507716435</v>
+        <v>46122.55174383102</v>
       </c>
       <c r="C135" s="8">
-        <v>46196.60293025463</v>
+        <v>46196.769596921295</v>
       </c>
       <c r="D135" s="8">
-        <v>46196.60294730324</v>
+        <v>46196.76961396991</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>350</v>
@@ -9573,13 +9573,13 @@
         <v>351</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.4344203125</v>
+        <v>46125.601086979164</v>
       </c>
       <c r="C136" s="5">
-        <v>46196.602804884256</v>
+        <v>46196.76947155093</v>
       </c>
       <c r="D136" s="5">
-        <v>46196.60280680556</v>
+        <v>46196.76947347222</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>200</v>
@@ -9626,13 +9626,13 @@
         <v>353</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.4344865162</v>
+        <v>46125.60115318287</v>
       </c>
       <c r="C137" s="8">
-        <v>46196.60283766204</v>
+        <v>46196.7695043287</v>
       </c>
       <c r="D137" s="8">
-        <v>46196.60284236111</v>
+        <v>46196.76950902778</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>200</v>
@@ -9679,13 +9679,13 @@
         <v>354</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.43453724537</v>
+        <v>46125.60120391204</v>
       </c>
       <c r="C138" s="5">
-        <v>46196.60283883102</v>
+        <v>46196.76950549769</v>
       </c>
       <c r="D138" s="5">
-        <v>46196.60284277778</v>
+        <v>46196.76950944445</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>200</v>
@@ -9732,13 +9732,13 @@
         <v>355</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.434591296296</v>
+        <v>46125.60125796296</v>
       </c>
       <c r="C139" s="8">
-        <v>46196.60283971065</v>
+        <v>46196.76950637731</v>
       </c>
       <c r="D139" s="8">
-        <v>46196.60284320602</v>
+        <v>46196.76950987268</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>200</v>
@@ -9785,13 +9785,13 @@
         <v>356</v>
       </c>
       <c r="B140" s="5">
-        <v>46125.43463761574</v>
+        <v>46125.601304282405</v>
       </c>
       <c r="C140" s="5">
-        <v>46196.60284063657</v>
+        <v>46196.76950730324</v>
       </c>
       <c r="D140" s="5">
-        <v>46196.60284359954</v>
+        <v>46196.769510266204</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>200</v>
@@ -9838,13 +9838,13 @@
         <v>357</v>
       </c>
       <c r="B141" s="8">
-        <v>46122.38508202546</v>
+        <v>46122.55174869213</v>
       </c>
       <c r="C141" s="8">
-        <v>46191.539318634255</v>
+        <v>46191.70598530093</v>
       </c>
       <c r="D141" s="8">
-        <v>46196.60304912037</v>
+        <v>46196.769715787035</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>358</v>
@@ -9901,13 +9901,13 @@
         <v>359</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.434919837964</v>
+        <v>46125.60158650463</v>
       </c>
       <c r="C142" s="5">
-        <v>46196.60301796296</v>
+        <v>46196.76968462963</v>
       </c>
       <c r="D142" s="5">
-        <v>46196.60302322917</v>
+        <v>46196.76968989584</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>200</v>
@@ -9954,13 +9954,13 @@
         <v>361</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.43496466435</v>
+        <v>46125.60163133102</v>
       </c>
       <c r="C143" s="8">
-        <v>46196.60301918982</v>
+        <v>46196.76968585648</v>
       </c>
       <c r="D143" s="8">
-        <v>46196.60302364583</v>
+        <v>46196.7696903125</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>200</v>
@@ -10007,13 +10007,13 @@
         <v>362</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.43500349537</v>
+        <v>46125.60167016204</v>
       </c>
       <c r="C144" s="5">
-        <v>46196.603019988426</v>
+        <v>46196.7696866551</v>
       </c>
       <c r="D144" s="5">
-        <v>46196.60302403935</v>
+        <v>46196.769690706016</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>200</v>
@@ -10060,13 +10060,13 @@
         <v>364</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.43503768518</v>
+        <v>46125.60170435185</v>
       </c>
       <c r="C145" s="8">
-        <v>46196.60302072916</v>
+        <v>46196.769687395834</v>
       </c>
       <c r="D145" s="8">
-        <v>46196.60302447916</v>
+        <v>46196.76969114583</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>200</v>
@@ -10113,13 +10113,13 @@
         <v>365</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.4350728125</v>
+        <v>46125.60173947917</v>
       </c>
       <c r="C146" s="5">
-        <v>46196.60302144676</v>
+        <v>46196.769688113425</v>
       </c>
       <c r="D146" s="5">
-        <v>46196.60302497685</v>
+        <v>46196.76969164352</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>200</v>
@@ -10166,13 +10166,13 @@
         <v>366</v>
       </c>
       <c r="B147" s="8">
-        <v>46122.38508680556</v>
+        <v>46122.551753472224</v>
       </c>
       <c r="C147" s="8">
-        <v>46191.53937342593</v>
+        <v>46191.70604009259</v>
       </c>
       <c r="D147" s="8">
-        <v>46196.60314438658</v>
+        <v>46196.76981105324</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>367</v>
@@ -10229,13 +10229,13 @@
         <v>369</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.43514888889</v>
+        <v>46125.60181555555</v>
       </c>
       <c r="C148" s="5">
-        <v>46196.60312598379</v>
+        <v>46196.76979265046</v>
       </c>
       <c r="D148" s="5">
-        <v>46196.603129027775</v>
+        <v>46196.76979569445</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>200</v>
@@ -10282,13 +10282,13 @@
         <v>370</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.43519024306</v>
+        <v>46125.60185690972</v>
       </c>
       <c r="C149" s="8">
-        <v>46196.603126898146</v>
+        <v>46196.76979356482</v>
       </c>
       <c r="D149" s="8">
-        <v>46196.60312947917</v>
+        <v>46196.76979614583</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>200</v>
@@ -10335,13 +10335,13 @@
         <v>371</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.43523282408</v>
+        <v>46125.601899490735</v>
       </c>
       <c r="C150" s="5">
-        <v>46196.60312755787</v>
+        <v>46196.769794224536</v>
       </c>
       <c r="D150" s="5">
-        <v>46196.603129814815</v>
+        <v>46196.76979648148</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>200</v>
@@ -10388,13 +10388,13 @@
         <v>372</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.43527268519</v>
+        <v>46125.60193935185</v>
       </c>
       <c r="C151" s="8">
-        <v>46196.603098101856</v>
+        <v>46196.76976476852</v>
       </c>
       <c r="D151" s="8">
-        <v>46196.60310020833</v>
+        <v>46196.769766875004</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>200</v>
@@ -10441,13 +10441,13 @@
         <v>373</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.43531043982</v>
+        <v>46125.60197710648</v>
       </c>
       <c r="C152" s="5">
-        <v>46196.603105393515</v>
+        <v>46196.76977206019</v>
       </c>
       <c r="D152" s="5">
-        <v>46196.60310703704</v>
+        <v>46196.76977370371</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>200</v>
@@ -10494,11 +10494,11 @@
         <v>374</v>
       </c>
       <c r="B153" s="8">
-        <v>46122.38509195602</v>
+        <v>46122.551758622685</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46125.422702118056</v>
+        <v>46125.58936878473</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>375</v>
@@ -10541,11 +10541,11 @@
         <v>377</v>
       </c>
       <c r="B154" s="5">
-        <v>46122.38509467593</v>
+        <v>46122.55176134259</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46191.53939100694</v>
+        <v>46191.70605767361</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>378</v>
@@ -10604,11 +10604,11 @@
         <v>381</v>
       </c>
       <c r="B155" s="8">
-        <v>46122.38509943287</v>
+        <v>46122.55176609954</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46192.80717747685</v>
+        <v>46192.97384414352</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>382</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4848,7 +4848,7 @@
         <v>46134.79245146991</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.18981792824</v>
+        <v>46199.18371805556</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>83</v>
@@ -4890,8 +4890,8 @@
       <c r="R53" s="8">
         <v>46198</v>
       </c>
-      <c r="S53" s="12" t="s">
-        <v>74</v>
+      <c r="S53" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T53" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -2778,7 +2778,7 @@
         <v>46181.666399050926</v>
       </c>
       <c r="D19" s="8">
-        <v>46195.20558476852</v>
+        <v>46203.203668229165</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2822,8 +2822,8 @@
       <c r="R19" s="8">
         <v>46202</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>74</v>
+      <c r="S19" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T19" s="9">
         <v>1</v>
@@ -2908,7 +2908,7 @@
         <v>46181.66636053241</v>
       </c>
       <c r="D21" s="8">
-        <v>46195.20558446759</v>
+        <v>46203.20366833333</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2952,8 +2952,8 @@
       <c r="R21" s="8">
         <v>46202</v>
       </c>
-      <c r="S21" s="12" t="s">
-        <v>74</v>
+      <c r="S21" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T21" s="9">
         <v>1</v>
@@ -2973,7 +2973,7 @@
         <v>46181.66637630787</v>
       </c>
       <c r="D22" s="5">
-        <v>46195.20558434028</v>
+        <v>46203.20366849537</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3017,8 +3017,8 @@
       <c r="R22" s="5">
         <v>46202</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>74</v>
+      <c r="S22" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -3038,7 +3038,7 @@
         <v>46181.66643224537</v>
       </c>
       <c r="D23" s="8">
-        <v>46195.205584386575</v>
+        <v>46203.2036682176</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -3082,8 +3082,8 @@
       <c r="R23" s="8">
         <v>46202</v>
       </c>
-      <c r="S23" s="12" t="s">
-        <v>74</v>
+      <c r="S23" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T23" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -1847,13 +1847,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46122.55118912037</v>
+        <v>46122.38452245371</v>
       </c>
       <c r="C4" s="5">
-        <v>46128.59300771991</v>
+        <v>46128.426341053244</v>
       </c>
       <c r="D4" s="5">
-        <v>46158.10300121528</v>
+        <v>46157.93633454861</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1896,13 +1896,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46122.55134571759</v>
+        <v>46122.38467905093</v>
       </c>
       <c r="C5" s="8">
-        <v>46128.59299462963</v>
+        <v>46128.42632796297</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.876021724536</v>
+        <v>46133.70935505787</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1959,13 +1959,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46122.55134947917</v>
+        <v>46122.384682812495</v>
       </c>
       <c r="C6" s="5">
-        <v>46128.59267868055</v>
+        <v>46128.42601201389</v>
       </c>
       <c r="D6" s="5">
-        <v>46128.60382631945</v>
+        <v>46128.43715965278</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2022,13 +2022,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46122.551352546296</v>
+        <v>46122.38468587963</v>
       </c>
       <c r="C7" s="8">
-        <v>46128.59269866898</v>
+        <v>46128.42603200232</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.62726047453</v>
+        <v>46161.460593807875</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2085,13 +2085,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46122.551355567135</v>
+        <v>46122.38468890046</v>
       </c>
       <c r="C8" s="5">
-        <v>46128.59271722222</v>
+        <v>46128.42605055556</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.60400607639</v>
+        <v>46128.43733940972</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2148,13 +2148,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46122.551359386576</v>
+        <v>46122.384692719905</v>
       </c>
       <c r="C9" s="8">
-        <v>46128.592850057874</v>
+        <v>46128.4261833912</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.83577310185</v>
+        <v>46156.66910643518</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2211,13 +2211,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46122.55119412037</v>
+        <v>46122.3845274537</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.93280347223</v>
+        <v>46193.766136805556</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.9328209838</v>
+        <v>46193.76615431713</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2264,13 +2264,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46122.5513631713</v>
+        <v>46122.384696504625</v>
       </c>
       <c r="C11" s="8">
-        <v>46128.60435520833</v>
+        <v>46128.43768854167</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.97382803241</v>
+        <v>46192.80716136574</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2329,13 +2329,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46122.551369050925</v>
+        <v>46122.38470238426</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.60643114583</v>
+        <v>46128.43976447917</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.97382813657</v>
+        <v>46192.80716146991</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2394,13 +2394,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46122.5513746875</v>
+        <v>46122.384708020836</v>
       </c>
       <c r="C13" s="8">
-        <v>46132.57072561343</v>
+        <v>46132.40405894676</v>
       </c>
       <c r="D13" s="8">
-        <v>46192.97382800926</v>
+        <v>46192.80716134259</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2459,13 +2459,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46122.553594178244</v>
+        <v>46122.38692751157</v>
       </c>
       <c r="C14" s="5">
-        <v>46128.60941575232</v>
+        <v>46128.44274908565</v>
       </c>
       <c r="D14" s="5">
-        <v>46136.20601917824</v>
+        <v>46136.03935251157</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2524,13 +2524,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46122.55119946759</v>
+        <v>46122.38453280093</v>
       </c>
       <c r="C15" s="8">
-        <v>46195.50723163194</v>
+        <v>46195.34056496528</v>
       </c>
       <c r="D15" s="8">
-        <v>46195.50724608796</v>
+        <v>46195.340579421296</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2577,13 +2577,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46122.55138855324</v>
+        <v>46122.38472188657</v>
       </c>
       <c r="C16" s="5">
-        <v>46128.60700391204</v>
+        <v>46128.44033724537</v>
       </c>
       <c r="D16" s="5">
-        <v>46133.17999505787</v>
+        <v>46133.0133283912</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2642,13 +2642,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46122.55139482639</v>
+        <v>46122.38472815973</v>
       </c>
       <c r="C17" s="8">
-        <v>46128.60701157407</v>
+        <v>46128.44034490741</v>
       </c>
       <c r="D17" s="8">
-        <v>46132.182206921294</v>
+        <v>46132.01554025463</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2707,13 +2707,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46122.55140040509</v>
+        <v>46122.38473373842</v>
       </c>
       <c r="C18" s="5">
-        <v>46195.50721171296</v>
+        <v>46195.340545046296</v>
       </c>
       <c r="D18" s="5">
-        <v>46195.50723229167</v>
+        <v>46195.340565624996</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2772,13 +2772,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46122.55140604167</v>
+        <v>46122.384739375004</v>
       </c>
       <c r="C19" s="8">
-        <v>46181.666399050926</v>
+        <v>46181.499732384254</v>
       </c>
       <c r="D19" s="8">
-        <v>46203.203668229165</v>
+        <v>46203.0370015625</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2837,13 +2837,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46122.55141162037</v>
+        <v>46122.3847449537</v>
       </c>
       <c r="C20" s="5">
-        <v>46128.609497881946</v>
+        <v>46128.442831215274</v>
       </c>
       <c r="D20" s="5">
-        <v>46132.1822065625</v>
+        <v>46132.01553989583</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>64</v>
@@ -2902,13 +2902,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46122.566545787035</v>
+        <v>46122.39987912037</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.66636053241</v>
+        <v>46181.49969386574</v>
       </c>
       <c r="D21" s="8">
-        <v>46203.20366833333</v>
+        <v>46203.03700166667</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2967,13 +2967,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46122.56661521991</v>
+        <v>46122.39994855324</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.66637630787</v>
+        <v>46181.499709641204</v>
       </c>
       <c r="D22" s="5">
-        <v>46203.20366849537</v>
+        <v>46203.03700182871</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3032,13 +3032,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="8">
-        <v>46122.57286273148</v>
+        <v>46122.40619606481</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.66643224537</v>
+        <v>46181.4997655787</v>
       </c>
       <c r="D23" s="8">
-        <v>46203.2036682176</v>
+        <v>46203.037001550925</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -3097,13 +3097,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46122.55120394676</v>
+        <v>46122.38453728009</v>
       </c>
       <c r="C24" s="5">
-        <v>46195.50733982639</v>
+        <v>46195.34067315972</v>
       </c>
       <c r="D24" s="5">
-        <v>46195.50735353009</v>
+        <v>46195.34068686343</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -3150,13 +3150,13 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46122.55141694444</v>
+        <v>46122.38475027778</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.626168703704</v>
+        <v>46174.45950203703</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.626181134256</v>
+        <v>46174.45951446759</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -3215,13 +3215,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46122.55142208333</v>
+        <v>46122.38475541667</v>
       </c>
       <c r="C26" s="5">
-        <v>46174.62325291667</v>
+        <v>46174.45658625</v>
       </c>
       <c r="D26" s="5">
-        <v>46174.62325449074</v>
+        <v>46174.456587824076</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3276,13 +3276,13 @@
         <v>110</v>
       </c>
       <c r="B27" s="8">
-        <v>46122.55142699074</v>
+        <v>46122.38476032407</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.626152893514</v>
+        <v>46174.45948622686</v>
       </c>
       <c r="D27" s="8">
-        <v>46174.62615429398</v>
+        <v>46174.45948762732</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>111</v>
@@ -3337,13 +3337,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46122.5514322338</v>
+        <v>46122.38476556713</v>
       </c>
       <c r="C28" s="5">
-        <v>46195.50732521991</v>
+        <v>46195.340658553236</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.71184679398</v>
+        <v>46195.545180127316</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3402,13 +3402,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="8">
-        <v>46122.551437546295</v>
+        <v>46122.38477087963</v>
       </c>
       <c r="C29" s="8">
-        <v>46195.71138274306</v>
+        <v>46195.54471607639</v>
       </c>
       <c r="D29" s="8">
-        <v>46195.71138517361</v>
+        <v>46195.54471850695</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>118</v>
@@ -3463,13 +3463,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46122.55144255787</v>
+        <v>46122.3847758912</v>
       </c>
       <c r="C30" s="5">
-        <v>46195.711830960645</v>
+        <v>46195.54516429398</v>
       </c>
       <c r="D30" s="5">
-        <v>46195.711832500005</v>
+        <v>46195.54516583333</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3524,13 +3524,13 @@
         <v>123</v>
       </c>
       <c r="B31" s="8">
-        <v>46122.551447708334</v>
+        <v>46122.38478104166</v>
       </c>
       <c r="C31" s="8">
-        <v>46133.82779993056</v>
+        <v>46133.661133263886</v>
       </c>
       <c r="D31" s="8">
-        <v>46133.82781321759</v>
+        <v>46133.66114655093</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>124</v>
@@ -3589,13 +3589,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46122.5514527662</v>
+        <v>46122.38478609954</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.827731122685</v>
+        <v>46133.66106445601</v>
       </c>
       <c r="D32" s="5">
-        <v>46133.82773260417</v>
+        <v>46133.6610659375</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3650,13 +3650,13 @@
         <v>129</v>
       </c>
       <c r="B33" s="8">
-        <v>46122.55145796297</v>
+        <v>46122.384791296296</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.827786875</v>
+        <v>46133.66112020833</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.82778807871</v>
+        <v>46133.661121412035</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>130</v>
@@ -3711,13 +3711,13 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46122.55146299768</v>
+        <v>46122.38479633102</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.82776796297</v>
+        <v>46133.6611012963</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.827769131945</v>
+        <v>46133.66110246528</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3772,13 +3772,13 @@
         <v>135</v>
       </c>
       <c r="B35" s="8">
-        <v>46122.55146795139</v>
+        <v>46122.38480128472</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.66687207176</v>
+        <v>46181.50020540509</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.66688577546</v>
+        <v>46181.5002191088</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3837,13 +3837,13 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46122.551472974534</v>
+        <v>46122.38480630787</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.66681767361</v>
+        <v>46181.50015100694</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.66681946759</v>
+        <v>46181.50015280093</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3898,13 +3898,13 @@
         <v>143</v>
       </c>
       <c r="B37" s="8">
-        <v>46122.55152253472</v>
+        <v>46122.384855868055</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.66685679398</v>
+        <v>46181.50019012731</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.66685818287</v>
+        <v>46181.5001915162</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>144</v>
@@ -3959,13 +3959,13 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46122.55152891204</v>
+        <v>46122.384862245366</v>
       </c>
       <c r="C38" s="5">
-        <v>46154.867667812505</v>
+        <v>46154.70100114583</v>
       </c>
       <c r="D38" s="5">
-        <v>46189.172213136575</v>
+        <v>46189.00554646991</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -4024,13 +4024,13 @@
         <v>149</v>
       </c>
       <c r="B39" s="8">
-        <v>46122.5515340625</v>
+        <v>46122.384867395835</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.86751693287</v>
+        <v>46154.70085026621</v>
       </c>
       <c r="D39" s="8">
-        <v>46154.86751927083</v>
+        <v>46154.70085260417</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>87</v>
@@ -4079,13 +4079,13 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46122.55153844907</v>
+        <v>46122.38487178241</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.867576273144</v>
+        <v>46154.70090960649</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.867577453704</v>
+        <v>46154.70091078704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4134,13 +4134,13 @@
         <v>154</v>
       </c>
       <c r="B41" s="8">
-        <v>46122.574933449076</v>
+        <v>46122.40826678241</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.666767002316</v>
+        <v>46181.500100335645</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.666783252316</v>
+        <v>46181.50011658565</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>155</v>
@@ -4199,13 +4199,13 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46122.575920972224</v>
+        <v>46122.40925430556</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.66670739584</v>
+        <v>46181.500040729166</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.66670855324</v>
+        <v>46181.500041886575</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>90</v>
@@ -4254,13 +4254,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46122.57608475695</v>
+        <v>46122.409418090276</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.666752812496</v>
+        <v>46181.50008614583</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.666754351856</v>
+        <v>46181.500087685185</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4309,13 +4309,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46122.57501438657</v>
+        <v>46122.40834771991</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.666958472226</v>
+        <v>46181.500291805554</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.66706865741</v>
+        <v>46181.500401990736</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4374,13 +4374,13 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46122.57922111111</v>
+        <v>46122.41255444444</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.666901516204</v>
+        <v>46181.50023484953</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.66690306713</v>
+        <v>46181.50023640046</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>96</v>
@@ -4429,13 +4429,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46122.57949202546</v>
+        <v>46122.4128253588</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.66694322917</v>
+        <v>46181.500276562496</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.66694460648</v>
+        <v>46181.50027793982</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4484,13 +4484,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46125.529618217595</v>
+        <v>46125.362951550924</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.66722120371</v>
+        <v>46181.50055453704</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.66723511574</v>
+        <v>46181.500568449075</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4549,13 +4549,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46125.52977997685</v>
+        <v>46125.36311331019</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.66715732639</v>
+        <v>46181.50049065972</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.66715912037</v>
+        <v>46181.500492453706</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>93</v>
@@ -4604,13 +4604,13 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46125.52991815972</v>
+        <v>46125.36325149305</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.66720412037</v>
+        <v>46181.5005374537</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.66720563658</v>
+        <v>46181.50053896991</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4659,13 +4659,13 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46122.55120855324</v>
+        <v>46122.384541886575</v>
       </c>
       <c r="C50" s="5">
-        <v>46195.5074512963</v>
+        <v>46195.34078462963</v>
       </c>
       <c r="D50" s="5">
-        <v>46195.50756488426</v>
+        <v>46195.34089821759</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4712,13 +4712,13 @@
         <v>183</v>
       </c>
       <c r="B51" s="8">
-        <v>46122.55154344907</v>
+        <v>46122.38487678241</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.79584481481</v>
+        <v>46133.62917814815</v>
       </c>
       <c r="D51" s="8">
-        <v>46143.171145879634</v>
+        <v>46143.00447921296</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>184</v>
@@ -4777,13 +4777,13 @@
         <v>188</v>
       </c>
       <c r="B52" s="5">
-        <v>46122.551548993055</v>
+        <v>46122.38488232639</v>
       </c>
       <c r="C52" s="5">
-        <v>46134.79240423611</v>
+        <v>46134.62573756944</v>
       </c>
       <c r="D52" s="5">
-        <v>46198.18781711806</v>
+        <v>46198.021150451386</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4842,13 +4842,13 @@
         <v>192</v>
       </c>
       <c r="B53" s="8">
-        <v>46122.55155721065</v>
+        <v>46122.38489054398</v>
       </c>
       <c r="C53" s="8">
-        <v>46134.79245146991</v>
+        <v>46134.62578480324</v>
       </c>
       <c r="D53" s="8">
-        <v>46199.18371805556</v>
+        <v>46199.01705138889</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>83</v>
@@ -4905,13 +4905,13 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46122.55156568287</v>
+        <v>46122.38489901621</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.50761325231</v>
+        <v>46195.34094658565</v>
       </c>
       <c r="D54" s="5">
-        <v>46196.76907818287</v>
+        <v>46196.6024115162</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -4968,13 +4968,13 @@
         <v>199</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.603622118055</v>
+        <v>46125.43695545139</v>
       </c>
       <c r="C55" s="8">
-        <v>46196.76904752315</v>
+        <v>46196.60238085648</v>
       </c>
       <c r="D55" s="8">
-        <v>46196.7690521412</v>
+        <v>46196.602385474536</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>200</v>
@@ -5021,13 +5021,13 @@
         <v>202</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.60367094907</v>
+        <v>46125.43700428241</v>
       </c>
       <c r="C56" s="5">
-        <v>46196.769048449074</v>
+        <v>46196.6023817824</v>
       </c>
       <c r="D56" s="5">
-        <v>46196.769052523145</v>
+        <v>46196.60238585648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -5074,13 +5074,13 @@
         <v>203</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.60371951389</v>
+        <v>46125.43705284722</v>
       </c>
       <c r="C57" s="8">
-        <v>46196.76904929398</v>
+        <v>46196.602382627316</v>
       </c>
       <c r="D57" s="8">
-        <v>46196.76905283565</v>
+        <v>46196.60238616898</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5127,13 +5127,13 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.60376462963</v>
+        <v>46125.43709796296</v>
       </c>
       <c r="C58" s="5">
-        <v>46196.769050069444</v>
+        <v>46196.60238340277</v>
       </c>
       <c r="D58" s="5">
-        <v>46196.76905314815</v>
+        <v>46196.60238648148</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>200</v>
@@ -5180,13 +5180,13 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.60381739584</v>
+        <v>46125.437150729165</v>
       </c>
       <c r="C59" s="8">
-        <v>46196.76905077546</v>
+        <v>46196.602384108795</v>
       </c>
       <c r="D59" s="8">
-        <v>46196.76905349537</v>
+        <v>46196.6023868287</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>200</v>
@@ -5233,13 +5233,13 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46122.551569710646</v>
+        <v>46122.38490304398</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.6677724537</v>
+        <v>46181.501105787036</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.66785324074</v>
+        <v>46181.501186574074</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5282,13 +5282,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46122.55157321759</v>
+        <v>46122.38490655093</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.667378032405</v>
+        <v>46181.50071136574</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.66739524306</v>
+        <v>46181.500728576386</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5347,13 +5347,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46122.58491638889</v>
+        <v>46122.41824972222</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.667413206014</v>
+        <v>46181.50074653935</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.667429016205</v>
+        <v>46181.50076234953</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5412,13 +5412,13 @@
         <v>217</v>
       </c>
       <c r="B63" s="8">
-        <v>46125.53102658565</v>
+        <v>46125.36435991898</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.667430127316</v>
+        <v>46181.500763460645</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.66744925926</v>
+        <v>46181.50078259259</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -5477,13 +5477,13 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46122.55157846065</v>
+        <v>46122.38491179398</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.66775587963</v>
+        <v>46181.501089212965</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.66777241898</v>
+        <v>46181.501105752315</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5542,13 +5542,13 @@
         <v>225</v>
       </c>
       <c r="B65" s="8">
-        <v>46122.551583831024</v>
+        <v>46122.38491716435</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.6687946875</v>
+        <v>46181.50212802083</v>
       </c>
       <c r="D65" s="8">
-        <v>46181.66890770833</v>
+        <v>46181.50224104167</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>226</v>
@@ -5591,13 +5591,13 @@
         <v>228</v>
       </c>
       <c r="B66" s="5">
-        <v>46122.55158688658</v>
+        <v>46122.384920219905</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.666093576394</v>
+        <v>46181.49942690972</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.66880932871</v>
+        <v>46181.50214266204</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>229</v>
@@ -5656,13 +5656,13 @@
         <v>233</v>
       </c>
       <c r="B67" s="8">
-        <v>46122.55159185185</v>
+        <v>46122.384925185186</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.6661986574</v>
+        <v>46181.49953199074</v>
       </c>
       <c r="D67" s="8">
-        <v>46181.668846064815</v>
+        <v>46181.50217939814</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>234</v>
@@ -5721,13 +5721,13 @@
         <v>236</v>
       </c>
       <c r="B68" s="5">
-        <v>46125.595811921296</v>
+        <v>46125.42914525463</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.66807699074</v>
+        <v>46181.501410324076</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.66807884259</v>
+        <v>46181.50141217593</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>237</v>
@@ -5776,13 +5776,13 @@
         <v>240</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.59610047453</v>
+        <v>46125.42943380787</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.66808581019</v>
+        <v>46181.50141914352</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.66808728009</v>
+        <v>46181.50142061342</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>200</v>
@@ -5831,13 +5831,13 @@
         <v>241</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.59621038195</v>
+        <v>46125.429543715276</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.66815399306</v>
+        <v>46181.501487326386</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.66815550926</v>
+        <v>46181.501488842594</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>200</v>
@@ -5886,13 +5886,13 @@
         <v>242</v>
       </c>
       <c r="B71" s="8">
-        <v>46125.59625472222</v>
+        <v>46125.42958805556</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.668166689815</v>
+        <v>46181.50150002315</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.66816819445</v>
+        <v>46181.501501527775</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>200</v>
@@ -5941,13 +5941,13 @@
         <v>243</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.59629915509</v>
+        <v>46125.42963248843</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.66817956018</v>
+        <v>46181.50151289352</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.66818078703</v>
+        <v>46181.50151412037</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>200</v>
@@ -5996,13 +5996,13 @@
         <v>244</v>
       </c>
       <c r="B73" s="8">
-        <v>46122.55159751157</v>
+        <v>46122.384930844906</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.66878061343</v>
+        <v>46181.50211394676</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.66878222222</v>
+        <v>46181.50211555556</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>245</v>
@@ -6061,13 +6061,13 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46125.59648849537</v>
+        <v>46125.4298218287</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.668651921296</v>
+        <v>46181.501985254625</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.6686533912</v>
+        <v>46181.501986724536</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>200</v>
@@ -6116,13 +6116,13 @@
         <v>249</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.59661854166</v>
+        <v>46125.429951875005</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.66866650463</v>
+        <v>46181.50199983796</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.66866782407</v>
+        <v>46181.50200115741</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>200</v>
@@ -6171,13 +6171,13 @@
         <v>251</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.596668750004</v>
+        <v>46125.43000208333</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.66867587963</v>
+        <v>46181.50200921296</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.66867745371</v>
+        <v>46181.50201078704</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>200</v>
@@ -6226,13 +6226,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="8">
-        <v>46125.59671550926</v>
+        <v>46125.430048842594</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.668685625</v>
+        <v>46181.50201895833</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.668687060184</v>
+        <v>46181.50202039352</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>200</v>
@@ -6281,13 +6281,13 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.59675546296</v>
+        <v>46125.430088796296</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.66870385417</v>
+        <v>46181.5020371875</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.66870502315</v>
+        <v>46181.502038356484</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>200</v>
@@ -6336,13 +6336,13 @@
         <v>255</v>
       </c>
       <c r="B79" s="8">
-        <v>46122.55160357639</v>
+        <v>46122.38493690972</v>
       </c>
       <c r="C79" s="8">
-        <v>46195.563125636574</v>
+        <v>46195.3964589699</v>
       </c>
       <c r="D79" s="8">
-        <v>46195.563290335645</v>
+        <v>46195.39662366898</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>207</v>
@@ -6389,13 +6389,13 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46122.55160679398</v>
+        <v>46122.38494012732</v>
       </c>
       <c r="C80" s="5">
-        <v>46195.563269363425</v>
+        <v>46195.39660269676</v>
       </c>
       <c r="D80" s="5">
-        <v>46195.711846817125</v>
+        <v>46195.54518015047</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6454,13 +6454,13 @@
         <v>260</v>
       </c>
       <c r="B81" s="8">
-        <v>46122.551612256946</v>
+        <v>46122.38494559028</v>
       </c>
       <c r="C81" s="8">
-        <v>46195.50751318287</v>
+        <v>46195.34084651621</v>
       </c>
       <c r="D81" s="8">
-        <v>46195.50753130787</v>
+        <v>46195.3408646412</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>261</v>
@@ -6519,13 +6519,13 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46122.55161756944</v>
+        <v>46122.38495090278</v>
       </c>
       <c r="C82" s="5">
-        <v>46195.50751851852</v>
+        <v>46195.340851851855</v>
       </c>
       <c r="D82" s="5">
-        <v>46195.50753259259</v>
+        <v>46195.34086592593</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6584,13 +6584,13 @@
         <v>264</v>
       </c>
       <c r="B83" s="8">
-        <v>46122.55162288195</v>
+        <v>46122.384956215275</v>
       </c>
       <c r="C83" s="8">
-        <v>46195.507523437496</v>
+        <v>46195.34085677083</v>
       </c>
       <c r="D83" s="8">
-        <v>46195.507539479164</v>
+        <v>46195.3408728125</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>265</v>
@@ -6649,13 +6649,13 @@
         <v>266</v>
       </c>
       <c r="B84" s="5">
-        <v>46122.59399163195</v>
+        <v>46122.427324965276</v>
       </c>
       <c r="C84" s="5">
-        <v>46193.93315311342</v>
+        <v>46193.76648644676</v>
       </c>
       <c r="D84" s="5">
-        <v>46193.9332800463</v>
+        <v>46193.76661337963</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>267</v>
@@ -6714,13 +6714,13 @@
         <v>269</v>
       </c>
       <c r="B85" s="8">
-        <v>46122.551628182875</v>
+        <v>46122.3849615162</v>
       </c>
       <c r="C85" s="8">
-        <v>46195.5630599537</v>
+        <v>46195.39639328704</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.769192685184</v>
+        <v>46196.60252601852</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>270</v>
@@ -6767,13 +6767,13 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46122.55163158565</v>
+        <v>46122.38496491898</v>
       </c>
       <c r="C86" s="5">
-        <v>46195.50768850694</v>
+        <v>46195.34102184028</v>
       </c>
       <c r="D86" s="5">
-        <v>46195.507707129625</v>
+        <v>46195.34104046296</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>273</v>
@@ -6832,13 +6832,13 @@
         <v>275</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.5974969213</v>
+        <v>46125.43083025463</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.76791707176</v>
+        <v>46196.60125040509</v>
       </c>
       <c r="D87" s="8">
-        <v>46196.767918831014</v>
+        <v>46196.60125216436</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>200</v>
@@ -6887,13 +6887,13 @@
         <v>277</v>
       </c>
       <c r="B88" s="5">
-        <v>46125.59754570602</v>
+        <v>46125.430879039355</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.76795405093</v>
+        <v>46196.601287384256</v>
       </c>
       <c r="D88" s="5">
-        <v>46196.76795645834</v>
+        <v>46196.601289791666</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>200</v>
@@ -6942,13 +6942,13 @@
         <v>278</v>
       </c>
       <c r="B89" s="8">
-        <v>46125.59760710648</v>
+        <v>46125.430940439815</v>
       </c>
       <c r="C89" s="8">
-        <v>46196.767928217596</v>
+        <v>46196.601261550924</v>
       </c>
       <c r="D89" s="8">
-        <v>46196.76793001157</v>
+        <v>46196.601263344906</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>200</v>
@@ -6997,13 +6997,13 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46125.59765891204</v>
+        <v>46125.43099224537</v>
       </c>
       <c r="C90" s="5">
-        <v>46196.76794651621</v>
+        <v>46196.601279849536</v>
       </c>
       <c r="D90" s="5">
-        <v>46196.76794809027</v>
+        <v>46196.60128142362</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>200</v>
@@ -7052,13 +7052,13 @@
         <v>280</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.597703391206</v>
+        <v>46125.431036724534</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.76794100694</v>
+        <v>46196.60127434028</v>
       </c>
       <c r="D91" s="8">
-        <v>46196.76794287037</v>
+        <v>46196.6012762037</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>200</v>
@@ -7107,13 +7107,13 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46122.55170659722</v>
+        <v>46122.38503993055</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.76755512731</v>
+        <v>46196.60088846065</v>
       </c>
       <c r="D92" s="5">
-        <v>46196.76807780092</v>
+        <v>46196.60141113426</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>282</v>
@@ -7172,13 +7172,13 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46125.59982741898</v>
+        <v>46125.43316075232</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.76800195602</v>
+        <v>46196.60133528935</v>
       </c>
       <c r="D93" s="8">
-        <v>46196.76800386574</v>
+        <v>46196.60133719907</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>200</v>
@@ -7227,13 +7227,13 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.599890833335</v>
+        <v>46125.43322416667</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.768023020835</v>
+        <v>46196.601356354164</v>
       </c>
       <c r="D94" s="5">
-        <v>46196.768024687495</v>
+        <v>46196.60135802084</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>200</v>
@@ -7282,13 +7282,13 @@
         <v>288</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.59993134259</v>
+        <v>46125.43326467593</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.76801494213</v>
+        <v>46196.601348275464</v>
       </c>
       <c r="D95" s="8">
-        <v>46196.76801675926</v>
+        <v>46196.60135009259</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>200</v>
@@ -7337,13 +7337,13 @@
         <v>289</v>
       </c>
       <c r="B96" s="5">
-        <v>46125.59996929398</v>
+        <v>46125.433302627316</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.76805109954</v>
+        <v>46196.60138443287</v>
       </c>
       <c r="D96" s="5">
-        <v>46196.76805278935</v>
+        <v>46196.60138612268</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>200</v>
@@ -7392,13 +7392,13 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46125.6000115162</v>
+        <v>46125.43334484954</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.76805706018</v>
+        <v>46196.60139039352</v>
       </c>
       <c r="D97" s="8">
-        <v>46196.76805907408</v>
+        <v>46196.60139240741</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>200</v>
@@ -7447,13 +7447,13 @@
         <v>291</v>
       </c>
       <c r="B98" s="5">
-        <v>46122.55164413195</v>
+        <v>46122.38497746528</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.76839824074</v>
+        <v>46196.601731574076</v>
       </c>
       <c r="D98" s="5">
-        <v>46196.76840872686</v>
+        <v>46196.601742060186</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>292</v>
@@ -7512,13 +7512,13 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46125.599162743056</v>
+        <v>46125.43249607639</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.76818966435</v>
+        <v>46196.601522997684</v>
       </c>
       <c r="D99" s="8">
-        <v>46196.7681912963</v>
+        <v>46196.60152462963</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>200</v>
@@ -7567,13 +7567,13 @@
         <v>297</v>
       </c>
       <c r="B100" s="5">
-        <v>46125.599302511575</v>
+        <v>46125.4326358449</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.76820421296</v>
+        <v>46196.601537546296</v>
       </c>
       <c r="D100" s="5">
-        <v>46196.76820597222</v>
+        <v>46196.60153930556</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>200</v>
@@ -7622,13 +7622,13 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46125.59934644676</v>
+        <v>46125.43267978009</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.768375949076</v>
+        <v>46196.601709282404</v>
       </c>
       <c r="D101" s="8">
-        <v>46196.76837958333</v>
+        <v>46196.60171291667</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>200</v>
@@ -7677,13 +7677,13 @@
         <v>299</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.59938857639</v>
+        <v>46125.43272190972</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.76837696759</v>
+        <v>46196.60171030092</v>
       </c>
       <c r="D102" s="5">
-        <v>46196.76838008102</v>
+        <v>46196.60171341435</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>200</v>
@@ -7732,13 +7732,13 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46125.59943094908</v>
+        <v>46125.43276428241</v>
       </c>
       <c r="C103" s="8">
-        <v>46196.76837790509</v>
+        <v>46196.60171123843</v>
       </c>
       <c r="D103" s="8">
-        <v>46196.768380520836</v>
+        <v>46196.601713854165</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>200</v>
@@ -7787,13 +7787,13 @@
         <v>301</v>
       </c>
       <c r="B104" s="5">
-        <v>46122.551650995374</v>
+        <v>46122.3849843287</v>
       </c>
       <c r="C104" s="5">
-        <v>46196.76854788195</v>
+        <v>46196.601881215276</v>
       </c>
       <c r="D104" s="5">
-        <v>46196.76856074074</v>
+        <v>46196.601894074076</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>302</v>
@@ -7852,13 +7852,13 @@
         <v>303</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.59953013889</v>
+        <v>46125.43286347222</v>
       </c>
       <c r="C105" s="8">
-        <v>46196.76852783565</v>
+        <v>46196.60186116898</v>
       </c>
       <c r="D105" s="8">
-        <v>46196.768531724534</v>
+        <v>46196.60186505787</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>200</v>
@@ -7907,13 +7907,13 @@
         <v>305</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.59961423611</v>
+        <v>46125.43294756944</v>
       </c>
       <c r="C106" s="5">
-        <v>46196.76846329861</v>
+        <v>46196.60179663195</v>
       </c>
       <c r="D106" s="5">
-        <v>46196.76846496528</v>
+        <v>46196.60179829861</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>200</v>
@@ -7962,13 +7962,13 @@
         <v>306</v>
       </c>
       <c r="B107" s="8">
-        <v>46125.599654317135</v>
+        <v>46125.43298765046</v>
       </c>
       <c r="C107" s="8">
-        <v>46196.768528796296</v>
+        <v>46196.601862129624</v>
       </c>
       <c r="D107" s="8">
-        <v>46196.76853203704</v>
+        <v>46196.601865370365</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>200</v>
@@ -8017,13 +8017,13 @@
         <v>307</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.59957065972</v>
+        <v>46125.43290399306</v>
       </c>
       <c r="C108" s="5">
-        <v>46196.768529548615</v>
+        <v>46196.601862881944</v>
       </c>
       <c r="D108" s="5">
-        <v>46196.76853233796</v>
+        <v>46196.6018656713</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>200</v>
@@ -8072,13 +8072,13 @@
         <v>308</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.59969711806</v>
+        <v>46125.433030451386</v>
       </c>
       <c r="C109" s="8">
-        <v>46196.7685304051</v>
+        <v>46196.601863738426</v>
       </c>
       <c r="D109" s="8">
-        <v>46196.76853265046</v>
+        <v>46196.6018659838</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>200</v>
@@ -8127,13 +8127,13 @@
         <v>309</v>
       </c>
       <c r="B110" s="5">
-        <v>46122.55163725694</v>
+        <v>46122.38497059028</v>
       </c>
       <c r="C110" s="5">
-        <v>46196.76866755787</v>
+        <v>46196.6020008912</v>
       </c>
       <c r="D110" s="5">
-        <v>46196.76867908565</v>
+        <v>46196.60201241898</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>310</v>
@@ -8192,13 +8192,13 @@
         <v>311</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.59780210648</v>
+        <v>46125.431135439816</v>
       </c>
       <c r="C111" s="8">
-        <v>46196.76864902778</v>
+        <v>46196.60198236111</v>
       </c>
       <c r="D111" s="8">
-        <v>46196.76865387731</v>
+        <v>46196.60198721065</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>200</v>
@@ -8247,13 +8247,13 @@
         <v>314</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.597836932866</v>
+        <v>46125.43117026621</v>
       </c>
       <c r="C112" s="5">
-        <v>46196.76865</v>
+        <v>46196.601983333334</v>
       </c>
       <c r="D112" s="5">
-        <v>46196.76865427083</v>
+        <v>46196.60198760417</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>200</v>
@@ -8302,13 +8302,13 @@
         <v>315</v>
       </c>
       <c r="B113" s="8">
-        <v>46125.5979208912</v>
+        <v>46125.43125422453</v>
       </c>
       <c r="C113" s="8">
-        <v>46196.76865077546</v>
+        <v>46196.6019841088</v>
       </c>
       <c r="D113" s="8">
-        <v>46196.76865460648</v>
+        <v>46196.601987939815</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>200</v>
@@ -8357,13 +8357,13 @@
         <v>316</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.59788087963</v>
+        <v>46125.431214212964</v>
       </c>
       <c r="C114" s="5">
-        <v>46196.768651527775</v>
+        <v>46196.60198486111</v>
       </c>
       <c r="D114" s="5">
-        <v>46196.768654942134</v>
+        <v>46196.60198827546</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>200</v>
@@ -8412,13 +8412,13 @@
         <v>317</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.597965023146</v>
+        <v>46125.43129835648</v>
       </c>
       <c r="C115" s="8">
-        <v>46196.768652314815</v>
+        <v>46196.60198564814</v>
       </c>
       <c r="D115" s="8">
-        <v>46196.768655312495</v>
+        <v>46196.60198864584</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>200</v>
@@ -8467,13 +8467,13 @@
         <v>318</v>
       </c>
       <c r="B116" s="5">
-        <v>46122.55172043982</v>
+        <v>46122.38505377315</v>
       </c>
       <c r="C116" s="5">
-        <v>46196.76877224537</v>
+        <v>46196.6021055787</v>
       </c>
       <c r="D116" s="5">
-        <v>46196.768798784724</v>
+        <v>46196.60213211806</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>319</v>
@@ -8532,13 +8532,13 @@
         <v>320</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.60038253472</v>
+        <v>46125.43371586806</v>
       </c>
       <c r="C117" s="8">
-        <v>46196.76875258102</v>
+        <v>46196.602085914354</v>
       </c>
       <c r="D117" s="8">
-        <v>46196.768757337966</v>
+        <v>46196.602090671295</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>200</v>
@@ -8585,13 +8585,13 @@
         <v>322</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.60043012731</v>
+        <v>46125.43376346065</v>
       </c>
       <c r="C118" s="5">
-        <v>46196.7687534838</v>
+        <v>46196.60208681713</v>
       </c>
       <c r="D118" s="5">
-        <v>46196.76875768519</v>
+        <v>46196.60209101852</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>200</v>
@@ -8638,13 +8638,13 @@
         <v>323</v>
       </c>
       <c r="B119" s="8">
-        <v>46125.60047290509</v>
+        <v>46125.43380623843</v>
       </c>
       <c r="C119" s="8">
-        <v>46196.768754178236</v>
+        <v>46196.60208751158</v>
       </c>
       <c r="D119" s="8">
-        <v>46196.76875800926</v>
+        <v>46196.60209134259</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>200</v>
@@ -8691,13 +8691,13 @@
         <v>324</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.600514074074</v>
+        <v>46125.4338474074</v>
       </c>
       <c r="C120" s="5">
-        <v>46196.768754930556</v>
+        <v>46196.602088263884</v>
       </c>
       <c r="D120" s="5">
-        <v>46196.76875832176</v>
+        <v>46196.60209165509</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>200</v>
@@ -8744,13 +8744,13 @@
         <v>325</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.60055859954</v>
+        <v>46125.43389193287</v>
       </c>
       <c r="C121" s="8">
-        <v>46196.7687558912</v>
+        <v>46196.602089224536</v>
       </c>
       <c r="D121" s="8">
-        <v>46196.76875862268</v>
+        <v>46196.60209195602</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>200</v>
@@ -8797,13 +8797,13 @@
         <v>326</v>
       </c>
       <c r="B122" s="5">
-        <v>46122.55172986111</v>
+        <v>46122.385063194444</v>
       </c>
       <c r="C122" s="5">
-        <v>46196.76917457176</v>
+        <v>46196.60250790509</v>
       </c>
       <c r="D122" s="5">
-        <v>46196.76918584491</v>
+        <v>46196.60251917824</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>327</v>
@@ -8862,13 +8862,13 @@
         <v>329</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.60064416667</v>
+        <v>46125.4339775</v>
       </c>
       <c r="C123" s="8">
-        <v>46196.76915099537</v>
+        <v>46196.6024843287</v>
       </c>
       <c r="D123" s="8">
-        <v>46196.76915743056</v>
+        <v>46196.60249076389</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>200</v>
@@ -8915,13 +8915,13 @@
         <v>331</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.60068740741</v>
+        <v>46125.43402074074</v>
       </c>
       <c r="C124" s="5">
-        <v>46196.76915237268</v>
+        <v>46196.60248570602</v>
       </c>
       <c r="D124" s="5">
-        <v>46196.76915791667</v>
+        <v>46196.60249125</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>200</v>
@@ -8968,13 +8968,13 @@
         <v>332</v>
       </c>
       <c r="B125" s="8">
-        <v>46125.60073844907</v>
+        <v>46125.43407178241</v>
       </c>
       <c r="C125" s="8">
-        <v>46196.76915341435</v>
+        <v>46196.60248674768</v>
       </c>
       <c r="D125" s="8">
-        <v>46196.76915841435</v>
+        <v>46196.60249174769</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>200</v>
@@ -9021,13 +9021,13 @@
         <v>333</v>
       </c>
       <c r="B126" s="5">
-        <v>46125.60077622686</v>
+        <v>46125.434109560185</v>
       </c>
       <c r="C126" s="5">
-        <v>46196.76915438657</v>
+        <v>46196.60248771991</v>
       </c>
       <c r="D126" s="5">
-        <v>46196.769158842595</v>
+        <v>46196.60249217592</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>200</v>
@@ -9074,13 +9074,13 @@
         <v>334</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.600829143514</v>
+        <v>46125.43416247686</v>
       </c>
       <c r="C127" s="8">
-        <v>46196.769155358794</v>
+        <v>46196.60248869213</v>
       </c>
       <c r="D127" s="8">
-        <v>46196.76915931713</v>
+        <v>46196.60249265046</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>200</v>
@@ -9127,13 +9127,13 @@
         <v>335</v>
       </c>
       <c r="B128" s="5">
-        <v>46122.5517350463</v>
+        <v>46122.38506837963</v>
       </c>
       <c r="C128" s="5">
-        <v>46195.56317517361</v>
+        <v>46195.39650850694</v>
       </c>
       <c r="D128" s="5">
-        <v>46196.76960409722</v>
+        <v>46196.60293743055</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>336</v>
@@ -9180,13 +9180,13 @@
         <v>338</v>
       </c>
       <c r="B129" s="8">
-        <v>46122.5517390625</v>
+        <v>46122.38507239583</v>
       </c>
       <c r="C129" s="8">
-        <v>46196.76936652778</v>
+        <v>46196.60269986111</v>
       </c>
       <c r="D129" s="8">
-        <v>46196.76939736111</v>
+        <v>46196.602730694445</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>339</v>
@@ -9245,13 +9245,13 @@
         <v>343</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.60093731481</v>
+        <v>46125.43427064815</v>
       </c>
       <c r="C130" s="5">
-        <v>46196.76934515046</v>
+        <v>46196.602678483796</v>
       </c>
       <c r="D130" s="5">
-        <v>46196.769350682865</v>
+        <v>46196.60268401621</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>200</v>
@@ -9298,13 +9298,13 @@
         <v>345</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.601380821754</v>
+        <v>46125.4347141551</v>
       </c>
       <c r="C131" s="8">
-        <v>46196.769346307876</v>
+        <v>46196.602679641204</v>
       </c>
       <c r="D131" s="8">
-        <v>46196.769351145835</v>
+        <v>46196.60268447916</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>200</v>
@@ -9351,13 +9351,13 @@
         <v>346</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.60142481481</v>
+        <v>46125.43475814815</v>
       </c>
       <c r="C132" s="5">
-        <v>46196.7693472338</v>
+        <v>46196.60268056713</v>
       </c>
       <c r="D132" s="5">
-        <v>46196.76935155093</v>
+        <v>46196.60268488426</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>200</v>
@@ -9404,13 +9404,13 @@
         <v>347</v>
       </c>
       <c r="B133" s="8">
-        <v>46125.60146085648</v>
+        <v>46125.434794189816</v>
       </c>
       <c r="C133" s="8">
-        <v>46196.769348125</v>
+        <v>46196.60268145833</v>
       </c>
       <c r="D133" s="8">
-        <v>46196.76935192129</v>
+        <v>46196.602685254635</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>200</v>
@@ -9457,13 +9457,13 @@
         <v>348</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.60150208333</v>
+        <v>46125.434835416665</v>
       </c>
       <c r="C134" s="5">
-        <v>46196.769348981485</v>
+        <v>46196.60268231481</v>
       </c>
       <c r="D134" s="5">
-        <v>46196.76935229167</v>
+        <v>46196.602685624996</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>200</v>
@@ -9510,13 +9510,13 @@
         <v>349</v>
       </c>
       <c r="B135" s="8">
-        <v>46122.55174383102</v>
+        <v>46122.38507716435</v>
       </c>
       <c r="C135" s="8">
-        <v>46196.769596921295</v>
+        <v>46196.60293025463</v>
       </c>
       <c r="D135" s="8">
-        <v>46196.76961396991</v>
+        <v>46196.60294730324</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>350</v>
@@ -9573,13 +9573,13 @@
         <v>351</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.601086979164</v>
+        <v>46125.4344203125</v>
       </c>
       <c r="C136" s="5">
-        <v>46196.76947155093</v>
+        <v>46196.602804884256</v>
       </c>
       <c r="D136" s="5">
-        <v>46196.76947347222</v>
+        <v>46196.60280680556</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>200</v>
@@ -9626,13 +9626,13 @@
         <v>353</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.60115318287</v>
+        <v>46125.4344865162</v>
       </c>
       <c r="C137" s="8">
-        <v>46196.7695043287</v>
+        <v>46196.60283766204</v>
       </c>
       <c r="D137" s="8">
-        <v>46196.76950902778</v>
+        <v>46196.60284236111</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>200</v>
@@ -9679,13 +9679,13 @@
         <v>354</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.60120391204</v>
+        <v>46125.43453724537</v>
       </c>
       <c r="C138" s="5">
-        <v>46196.76950549769</v>
+        <v>46196.60283883102</v>
       </c>
       <c r="D138" s="5">
-        <v>46196.76950944445</v>
+        <v>46196.60284277778</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>200</v>
@@ -9732,13 +9732,13 @@
         <v>355</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.60125796296</v>
+        <v>46125.434591296296</v>
       </c>
       <c r="C139" s="8">
-        <v>46196.76950637731</v>
+        <v>46196.60283971065</v>
       </c>
       <c r="D139" s="8">
-        <v>46196.76950987268</v>
+        <v>46196.60284320602</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>200</v>
@@ -9785,13 +9785,13 @@
         <v>356</v>
       </c>
       <c r="B140" s="5">
-        <v>46125.601304282405</v>
+        <v>46125.43463761574</v>
       </c>
       <c r="C140" s="5">
-        <v>46196.76950730324</v>
+        <v>46196.60284063657</v>
       </c>
       <c r="D140" s="5">
-        <v>46196.769510266204</v>
+        <v>46196.60284359954</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>200</v>
@@ -9838,13 +9838,13 @@
         <v>357</v>
       </c>
       <c r="B141" s="8">
-        <v>46122.55174869213</v>
+        <v>46122.38508202546</v>
       </c>
       <c r="C141" s="8">
-        <v>46191.70598530093</v>
+        <v>46191.539318634255</v>
       </c>
       <c r="D141" s="8">
-        <v>46196.769715787035</v>
+        <v>46196.60304912037</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>358</v>
@@ -9901,13 +9901,13 @@
         <v>359</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.60158650463</v>
+        <v>46125.434919837964</v>
       </c>
       <c r="C142" s="5">
-        <v>46196.76968462963</v>
+        <v>46196.60301796296</v>
       </c>
       <c r="D142" s="5">
-        <v>46196.76968989584</v>
+        <v>46196.60302322917</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>200</v>
@@ -9954,13 +9954,13 @@
         <v>361</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.60163133102</v>
+        <v>46125.43496466435</v>
       </c>
       <c r="C143" s="8">
-        <v>46196.76968585648</v>
+        <v>46196.60301918982</v>
       </c>
       <c r="D143" s="8">
-        <v>46196.7696903125</v>
+        <v>46196.60302364583</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>200</v>
@@ -10007,13 +10007,13 @@
         <v>362</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.60167016204</v>
+        <v>46125.43500349537</v>
       </c>
       <c r="C144" s="5">
-        <v>46196.7696866551</v>
+        <v>46196.603019988426</v>
       </c>
       <c r="D144" s="5">
-        <v>46196.769690706016</v>
+        <v>46196.60302403935</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>200</v>
@@ -10060,13 +10060,13 @@
         <v>364</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.60170435185</v>
+        <v>46125.43503768518</v>
       </c>
       <c r="C145" s="8">
-        <v>46196.769687395834</v>
+        <v>46196.60302072916</v>
       </c>
       <c r="D145" s="8">
-        <v>46196.76969114583</v>
+        <v>46196.60302447916</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>200</v>
@@ -10113,13 +10113,13 @@
         <v>365</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.60173947917</v>
+        <v>46125.4350728125</v>
       </c>
       <c r="C146" s="5">
-        <v>46196.769688113425</v>
+        <v>46196.60302144676</v>
       </c>
       <c r="D146" s="5">
-        <v>46196.76969164352</v>
+        <v>46196.60302497685</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>200</v>
@@ -10166,13 +10166,13 @@
         <v>366</v>
       </c>
       <c r="B147" s="8">
-        <v>46122.551753472224</v>
+        <v>46122.38508680556</v>
       </c>
       <c r="C147" s="8">
-        <v>46191.70604009259</v>
+        <v>46191.53937342593</v>
       </c>
       <c r="D147" s="8">
-        <v>46196.76981105324</v>
+        <v>46196.60314438658</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>367</v>
@@ -10229,13 +10229,13 @@
         <v>369</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.60181555555</v>
+        <v>46125.43514888889</v>
       </c>
       <c r="C148" s="5">
-        <v>46196.76979265046</v>
+        <v>46196.60312598379</v>
       </c>
       <c r="D148" s="5">
-        <v>46196.76979569445</v>
+        <v>46196.603129027775</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>200</v>
@@ -10282,13 +10282,13 @@
         <v>370</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.60185690972</v>
+        <v>46125.43519024306</v>
       </c>
       <c r="C149" s="8">
-        <v>46196.76979356482</v>
+        <v>46196.603126898146</v>
       </c>
       <c r="D149" s="8">
-        <v>46196.76979614583</v>
+        <v>46196.60312947917</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>200</v>
@@ -10335,13 +10335,13 @@
         <v>371</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.601899490735</v>
+        <v>46125.43523282408</v>
       </c>
       <c r="C150" s="5">
-        <v>46196.769794224536</v>
+        <v>46196.60312755787</v>
       </c>
       <c r="D150" s="5">
-        <v>46196.76979648148</v>
+        <v>46196.603129814815</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>200</v>
@@ -10388,13 +10388,13 @@
         <v>372</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.60193935185</v>
+        <v>46125.43527268519</v>
       </c>
       <c r="C151" s="8">
-        <v>46196.76976476852</v>
+        <v>46196.603098101856</v>
       </c>
       <c r="D151" s="8">
-        <v>46196.769766875004</v>
+        <v>46196.60310020833</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>200</v>
@@ -10441,13 +10441,13 @@
         <v>373</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.60197710648</v>
+        <v>46125.43531043982</v>
       </c>
       <c r="C152" s="5">
-        <v>46196.76977206019</v>
+        <v>46196.603105393515</v>
       </c>
       <c r="D152" s="5">
-        <v>46196.76977370371</v>
+        <v>46196.60310703704</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>200</v>
@@ -10494,11 +10494,11 @@
         <v>374</v>
       </c>
       <c r="B153" s="8">
-        <v>46122.551758622685</v>
+        <v>46122.38509195602</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46125.58936878473</v>
+        <v>46125.422702118056</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>375</v>
@@ -10541,11 +10541,11 @@
         <v>377</v>
       </c>
       <c r="B154" s="5">
-        <v>46122.55176134259</v>
+        <v>46122.38509467593</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46191.70605767361</v>
+        <v>46191.53939100694</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>378</v>
@@ -10604,11 +10604,11 @@
         <v>381</v>
       </c>
       <c r="B155" s="8">
-        <v>46122.55176609954</v>
+        <v>46122.38509943287</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46192.97384414352</v>
+        <v>46192.80717747685</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>382</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -1847,13 +1847,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46122.38452245371</v>
+        <v>46122.55118912037</v>
       </c>
       <c r="C4" s="5">
-        <v>46128.426341053244</v>
+        <v>46128.59300771991</v>
       </c>
       <c r="D4" s="5">
-        <v>46157.93633454861</v>
+        <v>46158.10300121528</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1896,13 +1896,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46122.38467905093</v>
+        <v>46122.55134571759</v>
       </c>
       <c r="C5" s="8">
-        <v>46128.42632796297</v>
+        <v>46128.59299462963</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.70935505787</v>
+        <v>46133.876021724536</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1959,13 +1959,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46122.384682812495</v>
+        <v>46122.55134947917</v>
       </c>
       <c r="C6" s="5">
-        <v>46128.42601201389</v>
+        <v>46128.59267868055</v>
       </c>
       <c r="D6" s="5">
-        <v>46128.43715965278</v>
+        <v>46128.60382631945</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2022,13 +2022,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46122.38468587963</v>
+        <v>46122.551352546296</v>
       </c>
       <c r="C7" s="8">
-        <v>46128.42603200232</v>
+        <v>46128.59269866898</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.460593807875</v>
+        <v>46161.62726047453</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2085,13 +2085,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46122.38468890046</v>
+        <v>46122.551355567135</v>
       </c>
       <c r="C8" s="5">
-        <v>46128.42605055556</v>
+        <v>46128.59271722222</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.43733940972</v>
+        <v>46128.60400607639</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2148,13 +2148,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46122.384692719905</v>
+        <v>46122.551359386576</v>
       </c>
       <c r="C9" s="8">
-        <v>46128.4261833912</v>
+        <v>46128.592850057874</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.66910643518</v>
+        <v>46156.83577310185</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2211,13 +2211,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46122.3845274537</v>
+        <v>46122.55119412037</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.766136805556</v>
+        <v>46193.93280347223</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.76615431713</v>
+        <v>46193.9328209838</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2264,13 +2264,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46122.384696504625</v>
+        <v>46122.5513631713</v>
       </c>
       <c r="C11" s="8">
-        <v>46128.43768854167</v>
+        <v>46128.60435520833</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.80716136574</v>
+        <v>46192.97382803241</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2329,13 +2329,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46122.38470238426</v>
+        <v>46122.551369050925</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.43976447917</v>
+        <v>46128.60643114583</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.80716146991</v>
+        <v>46192.97382813657</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2394,13 +2394,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46122.384708020836</v>
+        <v>46122.5513746875</v>
       </c>
       <c r="C13" s="8">
-        <v>46132.40405894676</v>
+        <v>46132.57072561343</v>
       </c>
       <c r="D13" s="8">
-        <v>46192.80716134259</v>
+        <v>46192.97382800926</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2459,13 +2459,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46122.38692751157</v>
+        <v>46122.553594178244</v>
       </c>
       <c r="C14" s="5">
-        <v>46128.44274908565</v>
+        <v>46128.60941575232</v>
       </c>
       <c r="D14" s="5">
-        <v>46136.03935251157</v>
+        <v>46136.20601917824</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2524,13 +2524,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46122.38453280093</v>
+        <v>46122.55119946759</v>
       </c>
       <c r="C15" s="8">
-        <v>46195.34056496528</v>
+        <v>46195.50723163194</v>
       </c>
       <c r="D15" s="8">
-        <v>46195.340579421296</v>
+        <v>46195.50724608796</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2577,13 +2577,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46122.38472188657</v>
+        <v>46122.55138855324</v>
       </c>
       <c r="C16" s="5">
-        <v>46128.44033724537</v>
+        <v>46128.60700391204</v>
       </c>
       <c r="D16" s="5">
-        <v>46133.0133283912</v>
+        <v>46133.17999505787</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2642,13 +2642,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46122.38472815973</v>
+        <v>46122.55139482639</v>
       </c>
       <c r="C17" s="8">
-        <v>46128.44034490741</v>
+        <v>46128.60701157407</v>
       </c>
       <c r="D17" s="8">
-        <v>46132.01554025463</v>
+        <v>46132.182206921294</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2707,13 +2707,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46122.38473373842</v>
+        <v>46122.55140040509</v>
       </c>
       <c r="C18" s="5">
-        <v>46195.340545046296</v>
+        <v>46195.50721171296</v>
       </c>
       <c r="D18" s="5">
-        <v>46195.340565624996</v>
+        <v>46195.50723229167</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2772,13 +2772,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46122.384739375004</v>
+        <v>46122.55140604167</v>
       </c>
       <c r="C19" s="8">
-        <v>46181.499732384254</v>
+        <v>46181.666399050926</v>
       </c>
       <c r="D19" s="8">
-        <v>46203.0370015625</v>
+        <v>46203.203668229165</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2837,13 +2837,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46122.3847449537</v>
+        <v>46122.55141162037</v>
       </c>
       <c r="C20" s="5">
-        <v>46128.442831215274</v>
+        <v>46128.609497881946</v>
       </c>
       <c r="D20" s="5">
-        <v>46132.01553989583</v>
+        <v>46132.1822065625</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>64</v>
@@ -2902,13 +2902,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46122.39987912037</v>
+        <v>46122.566545787035</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.49969386574</v>
+        <v>46181.66636053241</v>
       </c>
       <c r="D21" s="8">
-        <v>46203.03700166667</v>
+        <v>46203.20366833333</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2967,13 +2967,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46122.39994855324</v>
+        <v>46122.56661521991</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.499709641204</v>
+        <v>46181.66637630787</v>
       </c>
       <c r="D22" s="5">
-        <v>46203.03700182871</v>
+        <v>46203.20366849537</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3032,13 +3032,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="8">
-        <v>46122.40619606481</v>
+        <v>46122.57286273148</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.4997655787</v>
+        <v>46181.66643224537</v>
       </c>
       <c r="D23" s="8">
-        <v>46203.037001550925</v>
+        <v>46203.2036682176</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>95</v>
@@ -3097,13 +3097,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46122.38453728009</v>
+        <v>46122.55120394676</v>
       </c>
       <c r="C24" s="5">
-        <v>46195.34067315972</v>
+        <v>46195.50733982639</v>
       </c>
       <c r="D24" s="5">
-        <v>46195.34068686343</v>
+        <v>46195.50735353009</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -3150,13 +3150,13 @@
         <v>100</v>
       </c>
       <c r="B25" s="8">
-        <v>46122.38475027778</v>
+        <v>46122.55141694444</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.45950203703</v>
+        <v>46174.626168703704</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.45951446759</v>
+        <v>46174.626181134256</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>101</v>
@@ -3215,13 +3215,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46122.38475541667</v>
+        <v>46122.55142208333</v>
       </c>
       <c r="C26" s="5">
-        <v>46174.45658625</v>
+        <v>46174.62325291667</v>
       </c>
       <c r="D26" s="5">
-        <v>46174.456587824076</v>
+        <v>46174.62325449074</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3276,13 +3276,13 @@
         <v>110</v>
       </c>
       <c r="B27" s="8">
-        <v>46122.38476032407</v>
+        <v>46122.55142699074</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.45948622686</v>
+        <v>46174.626152893514</v>
       </c>
       <c r="D27" s="8">
-        <v>46174.45948762732</v>
+        <v>46174.62615429398</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>111</v>
@@ -3337,13 +3337,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46122.38476556713</v>
+        <v>46122.5514322338</v>
       </c>
       <c r="C28" s="5">
-        <v>46195.340658553236</v>
+        <v>46195.50732521991</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.545180127316</v>
+        <v>46195.71184679398</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3402,13 +3402,13 @@
         <v>117</v>
       </c>
       <c r="B29" s="8">
-        <v>46122.38477087963</v>
+        <v>46122.551437546295</v>
       </c>
       <c r="C29" s="8">
-        <v>46195.54471607639</v>
+        <v>46195.71138274306</v>
       </c>
       <c r="D29" s="8">
-        <v>46195.54471850695</v>
+        <v>46195.71138517361</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>118</v>
@@ -3463,13 +3463,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46122.3847758912</v>
+        <v>46122.55144255787</v>
       </c>
       <c r="C30" s="5">
-        <v>46195.54516429398</v>
+        <v>46195.711830960645</v>
       </c>
       <c r="D30" s="5">
-        <v>46195.54516583333</v>
+        <v>46195.711832500005</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3524,13 +3524,13 @@
         <v>123</v>
       </c>
       <c r="B31" s="8">
-        <v>46122.38478104166</v>
+        <v>46122.551447708334</v>
       </c>
       <c r="C31" s="8">
-        <v>46133.661133263886</v>
+        <v>46133.82779993056</v>
       </c>
       <c r="D31" s="8">
-        <v>46133.66114655093</v>
+        <v>46133.82781321759</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>124</v>
@@ -3589,13 +3589,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46122.38478609954</v>
+        <v>46122.5514527662</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.66106445601</v>
+        <v>46133.827731122685</v>
       </c>
       <c r="D32" s="5">
-        <v>46133.6610659375</v>
+        <v>46133.82773260417</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3650,13 +3650,13 @@
         <v>129</v>
       </c>
       <c r="B33" s="8">
-        <v>46122.384791296296</v>
+        <v>46122.55145796297</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.66112020833</v>
+        <v>46133.827786875</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.661121412035</v>
+        <v>46133.82778807871</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>130</v>
@@ -3711,13 +3711,13 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46122.38479633102</v>
+        <v>46122.55146299768</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.6611012963</v>
+        <v>46133.82776796297</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.66110246528</v>
+        <v>46133.827769131945</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3772,13 +3772,13 @@
         <v>135</v>
       </c>
       <c r="B35" s="8">
-        <v>46122.38480128472</v>
+        <v>46122.55146795139</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.50020540509</v>
+        <v>46181.66687207176</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.5002191088</v>
+        <v>46181.66688577546</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3837,13 +3837,13 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46122.38480630787</v>
+        <v>46122.551472974534</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.50015100694</v>
+        <v>46181.66681767361</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.50015280093</v>
+        <v>46181.66681946759</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3898,13 +3898,13 @@
         <v>143</v>
       </c>
       <c r="B37" s="8">
-        <v>46122.384855868055</v>
+        <v>46122.55152253472</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.50019012731</v>
+        <v>46181.66685679398</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.5001915162</v>
+        <v>46181.66685818287</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>144</v>
@@ -3959,13 +3959,13 @@
         <v>146</v>
       </c>
       <c r="B38" s="5">
-        <v>46122.384862245366</v>
+        <v>46122.55152891204</v>
       </c>
       <c r="C38" s="5">
-        <v>46154.70100114583</v>
+        <v>46154.867667812505</v>
       </c>
       <c r="D38" s="5">
-        <v>46189.00554646991</v>
+        <v>46189.172213136575</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>147</v>
@@ -4024,13 +4024,13 @@
         <v>149</v>
       </c>
       <c r="B39" s="8">
-        <v>46122.384867395835</v>
+        <v>46122.5515340625</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.70085026621</v>
+        <v>46154.86751693287</v>
       </c>
       <c r="D39" s="8">
-        <v>46154.70085260417</v>
+        <v>46154.86751927083</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>87</v>
@@ -4079,13 +4079,13 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46122.38487178241</v>
+        <v>46122.55153844907</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.70090960649</v>
+        <v>46154.867576273144</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.70091078704</v>
+        <v>46154.867577453704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4134,13 +4134,13 @@
         <v>154</v>
       </c>
       <c r="B41" s="8">
-        <v>46122.40826678241</v>
+        <v>46122.574933449076</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.500100335645</v>
+        <v>46181.666767002316</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.50011658565</v>
+        <v>46181.666783252316</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>155</v>
@@ -4199,13 +4199,13 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46122.40925430556</v>
+        <v>46122.575920972224</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.500040729166</v>
+        <v>46181.66670739584</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.500041886575</v>
+        <v>46181.66670855324</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>90</v>
@@ -4254,13 +4254,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46122.409418090276</v>
+        <v>46122.57608475695</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.50008614583</v>
+        <v>46181.666752812496</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.500087685185</v>
+        <v>46181.666754351856</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -4309,13 +4309,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46122.40834771991</v>
+        <v>46122.57501438657</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.500291805554</v>
+        <v>46181.666958472226</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.500401990736</v>
+        <v>46181.66706865741</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4374,13 +4374,13 @@
         <v>167</v>
       </c>
       <c r="B45" s="8">
-        <v>46122.41255444444</v>
+        <v>46122.57922111111</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.50023484953</v>
+        <v>46181.666901516204</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.50023640046</v>
+        <v>46181.66690306713</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>96</v>
@@ -4429,13 +4429,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46122.4128253588</v>
+        <v>46122.57949202546</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.500276562496</v>
+        <v>46181.66694322917</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.50027793982</v>
+        <v>46181.66694460648</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4484,13 +4484,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46125.362951550924</v>
+        <v>46125.529618217595</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.50055453704</v>
+        <v>46181.66722120371</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.500568449075</v>
+        <v>46181.66723511574</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4549,13 +4549,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46125.36311331019</v>
+        <v>46125.52977997685</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.50049065972</v>
+        <v>46181.66715732639</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.500492453706</v>
+        <v>46181.66715912037</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>93</v>
@@ -4604,13 +4604,13 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46125.36325149305</v>
+        <v>46125.52991815972</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.5005374537</v>
+        <v>46181.66720412037</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.50053896991</v>
+        <v>46181.66720563658</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4659,13 +4659,13 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46122.384541886575</v>
+        <v>46122.55120855324</v>
       </c>
       <c r="C50" s="5">
-        <v>46195.34078462963</v>
+        <v>46195.5074512963</v>
       </c>
       <c r="D50" s="5">
-        <v>46195.34089821759</v>
+        <v>46195.50756488426</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4712,13 +4712,13 @@
         <v>183</v>
       </c>
       <c r="B51" s="8">
-        <v>46122.38487678241</v>
+        <v>46122.55154344907</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.62917814815</v>
+        <v>46133.79584481481</v>
       </c>
       <c r="D51" s="8">
-        <v>46143.00447921296</v>
+        <v>46143.171145879634</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>184</v>
@@ -4777,13 +4777,13 @@
         <v>188</v>
       </c>
       <c r="B52" s="5">
-        <v>46122.38488232639</v>
+        <v>46122.551548993055</v>
       </c>
       <c r="C52" s="5">
-        <v>46134.62573756944</v>
+        <v>46134.79240423611</v>
       </c>
       <c r="D52" s="5">
-        <v>46198.021150451386</v>
+        <v>46198.18781711806</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4842,13 +4842,13 @@
         <v>192</v>
       </c>
       <c r="B53" s="8">
-        <v>46122.38489054398</v>
+        <v>46122.55155721065</v>
       </c>
       <c r="C53" s="8">
-        <v>46134.62578480324</v>
+        <v>46134.79245146991</v>
       </c>
       <c r="D53" s="8">
-        <v>46199.01705138889</v>
+        <v>46199.18371805556</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>83</v>
@@ -4905,13 +4905,13 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46122.38489901621</v>
+        <v>46122.55156568287</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.34094658565</v>
+        <v>46195.50761325231</v>
       </c>
       <c r="D54" s="5">
-        <v>46196.6024115162</v>
+        <v>46196.76907818287</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -4968,13 +4968,13 @@
         <v>199</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.43695545139</v>
+        <v>46125.603622118055</v>
       </c>
       <c r="C55" s="8">
-        <v>46196.60238085648</v>
+        <v>46196.76904752315</v>
       </c>
       <c r="D55" s="8">
-        <v>46196.602385474536</v>
+        <v>46196.7690521412</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>200</v>
@@ -5021,13 +5021,13 @@
         <v>202</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.43700428241</v>
+        <v>46125.60367094907</v>
       </c>
       <c r="C56" s="5">
-        <v>46196.6023817824</v>
+        <v>46196.769048449074</v>
       </c>
       <c r="D56" s="5">
-        <v>46196.60238585648</v>
+        <v>46196.769052523145</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>200</v>
@@ -5074,13 +5074,13 @@
         <v>203</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.43705284722</v>
+        <v>46125.60371951389</v>
       </c>
       <c r="C57" s="8">
-        <v>46196.602382627316</v>
+        <v>46196.76904929398</v>
       </c>
       <c r="D57" s="8">
-        <v>46196.60238616898</v>
+        <v>46196.76905283565</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5127,13 +5127,13 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.43709796296</v>
+        <v>46125.60376462963</v>
       </c>
       <c r="C58" s="5">
-        <v>46196.60238340277</v>
+        <v>46196.769050069444</v>
       </c>
       <c r="D58" s="5">
-        <v>46196.60238648148</v>
+        <v>46196.76905314815</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>200</v>
@@ -5180,13 +5180,13 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.437150729165</v>
+        <v>46125.60381739584</v>
       </c>
       <c r="C59" s="8">
-        <v>46196.602384108795</v>
+        <v>46196.76905077546</v>
       </c>
       <c r="D59" s="8">
-        <v>46196.6023868287</v>
+        <v>46196.76905349537</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>200</v>
@@ -5233,13 +5233,13 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46122.38490304398</v>
+        <v>46122.551569710646</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.501105787036</v>
+        <v>46181.6677724537</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.501186574074</v>
+        <v>46181.66785324074</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5282,13 +5282,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46122.38490655093</v>
+        <v>46122.55157321759</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.50071136574</v>
+        <v>46181.667378032405</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.500728576386</v>
+        <v>46181.66739524306</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5347,13 +5347,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46122.41824972222</v>
+        <v>46122.58491638889</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.50074653935</v>
+        <v>46181.667413206014</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.50076234953</v>
+        <v>46181.667429016205</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5412,13 +5412,13 @@
         <v>217</v>
       </c>
       <c r="B63" s="8">
-        <v>46125.36435991898</v>
+        <v>46125.53102658565</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.500763460645</v>
+        <v>46181.667430127316</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.50078259259</v>
+        <v>46181.66744925926</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -5477,13 +5477,13 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46122.38491179398</v>
+        <v>46122.55157846065</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.501089212965</v>
+        <v>46181.66775587963</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.501105752315</v>
+        <v>46181.66777241898</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5542,13 +5542,13 @@
         <v>225</v>
       </c>
       <c r="B65" s="8">
-        <v>46122.38491716435</v>
+        <v>46122.551583831024</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.50212802083</v>
+        <v>46181.6687946875</v>
       </c>
       <c r="D65" s="8">
-        <v>46181.50224104167</v>
+        <v>46181.66890770833</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>226</v>
@@ -5591,13 +5591,13 @@
         <v>228</v>
       </c>
       <c r="B66" s="5">
-        <v>46122.384920219905</v>
+        <v>46122.55158688658</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.49942690972</v>
+        <v>46181.666093576394</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.50214266204</v>
+        <v>46181.66880932871</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>229</v>
@@ -5656,13 +5656,13 @@
         <v>233</v>
       </c>
       <c r="B67" s="8">
-        <v>46122.384925185186</v>
+        <v>46122.55159185185</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.49953199074</v>
+        <v>46181.6661986574</v>
       </c>
       <c r="D67" s="8">
-        <v>46181.50217939814</v>
+        <v>46181.668846064815</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>234</v>
@@ -5721,13 +5721,13 @@
         <v>236</v>
       </c>
       <c r="B68" s="5">
-        <v>46125.42914525463</v>
+        <v>46125.595811921296</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.501410324076</v>
+        <v>46181.66807699074</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.50141217593</v>
+        <v>46181.66807884259</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>237</v>
@@ -5776,13 +5776,13 @@
         <v>240</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.42943380787</v>
+        <v>46125.59610047453</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.50141914352</v>
+        <v>46181.66808581019</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.50142061342</v>
+        <v>46181.66808728009</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>200</v>
@@ -5831,13 +5831,13 @@
         <v>241</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.429543715276</v>
+        <v>46125.59621038195</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.501487326386</v>
+        <v>46181.66815399306</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.501488842594</v>
+        <v>46181.66815550926</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>200</v>
@@ -5886,13 +5886,13 @@
         <v>242</v>
       </c>
       <c r="B71" s="8">
-        <v>46125.42958805556</v>
+        <v>46125.59625472222</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.50150002315</v>
+        <v>46181.668166689815</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.501501527775</v>
+        <v>46181.66816819445</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>200</v>
@@ -5941,13 +5941,13 @@
         <v>243</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.42963248843</v>
+        <v>46125.59629915509</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.50151289352</v>
+        <v>46181.66817956018</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.50151412037</v>
+        <v>46181.66818078703</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>200</v>
@@ -5996,13 +5996,13 @@
         <v>244</v>
       </c>
       <c r="B73" s="8">
-        <v>46122.384930844906</v>
+        <v>46122.55159751157</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.50211394676</v>
+        <v>46181.66878061343</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.50211555556</v>
+        <v>46181.66878222222</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>245</v>
@@ -6061,13 +6061,13 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46125.4298218287</v>
+        <v>46125.59648849537</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.501985254625</v>
+        <v>46181.668651921296</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.501986724536</v>
+        <v>46181.6686533912</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>200</v>
@@ -6116,13 +6116,13 @@
         <v>249</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.429951875005</v>
+        <v>46125.59661854166</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.50199983796</v>
+        <v>46181.66866650463</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.50200115741</v>
+        <v>46181.66866782407</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>200</v>
@@ -6171,13 +6171,13 @@
         <v>251</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.43000208333</v>
+        <v>46125.596668750004</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.50200921296</v>
+        <v>46181.66867587963</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.50201078704</v>
+        <v>46181.66867745371</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>200</v>
@@ -6226,13 +6226,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="8">
-        <v>46125.430048842594</v>
+        <v>46125.59671550926</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.50201895833</v>
+        <v>46181.668685625</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.50202039352</v>
+        <v>46181.668687060184</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>200</v>
@@ -6281,13 +6281,13 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.430088796296</v>
+        <v>46125.59675546296</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.5020371875</v>
+        <v>46181.66870385417</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.502038356484</v>
+        <v>46181.66870502315</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>200</v>
@@ -6336,13 +6336,13 @@
         <v>255</v>
       </c>
       <c r="B79" s="8">
-        <v>46122.38493690972</v>
+        <v>46122.55160357639</v>
       </c>
       <c r="C79" s="8">
-        <v>46195.3964589699</v>
+        <v>46195.563125636574</v>
       </c>
       <c r="D79" s="8">
-        <v>46195.39662366898</v>
+        <v>46195.563290335645</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>207</v>
@@ -6389,13 +6389,13 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46122.38494012732</v>
+        <v>46122.55160679398</v>
       </c>
       <c r="C80" s="5">
-        <v>46195.39660269676</v>
+        <v>46195.563269363425</v>
       </c>
       <c r="D80" s="5">
-        <v>46195.54518015047</v>
+        <v>46195.711846817125</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6454,13 +6454,13 @@
         <v>260</v>
       </c>
       <c r="B81" s="8">
-        <v>46122.38494559028</v>
+        <v>46122.551612256946</v>
       </c>
       <c r="C81" s="8">
-        <v>46195.34084651621</v>
+        <v>46195.50751318287</v>
       </c>
       <c r="D81" s="8">
-        <v>46195.3408646412</v>
+        <v>46195.50753130787</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>261</v>
@@ -6519,13 +6519,13 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46122.38495090278</v>
+        <v>46122.55161756944</v>
       </c>
       <c r="C82" s="5">
-        <v>46195.340851851855</v>
+        <v>46195.50751851852</v>
       </c>
       <c r="D82" s="5">
-        <v>46195.34086592593</v>
+        <v>46195.50753259259</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6584,13 +6584,13 @@
         <v>264</v>
       </c>
       <c r="B83" s="8">
-        <v>46122.384956215275</v>
+        <v>46122.55162288195</v>
       </c>
       <c r="C83" s="8">
-        <v>46195.34085677083</v>
+        <v>46195.507523437496</v>
       </c>
       <c r="D83" s="8">
-        <v>46195.3408728125</v>
+        <v>46195.507539479164</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>265</v>
@@ -6649,13 +6649,13 @@
         <v>266</v>
       </c>
       <c r="B84" s="5">
-        <v>46122.427324965276</v>
+        <v>46122.59399163195</v>
       </c>
       <c r="C84" s="5">
-        <v>46193.76648644676</v>
+        <v>46193.93315311342</v>
       </c>
       <c r="D84" s="5">
-        <v>46193.76661337963</v>
+        <v>46193.9332800463</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>267</v>
@@ -6714,13 +6714,13 @@
         <v>269</v>
       </c>
       <c r="B85" s="8">
-        <v>46122.3849615162</v>
+        <v>46122.551628182875</v>
       </c>
       <c r="C85" s="8">
-        <v>46195.39639328704</v>
+        <v>46195.5630599537</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.60252601852</v>
+        <v>46196.769192685184</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>270</v>
@@ -6767,13 +6767,13 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46122.38496491898</v>
+        <v>46122.55163158565</v>
       </c>
       <c r="C86" s="5">
-        <v>46195.34102184028</v>
+        <v>46195.50768850694</v>
       </c>
       <c r="D86" s="5">
-        <v>46195.34104046296</v>
+        <v>46195.507707129625</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>273</v>
@@ -6832,13 +6832,13 @@
         <v>275</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.43083025463</v>
+        <v>46125.5974969213</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.60125040509</v>
+        <v>46196.76791707176</v>
       </c>
       <c r="D87" s="8">
-        <v>46196.60125216436</v>
+        <v>46196.767918831014</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>200</v>
@@ -6887,13 +6887,13 @@
         <v>277</v>
       </c>
       <c r="B88" s="5">
-        <v>46125.430879039355</v>
+        <v>46125.59754570602</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.601287384256</v>
+        <v>46196.76795405093</v>
       </c>
       <c r="D88" s="5">
-        <v>46196.601289791666</v>
+        <v>46196.76795645834</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>200</v>
@@ -6942,13 +6942,13 @@
         <v>278</v>
       </c>
       <c r="B89" s="8">
-        <v>46125.430940439815</v>
+        <v>46125.59760710648</v>
       </c>
       <c r="C89" s="8">
-        <v>46196.601261550924</v>
+        <v>46196.767928217596</v>
       </c>
       <c r="D89" s="8">
-        <v>46196.601263344906</v>
+        <v>46196.76793001157</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>200</v>
@@ -6997,13 +6997,13 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46125.43099224537</v>
+        <v>46125.59765891204</v>
       </c>
       <c r="C90" s="5">
-        <v>46196.601279849536</v>
+        <v>46196.76794651621</v>
       </c>
       <c r="D90" s="5">
-        <v>46196.60128142362</v>
+        <v>46196.76794809027</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>200</v>
@@ -7052,13 +7052,13 @@
         <v>280</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.431036724534</v>
+        <v>46125.597703391206</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.60127434028</v>
+        <v>46196.76794100694</v>
       </c>
       <c r="D91" s="8">
-        <v>46196.6012762037</v>
+        <v>46196.76794287037</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>200</v>
@@ -7107,13 +7107,13 @@
         <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46122.38503993055</v>
+        <v>46122.55170659722</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.60088846065</v>
+        <v>46196.76755512731</v>
       </c>
       <c r="D92" s="5">
-        <v>46196.60141113426</v>
+        <v>46196.76807780092</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>282</v>
@@ -7172,13 +7172,13 @@
         <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46125.43316075232</v>
+        <v>46125.59982741898</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.60133528935</v>
+        <v>46196.76800195602</v>
       </c>
       <c r="D93" s="8">
-        <v>46196.60133719907</v>
+        <v>46196.76800386574</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>200</v>
@@ -7227,13 +7227,13 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.43322416667</v>
+        <v>46125.599890833335</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.601356354164</v>
+        <v>46196.768023020835</v>
       </c>
       <c r="D94" s="5">
-        <v>46196.60135802084</v>
+        <v>46196.768024687495</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>200</v>
@@ -7282,13 +7282,13 @@
         <v>288</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.43326467593</v>
+        <v>46125.59993134259</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.601348275464</v>
+        <v>46196.76801494213</v>
       </c>
       <c r="D95" s="8">
-        <v>46196.60135009259</v>
+        <v>46196.76801675926</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>200</v>
@@ -7337,13 +7337,13 @@
         <v>289</v>
       </c>
       <c r="B96" s="5">
-        <v>46125.433302627316</v>
+        <v>46125.59996929398</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.60138443287</v>
+        <v>46196.76805109954</v>
       </c>
       <c r="D96" s="5">
-        <v>46196.60138612268</v>
+        <v>46196.76805278935</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>200</v>
@@ -7392,13 +7392,13 @@
         <v>290</v>
       </c>
       <c r="B97" s="8">
-        <v>46125.43334484954</v>
+        <v>46125.6000115162</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.60139039352</v>
+        <v>46196.76805706018</v>
       </c>
       <c r="D97" s="8">
-        <v>46196.60139240741</v>
+        <v>46196.76805907408</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>200</v>
@@ -7447,13 +7447,13 @@
         <v>291</v>
       </c>
       <c r="B98" s="5">
-        <v>46122.38497746528</v>
+        <v>46122.55164413195</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.601731574076</v>
+        <v>46196.76839824074</v>
       </c>
       <c r="D98" s="5">
-        <v>46196.601742060186</v>
+        <v>46196.76840872686</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>292</v>
@@ -7512,13 +7512,13 @@
         <v>294</v>
       </c>
       <c r="B99" s="8">
-        <v>46125.43249607639</v>
+        <v>46125.599162743056</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.601522997684</v>
+        <v>46196.76818966435</v>
       </c>
       <c r="D99" s="8">
-        <v>46196.60152462963</v>
+        <v>46196.7681912963</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>200</v>
@@ -7567,13 +7567,13 @@
         <v>297</v>
       </c>
       <c r="B100" s="5">
-        <v>46125.4326358449</v>
+        <v>46125.599302511575</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.601537546296</v>
+        <v>46196.76820421296</v>
       </c>
       <c r="D100" s="5">
-        <v>46196.60153930556</v>
+        <v>46196.76820597222</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>200</v>
@@ -7622,13 +7622,13 @@
         <v>298</v>
       </c>
       <c r="B101" s="8">
-        <v>46125.43267978009</v>
+        <v>46125.59934644676</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.601709282404</v>
+        <v>46196.768375949076</v>
       </c>
       <c r="D101" s="8">
-        <v>46196.60171291667</v>
+        <v>46196.76837958333</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>200</v>
@@ -7677,13 +7677,13 @@
         <v>299</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.43272190972</v>
+        <v>46125.59938857639</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.60171030092</v>
+        <v>46196.76837696759</v>
       </c>
       <c r="D102" s="5">
-        <v>46196.60171341435</v>
+        <v>46196.76838008102</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>200</v>
@@ -7732,13 +7732,13 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46125.43276428241</v>
+        <v>46125.59943094908</v>
       </c>
       <c r="C103" s="8">
-        <v>46196.60171123843</v>
+        <v>46196.76837790509</v>
       </c>
       <c r="D103" s="8">
-        <v>46196.601713854165</v>
+        <v>46196.768380520836</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>200</v>
@@ -7787,13 +7787,13 @@
         <v>301</v>
       </c>
       <c r="B104" s="5">
-        <v>46122.3849843287</v>
+        <v>46122.551650995374</v>
       </c>
       <c r="C104" s="5">
-        <v>46196.601881215276</v>
+        <v>46196.76854788195</v>
       </c>
       <c r="D104" s="5">
-        <v>46196.601894074076</v>
+        <v>46196.76856074074</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>302</v>
@@ -7852,13 +7852,13 @@
         <v>303</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.43286347222</v>
+        <v>46125.59953013889</v>
       </c>
       <c r="C105" s="8">
-        <v>46196.60186116898</v>
+        <v>46196.76852783565</v>
       </c>
       <c r="D105" s="8">
-        <v>46196.60186505787</v>
+        <v>46196.768531724534</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>200</v>
@@ -7907,13 +7907,13 @@
         <v>305</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.43294756944</v>
+        <v>46125.59961423611</v>
       </c>
       <c r="C106" s="5">
-        <v>46196.60179663195</v>
+        <v>46196.76846329861</v>
       </c>
       <c r="D106" s="5">
-        <v>46196.60179829861</v>
+        <v>46196.76846496528</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>200</v>
@@ -7962,13 +7962,13 @@
         <v>306</v>
       </c>
       <c r="B107" s="8">
-        <v>46125.43298765046</v>
+        <v>46125.599654317135</v>
       </c>
       <c r="C107" s="8">
-        <v>46196.601862129624</v>
+        <v>46196.768528796296</v>
       </c>
       <c r="D107" s="8">
-        <v>46196.601865370365</v>
+        <v>46196.76853203704</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>200</v>
@@ -8017,13 +8017,13 @@
         <v>307</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.43290399306</v>
+        <v>46125.59957065972</v>
       </c>
       <c r="C108" s="5">
-        <v>46196.601862881944</v>
+        <v>46196.768529548615</v>
       </c>
       <c r="D108" s="5">
-        <v>46196.6018656713</v>
+        <v>46196.76853233796</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>200</v>
@@ -8072,13 +8072,13 @@
         <v>308</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.433030451386</v>
+        <v>46125.59969711806</v>
       </c>
       <c r="C109" s="8">
-        <v>46196.601863738426</v>
+        <v>46196.7685304051</v>
       </c>
       <c r="D109" s="8">
-        <v>46196.6018659838</v>
+        <v>46196.76853265046</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>200</v>
@@ -8127,13 +8127,13 @@
         <v>309</v>
       </c>
       <c r="B110" s="5">
-        <v>46122.38497059028</v>
+        <v>46122.55163725694</v>
       </c>
       <c r="C110" s="5">
-        <v>46196.6020008912</v>
+        <v>46196.76866755787</v>
       </c>
       <c r="D110" s="5">
-        <v>46196.60201241898</v>
+        <v>46196.76867908565</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>310</v>
@@ -8192,13 +8192,13 @@
         <v>311</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.431135439816</v>
+        <v>46125.59780210648</v>
       </c>
       <c r="C111" s="8">
-        <v>46196.60198236111</v>
+        <v>46196.76864902778</v>
       </c>
       <c r="D111" s="8">
-        <v>46196.60198721065</v>
+        <v>46196.76865387731</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>200</v>
@@ -8247,13 +8247,13 @@
         <v>314</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.43117026621</v>
+        <v>46125.597836932866</v>
       </c>
       <c r="C112" s="5">
-        <v>46196.601983333334</v>
+        <v>46196.76865</v>
       </c>
       <c r="D112" s="5">
-        <v>46196.60198760417</v>
+        <v>46196.76865427083</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>200</v>
@@ -8302,13 +8302,13 @@
         <v>315</v>
       </c>
       <c r="B113" s="8">
-        <v>46125.43125422453</v>
+        <v>46125.5979208912</v>
       </c>
       <c r="C113" s="8">
-        <v>46196.6019841088</v>
+        <v>46196.76865077546</v>
       </c>
       <c r="D113" s="8">
-        <v>46196.601987939815</v>
+        <v>46196.76865460648</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>200</v>
@@ -8357,13 +8357,13 @@
         <v>316</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.431214212964</v>
+        <v>46125.59788087963</v>
       </c>
       <c r="C114" s="5">
-        <v>46196.60198486111</v>
+        <v>46196.768651527775</v>
       </c>
       <c r="D114" s="5">
-        <v>46196.60198827546</v>
+        <v>46196.768654942134</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>200</v>
@@ -8412,13 +8412,13 @@
         <v>317</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.43129835648</v>
+        <v>46125.597965023146</v>
       </c>
       <c r="C115" s="8">
-        <v>46196.60198564814</v>
+        <v>46196.768652314815</v>
       </c>
       <c r="D115" s="8">
-        <v>46196.60198864584</v>
+        <v>46196.768655312495</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>200</v>
@@ -8467,13 +8467,13 @@
         <v>318</v>
       </c>
       <c r="B116" s="5">
-        <v>46122.38505377315</v>
+        <v>46122.55172043982</v>
       </c>
       <c r="C116" s="5">
-        <v>46196.6021055787</v>
+        <v>46196.76877224537</v>
       </c>
       <c r="D116" s="5">
-        <v>46196.60213211806</v>
+        <v>46196.768798784724</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>319</v>
@@ -8532,13 +8532,13 @@
         <v>320</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.43371586806</v>
+        <v>46125.60038253472</v>
       </c>
       <c r="C117" s="8">
-        <v>46196.602085914354</v>
+        <v>46196.76875258102</v>
       </c>
       <c r="D117" s="8">
-        <v>46196.602090671295</v>
+        <v>46196.768757337966</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>200</v>
@@ -8585,13 +8585,13 @@
         <v>322</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.43376346065</v>
+        <v>46125.60043012731</v>
       </c>
       <c r="C118" s="5">
-        <v>46196.60208681713</v>
+        <v>46196.7687534838</v>
       </c>
       <c r="D118" s="5">
-        <v>46196.60209101852</v>
+        <v>46196.76875768519</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>200</v>
@@ -8638,13 +8638,13 @@
         <v>323</v>
       </c>
       <c r="B119" s="8">
-        <v>46125.43380623843</v>
+        <v>46125.60047290509</v>
       </c>
       <c r="C119" s="8">
-        <v>46196.60208751158</v>
+        <v>46196.768754178236</v>
       </c>
       <c r="D119" s="8">
-        <v>46196.60209134259</v>
+        <v>46196.76875800926</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>200</v>
@@ -8691,13 +8691,13 @@
         <v>324</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.4338474074</v>
+        <v>46125.600514074074</v>
       </c>
       <c r="C120" s="5">
-        <v>46196.602088263884</v>
+        <v>46196.768754930556</v>
       </c>
       <c r="D120" s="5">
-        <v>46196.60209165509</v>
+        <v>46196.76875832176</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>200</v>
@@ -8744,13 +8744,13 @@
         <v>325</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.43389193287</v>
+        <v>46125.60055859954</v>
       </c>
       <c r="C121" s="8">
-        <v>46196.602089224536</v>
+        <v>46196.7687558912</v>
       </c>
       <c r="D121" s="8">
-        <v>46196.60209195602</v>
+        <v>46196.76875862268</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>200</v>
@@ -8797,13 +8797,13 @@
         <v>326</v>
       </c>
       <c r="B122" s="5">
-        <v>46122.385063194444</v>
+        <v>46122.55172986111</v>
       </c>
       <c r="C122" s="5">
-        <v>46196.60250790509</v>
+        <v>46196.76917457176</v>
       </c>
       <c r="D122" s="5">
-        <v>46196.60251917824</v>
+        <v>46196.76918584491</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>327</v>
@@ -8862,13 +8862,13 @@
         <v>329</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.4339775</v>
+        <v>46125.60064416667</v>
       </c>
       <c r="C123" s="8">
-        <v>46196.6024843287</v>
+        <v>46196.76915099537</v>
       </c>
       <c r="D123" s="8">
-        <v>46196.60249076389</v>
+        <v>46196.76915743056</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>200</v>
@@ -8915,13 +8915,13 @@
         <v>331</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.43402074074</v>
+        <v>46125.60068740741</v>
       </c>
       <c r="C124" s="5">
-        <v>46196.60248570602</v>
+        <v>46196.76915237268</v>
       </c>
       <c r="D124" s="5">
-        <v>46196.60249125</v>
+        <v>46196.76915791667</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>200</v>
@@ -8968,13 +8968,13 @@
         <v>332</v>
       </c>
       <c r="B125" s="8">
-        <v>46125.43407178241</v>
+        <v>46125.60073844907</v>
       </c>
       <c r="C125" s="8">
-        <v>46196.60248674768</v>
+        <v>46196.76915341435</v>
       </c>
       <c r="D125" s="8">
-        <v>46196.60249174769</v>
+        <v>46196.76915841435</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>200</v>
@@ -9021,13 +9021,13 @@
         <v>333</v>
       </c>
       <c r="B126" s="5">
-        <v>46125.434109560185</v>
+        <v>46125.60077622686</v>
       </c>
       <c r="C126" s="5">
-        <v>46196.60248771991</v>
+        <v>46196.76915438657</v>
       </c>
       <c r="D126" s="5">
-        <v>46196.60249217592</v>
+        <v>46196.769158842595</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>200</v>
@@ -9074,13 +9074,13 @@
         <v>334</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.43416247686</v>
+        <v>46125.600829143514</v>
       </c>
       <c r="C127" s="8">
-        <v>46196.60248869213</v>
+        <v>46196.769155358794</v>
       </c>
       <c r="D127" s="8">
-        <v>46196.60249265046</v>
+        <v>46196.76915931713</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>200</v>
@@ -9127,13 +9127,13 @@
         <v>335</v>
       </c>
       <c r="B128" s="5">
-        <v>46122.38506837963</v>
+        <v>46122.5517350463</v>
       </c>
       <c r="C128" s="5">
-        <v>46195.39650850694</v>
+        <v>46195.56317517361</v>
       </c>
       <c r="D128" s="5">
-        <v>46196.60293743055</v>
+        <v>46196.76960409722</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>336</v>
@@ -9180,13 +9180,13 @@
         <v>338</v>
       </c>
       <c r="B129" s="8">
-        <v>46122.38507239583</v>
+        <v>46122.5517390625</v>
       </c>
       <c r="C129" s="8">
-        <v>46196.60269986111</v>
+        <v>46196.76936652778</v>
       </c>
       <c r="D129" s="8">
-        <v>46196.602730694445</v>
+        <v>46196.76939736111</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>339</v>
@@ -9245,13 +9245,13 @@
         <v>343</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.43427064815</v>
+        <v>46125.60093731481</v>
       </c>
       <c r="C130" s="5">
-        <v>46196.602678483796</v>
+        <v>46196.76934515046</v>
       </c>
       <c r="D130" s="5">
-        <v>46196.60268401621</v>
+        <v>46196.769350682865</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>200</v>
@@ -9298,13 +9298,13 @@
         <v>345</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.4347141551</v>
+        <v>46125.601380821754</v>
       </c>
       <c r="C131" s="8">
-        <v>46196.602679641204</v>
+        <v>46196.769346307876</v>
       </c>
       <c r="D131" s="8">
-        <v>46196.60268447916</v>
+        <v>46196.769351145835</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>200</v>
@@ -9351,13 +9351,13 @@
         <v>346</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.43475814815</v>
+        <v>46125.60142481481</v>
       </c>
       <c r="C132" s="5">
-        <v>46196.60268056713</v>
+        <v>46196.7693472338</v>
       </c>
       <c r="D132" s="5">
-        <v>46196.60268488426</v>
+        <v>46196.76935155093</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>200</v>
@@ -9404,13 +9404,13 @@
         <v>347</v>
       </c>
       <c r="B133" s="8">
-        <v>46125.434794189816</v>
+        <v>46125.60146085648</v>
       </c>
       <c r="C133" s="8">
-        <v>46196.60268145833</v>
+        <v>46196.769348125</v>
       </c>
       <c r="D133" s="8">
-        <v>46196.602685254635</v>
+        <v>46196.76935192129</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>200</v>
@@ -9457,13 +9457,13 @@
         <v>348</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.434835416665</v>
+        <v>46125.60150208333</v>
       </c>
       <c r="C134" s="5">
-        <v>46196.60268231481</v>
+        <v>46196.769348981485</v>
       </c>
       <c r="D134" s="5">
-        <v>46196.602685624996</v>
+        <v>46196.76935229167</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>200</v>
@@ -9510,13 +9510,13 @@
         <v>349</v>
       </c>
       <c r="B135" s="8">
-        <v>46122.38507716435</v>
+        <v>46122.55174383102</v>
       </c>
       <c r="C135" s="8">
-        <v>46196.60293025463</v>
+        <v>46196.769596921295</v>
       </c>
       <c r="D135" s="8">
-        <v>46196.60294730324</v>
+        <v>46196.76961396991</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>350</v>
@@ -9573,13 +9573,13 @@
         <v>351</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.4344203125</v>
+        <v>46125.601086979164</v>
       </c>
       <c r="C136" s="5">
-        <v>46196.602804884256</v>
+        <v>46196.76947155093</v>
       </c>
       <c r="D136" s="5">
-        <v>46196.60280680556</v>
+        <v>46196.76947347222</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>200</v>
@@ -9626,13 +9626,13 @@
         <v>353</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.4344865162</v>
+        <v>46125.60115318287</v>
       </c>
       <c r="C137" s="8">
-        <v>46196.60283766204</v>
+        <v>46196.7695043287</v>
       </c>
       <c r="D137" s="8">
-        <v>46196.60284236111</v>
+        <v>46196.76950902778</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>200</v>
@@ -9679,13 +9679,13 @@
         <v>354</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.43453724537</v>
+        <v>46125.60120391204</v>
       </c>
       <c r="C138" s="5">
-        <v>46196.60283883102</v>
+        <v>46196.76950549769</v>
       </c>
       <c r="D138" s="5">
-        <v>46196.60284277778</v>
+        <v>46196.76950944445</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>200</v>
@@ -9732,13 +9732,13 @@
         <v>355</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.434591296296</v>
+        <v>46125.60125796296</v>
       </c>
       <c r="C139" s="8">
-        <v>46196.60283971065</v>
+        <v>46196.76950637731</v>
       </c>
       <c r="D139" s="8">
-        <v>46196.60284320602</v>
+        <v>46196.76950987268</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>200</v>
@@ -9785,13 +9785,13 @@
         <v>356</v>
       </c>
       <c r="B140" s="5">
-        <v>46125.43463761574</v>
+        <v>46125.601304282405</v>
       </c>
       <c r="C140" s="5">
-        <v>46196.60284063657</v>
+        <v>46196.76950730324</v>
       </c>
       <c r="D140" s="5">
-        <v>46196.60284359954</v>
+        <v>46196.769510266204</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>200</v>
@@ -9838,13 +9838,13 @@
         <v>357</v>
       </c>
       <c r="B141" s="8">
-        <v>46122.38508202546</v>
+        <v>46122.55174869213</v>
       </c>
       <c r="C141" s="8">
-        <v>46191.539318634255</v>
+        <v>46191.70598530093</v>
       </c>
       <c r="D141" s="8">
-        <v>46196.60304912037</v>
+        <v>46196.769715787035</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>358</v>
@@ -9901,13 +9901,13 @@
         <v>359</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.434919837964</v>
+        <v>46125.60158650463</v>
       </c>
       <c r="C142" s="5">
-        <v>46196.60301796296</v>
+        <v>46196.76968462963</v>
       </c>
       <c r="D142" s="5">
-        <v>46196.60302322917</v>
+        <v>46196.76968989584</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>200</v>
@@ -9954,13 +9954,13 @@
         <v>361</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.43496466435</v>
+        <v>46125.60163133102</v>
       </c>
       <c r="C143" s="8">
-        <v>46196.60301918982</v>
+        <v>46196.76968585648</v>
       </c>
       <c r="D143" s="8">
-        <v>46196.60302364583</v>
+        <v>46196.7696903125</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>200</v>
@@ -10007,13 +10007,13 @@
         <v>362</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.43500349537</v>
+        <v>46125.60167016204</v>
       </c>
       <c r="C144" s="5">
-        <v>46196.603019988426</v>
+        <v>46196.7696866551</v>
       </c>
       <c r="D144" s="5">
-        <v>46196.60302403935</v>
+        <v>46196.769690706016</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>200</v>
@@ -10060,13 +10060,13 @@
         <v>364</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.43503768518</v>
+        <v>46125.60170435185</v>
       </c>
       <c r="C145" s="8">
-        <v>46196.60302072916</v>
+        <v>46196.769687395834</v>
       </c>
       <c r="D145" s="8">
-        <v>46196.60302447916</v>
+        <v>46196.76969114583</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>200</v>
@@ -10113,13 +10113,13 @@
         <v>365</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.4350728125</v>
+        <v>46125.60173947917</v>
       </c>
       <c r="C146" s="5">
-        <v>46196.60302144676</v>
+        <v>46196.769688113425</v>
       </c>
       <c r="D146" s="5">
-        <v>46196.60302497685</v>
+        <v>46196.76969164352</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>200</v>
@@ -10166,13 +10166,13 @@
         <v>366</v>
       </c>
       <c r="B147" s="8">
-        <v>46122.38508680556</v>
+        <v>46122.551753472224</v>
       </c>
       <c r="C147" s="8">
-        <v>46191.53937342593</v>
+        <v>46191.70604009259</v>
       </c>
       <c r="D147" s="8">
-        <v>46196.60314438658</v>
+        <v>46196.76981105324</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>367</v>
@@ -10229,13 +10229,13 @@
         <v>369</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.43514888889</v>
+        <v>46125.60181555555</v>
       </c>
       <c r="C148" s="5">
-        <v>46196.60312598379</v>
+        <v>46196.76979265046</v>
       </c>
       <c r="D148" s="5">
-        <v>46196.603129027775</v>
+        <v>46196.76979569445</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>200</v>
@@ -10282,13 +10282,13 @@
         <v>370</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.43519024306</v>
+        <v>46125.60185690972</v>
       </c>
       <c r="C149" s="8">
-        <v>46196.603126898146</v>
+        <v>46196.76979356482</v>
       </c>
       <c r="D149" s="8">
-        <v>46196.60312947917</v>
+        <v>46196.76979614583</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>200</v>
@@ -10335,13 +10335,13 @@
         <v>371</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.43523282408</v>
+        <v>46125.601899490735</v>
       </c>
       <c r="C150" s="5">
-        <v>46196.60312755787</v>
+        <v>46196.769794224536</v>
       </c>
       <c r="D150" s="5">
-        <v>46196.603129814815</v>
+        <v>46196.76979648148</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>200</v>
@@ -10388,13 +10388,13 @@
         <v>372</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.43527268519</v>
+        <v>46125.60193935185</v>
       </c>
       <c r="C151" s="8">
-        <v>46196.603098101856</v>
+        <v>46196.76976476852</v>
       </c>
       <c r="D151" s="8">
-        <v>46196.60310020833</v>
+        <v>46196.769766875004</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>200</v>
@@ -10441,13 +10441,13 @@
         <v>373</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.43531043982</v>
+        <v>46125.60197710648</v>
       </c>
       <c r="C152" s="5">
-        <v>46196.603105393515</v>
+        <v>46196.76977206019</v>
       </c>
       <c r="D152" s="5">
-        <v>46196.60310703704</v>
+        <v>46196.76977370371</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>200</v>
@@ -10494,11 +10494,11 @@
         <v>374</v>
       </c>
       <c r="B153" s="8">
-        <v>46122.38509195602</v>
+        <v>46122.551758622685</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46125.422702118056</v>
+        <v>46125.58936878473</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>375</v>
@@ -10541,11 +10541,11 @@
         <v>377</v>
       </c>
       <c r="B154" s="5">
-        <v>46122.38509467593</v>
+        <v>46122.55176134259</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46191.53939100694</v>
+        <v>46191.70605767361</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>378</v>
@@ -10604,11 +10604,11 @@
         <v>381</v>
       </c>
       <c r="B155" s="8">
-        <v>46122.38509943287</v>
+        <v>46122.55176609954</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46192.80717747685</v>
+        <v>46192.97384414352</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>382</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -3778,7 +3778,7 @@
         <v>46181.66687207176</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.66688577546</v>
+        <v>46206.19763560186</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3822,8 +3822,8 @@
       <c r="R35" s="8">
         <v>46213</v>
       </c>
-      <c r="S35" s="11" t="s">
-        <v>105</v>
+      <c r="S35" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T35" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4490,7 +4490,7 @@
         <v>46181.66722120371</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.66723511574</v>
+        <v>46211.17825179399</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4534,8 +4534,8 @@
       <c r="R47" s="8">
         <v>46218</v>
       </c>
-      <c r="S47" s="11" t="s">
-        <v>105</v>
+      <c r="S47" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4140,7 +4140,7 @@
         <v>46181.666767002316</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.666783252316</v>
+        <v>46213.20535120371</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>155</v>
@@ -4184,8 +4184,8 @@
       <c r="R41" s="8">
         <v>46220</v>
       </c>
-      <c r="S41" s="11" t="s">
-        <v>105</v>
+      <c r="S41" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -5418,7 +5418,7 @@
         <v>46181.667430127316</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.66744925926</v>
+        <v>46213.20535071759</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -5462,8 +5462,8 @@
       <c r="R63" s="8">
         <v>46220</v>
       </c>
-      <c r="S63" s="11" t="s">
-        <v>105</v>
+      <c r="S63" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T63" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -3778,7 +3778,7 @@
         <v>46181.66687207176</v>
       </c>
       <c r="D35" s="8">
-        <v>46206.19763560186</v>
+        <v>46214.17760775463</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>136</v>
@@ -3822,8 +3822,8 @@
       <c r="R35" s="8">
         <v>46213</v>
       </c>
-      <c r="S35" s="12" t="s">
-        <v>74</v>
+      <c r="S35" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T35" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="380">
   <si>
     <t xml:space="preserve"> 50001466 - ZITRON PERU (PODEROSA) </t>
   </si>
@@ -305,9 +305,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
   </si>
   <si>
@@ -315,12 +312,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2722,11 +2713,9 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46136</v>
       </c>
@@ -2749,7 +2738,7 @@
         <v>55</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q18" s="5">
         <v>46136</v>
@@ -2769,7 +2758,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="8">
         <v>46122.55140604167</v>
@@ -2781,17 +2770,15 @@
         <v>46203.203668229165</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>82</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="9"/>
       <c r="I19" s="8">
         <v>46199</v>
       </c>
@@ -2811,10 +2798,10 @@
         <v>66</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="8">
         <v>46199</v>
@@ -2834,7 +2821,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46122.55141162037</v>
@@ -2867,7 +2854,7 @@
         <v>26</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>26</v>
@@ -2879,7 +2866,7 @@
         <v>62</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46136</v>
@@ -2899,7 +2886,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B21" s="8">
         <v>46122.566545787035</v>
@@ -2911,17 +2898,15 @@
         <v>46203.20366833333</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>82</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="9"/>
       <c r="I21" s="8">
         <v>46199</v>
       </c>
@@ -2941,10 +2926,10 @@
         <v>66</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="8">
         <v>46199</v>
@@ -2964,7 +2949,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46122.56661521991</v>
@@ -2976,17 +2961,15 @@
         <v>46203.20366849537</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>82</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>46199</v>
       </c>
@@ -3006,10 +2989,10 @@
         <v>66</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46199</v>
@@ -3029,7 +3012,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46122.57286273148</v>
@@ -3041,17 +3024,15 @@
         <v>46203.2036682176</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>82</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H23" s="9"/>
       <c r="I23" s="8">
         <v>46199</v>
       </c>
@@ -3071,10 +3052,10 @@
         <v>66</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="8">
         <v>46199</v>
@@ -3094,7 +3075,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46122.55120394676</v>
@@ -3106,7 +3087,7 @@
         <v>46195.50735353009</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>25</v>
@@ -3130,7 +3111,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -3147,7 +3128,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B25" s="8">
         <v>46122.55141694444</v>
@@ -3159,16 +3140,16 @@
         <v>46174.626181134256</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I25" s="8">
         <v>46140</v>
@@ -3186,13 +3167,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="8">
         <v>46142</v>
@@ -3201,7 +3182,7 @@
         <v>46265</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T25" s="9">
         <v>1</v>
@@ -3212,7 +3193,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46122.55142208333</v>
@@ -3224,16 +3205,16 @@
         <v>46174.62325449074</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I26" s="5">
         <v>46140</v>
@@ -3251,29 +3232,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46122.55142699074</v>
@@ -3285,16 +3266,16 @@
         <v>46174.62615429398</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I27" s="8">
         <v>46142</v>
@@ -3312,29 +3293,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46122.5514322338</v>
@@ -3346,16 +3327,16 @@
         <v>46195.71184679398</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I28" s="5">
         <v>46140</v>
@@ -3373,13 +3354,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q28" s="5">
         <v>46140</v>
@@ -3394,12 +3375,12 @@
         <v>1</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46122.551437546295</v>
@@ -3411,16 +3392,16 @@
         <v>46195.71138517361</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I29" s="8">
         <v>46140</v>
@@ -3438,29 +3419,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>76</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46122.55144255787</v>
@@ -3472,16 +3453,16 @@
         <v>46195.711832500005</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I30" s="5">
         <v>46142</v>
@@ -3499,29 +3480,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46122.551447708334</v>
@@ -3533,16 +3514,16 @@
         <v>46133.82781321759</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I31" s="8">
         <v>46133</v>
@@ -3560,13 +3541,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q31" s="8">
         <v>46133</v>
@@ -3575,7 +3556,7 @@
         <v>46308</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T31" s="9">
         <v>1</v>
@@ -3586,7 +3567,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46122.5514527662</v>
@@ -3598,16 +3579,16 @@
         <v>46133.82773260417</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I32" s="5">
         <v>46133</v>
@@ -3625,29 +3606,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46122.55145796297</v>
@@ -3659,16 +3640,16 @@
         <v>46133.82778807871</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I33" s="8">
         <v>46153</v>
@@ -3686,29 +3667,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="O33" s="9" t="s">
-        <v>127</v>
-      </c>
       <c r="P33" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46122.55146299768</v>
@@ -3720,16 +3701,16 @@
         <v>46133.827769131945</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I34" s="5">
         <v>46153</v>
@@ -3747,29 +3728,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="O34" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="O34" s="6" t="s">
-        <v>127</v>
-      </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46122.55146795139</v>
@@ -3781,16 +3762,16 @@
         <v>46214.17760775463</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I35" s="8">
         <v>46203</v>
@@ -3808,13 +3789,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q35" s="8">
         <v>46203</v>
@@ -3834,7 +3815,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46122.551472974534</v>
@@ -3846,16 +3827,16 @@
         <v>46181.66681946759</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46203</v>
@@ -3873,29 +3854,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>46122.55152253472</v>
@@ -3907,16 +3888,16 @@
         <v>46181.66685818287</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I37" s="8">
         <v>46205</v>
@@ -3934,29 +3915,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46122.55152891204</v>
@@ -3968,16 +3949,16 @@
         <v>46189.172213136575</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I38" s="5">
         <v>46140</v>
@@ -3995,13 +3976,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q38" s="5">
         <v>46140</v>
@@ -4021,7 +4002,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46122.5515340625</v>
@@ -4033,16 +4014,16 @@
         <v>46154.86751927083</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I39" s="8">
         <v>46140</v>
@@ -4060,13 +4041,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4076,7 +4057,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46122.55153844907</v>
@@ -4088,16 +4069,16 @@
         <v>46154.867577453704</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I40" s="5">
         <v>46160</v>
@@ -4115,13 +4096,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4131,7 +4112,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46122.574933449076</v>
@@ -4143,16 +4124,16 @@
         <v>46213.20535120371</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I41" s="8">
         <v>46203</v>
@@ -4170,10 +4151,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4196,7 +4177,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46122.575920972224</v>
@@ -4208,16 +4189,16 @@
         <v>46181.66670855324</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I42" s="5">
         <v>46203</v>
@@ -4235,13 +4216,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4251,7 +4232,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46122.57608475695</v>
@@ -4263,16 +4244,16 @@
         <v>46181.666754351856</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I43" s="8">
         <v>46212</v>
@@ -4290,13 +4271,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4306,7 +4287,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46122.57501438657</v>
@@ -4318,16 +4299,16 @@
         <v>46181.66706865741</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4345,10 +4326,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4360,7 +4341,7 @@
         <v>46238</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4371,7 +4352,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46122.57922111111</v>
@@ -4383,16 +4364,16 @@
         <v>46181.66690306713</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I45" s="8">
         <v>46203</v>
@@ -4410,13 +4391,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4426,7 +4407,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46122.57949202546</v>
@@ -4438,16 +4419,16 @@
         <v>46181.66694460648</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I46" s="5">
         <v>46210</v>
@@ -4465,13 +4446,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4481,7 +4462,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46125.529618217595</v>
@@ -4493,16 +4474,16 @@
         <v>46211.17825179399</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I47" s="8">
         <v>46203</v>
@@ -4520,10 +4501,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4546,7 +4527,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46125.52977997685</v>
@@ -4558,16 +4539,16 @@
         <v>46181.66715912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I48" s="5">
         <v>46203</v>
@@ -4585,13 +4566,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4601,7 +4582,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B49" s="8">
         <v>46125.52991815972</v>
@@ -4613,16 +4594,16 @@
         <v>46181.66720563658</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I49" s="8">
         <v>46210</v>
@@ -4640,13 +4621,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4656,7 +4637,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B50" s="5">
         <v>46122.55120855324</v>
@@ -4668,7 +4649,7 @@
         <v>46195.50756488426</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4692,7 +4673,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4709,7 +4690,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B51" s="8">
         <v>46122.55154344907</v>
@@ -4721,16 +4702,16 @@
         <v>46143.171145879634</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I51" s="8">
         <v>46136</v>
@@ -4748,13 +4729,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Q51" s="8">
         <v>46136</v>
@@ -4774,7 +4755,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B52" s="5">
         <v>46122.551548993055</v>
@@ -4786,16 +4767,16 @@
         <v>46198.18781711806</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I52" s="5">
         <v>46191</v>
@@ -4813,13 +4794,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q52" s="5">
         <v>46191</v>
@@ -4839,7 +4820,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B53" s="8">
         <v>46122.55155721065</v>
@@ -4851,16 +4832,16 @@
         <v>46199.18371805556</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4876,13 +4857,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="8">
         <v>46198</v>
@@ -4902,7 +4883,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5">
         <v>46122.55156568287</v>
@@ -4914,16 +4895,16 @@
         <v>46196.76907818287</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4939,10 +4920,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4954,18 +4935,18 @@
         <v>46316</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46125.603622118055</v>
@@ -4977,16 +4958,16 @@
         <v>46196.7690521412</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -5002,13 +4983,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -5018,7 +4999,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46125.60367094907</v>
@@ -5030,16 +5011,16 @@
         <v>46196.769052523145</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5055,13 +5036,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5071,7 +5052,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46125.60371951389</v>
@@ -5083,16 +5064,16 @@
         <v>46196.76905283565</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -5108,13 +5089,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5124,7 +5105,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46125.60376462963</v>
@@ -5136,16 +5117,16 @@
         <v>46196.76905314815</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5161,13 +5142,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5177,7 +5158,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B59" s="8">
         <v>46125.60381739584</v>
@@ -5189,16 +5170,16 @@
         <v>46196.76905349537</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5214,13 +5195,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5230,7 +5211,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46122.551569710646</v>
@@ -5242,7 +5223,7 @@
         <v>46181.66785324074</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5266,7 +5247,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5279,7 +5260,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B61" s="8">
         <v>46122.55157321759</v>
@@ -5291,16 +5272,16 @@
         <v>46181.66739524306</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I61" s="8">
         <v>46216</v>
@@ -5318,13 +5299,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q61" s="8">
         <v>46216</v>
@@ -5344,7 +5325,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B62" s="5">
         <v>46122.58491638889</v>
@@ -5356,16 +5337,16 @@
         <v>46181.667429016205</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46223</v>
@@ -5383,13 +5364,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q62" s="5">
         <v>46132</v>
@@ -5409,7 +5390,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B63" s="8">
         <v>46125.53102658565</v>
@@ -5421,16 +5402,16 @@
         <v>46213.20535071759</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I63" s="8">
         <v>46219</v>
@@ -5448,13 +5429,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q63" s="8">
         <v>46219</v>
@@ -5474,7 +5455,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B64" s="5">
         <v>46122.55157846065</v>
@@ -5486,16 +5467,16 @@
         <v>46181.66777241898</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I64" s="5">
         <v>46225</v>
@@ -5513,13 +5494,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="5">
         <v>46225</v>
@@ -5528,7 +5509,7 @@
         <v>46226</v>
       </c>
       <c r="S64" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T64" s="6">
         <v>1</v>
@@ -5539,7 +5520,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B65" s="8">
         <v>46122.551583831024</v>
@@ -5551,7 +5532,7 @@
         <v>46181.66890770833</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5575,7 +5556,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5588,7 +5569,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
         <v>46122.55158688658</v>
@@ -5600,16 +5581,16 @@
         <v>46181.66880932871</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I66" s="5">
         <v>46227</v>
@@ -5627,13 +5608,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q66" s="5">
         <v>46227</v>
@@ -5642,7 +5623,7 @@
         <v>46237</v>
       </c>
       <c r="S66" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -5653,7 +5634,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B67" s="8">
         <v>46122.55159185185</v>
@@ -5665,16 +5646,16 @@
         <v>46181.668846064815</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I67" s="8">
         <v>46238</v>
@@ -5692,13 +5673,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5707,7 +5688,7 @@
         <v>46255</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>
@@ -5718,7 +5699,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46125.595811921296</v>
@@ -5730,16 +5711,16 @@
         <v>46181.66807884259</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I68" s="5">
         <v>46238</v>
@@ -5757,13 +5738,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5773,7 +5754,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B69" s="8">
         <v>46125.59610047453</v>
@@ -5785,16 +5766,16 @@
         <v>46181.66808728009</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I69" s="8">
         <v>46238</v>
@@ -5812,13 +5793,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5828,7 +5809,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46125.59621038195</v>
@@ -5840,16 +5821,16 @@
         <v>46181.66815550926</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I70" s="5">
         <v>46238</v>
@@ -5867,13 +5848,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5883,7 +5864,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46125.59625472222</v>
@@ -5895,16 +5876,16 @@
         <v>46181.66816819445</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I71" s="8">
         <v>46238</v>
@@ -5922,13 +5903,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5938,7 +5919,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46125.59629915509</v>
@@ -5950,16 +5931,16 @@
         <v>46181.66818078703</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I72" s="5">
         <v>46238</v>
@@ -5977,13 +5958,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5993,7 +5974,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B73" s="8">
         <v>46122.55159751157</v>
@@ -6005,16 +5986,16 @@
         <v>46181.66878222222</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I73" s="8">
         <v>46258</v>
@@ -6032,13 +6013,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q73" s="8">
         <v>46258</v>
@@ -6047,7 +6028,7 @@
         <v>46259</v>
       </c>
       <c r="S73" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T73" s="9">
         <v>1</v>
@@ -6058,7 +6039,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46125.59648849537</v>
@@ -6070,16 +6051,16 @@
         <v>46181.6686533912</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I74" s="5">
         <v>46258</v>
@@ -6097,13 +6078,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>245</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6113,7 +6094,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B75" s="8">
         <v>46125.59661854166</v>
@@ -6125,16 +6106,16 @@
         <v>46181.66866782407</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6152,13 +6133,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="O75" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="P75" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6168,7 +6149,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
         <v>46125.596668750004</v>
@@ -6180,16 +6161,16 @@
         <v>46181.66867745371</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6207,13 +6188,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>245</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6223,7 +6204,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B77" s="8">
         <v>46125.59671550926</v>
@@ -6235,16 +6216,16 @@
         <v>46181.668687060184</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6262,13 +6243,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="O77" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="P77" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>253</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6278,7 +6259,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46125.59675546296</v>
@@ -6290,16 +6271,16 @@
         <v>46181.66870502315</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I78" s="5">
         <v>46258</v>
@@ -6317,13 +6298,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6333,7 +6314,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>46122.55160357639</v>
@@ -6345,7 +6326,7 @@
         <v>46195.563290335645</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6369,7 +6350,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6381,12 +6362,12 @@
         <v>1</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46122.55160679398</v>
@@ -6398,16 +6379,16 @@
         <v>46195.711846817125</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I80" s="5">
         <v>46191</v>
@@ -6425,13 +6406,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q80" s="5">
         <v>46191</v>
@@ -6446,12 +6427,12 @@
         <v>1</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B81" s="8">
         <v>46122.551612256946</v>
@@ -6463,16 +6444,16 @@
         <v>46195.50753130787</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I81" s="8">
         <v>46266</v>
@@ -6490,13 +6471,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q81" s="8">
         <v>46266</v>
@@ -6505,7 +6486,7 @@
         <v>46267</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>
@@ -6516,7 +6497,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46122.55161756944</v>
@@ -6528,16 +6509,16 @@
         <v>46195.50753259259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I82" s="5">
         <v>46309</v>
@@ -6555,13 +6536,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q82" s="5">
         <v>46309</v>
@@ -6570,7 +6551,7 @@
         <v>46310</v>
       </c>
       <c r="S82" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6581,7 +6562,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B83" s="8">
         <v>46122.55162288195</v>
@@ -6593,16 +6574,16 @@
         <v>46195.507539479164</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I83" s="8">
         <v>46189</v>
@@ -6620,13 +6601,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q83" s="8">
         <v>46189</v>
@@ -6646,7 +6627,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B84" s="5">
         <v>46122.59399163195</v>
@@ -6658,16 +6639,16 @@
         <v>46193.9332800463</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I84" s="5">
         <v>46239</v>
@@ -6685,13 +6666,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Q84" s="5">
         <v>46239</v>
@@ -6700,7 +6681,7 @@
         <v>46240</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T84" s="6">
         <v>1</v>
@@ -6711,7 +6692,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B85" s="8">
         <v>46122.551628182875</v>
@@ -6723,7 +6704,7 @@
         <v>46196.769192685184</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6747,7 +6728,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6759,12 +6740,12 @@
         <v>1</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B86" s="5">
         <v>46122.55163158565</v>
@@ -6776,17 +6757,15 @@
         <v>46195.507707129625</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H86" s="6"/>
       <c r="I86" s="5">
         <v>46260</v>
       </c>
@@ -6803,13 +6782,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q86" s="5">
         <v>46260</v>
@@ -6818,7 +6797,7 @@
         <v>46279</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -6829,7 +6808,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B87" s="8">
         <v>46125.5974969213</v>
@@ -6841,17 +6820,15 @@
         <v>46196.767918831014</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H87" s="9"/>
       <c r="I87" s="8">
         <v>46260</v>
       </c>
@@ -6868,13 +6845,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="O87" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="O87" s="9" t="s">
-        <v>276</v>
-      </c>
       <c r="P87" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6884,7 +6861,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46125.59754570602</v>
@@ -6896,17 +6873,15 @@
         <v>46196.76795645834</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="I88" s="5">
         <v>46260</v>
       </c>
@@ -6923,13 +6898,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="O88" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="O88" s="6" t="s">
-        <v>276</v>
-      </c>
       <c r="P88" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6939,7 +6914,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B89" s="8">
         <v>46125.59760710648</v>
@@ -6951,17 +6926,15 @@
         <v>46196.76793001157</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H89" s="9"/>
       <c r="I89" s="8">
         <v>46260</v>
       </c>
@@ -6978,13 +6951,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="O89" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="O89" s="9" t="s">
-        <v>276</v>
-      </c>
       <c r="P89" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6994,7 +6967,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B90" s="5">
         <v>46125.59765891204</v>
@@ -7006,17 +6979,15 @@
         <v>46196.76794809027</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
       <c r="I90" s="5">
         <v>46260</v>
       </c>
@@ -7033,13 +7004,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="O90" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="O90" s="6" t="s">
-        <v>276</v>
-      </c>
       <c r="P90" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7049,7 +7020,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B91" s="8">
         <v>46125.597703391206</v>
@@ -7061,17 +7032,15 @@
         <v>46196.76794287037</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H91" s="9"/>
       <c r="I91" s="8">
         <v>46260</v>
       </c>
@@ -7088,13 +7057,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="O91" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="O91" s="9" t="s">
-        <v>276</v>
-      </c>
       <c r="P91" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7104,7 +7073,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B92" s="5">
         <v>46122.55170659722</v>
@@ -7116,17 +7085,15 @@
         <v>46196.76807780092</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H92" s="6"/>
       <c r="I92" s="5">
         <v>46280</v>
       </c>
@@ -7143,13 +7110,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q92" s="5">
         <v>46280</v>
@@ -7158,18 +7125,18 @@
         <v>46282</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B93" s="8">
         <v>46125.59982741898</v>
@@ -7181,17 +7148,15 @@
         <v>46196.76800386574</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="9"/>
       <c r="I93" s="8">
         <v>46280</v>
       </c>
@@ -7208,13 +7173,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="O93" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="P93" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="O93" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7224,7 +7189,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B94" s="5">
         <v>46125.599890833335</v>
@@ -7236,17 +7201,15 @@
         <v>46196.768024687495</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="5">
         <v>46280</v>
       </c>
@@ -7263,13 +7226,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O94" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>287</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7279,7 +7242,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B95" s="8">
         <v>46125.59993134259</v>
@@ -7291,17 +7254,15 @@
         <v>46196.76801675926</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H95" s="9"/>
       <c r="I95" s="8">
         <v>46280</v>
       </c>
@@ -7318,13 +7279,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="O95" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7334,7 +7295,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B96" s="5">
         <v>46125.59996929398</v>
@@ -7346,17 +7307,15 @@
         <v>46196.76805278935</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
       <c r="I96" s="5">
         <v>46280</v>
       </c>
@@ -7373,13 +7332,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7389,7 +7348,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B97" s="8">
         <v>46125.6000115162</v>
@@ -7401,17 +7360,15 @@
         <v>46196.76805907408</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H97" s="9"/>
       <c r="I97" s="8">
         <v>46280</v>
       </c>
@@ -7428,13 +7385,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="O97" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="P97" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="O97" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7444,7 +7401,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B98" s="5">
         <v>46122.55164413195</v>
@@ -7456,17 +7413,15 @@
         <v>46196.76840872686</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H98" s="6"/>
       <c r="I98" s="5">
         <v>46286</v>
       </c>
@@ -7483,13 +7438,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q98" s="5">
         <v>46286</v>
@@ -7498,7 +7453,7 @@
         <v>46288</v>
       </c>
       <c r="S98" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T98" s="6">
         <v>1</v>
@@ -7509,7 +7464,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B99" s="8">
         <v>46125.599162743056</v>
@@ -7521,17 +7476,15 @@
         <v>46196.7681912963</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H99" s="9"/>
       <c r="I99" s="8">
         <v>46286</v>
       </c>
@@ -7548,13 +7501,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="O99" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="O99" s="9" t="s">
-        <v>295</v>
-      </c>
       <c r="P99" s="9" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7564,7 +7517,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B100" s="5">
         <v>46125.599302511575</v>
@@ -7576,17 +7529,15 @@
         <v>46196.76820597222</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H100" s="6"/>
       <c r="I100" s="5">
         <v>46286</v>
       </c>
@@ -7603,13 +7554,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="O100" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="O100" s="6" t="s">
-        <v>295</v>
-      </c>
       <c r="P100" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7619,7 +7570,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B101" s="8">
         <v>46125.59934644676</v>
@@ -7631,17 +7582,15 @@
         <v>46196.76837958333</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H101" s="9"/>
       <c r="I101" s="8">
         <v>46286</v>
       </c>
@@ -7658,13 +7607,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="O101" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="O101" s="9" t="s">
-        <v>295</v>
-      </c>
       <c r="P101" s="9" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7674,7 +7623,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B102" s="5">
         <v>46125.59938857639</v>
@@ -7686,17 +7635,15 @@
         <v>46196.76838008102</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H102" s="6"/>
       <c r="I102" s="5">
         <v>46286</v>
       </c>
@@ -7713,13 +7660,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="O102" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="O102" s="6" t="s">
-        <v>295</v>
-      </c>
       <c r="P102" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7729,7 +7676,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B103" s="8">
         <v>46125.59943094908</v>
@@ -7741,17 +7688,15 @@
         <v>46196.768380520836</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H103" s="9"/>
       <c r="I103" s="8">
         <v>46286</v>
       </c>
@@ -7768,13 +7713,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="O103" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="O103" s="9" t="s">
-        <v>295</v>
-      </c>
       <c r="P103" s="9" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7784,7 +7729,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B104" s="5">
         <v>46122.551650995374</v>
@@ -7796,17 +7741,15 @@
         <v>46196.76856074074</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H104" s="6"/>
       <c r="I104" s="5">
         <v>46289</v>
       </c>
@@ -7823,13 +7766,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q104" s="5">
         <v>46289</v>
@@ -7838,18 +7781,18 @@
         <v>46293</v>
       </c>
       <c r="S104" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>
       </c>
       <c r="U104" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B105" s="8">
         <v>46125.59953013889</v>
@@ -7861,17 +7804,15 @@
         <v>46196.768531724534</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H105" s="9"/>
       <c r="I105" s="8">
         <v>46289</v>
       </c>
@@ -7888,13 +7829,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7904,7 +7845,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B106" s="5">
         <v>46125.59961423611</v>
@@ -7916,17 +7857,15 @@
         <v>46196.76846496528</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H106" s="6"/>
       <c r="I106" s="5">
         <v>46289</v>
       </c>
@@ -7943,13 +7882,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7959,7 +7898,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B107" s="8">
         <v>46125.599654317135</v>
@@ -7971,17 +7910,15 @@
         <v>46196.76853203704</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H107" s="9"/>
       <c r="I107" s="8">
         <v>46289</v>
       </c>
@@ -7998,13 +7935,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8014,7 +7951,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B108" s="5">
         <v>46125.59957065972</v>
@@ -8026,17 +7963,15 @@
         <v>46196.76853233796</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H108" s="6"/>
       <c r="I108" s="5">
         <v>46289</v>
       </c>
@@ -8053,13 +7988,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8069,7 +8004,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B109" s="8">
         <v>46125.59969711806</v>
@@ -8081,17 +8016,15 @@
         <v>46196.76853265046</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H109" s="9"/>
       <c r="I109" s="8">
         <v>46289</v>
       </c>
@@ -8108,13 +8041,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8124,7 +8057,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B110" s="5">
         <v>46122.55163725694</v>
@@ -8136,17 +8069,15 @@
         <v>46196.76867908565</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H110" s="6"/>
       <c r="I110" s="5">
         <v>46311</v>
       </c>
@@ -8163,13 +8094,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q110" s="5">
         <v>46311</v>
@@ -8178,7 +8109,7 @@
         <v>46314</v>
       </c>
       <c r="S110" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T110" s="6">
         <v>1</v>
@@ -8189,7 +8120,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B111" s="8">
         <v>46125.59780210648</v>
@@ -8201,17 +8132,15 @@
         <v>46196.76865387731</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H111" s="9"/>
       <c r="I111" s="8">
         <v>46311</v>
       </c>
@@ -8228,13 +8157,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="O111" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="P111" s="9" t="s">
         <v>310</v>
-      </c>
-      <c r="O111" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="P111" s="9" t="s">
-        <v>313</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8244,7 +8173,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B112" s="5">
         <v>46125.597836932866</v>
@@ -8256,17 +8185,15 @@
         <v>46196.76865427083</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H112" s="6"/>
       <c r="I112" s="5">
         <v>46311</v>
       </c>
@@ -8283,13 +8210,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="O112" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="P112" s="6" t="s">
         <v>310</v>
-      </c>
-      <c r="O112" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="P112" s="6" t="s">
-        <v>313</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8299,7 +8226,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B113" s="8">
         <v>46125.5979208912</v>
@@ -8311,17 +8238,15 @@
         <v>46196.76865460648</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H113" s="9"/>
       <c r="I113" s="8">
         <v>46311</v>
       </c>
@@ -8338,13 +8263,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="O113" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="P113" s="9" t="s">
         <v>310</v>
-      </c>
-      <c r="O113" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="P113" s="9" t="s">
-        <v>313</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8354,7 +8279,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B114" s="5">
         <v>46125.59788087963</v>
@@ -8366,17 +8291,15 @@
         <v>46196.768654942134</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H114" s="6"/>
       <c r="I114" s="5">
         <v>46311</v>
       </c>
@@ -8393,13 +8316,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="O114" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="P114" s="6" t="s">
         <v>310</v>
-      </c>
-      <c r="O114" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>313</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8409,7 +8332,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B115" s="8">
         <v>46125.597965023146</v>
@@ -8421,17 +8344,15 @@
         <v>46196.768655312495</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H115" s="9"/>
       <c r="I115" s="8">
         <v>46311</v>
       </c>
@@ -8448,13 +8369,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="O115" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="P115" s="9" t="s">
         <v>310</v>
-      </c>
-      <c r="O115" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="P115" s="9" t="s">
-        <v>313</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8464,7 +8385,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B116" s="5">
         <v>46122.55172043982</v>
@@ -8476,17 +8397,15 @@
         <v>46196.768798784724</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H116" s="6"/>
       <c r="I116" s="5">
         <v>46315</v>
       </c>
@@ -8503,13 +8422,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q116" s="5">
         <v>46315</v>
@@ -8518,18 +8437,18 @@
         <v>46315</v>
       </c>
       <c r="S116" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T116" s="6">
         <v>1</v>
       </c>
       <c r="U116" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B117" s="8">
         <v>46125.60038253472</v>
@@ -8541,17 +8460,15 @@
         <v>46196.768757337966</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H117" s="9"/>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
         <v>46315</v>
@@ -8566,13 +8483,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8582,7 +8499,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B118" s="5">
         <v>46125.60043012731</v>
@@ -8594,17 +8511,15 @@
         <v>46196.76875768519</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H118" s="6"/>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
         <v>46315</v>
@@ -8619,13 +8534,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8635,7 +8550,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B119" s="8">
         <v>46125.60047290509</v>
@@ -8647,17 +8562,15 @@
         <v>46196.76875800926</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H119" s="9"/>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
         <v>46315</v>
@@ -8672,13 +8585,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8688,7 +8601,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B120" s="5">
         <v>46125.600514074074</v>
@@ -8700,17 +8613,15 @@
         <v>46196.76875832176</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H120" s="6"/>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
         <v>46315</v>
@@ -8725,13 +8636,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8741,7 +8652,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B121" s="8">
         <v>46125.60055859954</v>
@@ -8753,17 +8664,15 @@
         <v>46196.76875862268</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H121" s="9"/>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
         <v>46315</v>
@@ -8778,13 +8687,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8794,7 +8703,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B122" s="5">
         <v>46122.55172986111</v>
@@ -8806,17 +8715,15 @@
         <v>46196.76918584491</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H122" s="6"/>
       <c r="I122" s="5">
         <v>46317</v>
       </c>
@@ -8833,13 +8740,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="Q122" s="5">
         <v>46317</v>
@@ -8848,7 +8755,7 @@
         <v>46317</v>
       </c>
       <c r="S122" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T122" s="6">
         <v>1</v>
@@ -8859,7 +8766,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B123" s="8">
         <v>46125.60064416667</v>
@@ -8871,17 +8778,15 @@
         <v>46196.76915743056</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="9"/>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
         <v>46317</v>
@@ -8896,13 +8801,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="O123" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="P123" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="O123" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="P123" s="9" t="s">
-        <v>330</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8912,7 +8817,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B124" s="5">
         <v>46125.60068740741</v>
@@ -8924,17 +8829,15 @@
         <v>46196.76915791667</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H124" s="6"/>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
         <v>46317</v>
@@ -8949,13 +8852,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="O124" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="P124" s="6" t="s">
         <v>327</v>
-      </c>
-      <c r="O124" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="P124" s="6" t="s">
-        <v>330</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8965,7 +8868,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B125" s="8">
         <v>46125.60073844907</v>
@@ -8977,17 +8880,15 @@
         <v>46196.76915841435</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H125" s="9"/>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
         <v>46317</v>
@@ -9002,13 +8903,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="O125" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="P125" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="O125" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="P125" s="9" t="s">
-        <v>330</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9018,7 +8919,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B126" s="5">
         <v>46125.60077622686</v>
@@ -9030,17 +8931,15 @@
         <v>46196.769158842595</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H126" s="6"/>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
         <v>46317</v>
@@ -9055,13 +8954,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="O126" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="P126" s="6" t="s">
         <v>327</v>
-      </c>
-      <c r="O126" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="P126" s="6" t="s">
-        <v>330</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9071,7 +8970,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B127" s="8">
         <v>46125.600829143514</v>
@@ -9083,17 +8982,15 @@
         <v>46196.76915931713</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H127" s="9"/>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
         <v>46317</v>
@@ -9108,13 +9005,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="O127" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="P127" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="O127" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="P127" s="9" t="s">
-        <v>330</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9124,7 +9021,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B128" s="5">
         <v>46122.5517350463</v>
@@ -9136,7 +9033,7 @@
         <v>46196.76960409722</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>25</v>
@@ -9160,7 +9057,7 @@
         <v>26</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>26</v>
@@ -9172,12 +9069,12 @@
         <v>1</v>
       </c>
       <c r="U128" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B129" s="8">
         <v>46122.5517390625</v>
@@ -9189,16 +9086,16 @@
         <v>46196.76939736111</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I129" s="8">
         <v>46318</v>
@@ -9216,13 +9113,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="Q129" s="8">
         <v>46318</v>
@@ -9231,18 +9128,18 @@
         <v>46318</v>
       </c>
       <c r="S129" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T129" s="9">
         <v>1</v>
       </c>
       <c r="U129" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B130" s="5">
         <v>46125.60093731481</v>
@@ -9254,16 +9151,16 @@
         <v>46196.769350682865</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9279,13 +9176,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9295,7 +9192,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B131" s="8">
         <v>46125.601380821754</v>
@@ -9307,16 +9204,16 @@
         <v>46196.769351145835</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9332,13 +9229,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9348,7 +9245,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B132" s="5">
         <v>46125.60142481481</v>
@@ -9360,16 +9257,16 @@
         <v>46196.76935155093</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9385,13 +9282,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9401,7 +9298,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B133" s="8">
         <v>46125.60146085648</v>
@@ -9413,16 +9310,16 @@
         <v>46196.76935192129</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9438,13 +9335,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9454,7 +9351,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B134" s="5">
         <v>46125.60150208333</v>
@@ -9466,16 +9363,16 @@
         <v>46196.76935229167</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9491,13 +9388,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9507,7 +9404,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B135" s="8">
         <v>46122.55174383102</v>
@@ -9519,17 +9416,15 @@
         <v>46196.76961396991</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H135" s="9"/>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
         <v>46321</v>
@@ -9544,13 +9439,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="Q135" s="8">
         <v>46321</v>
@@ -9559,7 +9454,7 @@
         <v>46321</v>
       </c>
       <c r="S135" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T135" s="9">
         <v>1</v>
@@ -9570,7 +9465,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B136" s="5">
         <v>46125.601086979164</v>
@@ -9582,17 +9477,15 @@
         <v>46196.76947347222</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H136" s="6"/>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
         <v>46321</v>
@@ -9607,13 +9500,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9623,7 +9516,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B137" s="8">
         <v>46125.60115318287</v>
@@ -9635,17 +9528,15 @@
         <v>46196.76950902778</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H137" s="9"/>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
         <v>46321</v>
@@ -9660,13 +9551,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9676,7 +9567,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B138" s="5">
         <v>46125.60120391204</v>
@@ -9688,17 +9579,15 @@
         <v>46196.76950944445</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H138" s="6"/>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
         <v>46321</v>
@@ -9713,13 +9602,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9729,7 +9618,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B139" s="8">
         <v>46125.60125796296</v>
@@ -9741,17 +9630,15 @@
         <v>46196.76950987268</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H139" s="9"/>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
         <v>46321</v>
@@ -9766,13 +9653,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9782,7 +9669,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B140" s="5">
         <v>46125.601304282405</v>
@@ -9794,17 +9681,15 @@
         <v>46196.769510266204</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>77</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H140" s="6"/>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
         <v>46321</v>
@@ -9819,13 +9704,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9835,7 +9720,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B141" s="8">
         <v>46122.55174869213</v>
@@ -9847,16 +9732,16 @@
         <v>46196.769715787035</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9872,13 +9757,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="Q141" s="8">
         <v>46322</v>
@@ -9887,18 +9772,18 @@
         <v>46322</v>
       </c>
       <c r="S141" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T141" s="9">
         <v>1</v>
       </c>
       <c r="U141" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B142" s="5">
         <v>46125.60158650463</v>
@@ -9910,16 +9795,16 @@
         <v>46196.76968989584</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9935,13 +9820,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9951,7 +9836,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B143" s="8">
         <v>46125.60163133102</v>
@@ -9963,16 +9848,16 @@
         <v>46196.7696903125</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -9988,13 +9873,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10004,7 +9889,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B144" s="5">
         <v>46125.60167016204</v>
@@ -10016,16 +9901,16 @@
         <v>46196.769690706016</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -10041,13 +9926,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10057,7 +9942,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B145" s="8">
         <v>46125.60170435185</v>
@@ -10069,16 +9954,16 @@
         <v>46196.76969114583</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -10094,13 +9979,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10110,7 +9995,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B146" s="5">
         <v>46125.60173947917</v>
@@ -10122,16 +10007,16 @@
         <v>46196.76969164352</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10147,13 +10032,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10163,7 +10048,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B147" s="8">
         <v>46122.551753472224</v>
@@ -10175,16 +10060,16 @@
         <v>46196.76981105324</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -10200,13 +10085,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="Q147" s="8">
         <v>46323</v>
@@ -10215,18 +10100,18 @@
         <v>46323</v>
       </c>
       <c r="S147" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T147" s="9">
         <v>1</v>
       </c>
       <c r="U147" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B148" s="5">
         <v>46125.60181555555</v>
@@ -10238,16 +10123,16 @@
         <v>46196.76979569445</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10263,13 +10148,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10279,7 +10164,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B149" s="8">
         <v>46125.60185690972</v>
@@ -10291,16 +10176,16 @@
         <v>46196.76979614583</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10316,13 +10201,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10332,7 +10217,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B150" s="5">
         <v>46125.601899490735</v>
@@ -10344,16 +10229,16 @@
         <v>46196.76979648148</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10369,13 +10254,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10385,7 +10270,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B151" s="8">
         <v>46125.60193935185</v>
@@ -10397,16 +10282,16 @@
         <v>46196.769766875004</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10422,13 +10307,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10438,7 +10323,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B152" s="5">
         <v>46125.60197710648</v>
@@ -10450,16 +10335,16 @@
         <v>46196.76977370371</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10475,13 +10360,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10491,7 +10376,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B153" s="8">
         <v>46122.551758622685</v>
@@ -10501,7 +10386,7 @@
         <v>46125.58936878473</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>25</v>
@@ -10525,7 +10410,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>26</v>
@@ -10538,7 +10423,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B154" s="5">
         <v>46122.55176134259</v>
@@ -10548,16 +10433,16 @@
         <v>46191.70605767361</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I154" s="5">
         <v>46324</v>
@@ -10575,13 +10460,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="Q154" s="5">
         <v>46324</v>
@@ -10590,18 +10475,18 @@
         <v>46332</v>
       </c>
       <c r="S154" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T154" s="6">
         <v>0</v>
       </c>
       <c r="U154" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B155" s="8">
         <v>46122.55176609954</v>
@@ -10611,16 +10496,16 @@
         <v>46192.97384414352</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I155" s="8">
         <v>46324</v>
@@ -10638,13 +10523,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="Q155" s="8">
         <v>46324</v>
@@ -10653,13 +10538,13 @@
         <v>46332</v>
       </c>
       <c r="S155" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T155" s="9">
         <v>0</v>
       </c>
       <c r="U155" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4471,7 +4471,7 @@
         <v>46181.66722120371</v>
       </c>
       <c r="D47" s="8">
-        <v>46211.17825179399</v>
+        <v>46219.16816725694</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>170</v>
@@ -4515,8 +4515,8 @@
       <c r="R47" s="8">
         <v>46218</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>74</v>
+      <c r="S47" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -5464,7 +5464,7 @@
         <v>46181.66775587963</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.66777241898</v>
+        <v>46219.19909722223</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>213</v>
@@ -5508,8 +5508,8 @@
       <c r="R64" s="5">
         <v>46226</v>
       </c>
-      <c r="S64" s="11" t="s">
-        <v>102</v>
+      <c r="S64" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T64" s="6">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4121,7 +4121,7 @@
         <v>46181.666767002316</v>
       </c>
       <c r="D41" s="8">
-        <v>46213.20535120371</v>
+        <v>46221.20228239583</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -4165,8 +4165,8 @@
       <c r="R41" s="8">
         <v>46220</v>
       </c>
-      <c r="S41" s="12" t="s">
-        <v>74</v>
+      <c r="S41" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -5399,7 +5399,7 @@
         <v>46181.667430127316</v>
       </c>
       <c r="D63" s="8">
-        <v>46213.20535071759</v>
+        <v>46221.202281238424</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>215</v>
@@ -5443,8 +5443,8 @@
       <c r="R63" s="8">
         <v>46220</v>
       </c>
-      <c r="S63" s="12" t="s">
-        <v>74</v>
+      <c r="S63" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T63" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="381">
   <si>
     <t xml:space="preserve"> 50001466 - ZITRON PERU (PODEROSA) </t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
@@ -2208,7 +2211,7 @@
         <v>46193.93280347223</v>
       </c>
       <c r="D10" s="5">
-        <v>46193.9328209838</v>
+        <v>46223.423621180555</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2521,7 +2524,7 @@
         <v>46195.50723163194</v>
       </c>
       <c r="D15" s="8">
-        <v>46195.50724608796</v>
+        <v>46223.425324826385</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2704,7 +2707,7 @@
         <v>46195.50721171296</v>
       </c>
       <c r="D18" s="5">
-        <v>46195.50723229167</v>
+        <v>46223.606554259255</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2713,9 +2716,11 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I18" s="5">
         <v>46136</v>
       </c>
@@ -2738,7 +2743,7 @@
         <v>55</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="5">
         <v>46136</v>
@@ -2758,7 +2763,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="8">
         <v>46122.55140604167</v>
@@ -2767,18 +2772,20 @@
         <v>46181.666399050926</v>
       </c>
       <c r="D19" s="8">
-        <v>46203.203668229165</v>
+        <v>46223.606550833334</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I19" s="8">
         <v>46199</v>
       </c>
@@ -2798,10 +2805,10 @@
         <v>66</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="8">
         <v>46199</v>
@@ -2821,7 +2828,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46122.55141162037</v>
@@ -2854,7 +2861,7 @@
         <v>26</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>26</v>
@@ -2866,7 +2873,7 @@
         <v>62</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46136</v>
@@ -2886,7 +2893,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="8">
         <v>46122.566545787035</v>
@@ -2895,18 +2902,20 @@
         <v>46181.66636053241</v>
       </c>
       <c r="D21" s="8">
-        <v>46203.20366833333</v>
+        <v>46223.60654709491</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I21" s="8">
         <v>46199</v>
       </c>
@@ -2926,10 +2935,10 @@
         <v>66</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="8">
         <v>46199</v>
@@ -2949,7 +2958,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46122.56661521991</v>
@@ -2958,18 +2967,20 @@
         <v>46181.66637630787</v>
       </c>
       <c r="D22" s="5">
-        <v>46203.20366849537</v>
+        <v>46223.60654385417</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I22" s="5">
         <v>46199</v>
       </c>
@@ -2989,10 +3000,10 @@
         <v>66</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46199</v>
@@ -3012,7 +3023,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46122.57286273148</v>
@@ -3021,18 +3032,20 @@
         <v>46181.66643224537</v>
       </c>
       <c r="D23" s="8">
-        <v>46203.2036682176</v>
+        <v>46223.60653833333</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I23" s="8">
         <v>46199</v>
       </c>
@@ -3052,10 +3065,10 @@
         <v>66</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="8">
         <v>46199</v>
@@ -3075,7 +3088,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46122.55120394676</v>
@@ -3084,10 +3097,10 @@
         <v>46195.50733982639</v>
       </c>
       <c r="D24" s="5">
-        <v>46195.50735353009</v>
+        <v>46223.425103263886</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>25</v>
@@ -3111,7 +3124,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -3128,7 +3141,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="8">
         <v>46122.55141694444</v>
@@ -3140,16 +3153,16 @@
         <v>46174.626181134256</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I25" s="8">
         <v>46140</v>
@@ -3167,13 +3180,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q25" s="8">
         <v>46142</v>
@@ -3182,7 +3195,7 @@
         <v>46265</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T25" s="9">
         <v>1</v>
@@ -3193,7 +3206,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46122.55142208333</v>
@@ -3205,16 +3218,16 @@
         <v>46174.62325449074</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I26" s="5">
         <v>46140</v>
@@ -3232,29 +3245,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46122.55142699074</v>
@@ -3266,16 +3279,16 @@
         <v>46174.62615429398</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I27" s="8">
         <v>46142</v>
@@ -3293,29 +3306,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46122.5514322338</v>
@@ -3327,16 +3340,16 @@
         <v>46195.71184679398</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I28" s="5">
         <v>46140</v>
@@ -3354,13 +3367,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q28" s="5">
         <v>46140</v>
@@ -3375,12 +3388,12 @@
         <v>1</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="8">
         <v>46122.551437546295</v>
@@ -3392,16 +3405,16 @@
         <v>46195.71138517361</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I29" s="8">
         <v>46140</v>
@@ -3419,29 +3432,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>76</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46122.55144255787</v>
@@ -3453,16 +3466,16 @@
         <v>46195.711832500005</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I30" s="5">
         <v>46142</v>
@@ -3480,29 +3493,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="8">
         <v>46122.551447708334</v>
@@ -3514,16 +3527,16 @@
         <v>46133.82781321759</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I31" s="8">
         <v>46133</v>
@@ -3541,13 +3554,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q31" s="8">
         <v>46133</v>
@@ -3556,7 +3569,7 @@
         <v>46308</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T31" s="9">
         <v>1</v>
@@ -3567,7 +3580,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46122.5514527662</v>
@@ -3579,16 +3592,16 @@
         <v>46133.82773260417</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I32" s="5">
         <v>46133</v>
@@ -3606,29 +3619,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46122.55145796297</v>
@@ -3640,16 +3653,16 @@
         <v>46133.82778807871</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I33" s="8">
         <v>46153</v>
@@ -3667,29 +3680,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46122.55146299768</v>
@@ -3701,16 +3714,16 @@
         <v>46133.827769131945</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I34" s="5">
         <v>46153</v>
@@ -3728,29 +3741,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46122.55146795139</v>
@@ -3762,16 +3775,16 @@
         <v>46214.17760775463</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I35" s="8">
         <v>46203</v>
@@ -3789,13 +3802,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q35" s="8">
         <v>46203</v>
@@ -3815,7 +3828,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46122.551472974534</v>
@@ -3827,16 +3840,16 @@
         <v>46181.66681946759</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I36" s="5">
         <v>46203</v>
@@ -3854,29 +3867,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="8">
         <v>46122.55152253472</v>
@@ -3888,16 +3901,16 @@
         <v>46181.66685818287</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I37" s="8">
         <v>46205</v>
@@ -3915,29 +3928,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46122.55152891204</v>
@@ -3949,16 +3962,16 @@
         <v>46189.172213136575</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I38" s="5">
         <v>46140</v>
@@ -3976,13 +3989,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q38" s="5">
         <v>46140</v>
@@ -4002,7 +4015,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B39" s="8">
         <v>46122.5515340625</v>
@@ -4014,16 +4027,16 @@
         <v>46154.86751927083</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I39" s="8">
         <v>46140</v>
@@ -4041,13 +4054,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4057,7 +4070,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46122.55153844907</v>
@@ -4069,16 +4082,16 @@
         <v>46154.867577453704</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I40" s="5">
         <v>46160</v>
@@ -4096,13 +4109,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4112,7 +4125,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46122.574933449076</v>
@@ -4124,16 +4137,16 @@
         <v>46221.20228239583</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I41" s="8">
         <v>46203</v>
@@ -4151,10 +4164,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4177,7 +4190,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46122.575920972224</v>
@@ -4189,16 +4202,16 @@
         <v>46181.66670855324</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I42" s="5">
         <v>46203</v>
@@ -4216,13 +4229,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4232,7 +4245,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46122.57608475695</v>
@@ -4244,16 +4257,16 @@
         <v>46181.666754351856</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I43" s="8">
         <v>46212</v>
@@ -4271,13 +4284,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4287,7 +4300,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46122.57501438657</v>
@@ -4296,19 +4309,19 @@
         <v>46181.666958472226</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.66706865741</v>
+        <v>46223.42579010417</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4326,10 +4339,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4341,7 +4354,7 @@
         <v>46238</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4352,7 +4365,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46122.57922111111</v>
@@ -4364,16 +4377,16 @@
         <v>46181.66690306713</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I45" s="8">
         <v>46203</v>
@@ -4391,13 +4404,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4407,7 +4420,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46122.57949202546</v>
@@ -4419,16 +4432,16 @@
         <v>46181.66694460648</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I46" s="5">
         <v>46210</v>
@@ -4446,13 +4459,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4462,7 +4475,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46125.529618217595</v>
@@ -4474,16 +4487,16 @@
         <v>46219.16816725694</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I47" s="8">
         <v>46203</v>
@@ -4501,10 +4514,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4527,7 +4540,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46125.52977997685</v>
@@ -4539,16 +4552,16 @@
         <v>46181.66715912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I48" s="5">
         <v>46203</v>
@@ -4566,13 +4579,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4582,7 +4595,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B49" s="8">
         <v>46125.52991815972</v>
@@ -4594,16 +4607,16 @@
         <v>46181.66720563658</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I49" s="8">
         <v>46210</v>
@@ -4621,13 +4634,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4637,7 +4650,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B50" s="5">
         <v>46122.55120855324</v>
@@ -4649,7 +4662,7 @@
         <v>46195.50756488426</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4673,7 +4686,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4690,7 +4703,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B51" s="8">
         <v>46122.55154344907</v>
@@ -4702,16 +4715,16 @@
         <v>46143.171145879634</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I51" s="8">
         <v>46136</v>
@@ -4729,13 +4742,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q51" s="8">
         <v>46136</v>
@@ -4755,7 +4768,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B52" s="5">
         <v>46122.551548993055</v>
@@ -4767,16 +4780,16 @@
         <v>46198.18781711806</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46191</v>
@@ -4794,13 +4807,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52" s="5">
         <v>46191</v>
@@ -4820,7 +4833,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46122.55155721065</v>
@@ -4832,16 +4845,16 @@
         <v>46199.18371805556</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4857,13 +4870,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="8">
         <v>46198</v>
@@ -4883,7 +4896,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46122.55156568287</v>
@@ -4895,16 +4908,16 @@
         <v>46196.76907818287</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4920,10 +4933,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4935,18 +4948,18 @@
         <v>46316</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8">
         <v>46125.603622118055</v>
@@ -4958,16 +4971,16 @@
         <v>46196.7690521412</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4983,13 +4996,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4999,7 +5012,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46125.60367094907</v>
@@ -5008,19 +5021,19 @@
         <v>46196.769048449074</v>
       </c>
       <c r="D56" s="5">
-        <v>46196.769052523145</v>
+        <v>46223.607461875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5036,13 +5049,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5052,7 +5065,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46125.60371951389</v>
@@ -5064,16 +5077,16 @@
         <v>46196.76905283565</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -5089,13 +5102,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5105,7 +5118,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B58" s="5">
         <v>46125.60376462963</v>
@@ -5117,16 +5130,16 @@
         <v>46196.76905314815</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5142,13 +5155,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5158,7 +5171,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B59" s="8">
         <v>46125.60381739584</v>
@@ -5170,16 +5183,16 @@
         <v>46196.76905349537</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5195,13 +5208,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5211,7 +5224,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B60" s="5">
         <v>46122.551569710646</v>
@@ -5223,7 +5236,7 @@
         <v>46181.66785324074</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5247,7 +5260,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5260,7 +5273,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B61" s="8">
         <v>46122.55157321759</v>
@@ -5272,16 +5285,16 @@
         <v>46181.66739524306</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I61" s="8">
         <v>46216</v>
@@ -5299,13 +5312,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q61" s="8">
         <v>46216</v>
@@ -5325,7 +5338,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B62" s="5">
         <v>46122.58491638889</v>
@@ -5337,16 +5350,16 @@
         <v>46181.667429016205</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46223</v>
@@ -5364,13 +5377,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46132</v>
@@ -5390,7 +5403,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B63" s="8">
         <v>46125.53102658565</v>
@@ -5402,16 +5415,16 @@
         <v>46221.202281238424</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I63" s="8">
         <v>46219</v>
@@ -5429,13 +5442,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q63" s="8">
         <v>46219</v>
@@ -5455,7 +5468,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B64" s="5">
         <v>46122.55157846065</v>
@@ -5467,16 +5480,16 @@
         <v>46219.19909722223</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46225</v>
@@ -5494,13 +5507,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="5">
         <v>46225</v>
@@ -5520,7 +5533,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B65" s="8">
         <v>46122.551583831024</v>
@@ -5532,7 +5545,7 @@
         <v>46181.66890770833</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5556,7 +5569,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5569,7 +5582,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46122.55158688658</v>
@@ -5581,16 +5594,16 @@
         <v>46181.66880932871</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I66" s="5">
         <v>46227</v>
@@ -5608,13 +5621,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q66" s="5">
         <v>46227</v>
@@ -5623,7 +5636,7 @@
         <v>46237</v>
       </c>
       <c r="S66" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -5634,7 +5647,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B67" s="8">
         <v>46122.55159185185</v>
@@ -5646,16 +5659,16 @@
         <v>46181.668846064815</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I67" s="8">
         <v>46238</v>
@@ -5673,13 +5686,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5688,7 +5701,7 @@
         <v>46255</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>
@@ -5699,7 +5712,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46125.595811921296</v>
@@ -5711,16 +5724,16 @@
         <v>46181.66807884259</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I68" s="5">
         <v>46238</v>
@@ -5738,13 +5751,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5754,7 +5767,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B69" s="8">
         <v>46125.59610047453</v>
@@ -5766,16 +5779,16 @@
         <v>46181.66808728009</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I69" s="8">
         <v>46238</v>
@@ -5793,13 +5806,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5809,7 +5822,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B70" s="5">
         <v>46125.59621038195</v>
@@ -5821,16 +5834,16 @@
         <v>46181.66815550926</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I70" s="5">
         <v>46238</v>
@@ -5848,13 +5861,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5864,7 +5877,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B71" s="8">
         <v>46125.59625472222</v>
@@ -5876,16 +5889,16 @@
         <v>46181.66816819445</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I71" s="8">
         <v>46238</v>
@@ -5903,13 +5916,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5919,7 +5932,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46125.59629915509</v>
@@ -5931,16 +5944,16 @@
         <v>46181.66818078703</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I72" s="5">
         <v>46238</v>
@@ -5958,13 +5971,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5974,7 +5987,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B73" s="8">
         <v>46122.55159751157</v>
@@ -5986,16 +5999,16 @@
         <v>46181.66878222222</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I73" s="8">
         <v>46258</v>
@@ -6013,13 +6026,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q73" s="8">
         <v>46258</v>
@@ -6028,7 +6041,7 @@
         <v>46259</v>
       </c>
       <c r="S73" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T73" s="9">
         <v>1</v>
@@ -6039,7 +6052,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46125.59648849537</v>
@@ -6051,16 +6064,16 @@
         <v>46181.6686533912</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I74" s="5">
         <v>46258</v>
@@ -6078,13 +6091,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6094,7 +6107,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" s="8">
         <v>46125.59661854166</v>
@@ -6106,16 +6119,16 @@
         <v>46181.66866782407</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6133,13 +6146,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6149,7 +6162,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" s="5">
         <v>46125.596668750004</v>
@@ -6161,16 +6174,16 @@
         <v>46181.66867745371</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6188,13 +6201,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6204,7 +6217,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B77" s="8">
         <v>46125.59671550926</v>
@@ -6216,16 +6229,16 @@
         <v>46181.668687060184</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6243,13 +6256,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6259,7 +6272,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
         <v>46125.59675546296</v>
@@ -6271,16 +6284,16 @@
         <v>46181.66870502315</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I78" s="5">
         <v>46258</v>
@@ -6298,13 +6311,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6314,7 +6327,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="8">
         <v>46122.55160357639</v>
@@ -6326,7 +6339,7 @@
         <v>46195.563290335645</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6350,7 +6363,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6362,12 +6375,12 @@
         <v>1</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46122.55160679398</v>
@@ -6379,16 +6392,16 @@
         <v>46195.711846817125</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I80" s="5">
         <v>46191</v>
@@ -6406,13 +6419,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q80" s="5">
         <v>46191</v>
@@ -6427,12 +6440,12 @@
         <v>1</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B81" s="8">
         <v>46122.551612256946</v>
@@ -6444,16 +6457,16 @@
         <v>46195.50753130787</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I81" s="8">
         <v>46266</v>
@@ -6471,13 +6484,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q81" s="8">
         <v>46266</v>
@@ -6486,7 +6499,7 @@
         <v>46267</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>
@@ -6497,7 +6510,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46122.55161756944</v>
@@ -6509,16 +6522,16 @@
         <v>46195.50753259259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I82" s="5">
         <v>46309</v>
@@ -6536,13 +6549,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q82" s="5">
         <v>46309</v>
@@ -6551,7 +6564,7 @@
         <v>46310</v>
       </c>
       <c r="S82" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6562,7 +6575,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B83" s="8">
         <v>46122.55162288195</v>
@@ -6574,16 +6587,16 @@
         <v>46195.507539479164</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I83" s="8">
         <v>46189</v>
@@ -6601,13 +6614,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q83" s="8">
         <v>46189</v>
@@ -6627,7 +6640,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B84" s="5">
         <v>46122.59399163195</v>
@@ -6639,16 +6652,16 @@
         <v>46193.9332800463</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I84" s="5">
         <v>46239</v>
@@ -6666,13 +6679,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q84" s="5">
         <v>46239</v>
@@ -6681,7 +6694,7 @@
         <v>46240</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T84" s="6">
         <v>1</v>
@@ -6692,7 +6705,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B85" s="8">
         <v>46122.551628182875</v>
@@ -6704,7 +6717,7 @@
         <v>46196.769192685184</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6728,7 +6741,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6740,12 +6753,12 @@
         <v>1</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
         <v>46122.55163158565</v>
@@ -6754,18 +6767,20 @@
         <v>46195.50768850694</v>
       </c>
       <c r="D86" s="5">
-        <v>46195.507707129625</v>
+        <v>46223.60779484954</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I86" s="5">
         <v>46260</v>
       </c>
@@ -6782,13 +6797,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q86" s="5">
         <v>46260</v>
@@ -6797,7 +6812,7 @@
         <v>46279</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -6808,7 +6823,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B87" s="8">
         <v>46125.5974969213</v>
@@ -6817,18 +6832,20 @@
         <v>46196.76791707176</v>
       </c>
       <c r="D87" s="8">
-        <v>46196.767918831014</v>
+        <v>46223.60698247685</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I87" s="8">
         <v>46260</v>
       </c>
@@ -6845,13 +6862,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6861,7 +6878,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B88" s="5">
         <v>46125.59754570602</v>
@@ -6870,18 +6887,20 @@
         <v>46196.76795405093</v>
       </c>
       <c r="D88" s="5">
-        <v>46196.76795645834</v>
+        <v>46223.60697355324</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I88" s="5">
         <v>46260</v>
       </c>
@@ -6898,13 +6917,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6914,7 +6933,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="8">
         <v>46125.59760710648</v>
@@ -6923,18 +6942,20 @@
         <v>46196.767928217596</v>
       </c>
       <c r="D89" s="8">
-        <v>46196.76793001157</v>
+        <v>46223.60697</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I89" s="8">
         <v>46260</v>
       </c>
@@ -6951,13 +6972,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6967,7 +6988,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46125.59765891204</v>
@@ -6976,18 +6997,20 @@
         <v>46196.76794651621</v>
       </c>
       <c r="D90" s="5">
-        <v>46196.76794809027</v>
+        <v>46223.60696642361</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I90" s="5">
         <v>46260</v>
       </c>
@@ -7004,13 +7027,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7020,7 +7043,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46125.597703391206</v>
@@ -7029,18 +7052,20 @@
         <v>46196.76794100694</v>
       </c>
       <c r="D91" s="8">
-        <v>46196.76794287037</v>
+        <v>46223.606961412035</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I91" s="8">
         <v>46260</v>
       </c>
@@ -7057,13 +7082,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7073,7 +7098,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B92" s="5">
         <v>46122.55170659722</v>
@@ -7082,18 +7107,20 @@
         <v>46196.76755512731</v>
       </c>
       <c r="D92" s="5">
-        <v>46196.76807780092</v>
+        <v>46223.607791331015</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I92" s="5">
         <v>46280</v>
       </c>
@@ -7110,13 +7137,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q92" s="5">
         <v>46280</v>
@@ -7125,18 +7152,18 @@
         <v>46282</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B93" s="8">
         <v>46125.59982741898</v>
@@ -7145,18 +7172,20 @@
         <v>46196.76800195602</v>
       </c>
       <c r="D93" s="8">
-        <v>46196.76800386574</v>
+        <v>46223.60708418982</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I93" s="8">
         <v>46280</v>
       </c>
@@ -7173,13 +7202,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7189,7 +7218,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46125.599890833335</v>
@@ -7198,18 +7227,20 @@
         <v>46196.768023020835</v>
       </c>
       <c r="D94" s="5">
-        <v>46196.768024687495</v>
+        <v>46223.60707991898</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I94" s="5">
         <v>46280</v>
       </c>
@@ -7226,13 +7257,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7242,7 +7273,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B95" s="8">
         <v>46125.59993134259</v>
@@ -7251,18 +7282,20 @@
         <v>46196.76801494213</v>
       </c>
       <c r="D95" s="8">
-        <v>46196.76801675926</v>
+        <v>46223.60707583334</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I95" s="8">
         <v>46280</v>
       </c>
@@ -7279,13 +7312,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7295,7 +7328,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B96" s="5">
         <v>46125.59996929398</v>
@@ -7304,18 +7337,20 @@
         <v>46196.76805109954</v>
       </c>
       <c r="D96" s="5">
-        <v>46196.76805278935</v>
+        <v>46223.607072060186</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I96" s="5">
         <v>46280</v>
       </c>
@@ -7332,13 +7367,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7348,7 +7383,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B97" s="8">
         <v>46125.6000115162</v>
@@ -7357,18 +7392,20 @@
         <v>46196.76805706018</v>
       </c>
       <c r="D97" s="8">
-        <v>46196.76805907408</v>
+        <v>46223.607066192126</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I97" s="8">
         <v>46280</v>
       </c>
@@ -7385,13 +7422,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7401,7 +7438,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B98" s="5">
         <v>46122.55164413195</v>
@@ -7410,18 +7447,20 @@
         <v>46196.76839824074</v>
       </c>
       <c r="D98" s="5">
-        <v>46196.76840872686</v>
+        <v>46223.60778702547</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I98" s="5">
         <v>46286</v>
       </c>
@@ -7438,13 +7477,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q98" s="5">
         <v>46286</v>
@@ -7453,7 +7492,7 @@
         <v>46288</v>
       </c>
       <c r="S98" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T98" s="6">
         <v>1</v>
@@ -7464,7 +7503,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B99" s="8">
         <v>46125.599162743056</v>
@@ -7473,18 +7512,20 @@
         <v>46196.76818966435</v>
       </c>
       <c r="D99" s="8">
-        <v>46196.7681912963</v>
+        <v>46223.60720636574</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I99" s="8">
         <v>46286</v>
       </c>
@@ -7501,13 +7542,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7517,7 +7558,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B100" s="5">
         <v>46125.599302511575</v>
@@ -7526,18 +7567,20 @@
         <v>46196.76820421296</v>
       </c>
       <c r="D100" s="5">
-        <v>46196.76820597222</v>
+        <v>46223.60720247685</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I100" s="5">
         <v>46286</v>
       </c>
@@ -7554,13 +7597,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7570,7 +7613,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B101" s="8">
         <v>46125.59934644676</v>
@@ -7579,18 +7622,20 @@
         <v>46196.768375949076</v>
       </c>
       <c r="D101" s="8">
-        <v>46196.76837958333</v>
+        <v>46223.60719819444</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I101" s="8">
         <v>46286</v>
       </c>
@@ -7607,13 +7652,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7623,7 +7668,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B102" s="5">
         <v>46125.59938857639</v>
@@ -7632,18 +7677,20 @@
         <v>46196.76837696759</v>
       </c>
       <c r="D102" s="5">
-        <v>46196.76838008102</v>
+        <v>46223.60719417824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I102" s="5">
         <v>46286</v>
       </c>
@@ -7660,13 +7707,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7676,7 +7723,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B103" s="8">
         <v>46125.59943094908</v>
@@ -7685,18 +7732,20 @@
         <v>46196.76837790509</v>
       </c>
       <c r="D103" s="8">
-        <v>46196.768380520836</v>
+        <v>46223.60718841435</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I103" s="8">
         <v>46286</v>
       </c>
@@ -7713,13 +7762,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7729,7 +7778,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B104" s="5">
         <v>46122.551650995374</v>
@@ -7738,18 +7787,20 @@
         <v>46196.76854788195</v>
       </c>
       <c r="D104" s="5">
-        <v>46196.76856074074</v>
+        <v>46223.60778314815</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I104" s="5">
         <v>46289</v>
       </c>
@@ -7766,13 +7817,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q104" s="5">
         <v>46289</v>
@@ -7781,18 +7832,18 @@
         <v>46293</v>
       </c>
       <c r="S104" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>
       </c>
       <c r="U104" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B105" s="8">
         <v>46125.59953013889</v>
@@ -7801,18 +7852,20 @@
         <v>46196.76852783565</v>
       </c>
       <c r="D105" s="8">
-        <v>46196.768531724534</v>
+        <v>46223.60731153935</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I105" s="8">
         <v>46289</v>
       </c>
@@ -7829,13 +7882,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7845,7 +7898,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B106" s="5">
         <v>46125.59961423611</v>
@@ -7854,18 +7907,20 @@
         <v>46196.76846329861</v>
       </c>
       <c r="D106" s="5">
-        <v>46196.76846496528</v>
+        <v>46223.60730783565</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I106" s="5">
         <v>46289</v>
       </c>
@@ -7882,13 +7937,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7898,7 +7953,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B107" s="8">
         <v>46125.599654317135</v>
@@ -7907,18 +7962,20 @@
         <v>46196.768528796296</v>
       </c>
       <c r="D107" s="8">
-        <v>46196.76853203704</v>
+        <v>46223.60730394676</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I107" s="8">
         <v>46289</v>
       </c>
@@ -7935,13 +7992,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7951,7 +8008,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B108" s="5">
         <v>46125.59957065972</v>
@@ -7960,18 +8017,20 @@
         <v>46196.768529548615</v>
       </c>
       <c r="D108" s="5">
-        <v>46196.76853233796</v>
+        <v>46223.607299675925</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I108" s="5">
         <v>46289</v>
       </c>
@@ -7988,13 +8047,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8004,7 +8063,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B109" s="8">
         <v>46125.59969711806</v>
@@ -8013,18 +8072,20 @@
         <v>46196.7685304051</v>
       </c>
       <c r="D109" s="8">
-        <v>46196.76853265046</v>
+        <v>46223.60729373843</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I109" s="8">
         <v>46289</v>
       </c>
@@ -8041,13 +8102,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8057,7 +8118,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B110" s="5">
         <v>46122.55163725694</v>
@@ -8066,18 +8127,20 @@
         <v>46196.76866755787</v>
       </c>
       <c r="D110" s="5">
-        <v>46196.76867908565</v>
+        <v>46223.607779618054</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I110" s="5">
         <v>46311</v>
       </c>
@@ -8094,13 +8157,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q110" s="5">
         <v>46311</v>
@@ -8109,7 +8172,7 @@
         <v>46314</v>
       </c>
       <c r="S110" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T110" s="6">
         <v>1</v>
@@ -8120,7 +8183,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B111" s="8">
         <v>46125.59780210648</v>
@@ -8129,18 +8192,20 @@
         <v>46196.76864902778</v>
       </c>
       <c r="D111" s="8">
-        <v>46196.76865387731</v>
+        <v>46223.607408310185</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I111" s="8">
         <v>46311</v>
       </c>
@@ -8157,13 +8222,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8173,7 +8238,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B112" s="5">
         <v>46125.597836932866</v>
@@ -8182,18 +8247,20 @@
         <v>46196.76865</v>
       </c>
       <c r="D112" s="5">
-        <v>46196.76865427083</v>
+        <v>46223.60740443287</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I112" s="5">
         <v>46311</v>
       </c>
@@ -8210,13 +8277,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8226,7 +8293,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B113" s="8">
         <v>46125.5979208912</v>
@@ -8235,18 +8302,20 @@
         <v>46196.76865077546</v>
       </c>
       <c r="D113" s="8">
-        <v>46196.76865460648</v>
+        <v>46223.607400532404</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I113" s="8">
         <v>46311</v>
       </c>
@@ -8263,13 +8332,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8279,7 +8348,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B114" s="5">
         <v>46125.59788087963</v>
@@ -8288,18 +8357,20 @@
         <v>46196.768651527775</v>
       </c>
       <c r="D114" s="5">
-        <v>46196.768654942134</v>
+        <v>46223.60739668981</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I114" s="5">
         <v>46311</v>
       </c>
@@ -8316,13 +8387,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8332,7 +8403,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B115" s="8">
         <v>46125.597965023146</v>
@@ -8341,18 +8412,20 @@
         <v>46196.768652314815</v>
       </c>
       <c r="D115" s="8">
-        <v>46196.768655312495</v>
+        <v>46223.60739046296</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H115" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I115" s="8">
         <v>46311</v>
       </c>
@@ -8369,13 +8442,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8385,7 +8458,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B116" s="5">
         <v>46122.55172043982</v>
@@ -8394,18 +8467,20 @@
         <v>46196.76877224537</v>
       </c>
       <c r="D116" s="5">
-        <v>46196.768798784724</v>
+        <v>46223.607775474535</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H116" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I116" s="5">
         <v>46315</v>
       </c>
@@ -8422,13 +8497,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q116" s="5">
         <v>46315</v>
@@ -8437,18 +8512,18 @@
         <v>46315</v>
       </c>
       <c r="S116" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T116" s="6">
         <v>1</v>
       </c>
       <c r="U116" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B117" s="8">
         <v>46125.60038253472</v>
@@ -8457,18 +8532,20 @@
         <v>46196.76875258102</v>
       </c>
       <c r="D117" s="8">
-        <v>46196.768757337966</v>
+        <v>46223.60758443287</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H117" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
         <v>46315</v>
@@ -8483,13 +8560,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8499,27 +8576,29 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B118" s="5">
         <v>46125.60043012731</v>
       </c>
       <c r="C118" s="5">
-        <v>46196.7687534838</v>
+        <v>46223.60745270833</v>
       </c>
       <c r="D118" s="5">
-        <v>46196.76875768519</v>
+        <v>46223.60758005787</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H118" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
         <v>46315</v>
@@ -8534,13 +8613,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8550,7 +8629,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B119" s="8">
         <v>46125.60047290509</v>
@@ -8559,18 +8638,20 @@
         <v>46196.768754178236</v>
       </c>
       <c r="D119" s="8">
-        <v>46196.76875800926</v>
+        <v>46223.607575752314</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
         <v>46315</v>
@@ -8585,13 +8666,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8601,7 +8682,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B120" s="5">
         <v>46125.600514074074</v>
@@ -8610,18 +8691,20 @@
         <v>46196.768754930556</v>
       </c>
       <c r="D120" s="5">
-        <v>46196.76875832176</v>
+        <v>46223.607571597226</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
         <v>46315</v>
@@ -8636,13 +8719,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8652,7 +8735,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B121" s="8">
         <v>46125.60055859954</v>
@@ -8661,18 +8744,20 @@
         <v>46196.7687558912</v>
       </c>
       <c r="D121" s="8">
-        <v>46196.76875862268</v>
+        <v>46223.60756553241</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
         <v>46315</v>
@@ -8687,13 +8772,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8703,7 +8788,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B122" s="5">
         <v>46122.55172986111</v>
@@ -8712,18 +8797,20 @@
         <v>46196.76917457176</v>
       </c>
       <c r="D122" s="5">
-        <v>46196.76918584491</v>
+        <v>46223.60776988426</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H122" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I122" s="5">
         <v>46317</v>
       </c>
@@ -8740,13 +8827,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q122" s="5">
         <v>46317</v>
@@ -8755,7 +8842,7 @@
         <v>46317</v>
       </c>
       <c r="S122" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T122" s="6">
         <v>1</v>
@@ -8766,7 +8853,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B123" s="8">
         <v>46125.60064416667</v>
@@ -8775,18 +8862,20 @@
         <v>46196.76915099537</v>
       </c>
       <c r="D123" s="8">
-        <v>46196.76915743056</v>
+        <v>46223.607680601854</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
         <v>46317</v>
@@ -8801,13 +8890,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8817,7 +8906,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B124" s="5">
         <v>46125.60068740741</v>
@@ -8826,18 +8915,20 @@
         <v>46196.76915237268</v>
       </c>
       <c r="D124" s="5">
-        <v>46196.76915791667</v>
+        <v>46223.60767706019</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
         <v>46317</v>
@@ -8852,13 +8943,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8868,7 +8959,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B125" s="8">
         <v>46125.60073844907</v>
@@ -8877,18 +8968,20 @@
         <v>46196.76915341435</v>
       </c>
       <c r="D125" s="8">
-        <v>46196.76915841435</v>
+        <v>46223.607672812504</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
         <v>46317</v>
@@ -8903,13 +8996,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8919,7 +9012,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B126" s="5">
         <v>46125.60077622686</v>
@@ -8928,18 +9021,20 @@
         <v>46196.76915438657</v>
       </c>
       <c r="D126" s="5">
-        <v>46196.769158842595</v>
+        <v>46223.6076684375</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
         <v>46317</v>
@@ -8954,13 +9049,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8970,7 +9065,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B127" s="8">
         <v>46125.600829143514</v>
@@ -8979,18 +9074,20 @@
         <v>46196.769155358794</v>
       </c>
       <c r="D127" s="8">
-        <v>46196.76915931713</v>
+        <v>46223.60766289352</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
         <v>46317</v>
@@ -9005,13 +9102,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9021,7 +9118,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B128" s="5">
         <v>46122.5517350463</v>
@@ -9033,7 +9130,7 @@
         <v>46196.76960409722</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>25</v>
@@ -9057,7 +9154,7 @@
         <v>26</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>26</v>
@@ -9069,12 +9166,12 @@
         <v>1</v>
       </c>
       <c r="U128" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B129" s="8">
         <v>46122.5517390625</v>
@@ -9086,16 +9183,16 @@
         <v>46196.76939736111</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I129" s="8">
         <v>46318</v>
@@ -9113,13 +9210,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q129" s="8">
         <v>46318</v>
@@ -9128,18 +9225,18 @@
         <v>46318</v>
       </c>
       <c r="S129" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T129" s="9">
         <v>1</v>
       </c>
       <c r="U129" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B130" s="5">
         <v>46125.60093731481</v>
@@ -9151,16 +9248,16 @@
         <v>46196.769350682865</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9176,13 +9273,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9192,7 +9289,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B131" s="8">
         <v>46125.601380821754</v>
@@ -9204,16 +9301,16 @@
         <v>46196.769351145835</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9229,13 +9326,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9245,7 +9342,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B132" s="5">
         <v>46125.60142481481</v>
@@ -9257,16 +9354,16 @@
         <v>46196.76935155093</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9282,13 +9379,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9298,7 +9395,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B133" s="8">
         <v>46125.60146085648</v>
@@ -9310,16 +9407,16 @@
         <v>46196.76935192129</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9335,13 +9432,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9351,7 +9448,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B134" s="5">
         <v>46125.60150208333</v>
@@ -9363,16 +9460,16 @@
         <v>46196.76935229167</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9388,13 +9485,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9404,7 +9501,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B135" s="8">
         <v>46122.55174383102</v>
@@ -9413,18 +9510,20 @@
         <v>46196.769596921295</v>
       </c>
       <c r="D135" s="8">
-        <v>46196.76961396991</v>
+        <v>46223.6084731713</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H135" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H135" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
         <v>46321</v>
@@ -9439,13 +9538,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q135" s="8">
         <v>46321</v>
@@ -9454,7 +9553,7 @@
         <v>46321</v>
       </c>
       <c r="S135" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T135" s="9">
         <v>1</v>
@@ -9465,7 +9564,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B136" s="5">
         <v>46125.601086979164</v>
@@ -9474,18 +9573,20 @@
         <v>46196.76947155093</v>
       </c>
       <c r="D136" s="5">
-        <v>46196.76947347222</v>
+        <v>46223.60837070602</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H136" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
         <v>46321</v>
@@ -9500,13 +9601,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9516,7 +9617,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B137" s="8">
         <v>46125.60115318287</v>
@@ -9525,18 +9626,20 @@
         <v>46196.7695043287</v>
       </c>
       <c r="D137" s="8">
-        <v>46196.76950902778</v>
+        <v>46223.60836653935</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H137" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
         <v>46321</v>
@@ -9551,13 +9654,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9567,7 +9670,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B138" s="5">
         <v>46125.60120391204</v>
@@ -9576,18 +9679,20 @@
         <v>46196.76950549769</v>
       </c>
       <c r="D138" s="5">
-        <v>46196.76950944445</v>
+        <v>46223.608362604165</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H138" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
         <v>46321</v>
@@ -9602,13 +9707,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9618,7 +9723,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B139" s="8">
         <v>46125.60125796296</v>
@@ -9627,18 +9732,20 @@
         <v>46196.76950637731</v>
       </c>
       <c r="D139" s="8">
-        <v>46196.76950987268</v>
+        <v>46223.60835905092</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H139" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
         <v>46321</v>
@@ -9653,13 +9760,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9669,7 +9776,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B140" s="5">
         <v>46125.601304282405</v>
@@ -9678,18 +9785,20 @@
         <v>46196.76950730324</v>
       </c>
       <c r="D140" s="5">
-        <v>46196.769510266204</v>
+        <v>46223.60835267361</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H140" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
         <v>46321</v>
@@ -9704,13 +9813,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9720,7 +9829,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B141" s="8">
         <v>46122.55174869213</v>
@@ -9732,16 +9841,16 @@
         <v>46196.769715787035</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9757,13 +9866,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q141" s="8">
         <v>46322</v>
@@ -9772,18 +9881,18 @@
         <v>46322</v>
       </c>
       <c r="S141" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T141" s="9">
         <v>1</v>
       </c>
       <c r="U141" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B142" s="5">
         <v>46125.60158650463</v>
@@ -9795,16 +9904,16 @@
         <v>46196.76968989584</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9820,13 +9929,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9836,7 +9945,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B143" s="8">
         <v>46125.60163133102</v>
@@ -9848,16 +9957,16 @@
         <v>46196.7696903125</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -9873,13 +9982,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9889,7 +9998,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B144" s="5">
         <v>46125.60167016204</v>
@@ -9901,16 +10010,16 @@
         <v>46196.769690706016</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -9926,13 +10035,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9942,7 +10051,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B145" s="8">
         <v>46125.60170435185</v>
@@ -9954,16 +10063,16 @@
         <v>46196.76969114583</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -9979,13 +10088,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -9995,7 +10104,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B146" s="5">
         <v>46125.60173947917</v>
@@ -10007,16 +10116,16 @@
         <v>46196.76969164352</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10032,13 +10141,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10048,7 +10157,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B147" s="8">
         <v>46122.551753472224</v>
@@ -10060,16 +10169,16 @@
         <v>46196.76981105324</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -10085,13 +10194,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q147" s="8">
         <v>46323</v>
@@ -10100,18 +10209,18 @@
         <v>46323</v>
       </c>
       <c r="S147" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T147" s="9">
         <v>1</v>
       </c>
       <c r="U147" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B148" s="5">
         <v>46125.60181555555</v>
@@ -10123,16 +10232,16 @@
         <v>46196.76979569445</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10148,13 +10257,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10164,7 +10273,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B149" s="8">
         <v>46125.60185690972</v>
@@ -10176,16 +10285,16 @@
         <v>46196.76979614583</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10201,13 +10310,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10217,7 +10326,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B150" s="5">
         <v>46125.601899490735</v>
@@ -10229,16 +10338,16 @@
         <v>46196.76979648148</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10254,13 +10363,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10270,7 +10379,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B151" s="8">
         <v>46125.60193935185</v>
@@ -10282,16 +10391,16 @@
         <v>46196.769766875004</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10307,13 +10416,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10323,7 +10432,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B152" s="5">
         <v>46125.60197710648</v>
@@ -10335,16 +10444,16 @@
         <v>46196.76977370371</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10360,13 +10469,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10376,7 +10485,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B153" s="8">
         <v>46122.551758622685</v>
@@ -10386,7 +10495,7 @@
         <v>46125.58936878473</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>25</v>
@@ -10410,7 +10519,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>26</v>
@@ -10423,7 +10532,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B154" s="5">
         <v>46122.55176134259</v>
@@ -10433,16 +10542,16 @@
         <v>46191.70605767361</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I154" s="5">
         <v>46324</v>
@@ -10460,13 +10569,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q154" s="5">
         <v>46324</v>
@@ -10475,18 +10584,18 @@
         <v>46332</v>
       </c>
       <c r="S154" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T154" s="6">
         <v>0</v>
       </c>
       <c r="U154" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B155" s="8">
         <v>46122.55176609954</v>
@@ -10496,16 +10605,16 @@
         <v>46192.97384414352</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I155" s="8">
         <v>46324</v>
@@ -10523,13 +10632,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q155" s="8">
         <v>46324</v>
@@ -10538,13 +10647,13 @@
         <v>46332</v>
       </c>
       <c r="S155" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T155" s="9">
         <v>0</v>
       </c>
       <c r="U155" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="382">
   <si>
     <t xml:space="preserve"> 50001466 - ZITRON PERU (PODEROSA) </t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2719,7 +2722,7 @@
         <v>77</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" s="5">
         <v>46136</v>
@@ -2743,7 +2746,7 @@
         <v>55</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>46136</v>
@@ -2763,7 +2766,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8">
         <v>46122.55140604167</v>
@@ -2775,7 +2778,7 @@
         <v>46223.606550833334</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2784,7 +2787,7 @@
         <v>77</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I19" s="8">
         <v>46199</v>
@@ -2805,10 +2808,10 @@
         <v>66</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="8">
         <v>46199</v>
@@ -2828,7 +2831,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46122.55141162037</v>
@@ -2861,7 +2864,7 @@
         <v>26</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>26</v>
@@ -2873,7 +2876,7 @@
         <v>62</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46136</v>
@@ -2893,7 +2896,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" s="8">
         <v>46122.566545787035</v>
@@ -2905,7 +2908,7 @@
         <v>46223.60654709491</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2914,7 +2917,7 @@
         <v>77</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I21" s="8">
         <v>46199</v>
@@ -2935,10 +2938,10 @@
         <v>66</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="8">
         <v>46199</v>
@@ -2958,7 +2961,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46122.56661521991</v>
@@ -2970,7 +2973,7 @@
         <v>46223.60654385417</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2979,7 +2982,7 @@
         <v>77</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I22" s="5">
         <v>46199</v>
@@ -3000,10 +3003,10 @@
         <v>66</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q22" s="5">
         <v>46199</v>
@@ -3023,7 +3026,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="8">
         <v>46122.57286273148</v>
@@ -3035,7 +3038,7 @@
         <v>46223.60653833333</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -3044,7 +3047,7 @@
         <v>77</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I23" s="8">
         <v>46199</v>
@@ -3065,10 +3068,10 @@
         <v>66</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q23" s="8">
         <v>46199</v>
@@ -3088,7 +3091,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46122.55120394676</v>
@@ -3100,7 +3103,7 @@
         <v>46223.425103263886</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>25</v>
@@ -3124,7 +3127,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -3141,7 +3144,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="8">
         <v>46122.55141694444</v>
@@ -3153,16 +3156,16 @@
         <v>46174.626181134256</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I25" s="8">
         <v>46140</v>
@@ -3180,13 +3183,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q25" s="8">
         <v>46142</v>
@@ -3195,7 +3198,7 @@
         <v>46265</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T25" s="9">
         <v>1</v>
@@ -3206,7 +3209,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46122.55142208333</v>
@@ -3218,16 +3221,16 @@
         <v>46174.62325449074</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I26" s="5">
         <v>46140</v>
@@ -3245,29 +3248,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="8">
         <v>46122.55142699074</v>
@@ -3279,16 +3282,16 @@
         <v>46174.62615429398</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I27" s="8">
         <v>46142</v>
@@ -3306,29 +3309,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46122.5514322338</v>
@@ -3340,16 +3343,16 @@
         <v>46195.71184679398</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46140</v>
@@ -3367,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q28" s="5">
         <v>46140</v>
@@ -3388,12 +3391,12 @@
         <v>1</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="8">
         <v>46122.551437546295</v>
@@ -3405,16 +3408,16 @@
         <v>46195.71138517361</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I29" s="8">
         <v>46140</v>
@@ -3432,29 +3435,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>76</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46122.55144255787</v>
@@ -3466,16 +3469,16 @@
         <v>46195.711832500005</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46142</v>
@@ -3493,29 +3496,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B31" s="8">
         <v>46122.551447708334</v>
@@ -3527,16 +3530,16 @@
         <v>46133.82781321759</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I31" s="8">
         <v>46133</v>
@@ -3554,13 +3557,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q31" s="8">
         <v>46133</v>
@@ -3569,7 +3572,7 @@
         <v>46308</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T31" s="9">
         <v>1</v>
@@ -3580,7 +3583,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46122.5514527662</v>
@@ -3592,16 +3595,16 @@
         <v>46133.82773260417</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I32" s="5">
         <v>46133</v>
@@ -3619,29 +3622,29 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B33" s="8">
         <v>46122.55145796297</v>
@@ -3653,16 +3656,16 @@
         <v>46133.82778807871</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I33" s="8">
         <v>46153</v>
@@ -3680,29 +3683,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46122.55146299768</v>
@@ -3714,16 +3717,16 @@
         <v>46133.827769131945</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I34" s="5">
         <v>46153</v>
@@ -3741,29 +3744,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" s="8">
         <v>46122.55146795139</v>
@@ -3775,16 +3778,16 @@
         <v>46214.17760775463</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I35" s="8">
         <v>46203</v>
@@ -3802,13 +3805,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q35" s="8">
         <v>46203</v>
@@ -3828,7 +3831,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46122.551472974534</v>
@@ -3840,16 +3843,16 @@
         <v>46181.66681946759</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I36" s="5">
         <v>46203</v>
@@ -3867,29 +3870,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="8">
         <v>46122.55152253472</v>
@@ -3901,16 +3904,16 @@
         <v>46181.66685818287</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I37" s="8">
         <v>46205</v>
@@ -3928,29 +3931,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46122.55152891204</v>
@@ -3962,16 +3965,16 @@
         <v>46189.172213136575</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I38" s="5">
         <v>46140</v>
@@ -3989,13 +3992,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q38" s="5">
         <v>46140</v>
@@ -4015,7 +4018,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="8">
         <v>46122.5515340625</v>
@@ -4027,16 +4030,16 @@
         <v>46154.86751927083</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I39" s="8">
         <v>46140</v>
@@ -4054,13 +4057,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4070,7 +4073,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46122.55153844907</v>
@@ -4082,16 +4085,16 @@
         <v>46154.867577453704</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I40" s="5">
         <v>46160</v>
@@ -4109,13 +4112,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4125,7 +4128,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46122.574933449076</v>
@@ -4137,16 +4140,16 @@
         <v>46221.20228239583</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I41" s="8">
         <v>46203</v>
@@ -4164,10 +4167,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4190,7 +4193,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46122.575920972224</v>
@@ -4202,16 +4205,16 @@
         <v>46181.66670855324</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I42" s="5">
         <v>46203</v>
@@ -4229,13 +4232,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4245,7 +4248,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46122.57608475695</v>
@@ -4257,16 +4260,16 @@
         <v>46181.666754351856</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I43" s="8">
         <v>46212</v>
@@ -4284,13 +4287,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4300,7 +4303,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46122.57501438657</v>
@@ -4312,16 +4315,16 @@
         <v>46223.42579010417</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4339,10 +4342,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4354,7 +4357,7 @@
         <v>46238</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4365,7 +4368,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46122.57922111111</v>
@@ -4377,16 +4380,16 @@
         <v>46181.66690306713</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I45" s="8">
         <v>46203</v>
@@ -4404,13 +4407,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4420,7 +4423,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46122.57949202546</v>
@@ -4432,16 +4435,16 @@
         <v>46181.66694460648</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I46" s="5">
         <v>46210</v>
@@ -4459,13 +4462,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4475,7 +4478,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46125.529618217595</v>
@@ -4487,16 +4490,16 @@
         <v>46219.16816725694</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I47" s="8">
         <v>46203</v>
@@ -4514,10 +4517,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4540,7 +4543,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46125.52977997685</v>
@@ -4552,16 +4555,16 @@
         <v>46181.66715912037</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I48" s="5">
         <v>46203</v>
@@ -4579,13 +4582,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4595,7 +4598,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46125.52991815972</v>
@@ -4607,16 +4610,16 @@
         <v>46181.66720563658</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I49" s="8">
         <v>46210</v>
@@ -4634,13 +4637,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4650,7 +4653,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B50" s="5">
         <v>46122.55120855324</v>
@@ -4662,7 +4665,7 @@
         <v>46195.50756488426</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4686,7 +4689,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4703,7 +4706,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B51" s="8">
         <v>46122.55154344907</v>
@@ -4715,16 +4718,16 @@
         <v>46143.171145879634</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I51" s="8">
         <v>46136</v>
@@ -4742,13 +4745,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="8">
         <v>46136</v>
@@ -4768,7 +4771,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46122.551548993055</v>
@@ -4780,16 +4783,16 @@
         <v>46198.18781711806</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46191</v>
@@ -4807,13 +4810,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q52" s="5">
         <v>46191</v>
@@ -4833,7 +4836,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B53" s="8">
         <v>46122.55155721065</v>
@@ -4845,16 +4848,16 @@
         <v>46199.18371805556</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="8">
@@ -4870,13 +4873,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q53" s="8">
         <v>46198</v>
@@ -4896,7 +4899,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46122.55156568287</v>
@@ -4908,16 +4911,16 @@
         <v>46196.76907818287</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4933,10 +4936,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4948,18 +4951,18 @@
         <v>46316</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B55" s="8">
         <v>46125.603622118055</v>
@@ -4971,16 +4974,16 @@
         <v>46196.7690521412</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4996,13 +4999,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -5012,7 +5015,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46125.60367094907</v>
@@ -5024,16 +5027,16 @@
         <v>46223.607461875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -5049,13 +5052,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5065,7 +5068,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B57" s="8">
         <v>46125.60371951389</v>
@@ -5077,16 +5080,16 @@
         <v>46196.76905283565</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -5102,13 +5105,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5118,7 +5121,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
         <v>46125.60376462963</v>
@@ -5130,16 +5133,16 @@
         <v>46196.76905314815</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="5">
@@ -5155,13 +5158,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5171,7 +5174,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46125.60381739584</v>
@@ -5183,16 +5186,16 @@
         <v>46196.76905349537</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I59" s="9"/>
       <c r="J59" s="8">
@@ -5208,13 +5211,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5224,7 +5227,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B60" s="5">
         <v>46122.551569710646</v>
@@ -5236,7 +5239,7 @@
         <v>46181.66785324074</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5260,7 +5263,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5273,7 +5276,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B61" s="8">
         <v>46122.55157321759</v>
@@ -5285,16 +5288,16 @@
         <v>46181.66739524306</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I61" s="8">
         <v>46216</v>
@@ -5312,13 +5315,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q61" s="8">
         <v>46216</v>
@@ -5338,7 +5341,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B62" s="5">
         <v>46122.58491638889</v>
@@ -5350,16 +5353,16 @@
         <v>46181.667429016205</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I62" s="5">
         <v>46223</v>
@@ -5377,13 +5380,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46132</v>
@@ -5403,7 +5406,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B63" s="8">
         <v>46125.53102658565</v>
@@ -5415,16 +5418,16 @@
         <v>46221.202281238424</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I63" s="8">
         <v>46219</v>
@@ -5442,13 +5445,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q63" s="8">
         <v>46219</v>
@@ -5468,7 +5471,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B64" s="5">
         <v>46122.55157846065</v>
@@ -5480,16 +5483,16 @@
         <v>46219.19909722223</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I64" s="5">
         <v>46225</v>
@@ -5507,13 +5510,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q64" s="5">
         <v>46225</v>
@@ -5533,7 +5536,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B65" s="8">
         <v>46122.551583831024</v>
@@ -5545,7 +5548,7 @@
         <v>46181.66890770833</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5569,7 +5572,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5582,7 +5585,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46122.55158688658</v>
@@ -5594,16 +5597,16 @@
         <v>46181.66880932871</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I66" s="5">
         <v>46227</v>
@@ -5621,13 +5624,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q66" s="5">
         <v>46227</v>
@@ -5636,7 +5639,7 @@
         <v>46237</v>
       </c>
       <c r="S66" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -5647,7 +5650,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46122.55159185185</v>
@@ -5659,16 +5662,16 @@
         <v>46181.668846064815</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I67" s="8">
         <v>46238</v>
@@ -5686,13 +5689,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q67" s="8">
         <v>46238</v>
@@ -5701,7 +5704,7 @@
         <v>46255</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>
@@ -5712,7 +5715,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46125.595811921296</v>
@@ -5724,16 +5727,16 @@
         <v>46181.66807884259</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I68" s="5">
         <v>46238</v>
@@ -5751,13 +5754,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5767,7 +5770,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B69" s="8">
         <v>46125.59610047453</v>
@@ -5779,16 +5782,16 @@
         <v>46181.66808728009</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I69" s="8">
         <v>46238</v>
@@ -5806,13 +5809,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5822,7 +5825,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46125.59621038195</v>
@@ -5834,16 +5837,16 @@
         <v>46181.66815550926</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I70" s="5">
         <v>46238</v>
@@ -5861,13 +5864,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5877,7 +5880,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B71" s="8">
         <v>46125.59625472222</v>
@@ -5889,16 +5892,16 @@
         <v>46181.66816819445</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I71" s="8">
         <v>46238</v>
@@ -5916,13 +5919,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5932,7 +5935,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46125.59629915509</v>
@@ -5944,16 +5947,16 @@
         <v>46181.66818078703</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I72" s="5">
         <v>46238</v>
@@ -5971,13 +5974,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5987,7 +5990,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46122.55159751157</v>
@@ -5999,16 +6002,16 @@
         <v>46181.66878222222</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I73" s="8">
         <v>46258</v>
@@ -6026,13 +6029,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q73" s="8">
         <v>46258</v>
@@ -6041,7 +6044,7 @@
         <v>46259</v>
       </c>
       <c r="S73" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T73" s="9">
         <v>1</v>
@@ -6052,7 +6055,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46125.59648849537</v>
@@ -6064,16 +6067,16 @@
         <v>46181.6686533912</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I74" s="5">
         <v>46258</v>
@@ -6091,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6107,7 +6110,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B75" s="8">
         <v>46125.59661854166</v>
@@ -6119,16 +6122,16 @@
         <v>46181.66866782407</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6146,13 +6149,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6162,7 +6165,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B76" s="5">
         <v>46125.596668750004</v>
@@ -6174,16 +6177,16 @@
         <v>46181.66867745371</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6201,13 +6204,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6217,7 +6220,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B77" s="8">
         <v>46125.59671550926</v>
@@ -6229,16 +6232,16 @@
         <v>46181.668687060184</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6256,13 +6259,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6272,7 +6275,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B78" s="5">
         <v>46125.59675546296</v>
@@ -6284,16 +6287,16 @@
         <v>46181.66870502315</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I78" s="5">
         <v>46258</v>
@@ -6311,13 +6314,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6327,7 +6330,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B79" s="8">
         <v>46122.55160357639</v>
@@ -6339,7 +6342,7 @@
         <v>46195.563290335645</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6363,7 +6366,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6375,12 +6378,12 @@
         <v>1</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46122.55160679398</v>
@@ -6392,16 +6395,16 @@
         <v>46195.711846817125</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I80" s="5">
         <v>46191</v>
@@ -6419,13 +6422,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q80" s="5">
         <v>46191</v>
@@ -6440,12 +6443,12 @@
         <v>1</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B81" s="8">
         <v>46122.551612256946</v>
@@ -6457,16 +6460,16 @@
         <v>46195.50753130787</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I81" s="8">
         <v>46266</v>
@@ -6484,13 +6487,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q81" s="8">
         <v>46266</v>
@@ -6499,7 +6502,7 @@
         <v>46267</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>
@@ -6510,7 +6513,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46122.55161756944</v>
@@ -6522,16 +6525,16 @@
         <v>46195.50753259259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I82" s="5">
         <v>46309</v>
@@ -6549,13 +6552,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q82" s="5">
         <v>46309</v>
@@ -6564,7 +6567,7 @@
         <v>46310</v>
       </c>
       <c r="S82" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6575,7 +6578,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B83" s="8">
         <v>46122.55162288195</v>
@@ -6587,16 +6590,16 @@
         <v>46195.507539479164</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I83" s="8">
         <v>46189</v>
@@ -6614,13 +6617,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q83" s="8">
         <v>46189</v>
@@ -6640,7 +6643,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B84" s="5">
         <v>46122.59399163195</v>
@@ -6652,16 +6655,16 @@
         <v>46193.9332800463</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I84" s="5">
         <v>46239</v>
@@ -6679,13 +6682,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q84" s="5">
         <v>46239</v>
@@ -6694,7 +6697,7 @@
         <v>46240</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T84" s="6">
         <v>1</v>
@@ -6705,7 +6708,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B85" s="8">
         <v>46122.551628182875</v>
@@ -6717,7 +6720,7 @@
         <v>46196.769192685184</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6741,7 +6744,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6753,12 +6756,12 @@
         <v>1</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B86" s="5">
         <v>46122.55163158565</v>
@@ -6770,7 +6773,7 @@
         <v>46223.60779484954</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6779,7 +6782,7 @@
         <v>77</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I86" s="5">
         <v>46260</v>
@@ -6797,13 +6800,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86" s="5">
         <v>46260</v>
@@ -6812,7 +6815,7 @@
         <v>46279</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -6823,7 +6826,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B87" s="8">
         <v>46125.5974969213</v>
@@ -6835,7 +6838,7 @@
         <v>46223.60698247685</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6844,7 +6847,7 @@
         <v>77</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I87" s="8">
         <v>46260</v>
@@ -6862,13 +6865,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6878,7 +6881,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B88" s="5">
         <v>46125.59754570602</v>
@@ -6890,7 +6893,7 @@
         <v>46223.60697355324</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6899,7 +6902,7 @@
         <v>77</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I88" s="5">
         <v>46260</v>
@@ -6917,13 +6920,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6933,7 +6936,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B89" s="8">
         <v>46125.59760710648</v>
@@ -6945,7 +6948,7 @@
         <v>46223.60697</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6954,7 +6957,7 @@
         <v>77</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I89" s="8">
         <v>46260</v>
@@ -6972,13 +6975,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6988,7 +6991,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46125.59765891204</v>
@@ -7000,7 +7003,7 @@
         <v>46223.60696642361</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7009,7 +7012,7 @@
         <v>77</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I90" s="5">
         <v>46260</v>
@@ -7027,13 +7030,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7043,7 +7046,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B91" s="8">
         <v>46125.597703391206</v>
@@ -7055,7 +7058,7 @@
         <v>46223.606961412035</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7064,7 +7067,7 @@
         <v>77</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I91" s="8">
         <v>46260</v>
@@ -7082,13 +7085,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7098,7 +7101,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46122.55170659722</v>
@@ -7110,7 +7113,7 @@
         <v>46223.607791331015</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7119,7 +7122,7 @@
         <v>77</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I92" s="5">
         <v>46280</v>
@@ -7137,13 +7140,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q92" s="5">
         <v>46280</v>
@@ -7152,18 +7155,18 @@
         <v>46282</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B93" s="8">
         <v>46125.59982741898</v>
@@ -7175,7 +7178,7 @@
         <v>46223.60708418982</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7184,7 +7187,7 @@
         <v>77</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I93" s="8">
         <v>46280</v>
@@ -7202,13 +7205,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7218,7 +7221,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46125.599890833335</v>
@@ -7230,7 +7233,7 @@
         <v>46223.60707991898</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7239,7 +7242,7 @@
         <v>77</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I94" s="5">
         <v>46280</v>
@@ -7257,13 +7260,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7273,7 +7276,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B95" s="8">
         <v>46125.59993134259</v>
@@ -7285,7 +7288,7 @@
         <v>46223.60707583334</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7294,7 +7297,7 @@
         <v>77</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I95" s="8">
         <v>46280</v>
@@ -7312,13 +7315,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7328,7 +7331,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46125.59996929398</v>
@@ -7340,7 +7343,7 @@
         <v>46223.607072060186</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7349,7 +7352,7 @@
         <v>77</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I96" s="5">
         <v>46280</v>
@@ -7367,13 +7370,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7383,7 +7386,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B97" s="8">
         <v>46125.6000115162</v>
@@ -7395,7 +7398,7 @@
         <v>46223.607066192126</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7404,7 +7407,7 @@
         <v>77</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I97" s="8">
         <v>46280</v>
@@ -7422,13 +7425,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7438,7 +7441,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B98" s="5">
         <v>46122.55164413195</v>
@@ -7450,7 +7453,7 @@
         <v>46223.60778702547</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7459,7 +7462,7 @@
         <v>77</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I98" s="5">
         <v>46286</v>
@@ -7477,13 +7480,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q98" s="5">
         <v>46286</v>
@@ -7492,7 +7495,7 @@
         <v>46288</v>
       </c>
       <c r="S98" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T98" s="6">
         <v>1</v>
@@ -7503,7 +7506,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B99" s="8">
         <v>46125.599162743056</v>
@@ -7515,7 +7518,7 @@
         <v>46223.60720636574</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7524,7 +7527,7 @@
         <v>77</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I99" s="8">
         <v>46286</v>
@@ -7542,13 +7545,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7558,7 +7561,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B100" s="5">
         <v>46125.599302511575</v>
@@ -7570,7 +7573,7 @@
         <v>46223.60720247685</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7579,7 +7582,7 @@
         <v>77</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I100" s="5">
         <v>46286</v>
@@ -7597,13 +7600,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7613,7 +7616,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B101" s="8">
         <v>46125.59934644676</v>
@@ -7625,7 +7628,7 @@
         <v>46223.60719819444</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7634,7 +7637,7 @@
         <v>77</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I101" s="8">
         <v>46286</v>
@@ -7652,13 +7655,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7668,7 +7671,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B102" s="5">
         <v>46125.59938857639</v>
@@ -7680,7 +7683,7 @@
         <v>46223.60719417824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7689,7 +7692,7 @@
         <v>77</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I102" s="5">
         <v>46286</v>
@@ -7707,13 +7710,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7723,7 +7726,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B103" s="8">
         <v>46125.59943094908</v>
@@ -7735,7 +7738,7 @@
         <v>46223.60718841435</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7744,7 +7747,7 @@
         <v>77</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I103" s="8">
         <v>46286</v>
@@ -7762,13 +7765,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7778,7 +7781,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B104" s="5">
         <v>46122.551650995374</v>
@@ -7790,7 +7793,7 @@
         <v>46223.60778314815</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7799,7 +7802,7 @@
         <v>77</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I104" s="5">
         <v>46289</v>
@@ -7817,13 +7820,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q104" s="5">
         <v>46289</v>
@@ -7832,18 +7835,18 @@
         <v>46293</v>
       </c>
       <c r="S104" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>
       </c>
       <c r="U104" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B105" s="8">
         <v>46125.59953013889</v>
@@ -7855,7 +7858,7 @@
         <v>46223.60731153935</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7864,7 +7867,7 @@
         <v>77</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I105" s="8">
         <v>46289</v>
@@ -7882,13 +7885,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7898,7 +7901,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B106" s="5">
         <v>46125.59961423611</v>
@@ -7910,7 +7913,7 @@
         <v>46223.60730783565</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7919,7 +7922,7 @@
         <v>77</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I106" s="5">
         <v>46289</v>
@@ -7937,13 +7940,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7953,7 +7956,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B107" s="8">
         <v>46125.599654317135</v>
@@ -7965,7 +7968,7 @@
         <v>46223.60730394676</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7974,7 +7977,7 @@
         <v>77</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I107" s="8">
         <v>46289</v>
@@ -7992,13 +7995,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8008,7 +8011,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B108" s="5">
         <v>46125.59957065972</v>
@@ -8020,7 +8023,7 @@
         <v>46223.607299675925</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8029,7 +8032,7 @@
         <v>77</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I108" s="5">
         <v>46289</v>
@@ -8047,13 +8050,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8063,7 +8066,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B109" s="8">
         <v>46125.59969711806</v>
@@ -8075,7 +8078,7 @@
         <v>46223.60729373843</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8084,7 +8087,7 @@
         <v>77</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I109" s="8">
         <v>46289</v>
@@ -8102,13 +8105,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8118,7 +8121,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B110" s="5">
         <v>46122.55163725694</v>
@@ -8130,7 +8133,7 @@
         <v>46223.607779618054</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8139,7 +8142,7 @@
         <v>77</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I110" s="5">
         <v>46311</v>
@@ -8157,13 +8160,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q110" s="5">
         <v>46311</v>
@@ -8172,7 +8175,7 @@
         <v>46314</v>
       </c>
       <c r="S110" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T110" s="6">
         <v>1</v>
@@ -8183,7 +8186,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B111" s="8">
         <v>46125.59780210648</v>
@@ -8195,7 +8198,7 @@
         <v>46223.607408310185</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8204,7 +8207,7 @@
         <v>77</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I111" s="8">
         <v>46311</v>
@@ -8222,13 +8225,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8238,7 +8241,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B112" s="5">
         <v>46125.597836932866</v>
@@ -8250,7 +8253,7 @@
         <v>46223.60740443287</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8259,7 +8262,7 @@
         <v>77</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I112" s="5">
         <v>46311</v>
@@ -8277,13 +8280,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8293,7 +8296,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B113" s="8">
         <v>46125.5979208912</v>
@@ -8305,7 +8308,7 @@
         <v>46223.607400532404</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8314,7 +8317,7 @@
         <v>77</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I113" s="8">
         <v>46311</v>
@@ -8332,13 +8335,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8348,7 +8351,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B114" s="5">
         <v>46125.59788087963</v>
@@ -8360,7 +8363,7 @@
         <v>46223.60739668981</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8369,7 +8372,7 @@
         <v>77</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I114" s="5">
         <v>46311</v>
@@ -8387,13 +8390,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8403,7 +8406,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B115" s="8">
         <v>46125.597965023146</v>
@@ -8415,7 +8418,7 @@
         <v>46223.60739046296</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8424,7 +8427,7 @@
         <v>77</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I115" s="8">
         <v>46311</v>
@@ -8442,13 +8445,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8458,7 +8461,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B116" s="5">
         <v>46122.55172043982</v>
@@ -8470,7 +8473,7 @@
         <v>46223.607775474535</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8479,7 +8482,7 @@
         <v>77</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I116" s="5">
         <v>46315</v>
@@ -8497,13 +8500,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q116" s="5">
         <v>46315</v>
@@ -8512,18 +8515,18 @@
         <v>46315</v>
       </c>
       <c r="S116" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T116" s="6">
         <v>1</v>
       </c>
       <c r="U116" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B117" s="8">
         <v>46125.60038253472</v>
@@ -8535,7 +8538,7 @@
         <v>46223.60758443287</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8544,7 +8547,7 @@
         <v>77</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8560,13 +8563,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8576,7 +8579,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B118" s="5">
         <v>46125.60043012731</v>
@@ -8588,7 +8591,7 @@
         <v>46223.60758005787</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8597,7 +8600,7 @@
         <v>77</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8613,13 +8616,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8629,7 +8632,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B119" s="8">
         <v>46125.60047290509</v>
@@ -8641,7 +8644,7 @@
         <v>46223.607575752314</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8650,7 +8653,7 @@
         <v>77</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I119" s="9"/>
       <c r="J119" s="8">
@@ -8666,13 +8669,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8682,7 +8685,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B120" s="5">
         <v>46125.600514074074</v>
@@ -8694,7 +8697,7 @@
         <v>46223.607571597226</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8703,7 +8706,7 @@
         <v>77</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8719,13 +8722,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8735,7 +8738,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B121" s="8">
         <v>46125.60055859954</v>
@@ -8747,7 +8750,7 @@
         <v>46223.60756553241</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8756,7 +8759,7 @@
         <v>77</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8772,13 +8775,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8788,7 +8791,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B122" s="5">
         <v>46122.55172986111</v>
@@ -8800,7 +8803,7 @@
         <v>46223.60776988426</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8809,7 +8812,7 @@
         <v>77</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I122" s="5">
         <v>46317</v>
@@ -8827,13 +8830,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q122" s="5">
         <v>46317</v>
@@ -8842,7 +8845,7 @@
         <v>46317</v>
       </c>
       <c r="S122" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T122" s="6">
         <v>1</v>
@@ -8853,7 +8856,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B123" s="8">
         <v>46125.60064416667</v>
@@ -8865,7 +8868,7 @@
         <v>46223.607680601854</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8874,7 +8877,7 @@
         <v>77</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -8890,13 +8893,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8906,7 +8909,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B124" s="5">
         <v>46125.60068740741</v>
@@ -8918,7 +8921,7 @@
         <v>46223.60767706019</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8927,7 +8930,7 @@
         <v>77</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -8943,13 +8946,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8959,7 +8962,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B125" s="8">
         <v>46125.60073844907</v>
@@ -8971,7 +8974,7 @@
         <v>46223.607672812504</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8980,7 +8983,7 @@
         <v>77</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
@@ -8996,13 +8999,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9012,7 +9015,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B126" s="5">
         <v>46125.60077622686</v>
@@ -9024,7 +9027,7 @@
         <v>46223.6076684375</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9033,7 +9036,7 @@
         <v>77</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -9049,13 +9052,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9065,7 +9068,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B127" s="8">
         <v>46125.600829143514</v>
@@ -9077,7 +9080,7 @@
         <v>46223.60766289352</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9086,7 +9089,7 @@
         <v>77</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
@@ -9102,13 +9105,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9118,7 +9121,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B128" s="5">
         <v>46122.5517350463</v>
@@ -9130,7 +9133,7 @@
         <v>46196.76960409722</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>25</v>
@@ -9154,7 +9157,7 @@
         <v>26</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>26</v>
@@ -9166,12 +9169,12 @@
         <v>1</v>
       </c>
       <c r="U128" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B129" s="8">
         <v>46122.5517390625</v>
@@ -9183,16 +9186,16 @@
         <v>46196.76939736111</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I129" s="8">
         <v>46318</v>
@@ -9210,13 +9213,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q129" s="8">
         <v>46318</v>
@@ -9225,18 +9228,18 @@
         <v>46318</v>
       </c>
       <c r="S129" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T129" s="9">
         <v>1</v>
       </c>
       <c r="U129" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B130" s="5">
         <v>46125.60093731481</v>
@@ -9248,16 +9251,16 @@
         <v>46196.769350682865</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9273,13 +9276,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9289,7 +9292,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B131" s="8">
         <v>46125.601380821754</v>
@@ -9301,16 +9304,16 @@
         <v>46196.769351145835</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9326,13 +9329,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9342,7 +9345,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B132" s="5">
         <v>46125.60142481481</v>
@@ -9354,16 +9357,16 @@
         <v>46196.76935155093</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9379,13 +9382,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9395,7 +9398,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B133" s="8">
         <v>46125.60146085648</v>
@@ -9407,16 +9410,16 @@
         <v>46196.76935192129</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9432,13 +9435,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9448,7 +9451,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B134" s="5">
         <v>46125.60150208333</v>
@@ -9460,16 +9463,16 @@
         <v>46196.76935229167</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9485,13 +9488,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9501,7 +9504,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B135" s="8">
         <v>46122.55174383102</v>
@@ -9513,7 +9516,7 @@
         <v>46223.6084731713</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9522,7 +9525,7 @@
         <v>77</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9538,13 +9541,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q135" s="8">
         <v>46321</v>
@@ -9553,7 +9556,7 @@
         <v>46321</v>
       </c>
       <c r="S135" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T135" s="9">
         <v>1</v>
@@ -9564,7 +9567,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B136" s="5">
         <v>46125.601086979164</v>
@@ -9576,7 +9579,7 @@
         <v>46223.60837070602</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9585,7 +9588,7 @@
         <v>77</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9601,13 +9604,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9617,7 +9620,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B137" s="8">
         <v>46125.60115318287</v>
@@ -9629,7 +9632,7 @@
         <v>46223.60836653935</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9638,7 +9641,7 @@
         <v>77</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9654,13 +9657,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9670,7 +9673,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B138" s="5">
         <v>46125.60120391204</v>
@@ -9682,7 +9685,7 @@
         <v>46223.608362604165</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9691,7 +9694,7 @@
         <v>77</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9707,13 +9710,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9723,7 +9726,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B139" s="8">
         <v>46125.60125796296</v>
@@ -9735,7 +9738,7 @@
         <v>46223.60835905092</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9744,7 +9747,7 @@
         <v>77</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="8">
@@ -9760,13 +9763,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9776,7 +9779,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B140" s="5">
         <v>46125.601304282405</v>
@@ -9788,7 +9791,7 @@
         <v>46223.60835267361</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9797,7 +9800,7 @@
         <v>77</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9813,13 +9816,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9829,7 +9832,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B141" s="8">
         <v>46122.55174869213</v>
@@ -9841,16 +9844,16 @@
         <v>46196.769715787035</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9866,13 +9869,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q141" s="8">
         <v>46322</v>
@@ -9881,18 +9884,18 @@
         <v>46322</v>
       </c>
       <c r="S141" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T141" s="9">
         <v>1</v>
       </c>
       <c r="U141" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B142" s="5">
         <v>46125.60158650463</v>
@@ -9904,16 +9907,16 @@
         <v>46196.76968989584</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -9929,13 +9932,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9945,7 +9948,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B143" s="8">
         <v>46125.60163133102</v>
@@ -9957,16 +9960,16 @@
         <v>46196.7696903125</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -9982,13 +9985,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -9998,7 +10001,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B144" s="5">
         <v>46125.60167016204</v>
@@ -10010,16 +10013,16 @@
         <v>46196.769690706016</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -10035,13 +10038,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10051,7 +10054,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B145" s="8">
         <v>46125.60170435185</v>
@@ -10063,16 +10066,16 @@
         <v>46196.76969114583</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -10088,13 +10091,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10104,7 +10107,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B146" s="5">
         <v>46125.60173947917</v>
@@ -10116,16 +10119,16 @@
         <v>46196.76969164352</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10141,13 +10144,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10157,7 +10160,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B147" s="8">
         <v>46122.551753472224</v>
@@ -10169,16 +10172,16 @@
         <v>46196.76981105324</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -10194,13 +10197,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q147" s="8">
         <v>46323</v>
@@ -10209,18 +10212,18 @@
         <v>46323</v>
       </c>
       <c r="S147" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T147" s="9">
         <v>1</v>
       </c>
       <c r="U147" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B148" s="5">
         <v>46125.60181555555</v>
@@ -10232,16 +10235,16 @@
         <v>46196.76979569445</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10257,13 +10260,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10273,7 +10276,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B149" s="8">
         <v>46125.60185690972</v>
@@ -10285,16 +10288,16 @@
         <v>46196.76979614583</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10310,13 +10313,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10326,7 +10329,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B150" s="5">
         <v>46125.601899490735</v>
@@ -10338,16 +10341,16 @@
         <v>46196.76979648148</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10363,13 +10366,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10379,7 +10382,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B151" s="8">
         <v>46125.60193935185</v>
@@ -10391,16 +10394,16 @@
         <v>46196.769766875004</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10416,13 +10419,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10432,7 +10435,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B152" s="5">
         <v>46125.60197710648</v>
@@ -10444,16 +10447,16 @@
         <v>46196.76977370371</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10469,13 +10472,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10485,7 +10488,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B153" s="8">
         <v>46122.551758622685</v>
@@ -10495,7 +10498,7 @@
         <v>46125.58936878473</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>25</v>
@@ -10519,7 +10522,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>26</v>
@@ -10532,7 +10535,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B154" s="5">
         <v>46122.55176134259</v>
@@ -10542,16 +10545,16 @@
         <v>46191.70605767361</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I154" s="5">
         <v>46324</v>
@@ -10569,13 +10572,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q154" s="5">
         <v>46324</v>
@@ -10584,18 +10587,18 @@
         <v>46332</v>
       </c>
       <c r="S154" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T154" s="6">
         <v>0</v>
       </c>
       <c r="U154" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B155" s="8">
         <v>46122.55176609954</v>
@@ -10605,16 +10608,16 @@
         <v>46192.97384414352</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I155" s="8">
         <v>46324</v>
@@ -10632,13 +10635,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q155" s="8">
         <v>46324</v>
@@ -10647,13 +10650,13 @@
         <v>46332</v>
       </c>
       <c r="S155" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T155" s="9">
         <v>0</v>
       </c>
       <c r="U155" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -2527,7 +2527,7 @@
         <v>46195.50723163194</v>
       </c>
       <c r="D15" s="8">
-        <v>46223.425324826385</v>
+        <v>46228.10468802083</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -4487,7 +4487,7 @@
         <v>46181.66722120371</v>
       </c>
       <c r="D47" s="8">
-        <v>46219.16816725694</v>
+        <v>46228.07776863426</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -5480,7 +5480,7 @@
         <v>46181.66775587963</v>
       </c>
       <c r="D64" s="5">
-        <v>46219.19909722223</v>
+        <v>46227.182452106485</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>215</v>
@@ -5524,8 +5524,8 @@
       <c r="R64" s="5">
         <v>46226</v>
       </c>
-      <c r="S64" s="12" t="s">
-        <v>74</v>
+      <c r="S64" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T64" s="6">
         <v>1</v>
@@ -5594,7 +5594,7 @@
         <v>46181.666093576394</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.66880932871</v>
+        <v>46230.185321261575</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>228</v>
@@ -5638,8 +5638,8 @@
       <c r="R66" s="5">
         <v>46237</v>
       </c>
-      <c r="S66" s="11" t="s">
-        <v>104</v>
+      <c r="S66" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -5659,7 +5659,7 @@
         <v>46181.6661986574</v>
       </c>
       <c r="D67" s="8">
-        <v>46181.668846064815</v>
+        <v>46228.10617515046</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>233</v>
@@ -5999,7 +5999,7 @@
         <v>46181.66878061343</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.66878222222</v>
+        <v>46228.106273067126</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>244</v>
@@ -6717,7 +6717,7 @@
         <v>46195.5630599537</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.769192685184</v>
+        <v>46228.07806180556</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>269</v>
@@ -7110,7 +7110,7 @@
         <v>46196.76755512731</v>
       </c>
       <c r="D92" s="5">
-        <v>46223.607791331015</v>
+        <v>46228.123738159724</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>
@@ -7450,7 +7450,7 @@
         <v>46196.76839824074</v>
       </c>
       <c r="D98" s="5">
-        <v>46223.60778702547</v>
+        <v>46228.10704425926</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>291</v>
@@ -8470,7 +8470,7 @@
         <v>46196.76877224537</v>
       </c>
       <c r="D116" s="5">
-        <v>46223.607775474535</v>
+        <v>46228.10734545139</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>318</v>
@@ -9513,7 +9513,7 @@
         <v>46196.769596921295</v>
       </c>
       <c r="D135" s="8">
-        <v>46223.6084731713</v>
+        <v>46228.10760070602</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>349</v>
@@ -9841,7 +9841,7 @@
         <v>46191.70598530093</v>
       </c>
       <c r="D141" s="8">
-        <v>46196.769715787035</v>
+        <v>46228.14621358796</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>357</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4312,7 +4312,7 @@
         <v>46181.666958472226</v>
       </c>
       <c r="D44" s="5">
-        <v>46223.42579010417</v>
+        <v>46231.18084584491</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4356,8 +4356,8 @@
       <c r="R44" s="5">
         <v>46238</v>
       </c>
-      <c r="S44" s="11" t="s">
-        <v>104</v>
+      <c r="S44" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -6652,7 +6652,7 @@
         <v>46193.93315311342</v>
       </c>
       <c r="D84" s="5">
-        <v>46193.9332800463</v>
+        <v>46233.180653414354</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>266</v>
@@ -6696,8 +6696,8 @@
       <c r="R84" s="5">
         <v>46240</v>
       </c>
-      <c r="S84" s="11" t="s">
-        <v>104</v>
+      <c r="S84" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T84" s="6">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -7110,7 +7110,7 @@
         <v>46196.76755512731</v>
       </c>
       <c r="D92" s="5">
-        <v>46228.123738159724</v>
+        <v>46237.53492259259</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>
@@ -7160,8 +7160,8 @@
       <c r="T92" s="6">
         <v>1</v>
       </c>
-      <c r="U92" s="12" t="s">
-        <v>115</v>
+      <c r="U92" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7790,7 +7790,7 @@
         <v>46196.76854788195</v>
       </c>
       <c r="D104" s="5">
-        <v>46223.60778314815</v>
+        <v>46237.53494261574</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>301</v>
@@ -7840,8 +7840,8 @@
       <c r="T104" s="6">
         <v>1</v>
       </c>
-      <c r="U104" s="12" t="s">
-        <v>115</v>
+      <c r="U104" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -8470,7 +8470,7 @@
         <v>46196.76877224537</v>
       </c>
       <c r="D116" s="5">
-        <v>46228.10734545139</v>
+        <v>46237.53496467593</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>318</v>
@@ -8520,8 +8520,8 @@
       <c r="T116" s="6">
         <v>1</v>
       </c>
-      <c r="U116" s="12" t="s">
-        <v>115</v>
+      <c r="U116" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -5594,7 +5594,7 @@
         <v>46181.666093576394</v>
       </c>
       <c r="D66" s="5">
-        <v>46230.185321261575</v>
+        <v>46238.1884728125</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>228</v>
@@ -5638,8 +5638,8 @@
       <c r="R66" s="5">
         <v>46237</v>
       </c>
-      <c r="S66" s="12" t="s">
-        <v>74</v>
+      <c r="S66" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4312,7 +4312,7 @@
         <v>46181.666958472226</v>
       </c>
       <c r="D44" s="5">
-        <v>46231.18084584491</v>
+        <v>46239.17159243056</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4356,8 +4356,8 @@
       <c r="R44" s="5">
         <v>46238</v>
       </c>
-      <c r="S44" s="12" t="s">
-        <v>74</v>
+      <c r="S44" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -6392,7 +6392,7 @@
         <v>46195.563269363425</v>
       </c>
       <c r="D80" s="5">
-        <v>46195.711846817125</v>
+        <v>46240.605594189816</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>257</v>
@@ -6442,8 +6442,8 @@
       <c r="T80" s="6">
         <v>1</v>
       </c>
-      <c r="U80" s="12" t="s">
-        <v>115</v>
+      <c r="U80" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -9183,7 +9183,7 @@
         <v>46196.76936652778</v>
       </c>
       <c r="D129" s="8">
-        <v>46196.76939736111</v>
+        <v>46240.60562268519</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>338</v>
@@ -9233,8 +9233,8 @@
       <c r="T129" s="9">
         <v>1</v>
       </c>
-      <c r="U129" s="12" t="s">
-        <v>115</v>
+      <c r="U129" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -9841,7 +9841,7 @@
         <v>46191.70598530093</v>
       </c>
       <c r="D141" s="8">
-        <v>46228.14621358796</v>
+        <v>46240.605638368055</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>357</v>
@@ -9889,8 +9889,8 @@
       <c r="T141" s="9">
         <v>1</v>
       </c>
-      <c r="U141" s="12" t="s">
-        <v>115</v>
+      <c r="U141" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
@@ -10169,7 +10169,7 @@
         <v>46191.70604009259</v>
       </c>
       <c r="D147" s="8">
-        <v>46196.76981105324</v>
+        <v>46240.60565322917</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>366</v>
@@ -10217,8 +10217,8 @@
       <c r="T147" s="9">
         <v>1</v>
       </c>
-      <c r="U147" s="12" t="s">
-        <v>115</v>
+      <c r="U147" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="382">
   <si>
     <t xml:space="preserve"> 50001466 - ZITRON PERU (PODEROSA) </t>
   </si>
@@ -10493,9 +10493,11 @@
       <c r="B153" s="8">
         <v>46122.551758622685</v>
       </c>
-      <c r="C153" s="9"/>
+      <c r="C153" s="8">
+        <v>46240.65384241898</v>
+      </c>
       <c r="D153" s="8">
-        <v>46125.58936878473</v>
+        <v>46240.65385445602</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>374</v>
@@ -10530,8 +10532,12 @@
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
       <c r="S153" s="9"/>
-      <c r="T153" s="9"/>
-      <c r="U153" s="9"/>
+      <c r="T153" s="9">
+        <v>1</v>
+      </c>
+      <c r="U153" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
@@ -10540,9 +10546,11 @@
       <c r="B154" s="5">
         <v>46122.55176134259</v>
       </c>
-      <c r="C154" s="6"/>
+      <c r="C154" s="5">
+        <v>46240.65381834491</v>
+      </c>
       <c r="D154" s="5">
-        <v>46191.70605767361</v>
+        <v>46240.65383614584</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>377</v>
@@ -10590,10 +10598,10 @@
         <v>104</v>
       </c>
       <c r="T154" s="6">
-        <v>0</v>
-      </c>
-      <c r="U154" s="12" t="s">
-        <v>115</v>
+        <v>1</v>
+      </c>
+      <c r="U154" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
@@ -10603,9 +10611,11 @@
       <c r="B155" s="8">
         <v>46122.55176609954</v>
       </c>
-      <c r="C155" s="9"/>
+      <c r="C155" s="8">
+        <v>46240.65382724537</v>
+      </c>
       <c r="D155" s="8">
-        <v>46192.97384414352</v>
+        <v>46240.65384380787</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>381</v>
@@ -10653,10 +10663,10 @@
         <v>104</v>
       </c>
       <c r="T155" s="9">
-        <v>0</v>
-      </c>
-      <c r="U155" s="12" t="s">
-        <v>115</v>
+        <v>1</v>
+      </c>
+      <c r="U155" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -6652,7 +6652,7 @@
         <v>46193.93315311342</v>
       </c>
       <c r="D84" s="5">
-        <v>46233.180653414354</v>
+        <v>46241.18852804398</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>266</v>
@@ -6696,8 +6696,8 @@
       <c r="R84" s="5">
         <v>46240</v>
       </c>
-      <c r="S84" s="12" t="s">
-        <v>74</v>
+      <c r="S84" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T84" s="6">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -5659,7 +5659,7 @@
         <v>46181.6661986574</v>
       </c>
       <c r="D67" s="8">
-        <v>46228.10617515046</v>
+        <v>46248.187867650464</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>233</v>
@@ -5703,8 +5703,8 @@
       <c r="R67" s="8">
         <v>46255</v>
       </c>
-      <c r="S67" s="11" t="s">
-        <v>104</v>
+      <c r="S67" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -3153,7 +3153,7 @@
         <v>46174.626168703704</v>
       </c>
       <c r="D25" s="8">
-        <v>46174.626181134256</v>
+        <v>46250.21356391204</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -5999,7 +5999,7 @@
         <v>46181.66878061343</v>
       </c>
       <c r="D73" s="8">
-        <v>46228.106273067126</v>
+        <v>46252.20192400463</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>244</v>
@@ -6043,8 +6043,8 @@
       <c r="R73" s="8">
         <v>46259</v>
       </c>
-      <c r="S73" s="11" t="s">
-        <v>104</v>
+      <c r="S73" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T73" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -5659,7 +5659,7 @@
         <v>46181.6661986574</v>
       </c>
       <c r="D67" s="8">
-        <v>46248.187867650464</v>
+        <v>46256.20327105324</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>233</v>
@@ -5703,8 +5703,8 @@
       <c r="R67" s="8">
         <v>46255</v>
       </c>
-      <c r="S67" s="12" t="s">
-        <v>74</v>
+      <c r="S67" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -386,16 +386,16 @@
     <t>Generación OC Alabe - OT 4302,Fabricación Alabe - OT 4302</t>
   </si>
   <si>
+    <t>1214005097392571</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe - OT 4302</t>
+  </si>
+  <si>
+    <t>Alabe- OT 4302,Fabricación Alabe - OT 4302</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>1214005097392571</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe - OT 4302</t>
-  </si>
-  <si>
-    <t>Alabe- OT 4302,Fabricación Alabe - OT 4302</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -1844,13 +1844,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46122.55118912037</v>
+        <v>46122.38452245371</v>
       </c>
       <c r="C4" s="5">
-        <v>46128.59300771991</v>
+        <v>46128.426341053244</v>
       </c>
       <c r="D4" s="5">
-        <v>46158.10300121528</v>
+        <v>46157.93633454861</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1893,13 +1893,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46122.55134571759</v>
+        <v>46122.38467905093</v>
       </c>
       <c r="C5" s="8">
-        <v>46128.59299462963</v>
+        <v>46128.42632796297</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.876021724536</v>
+        <v>46133.70935505787</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1956,13 +1956,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46122.55134947917</v>
+        <v>46122.384682812495</v>
       </c>
       <c r="C6" s="5">
-        <v>46128.59267868055</v>
+        <v>46128.42601201389</v>
       </c>
       <c r="D6" s="5">
-        <v>46128.60382631945</v>
+        <v>46128.43715965278</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2019,13 +2019,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46122.551352546296</v>
+        <v>46122.38468587963</v>
       </c>
       <c r="C7" s="8">
-        <v>46128.59269866898</v>
+        <v>46128.42603200232</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.62726047453</v>
+        <v>46161.460593807875</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2082,13 +2082,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46122.551355567135</v>
+        <v>46122.38468890046</v>
       </c>
       <c r="C8" s="5">
-        <v>46128.59271722222</v>
+        <v>46128.42605055556</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.60400607639</v>
+        <v>46128.43733940972</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2145,13 +2145,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46122.551359386576</v>
+        <v>46122.384692719905</v>
       </c>
       <c r="C9" s="8">
-        <v>46128.592850057874</v>
+        <v>46128.4261833912</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.83577310185</v>
+        <v>46156.66910643518</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2208,13 +2208,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46122.55119412037</v>
+        <v>46122.3845274537</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.93280347223</v>
+        <v>46193.766136805556</v>
       </c>
       <c r="D10" s="5">
-        <v>46223.423621180555</v>
+        <v>46223.25695451389</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2261,13 +2261,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46122.5513631713</v>
+        <v>46122.384696504625</v>
       </c>
       <c r="C11" s="8">
-        <v>46128.60435520833</v>
+        <v>46128.43768854167</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.97382803241</v>
+        <v>46192.80716136574</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2326,13 +2326,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46122.551369050925</v>
+        <v>46122.38470238426</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.60643114583</v>
+        <v>46128.43976447917</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.97382813657</v>
+        <v>46192.80716146991</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2391,13 +2391,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46122.5513746875</v>
+        <v>46122.384708020836</v>
       </c>
       <c r="C13" s="8">
-        <v>46132.57072561343</v>
+        <v>46132.40405894676</v>
       </c>
       <c r="D13" s="8">
-        <v>46192.97382800926</v>
+        <v>46192.80716134259</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2456,13 +2456,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46122.553594178244</v>
+        <v>46122.38692751157</v>
       </c>
       <c r="C14" s="5">
-        <v>46128.60941575232</v>
+        <v>46128.44274908565</v>
       </c>
       <c r="D14" s="5">
-        <v>46136.20601917824</v>
+        <v>46136.03935251157</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2521,13 +2521,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46122.55119946759</v>
+        <v>46122.38453280093</v>
       </c>
       <c r="C15" s="8">
-        <v>46195.50723163194</v>
+        <v>46195.34056496528</v>
       </c>
       <c r="D15" s="8">
-        <v>46228.10468802083</v>
+        <v>46227.938021354166</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2574,13 +2574,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46122.55138855324</v>
+        <v>46122.38472188657</v>
       </c>
       <c r="C16" s="5">
-        <v>46128.60700391204</v>
+        <v>46128.44033724537</v>
       </c>
       <c r="D16" s="5">
-        <v>46133.17999505787</v>
+        <v>46133.0133283912</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2639,13 +2639,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46122.55139482639</v>
+        <v>46122.38472815973</v>
       </c>
       <c r="C17" s="8">
-        <v>46128.60701157407</v>
+        <v>46128.44034490741</v>
       </c>
       <c r="D17" s="8">
-        <v>46132.182206921294</v>
+        <v>46132.01554025463</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2704,13 +2704,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46122.55140040509</v>
+        <v>46122.38473373842</v>
       </c>
       <c r="C18" s="5">
-        <v>46195.50721171296</v>
+        <v>46195.340545046296</v>
       </c>
       <c r="D18" s="5">
-        <v>46223.606554259255</v>
+        <v>46223.43988759259</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2769,13 +2769,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="8">
-        <v>46122.55140604167</v>
+        <v>46122.384739375004</v>
       </c>
       <c r="C19" s="8">
-        <v>46181.666399050926</v>
+        <v>46181.499732384254</v>
       </c>
       <c r="D19" s="8">
-        <v>46223.606550833334</v>
+        <v>46223.43988416667</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>81</v>
@@ -2834,13 +2834,13 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46122.55141162037</v>
+        <v>46122.3847449537</v>
       </c>
       <c r="C20" s="5">
-        <v>46128.609497881946</v>
+        <v>46128.442831215274</v>
       </c>
       <c r="D20" s="5">
-        <v>46132.1822065625</v>
+        <v>46132.01553989583</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>64</v>
@@ -2899,13 +2899,13 @@
         <v>87</v>
       </c>
       <c r="B21" s="8">
-        <v>46122.566545787035</v>
+        <v>46122.39987912037</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.66636053241</v>
+        <v>46181.49969386574</v>
       </c>
       <c r="D21" s="8">
-        <v>46223.60654709491</v>
+        <v>46223.43988042824</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>88</v>
@@ -2964,13 +2964,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46122.56661521991</v>
+        <v>46122.39994855324</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.66637630787</v>
+        <v>46181.499709641204</v>
       </c>
       <c r="D22" s="5">
-        <v>46223.60654385417</v>
+        <v>46223.4398771875</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -3029,13 +3029,13 @@
         <v>93</v>
       </c>
       <c r="B23" s="8">
-        <v>46122.57286273148</v>
+        <v>46122.40619606481</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.66643224537</v>
+        <v>46181.4997655787</v>
       </c>
       <c r="D23" s="8">
-        <v>46223.60653833333</v>
+        <v>46223.43987166666</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>94</v>
@@ -3094,13 +3094,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46122.55120394676</v>
+        <v>46122.38453728009</v>
       </c>
       <c r="C24" s="5">
-        <v>46195.50733982639</v>
+        <v>46195.34067315972</v>
       </c>
       <c r="D24" s="5">
-        <v>46223.425103263886</v>
+        <v>46223.25843659722</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -3147,13 +3147,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46122.55141694444</v>
+        <v>46122.38475027778</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.626168703704</v>
+        <v>46174.45950203703</v>
       </c>
       <c r="D25" s="8">
-        <v>46250.21356391204</v>
+        <v>46258.02963747685</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -3197,8 +3197,8 @@
       <c r="R25" s="8">
         <v>46265</v>
       </c>
-      <c r="S25" s="11" t="s">
-        <v>104</v>
+      <c r="S25" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T25" s="9">
         <v>1</v>
@@ -3209,19 +3209,19 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46122.38475541667</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46174.45658625</v>
+      </c>
+      <c r="D26" s="5">
+        <v>46174.456587824076</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="B26" s="5">
-        <v>46122.55142208333</v>
-      </c>
-      <c r="C26" s="5">
-        <v>46174.62325291667</v>
-      </c>
-      <c r="D26" s="5">
-        <v>46174.62325449074</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3254,12 +3254,12 @@
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46122.55142699074</v>
+        <v>46122.38476032407</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.626152893514</v>
+        <v>46174.45948622686</v>
       </c>
       <c r="D27" s="8">
-        <v>46174.62615429398</v>
+        <v>46174.45948762732</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -3312,7 +3312,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>111</v>
@@ -3320,7 +3320,7 @@
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T27" s="9">
         <v>0</v>
@@ -3334,13 +3334,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46122.5514322338</v>
+        <v>46122.38476556713</v>
       </c>
       <c r="C28" s="5">
-        <v>46195.50732521991</v>
+        <v>46195.340658553236</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.71184679398</v>
+        <v>46195.545180127316</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3399,13 +3399,13 @@
         <v>116</v>
       </c>
       <c r="B29" s="8">
-        <v>46122.551437546295</v>
+        <v>46122.38477087963</v>
       </c>
       <c r="C29" s="8">
-        <v>46195.71138274306</v>
+        <v>46195.54471607639</v>
       </c>
       <c r="D29" s="8">
-        <v>46195.71138517361</v>
+        <v>46195.54471850695</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>117</v>
@@ -3446,7 +3446,7 @@
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
@@ -3460,13 +3460,13 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46122.55144255787</v>
+        <v>46122.3847758912</v>
       </c>
       <c r="C30" s="5">
-        <v>46195.711830960645</v>
+        <v>46195.54516429398</v>
       </c>
       <c r="D30" s="5">
-        <v>46195.711832500005</v>
+        <v>46195.54516583333</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3507,7 +3507,7 @@
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3521,13 +3521,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="8">
-        <v>46122.551447708334</v>
+        <v>46122.38478104166</v>
       </c>
       <c r="C31" s="8">
-        <v>46133.82779993056</v>
+        <v>46133.661133263886</v>
       </c>
       <c r="D31" s="8">
-        <v>46133.82781321759</v>
+        <v>46133.66114655093</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>123</v>
@@ -3572,7 +3572,7 @@
         <v>46308</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T31" s="9">
         <v>1</v>
@@ -3586,13 +3586,13 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46122.5514527662</v>
+        <v>46122.38478609954</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.827731122685</v>
+        <v>46133.66106445601</v>
       </c>
       <c r="D32" s="5">
-        <v>46133.82773260417</v>
+        <v>46133.6610659375</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3633,7 +3633,7 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
@@ -3647,13 +3647,13 @@
         <v>128</v>
       </c>
       <c r="B33" s="8">
-        <v>46122.55145796297</v>
+        <v>46122.384791296296</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.827786875</v>
+        <v>46133.66112020833</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.82778807871</v>
+        <v>46133.661121412035</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>129</v>
@@ -3694,7 +3694,7 @@
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46122.55146299768</v>
+        <v>46122.38479633102</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.82776796297</v>
+        <v>46133.6611012963</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.827769131945</v>
+        <v>46133.66110246528</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3755,7 +3755,7 @@
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3769,13 +3769,13 @@
         <v>134</v>
       </c>
       <c r="B35" s="8">
-        <v>46122.55146795139</v>
+        <v>46122.38480128472</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.66687207176</v>
+        <v>46181.50020540509</v>
       </c>
       <c r="D35" s="8">
-        <v>46214.17760775463</v>
+        <v>46214.01094108797</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>135</v>
@@ -3834,13 +3834,13 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46122.551472974534</v>
+        <v>46122.38480630787</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.66681767361</v>
+        <v>46181.50015100694</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.66681946759</v>
+        <v>46181.50015280093</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3881,7 +3881,7 @@
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="8">
-        <v>46122.55152253472</v>
+        <v>46122.384855868055</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.66685679398</v>
+        <v>46181.50019012731</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.66685818287</v>
+        <v>46181.5001915162</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>143</v>
@@ -3942,7 +3942,7 @@
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
@@ -3956,13 +3956,13 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46122.55152891204</v>
+        <v>46122.384862245366</v>
       </c>
       <c r="C38" s="5">
-        <v>46154.867667812505</v>
+        <v>46154.70100114583</v>
       </c>
       <c r="D38" s="5">
-        <v>46189.172213136575</v>
+        <v>46189.00554646991</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -4021,13 +4021,13 @@
         <v>148</v>
       </c>
       <c r="B39" s="8">
-        <v>46122.5515340625</v>
+        <v>46122.384867395835</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.86751693287</v>
+        <v>46154.70085026621</v>
       </c>
       <c r="D39" s="8">
-        <v>46154.86751927083</v>
+        <v>46154.70085260417</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>86</v>
@@ -4076,13 +4076,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46122.55153844907</v>
+        <v>46122.38487178241</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.867576273144</v>
+        <v>46154.70090960649</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.867577453704</v>
+        <v>46154.70091078704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -4131,13 +4131,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46122.574933449076</v>
+        <v>46122.40826678241</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.666767002316</v>
+        <v>46181.500100335645</v>
       </c>
       <c r="D41" s="8">
-        <v>46221.20228239583</v>
+        <v>46221.03561572917</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -4196,13 +4196,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46122.575920972224</v>
+        <v>46122.40925430556</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.66670739584</v>
+        <v>46181.500040729166</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.66670855324</v>
+        <v>46181.500041886575</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>89</v>
@@ -4251,13 +4251,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46122.57608475695</v>
+        <v>46122.409418090276</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.666752812496</v>
+        <v>46181.50008614583</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.666754351856</v>
+        <v>46181.500087685185</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4306,13 +4306,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46122.57501438657</v>
+        <v>46122.40834771991</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.666958472226</v>
+        <v>46181.500291805554</v>
       </c>
       <c r="D44" s="5">
-        <v>46239.17159243056</v>
+        <v>46239.00492576389</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4371,13 +4371,13 @@
         <v>166</v>
       </c>
       <c r="B45" s="8">
-        <v>46122.57922111111</v>
+        <v>46122.41255444444</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.666901516204</v>
+        <v>46181.50023484953</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.66690306713</v>
+        <v>46181.50023640046</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>95</v>
@@ -4426,13 +4426,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46122.57949202546</v>
+        <v>46122.4128253588</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.66694322917</v>
+        <v>46181.500276562496</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.66694460648</v>
+        <v>46181.50027793982</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4481,13 +4481,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46125.529618217595</v>
+        <v>46125.362951550924</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.66722120371</v>
+        <v>46181.50055453704</v>
       </c>
       <c r="D47" s="8">
-        <v>46228.07776863426</v>
+        <v>46227.91110196759</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4546,13 +4546,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46125.52977997685</v>
+        <v>46125.36311331019</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.66715732639</v>
+        <v>46181.50049065972</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.66715912037</v>
+        <v>46181.500492453706</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>92</v>
@@ -4601,13 +4601,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46125.52991815972</v>
+        <v>46125.36325149305</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.66720412037</v>
+        <v>46181.5005374537</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.66720563658</v>
+        <v>46181.50053896991</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4656,13 +4656,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46122.55120855324</v>
+        <v>46122.384541886575</v>
       </c>
       <c r="C50" s="5">
-        <v>46195.5074512963</v>
+        <v>46195.34078462963</v>
       </c>
       <c r="D50" s="5">
-        <v>46195.50756488426</v>
+        <v>46195.34089821759</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4709,13 +4709,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46122.55154344907</v>
+        <v>46122.38487678241</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.79584481481</v>
+        <v>46133.62917814815</v>
       </c>
       <c r="D51" s="8">
-        <v>46143.171145879634</v>
+        <v>46143.00447921296</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4774,13 +4774,13 @@
         <v>187</v>
       </c>
       <c r="B52" s="5">
-        <v>46122.551548993055</v>
+        <v>46122.38488232639</v>
       </c>
       <c r="C52" s="5">
-        <v>46134.79240423611</v>
+        <v>46134.62573756944</v>
       </c>
       <c r="D52" s="5">
-        <v>46198.18781711806</v>
+        <v>46198.021150451386</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4839,13 +4839,13 @@
         <v>191</v>
       </c>
       <c r="B53" s="8">
-        <v>46122.55155721065</v>
+        <v>46122.38489054398</v>
       </c>
       <c r="C53" s="8">
-        <v>46134.79245146991</v>
+        <v>46134.62578480324</v>
       </c>
       <c r="D53" s="8">
-        <v>46199.18371805556</v>
+        <v>46199.01705138889</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>82</v>
@@ -4902,13 +4902,13 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46122.55156568287</v>
+        <v>46122.38489901621</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.50761325231</v>
+        <v>46195.34094658565</v>
       </c>
       <c r="D54" s="5">
-        <v>46196.76907818287</v>
+        <v>46196.6024115162</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4951,7 +4951,7 @@
         <v>46316</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -4965,13 +4965,13 @@
         <v>198</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.603622118055</v>
+        <v>46125.43695545139</v>
       </c>
       <c r="C55" s="8">
-        <v>46196.76904752315</v>
+        <v>46196.60238085648</v>
       </c>
       <c r="D55" s="8">
-        <v>46196.7690521412</v>
+        <v>46196.602385474536</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>199</v>
@@ -5018,13 +5018,13 @@
         <v>201</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.60367094907</v>
+        <v>46125.43700428241</v>
       </c>
       <c r="C56" s="5">
-        <v>46196.769048449074</v>
+        <v>46196.6023817824</v>
       </c>
       <c r="D56" s="5">
-        <v>46223.607461875</v>
+        <v>46223.440795208335</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>199</v>
@@ -5071,13 +5071,13 @@
         <v>202</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.60371951389</v>
+        <v>46125.43705284722</v>
       </c>
       <c r="C57" s="8">
-        <v>46196.76904929398</v>
+        <v>46196.602382627316</v>
       </c>
       <c r="D57" s="8">
-        <v>46196.76905283565</v>
+        <v>46196.60238616898</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>199</v>
@@ -5124,13 +5124,13 @@
         <v>203</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.60376462963</v>
+        <v>46125.43709796296</v>
       </c>
       <c r="C58" s="5">
-        <v>46196.769050069444</v>
+        <v>46196.60238340277</v>
       </c>
       <c r="D58" s="5">
-        <v>46196.76905314815</v>
+        <v>46196.60238648148</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>199</v>
@@ -5177,13 +5177,13 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.60381739584</v>
+        <v>46125.437150729165</v>
       </c>
       <c r="C59" s="8">
-        <v>46196.76905077546</v>
+        <v>46196.602384108795</v>
       </c>
       <c r="D59" s="8">
-        <v>46196.76905349537</v>
+        <v>46196.6023868287</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5230,13 +5230,13 @@
         <v>205</v>
       </c>
       <c r="B60" s="5">
-        <v>46122.551569710646</v>
+        <v>46122.38490304398</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.6677724537</v>
+        <v>46181.501105787036</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.66785324074</v>
+        <v>46181.501186574074</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>206</v>
@@ -5279,13 +5279,13 @@
         <v>208</v>
       </c>
       <c r="B61" s="8">
-        <v>46122.55157321759</v>
+        <v>46122.38490655093</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.667378032405</v>
+        <v>46181.50071136574</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.66739524306</v>
+        <v>46181.500728576386</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>209</v>
@@ -5344,13 +5344,13 @@
         <v>213</v>
       </c>
       <c r="B62" s="5">
-        <v>46122.58491638889</v>
+        <v>46122.41824972222</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.667413206014</v>
+        <v>46181.50074653935</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.667429016205</v>
+        <v>46181.50076234953</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>214</v>
@@ -5409,13 +5409,13 @@
         <v>216</v>
       </c>
       <c r="B63" s="8">
-        <v>46125.53102658565</v>
+        <v>46125.36435991898</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.667430127316</v>
+        <v>46181.500763460645</v>
       </c>
       <c r="D63" s="8">
-        <v>46221.202281238424</v>
+        <v>46221.03561457176</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>217</v>
@@ -5474,13 +5474,13 @@
         <v>219</v>
       </c>
       <c r="B64" s="5">
-        <v>46122.55157846065</v>
+        <v>46122.38491179398</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.66775587963</v>
+        <v>46181.501089212965</v>
       </c>
       <c r="D64" s="5">
-        <v>46227.182452106485</v>
+        <v>46227.01578543981</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>215</v>
@@ -5539,13 +5539,13 @@
         <v>224</v>
       </c>
       <c r="B65" s="8">
-        <v>46122.551583831024</v>
+        <v>46122.38491716435</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.6687946875</v>
+        <v>46181.50212802083</v>
       </c>
       <c r="D65" s="8">
-        <v>46181.66890770833</v>
+        <v>46181.50224104167</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>225</v>
@@ -5588,13 +5588,13 @@
         <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46122.55158688658</v>
+        <v>46122.384920219905</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.666093576394</v>
+        <v>46181.49942690972</v>
       </c>
       <c r="D66" s="5">
-        <v>46238.1884728125</v>
+        <v>46238.02180614583</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>228</v>
@@ -5653,13 +5653,13 @@
         <v>232</v>
       </c>
       <c r="B67" s="8">
-        <v>46122.55159185185</v>
+        <v>46122.384925185186</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.6661986574</v>
+        <v>46181.49953199074</v>
       </c>
       <c r="D67" s="8">
-        <v>46256.20327105324</v>
+        <v>46256.03660438657</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>233</v>
@@ -5718,13 +5718,13 @@
         <v>235</v>
       </c>
       <c r="B68" s="5">
-        <v>46125.595811921296</v>
+        <v>46125.42914525463</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.66807699074</v>
+        <v>46181.501410324076</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.66807884259</v>
+        <v>46181.50141217593</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>236</v>
@@ -5773,13 +5773,13 @@
         <v>239</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.59610047453</v>
+        <v>46125.42943380787</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.66808581019</v>
+        <v>46181.50141914352</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.66808728009</v>
+        <v>46181.50142061342</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>199</v>
@@ -5828,13 +5828,13 @@
         <v>240</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.59621038195</v>
+        <v>46125.429543715276</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.66815399306</v>
+        <v>46181.501487326386</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.66815550926</v>
+        <v>46181.501488842594</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>199</v>
@@ -5883,13 +5883,13 @@
         <v>241</v>
       </c>
       <c r="B71" s="8">
-        <v>46125.59625472222</v>
+        <v>46125.42958805556</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.668166689815</v>
+        <v>46181.50150002315</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.66816819445</v>
+        <v>46181.501501527775</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>199</v>
@@ -5938,13 +5938,13 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.59629915509</v>
+        <v>46125.42963248843</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.66817956018</v>
+        <v>46181.50151289352</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.66818078703</v>
+        <v>46181.50151412037</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>199</v>
@@ -5993,13 +5993,13 @@
         <v>243</v>
       </c>
       <c r="B73" s="8">
-        <v>46122.55159751157</v>
+        <v>46122.384930844906</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.66878061343</v>
+        <v>46181.50211394676</v>
       </c>
       <c r="D73" s="8">
-        <v>46252.20192400463</v>
+        <v>46252.035257337964</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>244</v>
@@ -6058,13 +6058,13 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46125.59648849537</v>
+        <v>46125.4298218287</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.668651921296</v>
+        <v>46181.501985254625</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.6686533912</v>
+        <v>46181.501986724536</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>199</v>
@@ -6113,13 +6113,13 @@
         <v>248</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.59661854166</v>
+        <v>46125.429951875005</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.66866650463</v>
+        <v>46181.50199983796</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.66866782407</v>
+        <v>46181.50200115741</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>199</v>
@@ -6168,13 +6168,13 @@
         <v>250</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.596668750004</v>
+        <v>46125.43000208333</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.66867587963</v>
+        <v>46181.50200921296</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.66867745371</v>
+        <v>46181.50201078704</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>199</v>
@@ -6223,13 +6223,13 @@
         <v>251</v>
       </c>
       <c r="B77" s="8">
-        <v>46125.59671550926</v>
+        <v>46125.430048842594</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.668685625</v>
+        <v>46181.50201895833</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.668687060184</v>
+        <v>46181.50202039352</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>199</v>
@@ -6278,13 +6278,13 @@
         <v>253</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.59675546296</v>
+        <v>46125.430088796296</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.66870385417</v>
+        <v>46181.5020371875</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.66870502315</v>
+        <v>46181.502038356484</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>199</v>
@@ -6333,13 +6333,13 @@
         <v>254</v>
       </c>
       <c r="B79" s="8">
-        <v>46122.55160357639</v>
+        <v>46122.38493690972</v>
       </c>
       <c r="C79" s="8">
-        <v>46195.563125636574</v>
+        <v>46195.3964589699</v>
       </c>
       <c r="D79" s="8">
-        <v>46195.563290335645</v>
+        <v>46195.39662366898</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>206</v>
@@ -6386,13 +6386,13 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46122.55160679398</v>
+        <v>46122.38494012732</v>
       </c>
       <c r="C80" s="5">
-        <v>46195.563269363425</v>
+        <v>46195.39660269676</v>
       </c>
       <c r="D80" s="5">
-        <v>46240.605594189816</v>
+        <v>46240.43892752315</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>257</v>
@@ -6451,13 +6451,13 @@
         <v>259</v>
       </c>
       <c r="B81" s="8">
-        <v>46122.551612256946</v>
+        <v>46122.38494559028</v>
       </c>
       <c r="C81" s="8">
-        <v>46195.50751318287</v>
+        <v>46195.34084651621</v>
       </c>
       <c r="D81" s="8">
-        <v>46195.50753130787</v>
+        <v>46195.3408646412</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>260</v>
@@ -6502,7 +6502,7 @@
         <v>46267</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>
@@ -6516,13 +6516,13 @@
         <v>261</v>
       </c>
       <c r="B82" s="5">
-        <v>46122.55161756944</v>
+        <v>46122.38495090278</v>
       </c>
       <c r="C82" s="5">
-        <v>46195.50751851852</v>
+        <v>46195.340851851855</v>
       </c>
       <c r="D82" s="5">
-        <v>46195.50753259259</v>
+        <v>46195.34086592593</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>262</v>
@@ -6567,7 +6567,7 @@
         <v>46310</v>
       </c>
       <c r="S82" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6581,13 +6581,13 @@
         <v>263</v>
       </c>
       <c r="B83" s="8">
-        <v>46122.55162288195</v>
+        <v>46122.384956215275</v>
       </c>
       <c r="C83" s="8">
-        <v>46195.507523437496</v>
+        <v>46195.34085677083</v>
       </c>
       <c r="D83" s="8">
-        <v>46195.507539479164</v>
+        <v>46195.3408728125</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>264</v>
@@ -6646,13 +6646,13 @@
         <v>265</v>
       </c>
       <c r="B84" s="5">
-        <v>46122.59399163195</v>
+        <v>46122.427324965276</v>
       </c>
       <c r="C84" s="5">
-        <v>46193.93315311342</v>
+        <v>46193.76648644676</v>
       </c>
       <c r="D84" s="5">
-        <v>46241.18852804398</v>
+        <v>46241.02186137732</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>266</v>
@@ -6711,13 +6711,13 @@
         <v>268</v>
       </c>
       <c r="B85" s="8">
-        <v>46122.551628182875</v>
+        <v>46122.3849615162</v>
       </c>
       <c r="C85" s="8">
-        <v>46195.5630599537</v>
+        <v>46195.39639328704</v>
       </c>
       <c r="D85" s="8">
-        <v>46228.07806180556</v>
+        <v>46227.911395138886</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>269</v>
@@ -6764,13 +6764,13 @@
         <v>271</v>
       </c>
       <c r="B86" s="5">
-        <v>46122.55163158565</v>
+        <v>46122.38496491898</v>
       </c>
       <c r="C86" s="5">
-        <v>46195.50768850694</v>
+        <v>46195.34102184028</v>
       </c>
       <c r="D86" s="5">
-        <v>46223.60779484954</v>
+        <v>46223.441128182865</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>272</v>
@@ -6815,7 +6815,7 @@
         <v>46279</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -6829,13 +6829,13 @@
         <v>274</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.5974969213</v>
+        <v>46125.43083025463</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.76791707176</v>
+        <v>46196.60125040509</v>
       </c>
       <c r="D87" s="8">
-        <v>46223.60698247685</v>
+        <v>46223.440315810185</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>199</v>
@@ -6884,13 +6884,13 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46125.59754570602</v>
+        <v>46125.430879039355</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.76795405093</v>
+        <v>46196.601287384256</v>
       </c>
       <c r="D88" s="5">
-        <v>46223.60697355324</v>
+        <v>46223.44030688658</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>199</v>
@@ -6939,13 +6939,13 @@
         <v>277</v>
       </c>
       <c r="B89" s="8">
-        <v>46125.59760710648</v>
+        <v>46125.430940439815</v>
       </c>
       <c r="C89" s="8">
-        <v>46196.767928217596</v>
+        <v>46196.601261550924</v>
       </c>
       <c r="D89" s="8">
-        <v>46223.60697</v>
+        <v>46223.44030333334</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>199</v>
@@ -6994,13 +6994,13 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46125.59765891204</v>
+        <v>46125.43099224537</v>
       </c>
       <c r="C90" s="5">
-        <v>46196.76794651621</v>
+        <v>46196.601279849536</v>
       </c>
       <c r="D90" s="5">
-        <v>46223.60696642361</v>
+        <v>46223.44029975694</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>199</v>
@@ -7049,13 +7049,13 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.597703391206</v>
+        <v>46125.431036724534</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.76794100694</v>
+        <v>46196.60127434028</v>
       </c>
       <c r="D91" s="8">
-        <v>46223.606961412035</v>
+        <v>46223.44029474537</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>199</v>
@@ -7104,13 +7104,13 @@
         <v>280</v>
       </c>
       <c r="B92" s="5">
-        <v>46122.55170659722</v>
+        <v>46122.38503993055</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.76755512731</v>
+        <v>46196.60088846065</v>
       </c>
       <c r="D92" s="5">
-        <v>46237.53492259259</v>
+        <v>46237.368255925925</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>
@@ -7155,7 +7155,7 @@
         <v>46282</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -7169,13 +7169,13 @@
         <v>282</v>
       </c>
       <c r="B93" s="8">
-        <v>46125.59982741898</v>
+        <v>46125.43316075232</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.76800195602</v>
+        <v>46196.60133528935</v>
       </c>
       <c r="D93" s="8">
-        <v>46223.60708418982</v>
+        <v>46223.44041752315</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>199</v>
@@ -7224,13 +7224,13 @@
         <v>285</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.599890833335</v>
+        <v>46125.43322416667</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.768023020835</v>
+        <v>46196.601356354164</v>
       </c>
       <c r="D94" s="5">
-        <v>46223.60707991898</v>
+        <v>46223.44041325232</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>199</v>
@@ -7279,13 +7279,13 @@
         <v>287</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.59993134259</v>
+        <v>46125.43326467593</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.76801494213</v>
+        <v>46196.601348275464</v>
       </c>
       <c r="D95" s="8">
-        <v>46223.60707583334</v>
+        <v>46223.440409166666</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>199</v>
@@ -7334,13 +7334,13 @@
         <v>288</v>
       </c>
       <c r="B96" s="5">
-        <v>46125.59996929398</v>
+        <v>46125.433302627316</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.76805109954</v>
+        <v>46196.60138443287</v>
       </c>
       <c r="D96" s="5">
-        <v>46223.607072060186</v>
+        <v>46223.440405393514</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>199</v>
@@ -7389,13 +7389,13 @@
         <v>289</v>
       </c>
       <c r="B97" s="8">
-        <v>46125.6000115162</v>
+        <v>46125.43334484954</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.76805706018</v>
+        <v>46196.60139039352</v>
       </c>
       <c r="D97" s="8">
-        <v>46223.607066192126</v>
+        <v>46223.44039952546</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>199</v>
@@ -7444,13 +7444,13 @@
         <v>290</v>
       </c>
       <c r="B98" s="5">
-        <v>46122.55164413195</v>
+        <v>46122.38497746528</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.76839824074</v>
+        <v>46196.601731574076</v>
       </c>
       <c r="D98" s="5">
-        <v>46228.10704425926</v>
+        <v>46227.94037759259</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>291</v>
@@ -7495,7 +7495,7 @@
         <v>46288</v>
       </c>
       <c r="S98" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T98" s="6">
         <v>1</v>
@@ -7509,13 +7509,13 @@
         <v>293</v>
       </c>
       <c r="B99" s="8">
-        <v>46125.599162743056</v>
+        <v>46125.43249607639</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.76818966435</v>
+        <v>46196.601522997684</v>
       </c>
       <c r="D99" s="8">
-        <v>46223.60720636574</v>
+        <v>46223.44053969908</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>199</v>
@@ -7564,13 +7564,13 @@
         <v>296</v>
       </c>
       <c r="B100" s="5">
-        <v>46125.599302511575</v>
+        <v>46125.4326358449</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.76820421296</v>
+        <v>46196.601537546296</v>
       </c>
       <c r="D100" s="5">
-        <v>46223.60720247685</v>
+        <v>46223.44053581019</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>199</v>
@@ -7619,13 +7619,13 @@
         <v>297</v>
       </c>
       <c r="B101" s="8">
-        <v>46125.59934644676</v>
+        <v>46125.43267978009</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.768375949076</v>
+        <v>46196.601709282404</v>
       </c>
       <c r="D101" s="8">
-        <v>46223.60719819444</v>
+        <v>46223.440531527776</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>199</v>
@@ -7674,13 +7674,13 @@
         <v>298</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.59938857639</v>
+        <v>46125.43272190972</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.76837696759</v>
+        <v>46196.60171030092</v>
       </c>
       <c r="D102" s="5">
-        <v>46223.60719417824</v>
+        <v>46223.44052751157</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>199</v>
@@ -7729,13 +7729,13 @@
         <v>299</v>
       </c>
       <c r="B103" s="8">
-        <v>46125.59943094908</v>
+        <v>46125.43276428241</v>
       </c>
       <c r="C103" s="8">
-        <v>46196.76837790509</v>
+        <v>46196.60171123843</v>
       </c>
       <c r="D103" s="8">
-        <v>46223.60718841435</v>
+        <v>46223.44052174769</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>199</v>
@@ -7784,13 +7784,13 @@
         <v>300</v>
       </c>
       <c r="B104" s="5">
-        <v>46122.551650995374</v>
+        <v>46122.3849843287</v>
       </c>
       <c r="C104" s="5">
-        <v>46196.76854788195</v>
+        <v>46196.601881215276</v>
       </c>
       <c r="D104" s="5">
-        <v>46237.53494261574</v>
+        <v>46237.36827594908</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>301</v>
@@ -7835,7 +7835,7 @@
         <v>46293</v>
       </c>
       <c r="S104" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>
@@ -7849,13 +7849,13 @@
         <v>302</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.59953013889</v>
+        <v>46125.43286347222</v>
       </c>
       <c r="C105" s="8">
-        <v>46196.76852783565</v>
+        <v>46196.60186116898</v>
       </c>
       <c r="D105" s="8">
-        <v>46223.60731153935</v>
+        <v>46223.44064487268</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>199</v>
@@ -7904,13 +7904,13 @@
         <v>304</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.59961423611</v>
+        <v>46125.43294756944</v>
       </c>
       <c r="C106" s="5">
-        <v>46196.76846329861</v>
+        <v>46196.60179663195</v>
       </c>
       <c r="D106" s="5">
-        <v>46223.60730783565</v>
+        <v>46223.440641168985</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>199</v>
@@ -7959,13 +7959,13 @@
         <v>305</v>
       </c>
       <c r="B107" s="8">
-        <v>46125.599654317135</v>
+        <v>46125.43298765046</v>
       </c>
       <c r="C107" s="8">
-        <v>46196.768528796296</v>
+        <v>46196.601862129624</v>
       </c>
       <c r="D107" s="8">
-        <v>46223.60730394676</v>
+        <v>46223.44063728009</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>199</v>
@@ -8014,13 +8014,13 @@
         <v>306</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.59957065972</v>
+        <v>46125.43290399306</v>
       </c>
       <c r="C108" s="5">
-        <v>46196.768529548615</v>
+        <v>46196.601862881944</v>
       </c>
       <c r="D108" s="5">
-        <v>46223.607299675925</v>
+        <v>46223.44063300926</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>199</v>
@@ -8069,13 +8069,13 @@
         <v>307</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.59969711806</v>
+        <v>46125.433030451386</v>
       </c>
       <c r="C109" s="8">
-        <v>46196.7685304051</v>
+        <v>46196.601863738426</v>
       </c>
       <c r="D109" s="8">
-        <v>46223.60729373843</v>
+        <v>46223.44062707176</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>199</v>
@@ -8124,13 +8124,13 @@
         <v>308</v>
       </c>
       <c r="B110" s="5">
-        <v>46122.55163725694</v>
+        <v>46122.38497059028</v>
       </c>
       <c r="C110" s="5">
-        <v>46196.76866755787</v>
+        <v>46196.6020008912</v>
       </c>
       <c r="D110" s="5">
-        <v>46223.607779618054</v>
+        <v>46223.44111295139</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>309</v>
@@ -8175,7 +8175,7 @@
         <v>46314</v>
       </c>
       <c r="S110" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T110" s="6">
         <v>1</v>
@@ -8189,13 +8189,13 @@
         <v>310</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.59780210648</v>
+        <v>46125.431135439816</v>
       </c>
       <c r="C111" s="8">
-        <v>46196.76864902778</v>
+        <v>46196.60198236111</v>
       </c>
       <c r="D111" s="8">
-        <v>46223.607408310185</v>
+        <v>46223.44074164351</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>199</v>
@@ -8244,13 +8244,13 @@
         <v>313</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.597836932866</v>
+        <v>46125.43117026621</v>
       </c>
       <c r="C112" s="5">
-        <v>46196.76865</v>
+        <v>46196.601983333334</v>
       </c>
       <c r="D112" s="5">
-        <v>46223.60740443287</v>
+        <v>46223.4407377662</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>199</v>
@@ -8299,13 +8299,13 @@
         <v>314</v>
       </c>
       <c r="B113" s="8">
-        <v>46125.5979208912</v>
+        <v>46125.43125422453</v>
       </c>
       <c r="C113" s="8">
-        <v>46196.76865077546</v>
+        <v>46196.6019841088</v>
       </c>
       <c r="D113" s="8">
-        <v>46223.607400532404</v>
+        <v>46223.44073386574</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>199</v>
@@ -8354,13 +8354,13 @@
         <v>315</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.59788087963</v>
+        <v>46125.431214212964</v>
       </c>
       <c r="C114" s="5">
-        <v>46196.768651527775</v>
+        <v>46196.60198486111</v>
       </c>
       <c r="D114" s="5">
-        <v>46223.60739668981</v>
+        <v>46223.44073002315</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>199</v>
@@ -8409,13 +8409,13 @@
         <v>316</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.597965023146</v>
+        <v>46125.43129835648</v>
       </c>
       <c r="C115" s="8">
-        <v>46196.768652314815</v>
+        <v>46196.60198564814</v>
       </c>
       <c r="D115" s="8">
-        <v>46223.60739046296</v>
+        <v>46223.440723796295</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>199</v>
@@ -8464,13 +8464,13 @@
         <v>317</v>
       </c>
       <c r="B116" s="5">
-        <v>46122.55172043982</v>
+        <v>46122.38505377315</v>
       </c>
       <c r="C116" s="5">
-        <v>46196.76877224537</v>
+        <v>46196.6021055787</v>
       </c>
       <c r="D116" s="5">
-        <v>46237.53496467593</v>
+        <v>46237.368298009256</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>318</v>
@@ -8515,7 +8515,7 @@
         <v>46315</v>
       </c>
       <c r="S116" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T116" s="6">
         <v>1</v>
@@ -8529,13 +8529,13 @@
         <v>319</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.60038253472</v>
+        <v>46125.43371586806</v>
       </c>
       <c r="C117" s="8">
-        <v>46196.76875258102</v>
+        <v>46196.602085914354</v>
       </c>
       <c r="D117" s="8">
-        <v>46223.60758443287</v>
+        <v>46223.4409177662</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>199</v>
@@ -8582,13 +8582,13 @@
         <v>321</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.60043012731</v>
+        <v>46125.43376346065</v>
       </c>
       <c r="C118" s="5">
-        <v>46223.60745270833</v>
+        <v>46223.44078604167</v>
       </c>
       <c r="D118" s="5">
-        <v>46223.60758005787</v>
+        <v>46223.440913391205</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>199</v>
@@ -8635,13 +8635,13 @@
         <v>322</v>
       </c>
       <c r="B119" s="8">
-        <v>46125.60047290509</v>
+        <v>46125.43380623843</v>
       </c>
       <c r="C119" s="8">
-        <v>46196.768754178236</v>
+        <v>46196.60208751158</v>
       </c>
       <c r="D119" s="8">
-        <v>46223.607575752314</v>
+        <v>46223.44090908565</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>199</v>
@@ -8688,13 +8688,13 @@
         <v>323</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.600514074074</v>
+        <v>46125.4338474074</v>
       </c>
       <c r="C120" s="5">
-        <v>46196.768754930556</v>
+        <v>46196.602088263884</v>
       </c>
       <c r="D120" s="5">
-        <v>46223.607571597226</v>
+        <v>46223.440904930554</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>199</v>
@@ -8741,13 +8741,13 @@
         <v>324</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.60055859954</v>
+        <v>46125.43389193287</v>
       </c>
       <c r="C121" s="8">
-        <v>46196.7687558912</v>
+        <v>46196.602089224536</v>
       </c>
       <c r="D121" s="8">
-        <v>46223.60756553241</v>
+        <v>46223.44089886574</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>199</v>
@@ -8794,13 +8794,13 @@
         <v>325</v>
       </c>
       <c r="B122" s="5">
-        <v>46122.55172986111</v>
+        <v>46122.385063194444</v>
       </c>
       <c r="C122" s="5">
-        <v>46196.76917457176</v>
+        <v>46196.60250790509</v>
       </c>
       <c r="D122" s="5">
-        <v>46223.60776988426</v>
+        <v>46223.44110321759</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>326</v>
@@ -8845,7 +8845,7 @@
         <v>46317</v>
       </c>
       <c r="S122" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T122" s="6">
         <v>1</v>
@@ -8859,13 +8859,13 @@
         <v>328</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.60064416667</v>
+        <v>46125.4339775</v>
       </c>
       <c r="C123" s="8">
-        <v>46196.76915099537</v>
+        <v>46196.6024843287</v>
       </c>
       <c r="D123" s="8">
-        <v>46223.607680601854</v>
+        <v>46223.44101393518</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>199</v>
@@ -8912,13 +8912,13 @@
         <v>330</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.60068740741</v>
+        <v>46125.43402074074</v>
       </c>
       <c r="C124" s="5">
-        <v>46196.76915237268</v>
+        <v>46196.60248570602</v>
       </c>
       <c r="D124" s="5">
-        <v>46223.60767706019</v>
+        <v>46223.44101039352</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>199</v>
@@ -8965,13 +8965,13 @@
         <v>331</v>
       </c>
       <c r="B125" s="8">
-        <v>46125.60073844907</v>
+        <v>46125.43407178241</v>
       </c>
       <c r="C125" s="8">
-        <v>46196.76915341435</v>
+        <v>46196.60248674768</v>
       </c>
       <c r="D125" s="8">
-        <v>46223.607672812504</v>
+        <v>46223.44100614583</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>199</v>
@@ -9018,13 +9018,13 @@
         <v>332</v>
       </c>
       <c r="B126" s="5">
-        <v>46125.60077622686</v>
+        <v>46125.434109560185</v>
       </c>
       <c r="C126" s="5">
-        <v>46196.76915438657</v>
+        <v>46196.60248771991</v>
       </c>
       <c r="D126" s="5">
-        <v>46223.6076684375</v>
+        <v>46223.44100177083</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>199</v>
@@ -9071,13 +9071,13 @@
         <v>333</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.600829143514</v>
+        <v>46125.43416247686</v>
       </c>
       <c r="C127" s="8">
-        <v>46196.769155358794</v>
+        <v>46196.60248869213</v>
       </c>
       <c r="D127" s="8">
-        <v>46223.60766289352</v>
+        <v>46223.440996226855</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>199</v>
@@ -9124,13 +9124,13 @@
         <v>334</v>
       </c>
       <c r="B128" s="5">
-        <v>46122.5517350463</v>
+        <v>46122.38506837963</v>
       </c>
       <c r="C128" s="5">
-        <v>46195.56317517361</v>
+        <v>46195.39650850694</v>
       </c>
       <c r="D128" s="5">
-        <v>46196.76960409722</v>
+        <v>46196.60293743055</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>335</v>
@@ -9177,13 +9177,13 @@
         <v>337</v>
       </c>
       <c r="B129" s="8">
-        <v>46122.5517390625</v>
+        <v>46122.38507239583</v>
       </c>
       <c r="C129" s="8">
-        <v>46196.76936652778</v>
+        <v>46196.60269986111</v>
       </c>
       <c r="D129" s="8">
-        <v>46240.60562268519</v>
+        <v>46240.43895601852</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>338</v>
@@ -9228,7 +9228,7 @@
         <v>46318</v>
       </c>
       <c r="S129" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T129" s="9">
         <v>1</v>
@@ -9242,13 +9242,13 @@
         <v>342</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.60093731481</v>
+        <v>46125.43427064815</v>
       </c>
       <c r="C130" s="5">
-        <v>46196.76934515046</v>
+        <v>46196.602678483796</v>
       </c>
       <c r="D130" s="5">
-        <v>46196.769350682865</v>
+        <v>46196.60268401621</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>199</v>
@@ -9295,13 +9295,13 @@
         <v>344</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.601380821754</v>
+        <v>46125.4347141551</v>
       </c>
       <c r="C131" s="8">
-        <v>46196.769346307876</v>
+        <v>46196.602679641204</v>
       </c>
       <c r="D131" s="8">
-        <v>46196.769351145835</v>
+        <v>46196.60268447916</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>199</v>
@@ -9348,13 +9348,13 @@
         <v>345</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.60142481481</v>
+        <v>46125.43475814815</v>
       </c>
       <c r="C132" s="5">
-        <v>46196.7693472338</v>
+        <v>46196.60268056713</v>
       </c>
       <c r="D132" s="5">
-        <v>46196.76935155093</v>
+        <v>46196.60268488426</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>199</v>
@@ -9401,13 +9401,13 @@
         <v>346</v>
       </c>
       <c r="B133" s="8">
-        <v>46125.60146085648</v>
+        <v>46125.434794189816</v>
       </c>
       <c r="C133" s="8">
-        <v>46196.769348125</v>
+        <v>46196.60268145833</v>
       </c>
       <c r="D133" s="8">
-        <v>46196.76935192129</v>
+        <v>46196.602685254635</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>199</v>
@@ -9454,13 +9454,13 @@
         <v>347</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.60150208333</v>
+        <v>46125.434835416665</v>
       </c>
       <c r="C134" s="5">
-        <v>46196.769348981485</v>
+        <v>46196.60268231481</v>
       </c>
       <c r="D134" s="5">
-        <v>46196.76935229167</v>
+        <v>46196.602685624996</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>199</v>
@@ -9507,13 +9507,13 @@
         <v>348</v>
       </c>
       <c r="B135" s="8">
-        <v>46122.55174383102</v>
+        <v>46122.38507716435</v>
       </c>
       <c r="C135" s="8">
-        <v>46196.769596921295</v>
+        <v>46196.60293025463</v>
       </c>
       <c r="D135" s="8">
-        <v>46228.10760070602</v>
+        <v>46227.94093403935</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>349</v>
@@ -9556,7 +9556,7 @@
         <v>46321</v>
       </c>
       <c r="S135" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T135" s="9">
         <v>1</v>
@@ -9570,13 +9570,13 @@
         <v>350</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.601086979164</v>
+        <v>46125.4344203125</v>
       </c>
       <c r="C136" s="5">
-        <v>46196.76947155093</v>
+        <v>46196.602804884256</v>
       </c>
       <c r="D136" s="5">
-        <v>46223.60837070602</v>
+        <v>46223.44170403935</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>199</v>
@@ -9623,13 +9623,13 @@
         <v>352</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.60115318287</v>
+        <v>46125.4344865162</v>
       </c>
       <c r="C137" s="8">
-        <v>46196.7695043287</v>
+        <v>46196.60283766204</v>
       </c>
       <c r="D137" s="8">
-        <v>46223.60836653935</v>
+        <v>46223.44169987268</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>199</v>
@@ -9676,13 +9676,13 @@
         <v>353</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.60120391204</v>
+        <v>46125.43453724537</v>
       </c>
       <c r="C138" s="5">
-        <v>46196.76950549769</v>
+        <v>46196.60283883102</v>
       </c>
       <c r="D138" s="5">
-        <v>46223.608362604165</v>
+        <v>46223.4416959375</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>199</v>
@@ -9729,13 +9729,13 @@
         <v>354</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.60125796296</v>
+        <v>46125.434591296296</v>
       </c>
       <c r="C139" s="8">
-        <v>46196.76950637731</v>
+        <v>46196.60283971065</v>
       </c>
       <c r="D139" s="8">
-        <v>46223.60835905092</v>
+        <v>46223.44169238426</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>199</v>
@@ -9782,13 +9782,13 @@
         <v>355</v>
       </c>
       <c r="B140" s="5">
-        <v>46125.601304282405</v>
+        <v>46125.43463761574</v>
       </c>
       <c r="C140" s="5">
-        <v>46196.76950730324</v>
+        <v>46196.60284063657</v>
       </c>
       <c r="D140" s="5">
-        <v>46223.60835267361</v>
+        <v>46223.44168600695</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>199</v>
@@ -9835,13 +9835,13 @@
         <v>356</v>
       </c>
       <c r="B141" s="8">
-        <v>46122.55174869213</v>
+        <v>46122.38508202546</v>
       </c>
       <c r="C141" s="8">
-        <v>46191.70598530093</v>
+        <v>46191.539318634255</v>
       </c>
       <c r="D141" s="8">
-        <v>46240.605638368055</v>
+        <v>46240.438971701384</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>357</v>
@@ -9884,7 +9884,7 @@
         <v>46322</v>
       </c>
       <c r="S141" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T141" s="9">
         <v>1</v>
@@ -9898,13 +9898,13 @@
         <v>358</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.60158650463</v>
+        <v>46125.434919837964</v>
       </c>
       <c r="C142" s="5">
-        <v>46196.76968462963</v>
+        <v>46196.60301796296</v>
       </c>
       <c r="D142" s="5">
-        <v>46196.76968989584</v>
+        <v>46196.60302322917</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>199</v>
@@ -9951,13 +9951,13 @@
         <v>360</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.60163133102</v>
+        <v>46125.43496466435</v>
       </c>
       <c r="C143" s="8">
-        <v>46196.76968585648</v>
+        <v>46196.60301918982</v>
       </c>
       <c r="D143" s="8">
-        <v>46196.7696903125</v>
+        <v>46196.60302364583</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>199</v>
@@ -10004,13 +10004,13 @@
         <v>361</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.60167016204</v>
+        <v>46125.43500349537</v>
       </c>
       <c r="C144" s="5">
-        <v>46196.7696866551</v>
+        <v>46196.603019988426</v>
       </c>
       <c r="D144" s="5">
-        <v>46196.769690706016</v>
+        <v>46196.60302403935</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>199</v>
@@ -10057,13 +10057,13 @@
         <v>363</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.60170435185</v>
+        <v>46125.43503768518</v>
       </c>
       <c r="C145" s="8">
-        <v>46196.769687395834</v>
+        <v>46196.60302072916</v>
       </c>
       <c r="D145" s="8">
-        <v>46196.76969114583</v>
+        <v>46196.60302447916</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>199</v>
@@ -10110,13 +10110,13 @@
         <v>364</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.60173947917</v>
+        <v>46125.4350728125</v>
       </c>
       <c r="C146" s="5">
-        <v>46196.769688113425</v>
+        <v>46196.60302144676</v>
       </c>
       <c r="D146" s="5">
-        <v>46196.76969164352</v>
+        <v>46196.60302497685</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>199</v>
@@ -10163,13 +10163,13 @@
         <v>365</v>
       </c>
       <c r="B147" s="8">
-        <v>46122.551753472224</v>
+        <v>46122.38508680556</v>
       </c>
       <c r="C147" s="8">
-        <v>46191.70604009259</v>
+        <v>46191.53937342593</v>
       </c>
       <c r="D147" s="8">
-        <v>46240.60565322917</v>
+        <v>46240.4389865625</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>366</v>
@@ -10212,7 +10212,7 @@
         <v>46323</v>
       </c>
       <c r="S147" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T147" s="9">
         <v>1</v>
@@ -10226,13 +10226,13 @@
         <v>368</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.60181555555</v>
+        <v>46125.43514888889</v>
       </c>
       <c r="C148" s="5">
-        <v>46196.76979265046</v>
+        <v>46196.60312598379</v>
       </c>
       <c r="D148" s="5">
-        <v>46196.76979569445</v>
+        <v>46196.603129027775</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>199</v>
@@ -10279,13 +10279,13 @@
         <v>369</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.60185690972</v>
+        <v>46125.43519024306</v>
       </c>
       <c r="C149" s="8">
-        <v>46196.76979356482</v>
+        <v>46196.603126898146</v>
       </c>
       <c r="D149" s="8">
-        <v>46196.76979614583</v>
+        <v>46196.60312947917</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>199</v>
@@ -10332,13 +10332,13 @@
         <v>370</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.601899490735</v>
+        <v>46125.43523282408</v>
       </c>
       <c r="C150" s="5">
-        <v>46196.769794224536</v>
+        <v>46196.60312755787</v>
       </c>
       <c r="D150" s="5">
-        <v>46196.76979648148</v>
+        <v>46196.603129814815</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>199</v>
@@ -10385,13 +10385,13 @@
         <v>371</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.60193935185</v>
+        <v>46125.43527268519</v>
       </c>
       <c r="C151" s="8">
-        <v>46196.76976476852</v>
+        <v>46196.603098101856</v>
       </c>
       <c r="D151" s="8">
-        <v>46196.769766875004</v>
+        <v>46196.60310020833</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>199</v>
@@ -10438,13 +10438,13 @@
         <v>372</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.60197710648</v>
+        <v>46125.43531043982</v>
       </c>
       <c r="C152" s="5">
-        <v>46196.76977206019</v>
+        <v>46196.603105393515</v>
       </c>
       <c r="D152" s="5">
-        <v>46196.76977370371</v>
+        <v>46196.60310703704</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>199</v>
@@ -10491,13 +10491,13 @@
         <v>373</v>
       </c>
       <c r="B153" s="8">
-        <v>46122.551758622685</v>
+        <v>46122.38509195602</v>
       </c>
       <c r="C153" s="8">
-        <v>46240.65384241898</v>
+        <v>46240.487175752314</v>
       </c>
       <c r="D153" s="8">
-        <v>46240.65385445602</v>
+        <v>46240.48718778935</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>374</v>
@@ -10544,13 +10544,13 @@
         <v>376</v>
       </c>
       <c r="B154" s="5">
-        <v>46122.55176134259</v>
+        <v>46122.38509467593</v>
       </c>
       <c r="C154" s="5">
-        <v>46240.65381834491</v>
+        <v>46240.487151678244</v>
       </c>
       <c r="D154" s="5">
-        <v>46240.65383614584</v>
+        <v>46240.487169479165</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>377</v>
@@ -10595,7 +10595,7 @@
         <v>46332</v>
       </c>
       <c r="S154" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T154" s="6">
         <v>1</v>
@@ -10609,13 +10609,13 @@
         <v>380</v>
       </c>
       <c r="B155" s="8">
-        <v>46122.55176609954</v>
+        <v>46122.38509943287</v>
       </c>
       <c r="C155" s="8">
-        <v>46240.65382724537</v>
+        <v>46240.487160578705</v>
       </c>
       <c r="D155" s="8">
-        <v>46240.65384380787</v>
+        <v>46240.4871771412</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>381</v>
@@ -10660,7 +10660,7 @@
         <v>46332</v>
       </c>
       <c r="S155" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T155" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -1844,13 +1844,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46122.38452245371</v>
+        <v>46122.55118912037</v>
       </c>
       <c r="C4" s="5">
-        <v>46128.426341053244</v>
+        <v>46128.59300771991</v>
       </c>
       <c r="D4" s="5">
-        <v>46157.93633454861</v>
+        <v>46158.10300121528</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1893,13 +1893,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46122.38467905093</v>
+        <v>46122.55134571759</v>
       </c>
       <c r="C5" s="8">
-        <v>46128.42632796297</v>
+        <v>46128.59299462963</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.70935505787</v>
+        <v>46133.876021724536</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1956,13 +1956,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46122.384682812495</v>
+        <v>46122.55134947917</v>
       </c>
       <c r="C6" s="5">
-        <v>46128.42601201389</v>
+        <v>46128.59267868055</v>
       </c>
       <c r="D6" s="5">
-        <v>46128.43715965278</v>
+        <v>46128.60382631945</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2019,13 +2019,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46122.38468587963</v>
+        <v>46122.551352546296</v>
       </c>
       <c r="C7" s="8">
-        <v>46128.42603200232</v>
+        <v>46128.59269866898</v>
       </c>
       <c r="D7" s="8">
-        <v>46161.460593807875</v>
+        <v>46161.62726047453</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2082,13 +2082,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46122.38468890046</v>
+        <v>46122.551355567135</v>
       </c>
       <c r="C8" s="5">
-        <v>46128.42605055556</v>
+        <v>46128.59271722222</v>
       </c>
       <c r="D8" s="5">
-        <v>46128.43733940972</v>
+        <v>46128.60400607639</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2145,13 +2145,13 @@
         <v>44</v>
       </c>
       <c r="B9" s="8">
-        <v>46122.384692719905</v>
+        <v>46122.551359386576</v>
       </c>
       <c r="C9" s="8">
-        <v>46128.4261833912</v>
+        <v>46128.592850057874</v>
       </c>
       <c r="D9" s="8">
-        <v>46156.66910643518</v>
+        <v>46156.83577310185</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>45</v>
@@ -2208,13 +2208,13 @@
         <v>47</v>
       </c>
       <c r="B10" s="5">
-        <v>46122.3845274537</v>
+        <v>46122.55119412037</v>
       </c>
       <c r="C10" s="5">
-        <v>46193.766136805556</v>
+        <v>46193.93280347223</v>
       </c>
       <c r="D10" s="5">
-        <v>46223.25695451389</v>
+        <v>46223.423621180555</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2261,13 +2261,13 @@
         <v>50</v>
       </c>
       <c r="B11" s="8">
-        <v>46122.384696504625</v>
+        <v>46122.5513631713</v>
       </c>
       <c r="C11" s="8">
-        <v>46128.43768854167</v>
+        <v>46128.60435520833</v>
       </c>
       <c r="D11" s="8">
-        <v>46192.80716136574</v>
+        <v>46192.97382803241</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>51</v>
@@ -2326,13 +2326,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46122.38470238426</v>
+        <v>46122.551369050925</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.43976447917</v>
+        <v>46128.60643114583</v>
       </c>
       <c r="D12" s="5">
-        <v>46192.80716146991</v>
+        <v>46192.97382813657</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2391,13 +2391,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46122.384708020836</v>
+        <v>46122.5513746875</v>
       </c>
       <c r="C13" s="8">
-        <v>46132.40405894676</v>
+        <v>46132.57072561343</v>
       </c>
       <c r="D13" s="8">
-        <v>46192.80716134259</v>
+        <v>46192.97382800926</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2456,13 +2456,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46122.38692751157</v>
+        <v>46122.553594178244</v>
       </c>
       <c r="C14" s="5">
-        <v>46128.44274908565</v>
+        <v>46128.60941575232</v>
       </c>
       <c r="D14" s="5">
-        <v>46136.03935251157</v>
+        <v>46136.20601917824</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2521,13 +2521,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46122.38453280093</v>
+        <v>46122.55119946759</v>
       </c>
       <c r="C15" s="8">
-        <v>46195.34056496528</v>
+        <v>46195.50723163194</v>
       </c>
       <c r="D15" s="8">
-        <v>46227.938021354166</v>
+        <v>46228.10468802083</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2574,13 +2574,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46122.38472188657</v>
+        <v>46122.55138855324</v>
       </c>
       <c r="C16" s="5">
-        <v>46128.44033724537</v>
+        <v>46128.60700391204</v>
       </c>
       <c r="D16" s="5">
-        <v>46133.0133283912</v>
+        <v>46133.17999505787</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2639,13 +2639,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46122.38472815973</v>
+        <v>46122.55139482639</v>
       </c>
       <c r="C17" s="8">
-        <v>46128.44034490741</v>
+        <v>46128.60701157407</v>
       </c>
       <c r="D17" s="8">
-        <v>46132.01554025463</v>
+        <v>46132.182206921294</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2704,13 +2704,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46122.38473373842</v>
+        <v>46122.55140040509</v>
       </c>
       <c r="C18" s="5">
-        <v>46195.340545046296</v>
+        <v>46195.50721171296</v>
       </c>
       <c r="D18" s="5">
-        <v>46223.43988759259</v>
+        <v>46223.606554259255</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2769,13 +2769,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="8">
-        <v>46122.384739375004</v>
+        <v>46122.55140604167</v>
       </c>
       <c r="C19" s="8">
-        <v>46181.499732384254</v>
+        <v>46181.666399050926</v>
       </c>
       <c r="D19" s="8">
-        <v>46223.43988416667</v>
+        <v>46223.606550833334</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>81</v>
@@ -2834,13 +2834,13 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46122.3847449537</v>
+        <v>46122.55141162037</v>
       </c>
       <c r="C20" s="5">
-        <v>46128.442831215274</v>
+        <v>46128.609497881946</v>
       </c>
       <c r="D20" s="5">
-        <v>46132.01553989583</v>
+        <v>46132.1822065625</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>64</v>
@@ -2899,13 +2899,13 @@
         <v>87</v>
       </c>
       <c r="B21" s="8">
-        <v>46122.39987912037</v>
+        <v>46122.566545787035</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.49969386574</v>
+        <v>46181.66636053241</v>
       </c>
       <c r="D21" s="8">
-        <v>46223.43988042824</v>
+        <v>46223.60654709491</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>88</v>
@@ -2964,13 +2964,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46122.39994855324</v>
+        <v>46122.56661521991</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.499709641204</v>
+        <v>46181.66637630787</v>
       </c>
       <c r="D22" s="5">
-        <v>46223.4398771875</v>
+        <v>46223.60654385417</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -3029,13 +3029,13 @@
         <v>93</v>
       </c>
       <c r="B23" s="8">
-        <v>46122.40619606481</v>
+        <v>46122.57286273148</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.4997655787</v>
+        <v>46181.66643224537</v>
       </c>
       <c r="D23" s="8">
-        <v>46223.43987166666</v>
+        <v>46223.60653833333</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>94</v>
@@ -3094,13 +3094,13 @@
         <v>96</v>
       </c>
       <c r="B24" s="5">
-        <v>46122.38453728009</v>
+        <v>46122.55120394676</v>
       </c>
       <c r="C24" s="5">
-        <v>46195.34067315972</v>
+        <v>46195.50733982639</v>
       </c>
       <c r="D24" s="5">
-        <v>46223.25843659722</v>
+        <v>46223.425103263886</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
@@ -3147,13 +3147,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46122.38475027778</v>
+        <v>46122.55141694444</v>
       </c>
       <c r="C25" s="8">
-        <v>46174.45950203703</v>
+        <v>46174.626168703704</v>
       </c>
       <c r="D25" s="8">
-        <v>46258.02963747685</v>
+        <v>46258.19630414352</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -3212,13 +3212,13 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46122.38475541667</v>
+        <v>46122.55142208333</v>
       </c>
       <c r="C26" s="5">
-        <v>46174.45658625</v>
+        <v>46174.62325291667</v>
       </c>
       <c r="D26" s="5">
-        <v>46174.456587824076</v>
+        <v>46174.62325449074</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -3273,13 +3273,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46122.38476032407</v>
+        <v>46122.55142699074</v>
       </c>
       <c r="C27" s="8">
-        <v>46174.45948622686</v>
+        <v>46174.626152893514</v>
       </c>
       <c r="D27" s="8">
-        <v>46174.45948762732</v>
+        <v>46174.62615429398</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -3334,13 +3334,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46122.38476556713</v>
+        <v>46122.5514322338</v>
       </c>
       <c r="C28" s="5">
-        <v>46195.340658553236</v>
+        <v>46195.50732521991</v>
       </c>
       <c r="D28" s="5">
-        <v>46195.545180127316</v>
+        <v>46195.71184679398</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3399,13 +3399,13 @@
         <v>116</v>
       </c>
       <c r="B29" s="8">
-        <v>46122.38477087963</v>
+        <v>46122.551437546295</v>
       </c>
       <c r="C29" s="8">
-        <v>46195.54471607639</v>
+        <v>46195.71138274306</v>
       </c>
       <c r="D29" s="8">
-        <v>46195.54471850695</v>
+        <v>46195.71138517361</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>117</v>
@@ -3460,13 +3460,13 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46122.3847758912</v>
+        <v>46122.55144255787</v>
       </c>
       <c r="C30" s="5">
-        <v>46195.54516429398</v>
+        <v>46195.711830960645</v>
       </c>
       <c r="D30" s="5">
-        <v>46195.54516583333</v>
+        <v>46195.711832500005</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3521,13 +3521,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="8">
-        <v>46122.38478104166</v>
+        <v>46122.551447708334</v>
       </c>
       <c r="C31" s="8">
-        <v>46133.661133263886</v>
+        <v>46133.82779993056</v>
       </c>
       <c r="D31" s="8">
-        <v>46133.66114655093</v>
+        <v>46133.82781321759</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>123</v>
@@ -3586,13 +3586,13 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46122.38478609954</v>
+        <v>46122.5514527662</v>
       </c>
       <c r="C32" s="5">
-        <v>46133.66106445601</v>
+        <v>46133.827731122685</v>
       </c>
       <c r="D32" s="5">
-        <v>46133.6610659375</v>
+        <v>46133.82773260417</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3647,13 +3647,13 @@
         <v>128</v>
       </c>
       <c r="B33" s="8">
-        <v>46122.384791296296</v>
+        <v>46122.55145796297</v>
       </c>
       <c r="C33" s="8">
-        <v>46133.66112020833</v>
+        <v>46133.827786875</v>
       </c>
       <c r="D33" s="8">
-        <v>46133.661121412035</v>
+        <v>46133.82778807871</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>129</v>
@@ -3708,13 +3708,13 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46122.38479633102</v>
+        <v>46122.55146299768</v>
       </c>
       <c r="C34" s="5">
-        <v>46133.6611012963</v>
+        <v>46133.82776796297</v>
       </c>
       <c r="D34" s="5">
-        <v>46133.66110246528</v>
+        <v>46133.827769131945</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3769,13 +3769,13 @@
         <v>134</v>
       </c>
       <c r="B35" s="8">
-        <v>46122.38480128472</v>
+        <v>46122.55146795139</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.50020540509</v>
+        <v>46181.66687207176</v>
       </c>
       <c r="D35" s="8">
-        <v>46214.01094108797</v>
+        <v>46214.17760775463</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>135</v>
@@ -3834,13 +3834,13 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46122.38480630787</v>
+        <v>46122.551472974534</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.50015100694</v>
+        <v>46181.66681767361</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.50015280093</v>
+        <v>46181.66681946759</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3895,13 +3895,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="8">
-        <v>46122.384855868055</v>
+        <v>46122.55152253472</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.50019012731</v>
+        <v>46181.66685679398</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.5001915162</v>
+        <v>46181.66685818287</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>143</v>
@@ -3956,13 +3956,13 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46122.384862245366</v>
+        <v>46122.55152891204</v>
       </c>
       <c r="C38" s="5">
-        <v>46154.70100114583</v>
+        <v>46154.867667812505</v>
       </c>
       <c r="D38" s="5">
-        <v>46189.00554646991</v>
+        <v>46189.172213136575</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -4021,13 +4021,13 @@
         <v>148</v>
       </c>
       <c r="B39" s="8">
-        <v>46122.384867395835</v>
+        <v>46122.5515340625</v>
       </c>
       <c r="C39" s="8">
-        <v>46154.70085026621</v>
+        <v>46154.86751693287</v>
       </c>
       <c r="D39" s="8">
-        <v>46154.70085260417</v>
+        <v>46154.86751927083</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>86</v>
@@ -4076,13 +4076,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46122.38487178241</v>
+        <v>46122.55153844907</v>
       </c>
       <c r="C40" s="5">
-        <v>46154.70090960649</v>
+        <v>46154.867576273144</v>
       </c>
       <c r="D40" s="5">
-        <v>46154.70091078704</v>
+        <v>46154.867577453704</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -4131,13 +4131,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46122.40826678241</v>
+        <v>46122.574933449076</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.500100335645</v>
+        <v>46181.666767002316</v>
       </c>
       <c r="D41" s="8">
-        <v>46221.03561572917</v>
+        <v>46221.20228239583</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -4196,13 +4196,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46122.40925430556</v>
+        <v>46122.575920972224</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.500040729166</v>
+        <v>46181.66670739584</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.500041886575</v>
+        <v>46181.66670855324</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>89</v>
@@ -4251,13 +4251,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46122.409418090276</v>
+        <v>46122.57608475695</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.50008614583</v>
+        <v>46181.666752812496</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.500087685185</v>
+        <v>46181.666754351856</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4306,13 +4306,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46122.40834771991</v>
+        <v>46122.57501438657</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.500291805554</v>
+        <v>46181.666958472226</v>
       </c>
       <c r="D44" s="5">
-        <v>46239.00492576389</v>
+        <v>46239.17159243056</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4371,13 +4371,13 @@
         <v>166</v>
       </c>
       <c r="B45" s="8">
-        <v>46122.41255444444</v>
+        <v>46122.57922111111</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.50023484953</v>
+        <v>46181.666901516204</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.50023640046</v>
+        <v>46181.66690306713</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>95</v>
@@ -4426,13 +4426,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46122.4128253588</v>
+        <v>46122.57949202546</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.500276562496</v>
+        <v>46181.66694322917</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.50027793982</v>
+        <v>46181.66694460648</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4481,13 +4481,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46125.362951550924</v>
+        <v>46125.529618217595</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.50055453704</v>
+        <v>46181.66722120371</v>
       </c>
       <c r="D47" s="8">
-        <v>46227.91110196759</v>
+        <v>46228.07776863426</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>172</v>
@@ -4546,13 +4546,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46125.36311331019</v>
+        <v>46125.52977997685</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.50049065972</v>
+        <v>46181.66715732639</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.500492453706</v>
+        <v>46181.66715912037</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>92</v>
@@ -4601,13 +4601,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46125.36325149305</v>
+        <v>46125.52991815972</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.5005374537</v>
+        <v>46181.66720412037</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.50053896991</v>
+        <v>46181.66720563658</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4656,13 +4656,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46122.384541886575</v>
+        <v>46122.55120855324</v>
       </c>
       <c r="C50" s="5">
-        <v>46195.34078462963</v>
+        <v>46195.5074512963</v>
       </c>
       <c r="D50" s="5">
-        <v>46195.34089821759</v>
+        <v>46195.50756488426</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4709,13 +4709,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46122.38487678241</v>
+        <v>46122.55154344907</v>
       </c>
       <c r="C51" s="8">
-        <v>46133.62917814815</v>
+        <v>46133.79584481481</v>
       </c>
       <c r="D51" s="8">
-        <v>46143.00447921296</v>
+        <v>46143.171145879634</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4774,13 +4774,13 @@
         <v>187</v>
       </c>
       <c r="B52" s="5">
-        <v>46122.38488232639</v>
+        <v>46122.551548993055</v>
       </c>
       <c r="C52" s="5">
-        <v>46134.62573756944</v>
+        <v>46134.79240423611</v>
       </c>
       <c r="D52" s="5">
-        <v>46198.021150451386</v>
+        <v>46198.18781711806</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4839,13 +4839,13 @@
         <v>191</v>
       </c>
       <c r="B53" s="8">
-        <v>46122.38489054398</v>
+        <v>46122.55155721065</v>
       </c>
       <c r="C53" s="8">
-        <v>46134.62578480324</v>
+        <v>46134.79245146991</v>
       </c>
       <c r="D53" s="8">
-        <v>46199.01705138889</v>
+        <v>46199.18371805556</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>82</v>
@@ -4902,13 +4902,13 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46122.38489901621</v>
+        <v>46122.55156568287</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.34094658565</v>
+        <v>46195.50761325231</v>
       </c>
       <c r="D54" s="5">
-        <v>46196.6024115162</v>
+        <v>46196.76907818287</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4965,13 +4965,13 @@
         <v>198</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.43695545139</v>
+        <v>46125.603622118055</v>
       </c>
       <c r="C55" s="8">
-        <v>46196.60238085648</v>
+        <v>46196.76904752315</v>
       </c>
       <c r="D55" s="8">
-        <v>46196.602385474536</v>
+        <v>46196.7690521412</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>199</v>
@@ -5018,13 +5018,13 @@
         <v>201</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.43700428241</v>
+        <v>46125.60367094907</v>
       </c>
       <c r="C56" s="5">
-        <v>46196.6023817824</v>
+        <v>46196.769048449074</v>
       </c>
       <c r="D56" s="5">
-        <v>46223.440795208335</v>
+        <v>46223.607461875</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>199</v>
@@ -5071,13 +5071,13 @@
         <v>202</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.43705284722</v>
+        <v>46125.60371951389</v>
       </c>
       <c r="C57" s="8">
-        <v>46196.602382627316</v>
+        <v>46196.76904929398</v>
       </c>
       <c r="D57" s="8">
-        <v>46196.60238616898</v>
+        <v>46196.76905283565</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>199</v>
@@ -5124,13 +5124,13 @@
         <v>203</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.43709796296</v>
+        <v>46125.60376462963</v>
       </c>
       <c r="C58" s="5">
-        <v>46196.60238340277</v>
+        <v>46196.769050069444</v>
       </c>
       <c r="D58" s="5">
-        <v>46196.60238648148</v>
+        <v>46196.76905314815</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>199</v>
@@ -5177,13 +5177,13 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.437150729165</v>
+        <v>46125.60381739584</v>
       </c>
       <c r="C59" s="8">
-        <v>46196.602384108795</v>
+        <v>46196.76905077546</v>
       </c>
       <c r="D59" s="8">
-        <v>46196.6023868287</v>
+        <v>46196.76905349537</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>199</v>
@@ -5230,13 +5230,13 @@
         <v>205</v>
       </c>
       <c r="B60" s="5">
-        <v>46122.38490304398</v>
+        <v>46122.551569710646</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.501105787036</v>
+        <v>46181.6677724537</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.501186574074</v>
+        <v>46181.66785324074</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>206</v>
@@ -5279,13 +5279,13 @@
         <v>208</v>
       </c>
       <c r="B61" s="8">
-        <v>46122.38490655093</v>
+        <v>46122.55157321759</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.50071136574</v>
+        <v>46181.667378032405</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.500728576386</v>
+        <v>46181.66739524306</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>209</v>
@@ -5344,13 +5344,13 @@
         <v>213</v>
       </c>
       <c r="B62" s="5">
-        <v>46122.41824972222</v>
+        <v>46122.58491638889</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.50074653935</v>
+        <v>46181.667413206014</v>
       </c>
       <c r="D62" s="5">
-        <v>46181.50076234953</v>
+        <v>46181.667429016205</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>214</v>
@@ -5409,13 +5409,13 @@
         <v>216</v>
       </c>
       <c r="B63" s="8">
-        <v>46125.36435991898</v>
+        <v>46125.53102658565</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.500763460645</v>
+        <v>46181.667430127316</v>
       </c>
       <c r="D63" s="8">
-        <v>46221.03561457176</v>
+        <v>46221.202281238424</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>217</v>
@@ -5474,13 +5474,13 @@
         <v>219</v>
       </c>
       <c r="B64" s="5">
-        <v>46122.38491179398</v>
+        <v>46122.55157846065</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.501089212965</v>
+        <v>46181.66775587963</v>
       </c>
       <c r="D64" s="5">
-        <v>46227.01578543981</v>
+        <v>46227.182452106485</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>215</v>
@@ -5539,13 +5539,13 @@
         <v>224</v>
       </c>
       <c r="B65" s="8">
-        <v>46122.38491716435</v>
+        <v>46122.551583831024</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.50212802083</v>
+        <v>46181.6687946875</v>
       </c>
       <c r="D65" s="8">
-        <v>46181.50224104167</v>
+        <v>46181.66890770833</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>225</v>
@@ -5588,13 +5588,13 @@
         <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46122.384920219905</v>
+        <v>46122.55158688658</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.49942690972</v>
+        <v>46181.666093576394</v>
       </c>
       <c r="D66" s="5">
-        <v>46238.02180614583</v>
+        <v>46238.1884728125</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>228</v>
@@ -5653,13 +5653,13 @@
         <v>232</v>
       </c>
       <c r="B67" s="8">
-        <v>46122.384925185186</v>
+        <v>46122.55159185185</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.49953199074</v>
+        <v>46181.6661986574</v>
       </c>
       <c r="D67" s="8">
-        <v>46256.03660438657</v>
+        <v>46256.20327105324</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>233</v>
@@ -5718,13 +5718,13 @@
         <v>235</v>
       </c>
       <c r="B68" s="5">
-        <v>46125.42914525463</v>
+        <v>46125.595811921296</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.501410324076</v>
+        <v>46181.66807699074</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.50141217593</v>
+        <v>46181.66807884259</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>236</v>
@@ -5773,13 +5773,13 @@
         <v>239</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.42943380787</v>
+        <v>46125.59610047453</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.50141914352</v>
+        <v>46181.66808581019</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.50142061342</v>
+        <v>46181.66808728009</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>199</v>
@@ -5828,13 +5828,13 @@
         <v>240</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.429543715276</v>
+        <v>46125.59621038195</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.501487326386</v>
+        <v>46181.66815399306</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.501488842594</v>
+        <v>46181.66815550926</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>199</v>
@@ -5883,13 +5883,13 @@
         <v>241</v>
       </c>
       <c r="B71" s="8">
-        <v>46125.42958805556</v>
+        <v>46125.59625472222</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.50150002315</v>
+        <v>46181.668166689815</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.501501527775</v>
+        <v>46181.66816819445</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>199</v>
@@ -5938,13 +5938,13 @@
         <v>242</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.42963248843</v>
+        <v>46125.59629915509</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.50151289352</v>
+        <v>46181.66817956018</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.50151412037</v>
+        <v>46181.66818078703</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>199</v>
@@ -5993,13 +5993,13 @@
         <v>243</v>
       </c>
       <c r="B73" s="8">
-        <v>46122.384930844906</v>
+        <v>46122.55159751157</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.50211394676</v>
+        <v>46181.66878061343</v>
       </c>
       <c r="D73" s="8">
-        <v>46252.035257337964</v>
+        <v>46252.20192400463</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>244</v>
@@ -6058,13 +6058,13 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46125.4298218287</v>
+        <v>46125.59648849537</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.501985254625</v>
+        <v>46181.668651921296</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.501986724536</v>
+        <v>46181.6686533912</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>199</v>
@@ -6113,13 +6113,13 @@
         <v>248</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.429951875005</v>
+        <v>46125.59661854166</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.50199983796</v>
+        <v>46181.66866650463</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.50200115741</v>
+        <v>46181.66866782407</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>199</v>
@@ -6168,13 +6168,13 @@
         <v>250</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.43000208333</v>
+        <v>46125.596668750004</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.50200921296</v>
+        <v>46181.66867587963</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.50201078704</v>
+        <v>46181.66867745371</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>199</v>
@@ -6223,13 +6223,13 @@
         <v>251</v>
       </c>
       <c r="B77" s="8">
-        <v>46125.430048842594</v>
+        <v>46125.59671550926</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.50201895833</v>
+        <v>46181.668685625</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.50202039352</v>
+        <v>46181.668687060184</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>199</v>
@@ -6278,13 +6278,13 @@
         <v>253</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.430088796296</v>
+        <v>46125.59675546296</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.5020371875</v>
+        <v>46181.66870385417</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.502038356484</v>
+        <v>46181.66870502315</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>199</v>
@@ -6333,13 +6333,13 @@
         <v>254</v>
       </c>
       <c r="B79" s="8">
-        <v>46122.38493690972</v>
+        <v>46122.55160357639</v>
       </c>
       <c r="C79" s="8">
-        <v>46195.3964589699</v>
+        <v>46195.563125636574</v>
       </c>
       <c r="D79" s="8">
-        <v>46195.39662366898</v>
+        <v>46195.563290335645</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>206</v>
@@ -6386,13 +6386,13 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46122.38494012732</v>
+        <v>46122.55160679398</v>
       </c>
       <c r="C80" s="5">
-        <v>46195.39660269676</v>
+        <v>46195.563269363425</v>
       </c>
       <c r="D80" s="5">
-        <v>46240.43892752315</v>
+        <v>46240.605594189816</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>257</v>
@@ -6451,13 +6451,13 @@
         <v>259</v>
       </c>
       <c r="B81" s="8">
-        <v>46122.38494559028</v>
+        <v>46122.551612256946</v>
       </c>
       <c r="C81" s="8">
-        <v>46195.34084651621</v>
+        <v>46195.50751318287</v>
       </c>
       <c r="D81" s="8">
-        <v>46195.3408646412</v>
+        <v>46195.50753130787</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>260</v>
@@ -6516,13 +6516,13 @@
         <v>261</v>
       </c>
       <c r="B82" s="5">
-        <v>46122.38495090278</v>
+        <v>46122.55161756944</v>
       </c>
       <c r="C82" s="5">
-        <v>46195.340851851855</v>
+        <v>46195.50751851852</v>
       </c>
       <c r="D82" s="5">
-        <v>46195.34086592593</v>
+        <v>46195.50753259259</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>262</v>
@@ -6581,13 +6581,13 @@
         <v>263</v>
       </c>
       <c r="B83" s="8">
-        <v>46122.384956215275</v>
+        <v>46122.55162288195</v>
       </c>
       <c r="C83" s="8">
-        <v>46195.34085677083</v>
+        <v>46195.507523437496</v>
       </c>
       <c r="D83" s="8">
-        <v>46195.3408728125</v>
+        <v>46195.507539479164</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>264</v>
@@ -6646,13 +6646,13 @@
         <v>265</v>
       </c>
       <c r="B84" s="5">
-        <v>46122.427324965276</v>
+        <v>46122.59399163195</v>
       </c>
       <c r="C84" s="5">
-        <v>46193.76648644676</v>
+        <v>46193.93315311342</v>
       </c>
       <c r="D84" s="5">
-        <v>46241.02186137732</v>
+        <v>46241.18852804398</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>266</v>
@@ -6711,13 +6711,13 @@
         <v>268</v>
       </c>
       <c r="B85" s="8">
-        <v>46122.3849615162</v>
+        <v>46122.551628182875</v>
       </c>
       <c r="C85" s="8">
-        <v>46195.39639328704</v>
+        <v>46195.5630599537</v>
       </c>
       <c r="D85" s="8">
-        <v>46227.911395138886</v>
+        <v>46228.07806180556</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>269</v>
@@ -6764,13 +6764,13 @@
         <v>271</v>
       </c>
       <c r="B86" s="5">
-        <v>46122.38496491898</v>
+        <v>46122.55163158565</v>
       </c>
       <c r="C86" s="5">
-        <v>46195.34102184028</v>
+        <v>46195.50768850694</v>
       </c>
       <c r="D86" s="5">
-        <v>46223.441128182865</v>
+        <v>46223.60779484954</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>272</v>
@@ -6829,13 +6829,13 @@
         <v>274</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.43083025463</v>
+        <v>46125.5974969213</v>
       </c>
       <c r="C87" s="8">
-        <v>46196.60125040509</v>
+        <v>46196.76791707176</v>
       </c>
       <c r="D87" s="8">
-        <v>46223.440315810185</v>
+        <v>46223.60698247685</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>199</v>
@@ -6884,13 +6884,13 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46125.430879039355</v>
+        <v>46125.59754570602</v>
       </c>
       <c r="C88" s="5">
-        <v>46196.601287384256</v>
+        <v>46196.76795405093</v>
       </c>
       <c r="D88" s="5">
-        <v>46223.44030688658</v>
+        <v>46223.60697355324</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>199</v>
@@ -6939,13 +6939,13 @@
         <v>277</v>
       </c>
       <c r="B89" s="8">
-        <v>46125.430940439815</v>
+        <v>46125.59760710648</v>
       </c>
       <c r="C89" s="8">
-        <v>46196.601261550924</v>
+        <v>46196.767928217596</v>
       </c>
       <c r="D89" s="8">
-        <v>46223.44030333334</v>
+        <v>46223.60697</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>199</v>
@@ -6994,13 +6994,13 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46125.43099224537</v>
+        <v>46125.59765891204</v>
       </c>
       <c r="C90" s="5">
-        <v>46196.601279849536</v>
+        <v>46196.76794651621</v>
       </c>
       <c r="D90" s="5">
-        <v>46223.44029975694</v>
+        <v>46223.60696642361</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>199</v>
@@ -7049,13 +7049,13 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.431036724534</v>
+        <v>46125.597703391206</v>
       </c>
       <c r="C91" s="8">
-        <v>46196.60127434028</v>
+        <v>46196.76794100694</v>
       </c>
       <c r="D91" s="8">
-        <v>46223.44029474537</v>
+        <v>46223.606961412035</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>199</v>
@@ -7104,13 +7104,13 @@
         <v>280</v>
       </c>
       <c r="B92" s="5">
-        <v>46122.38503993055</v>
+        <v>46122.55170659722</v>
       </c>
       <c r="C92" s="5">
-        <v>46196.60088846065</v>
+        <v>46196.76755512731</v>
       </c>
       <c r="D92" s="5">
-        <v>46237.368255925925</v>
+        <v>46237.53492259259</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>
@@ -7169,13 +7169,13 @@
         <v>282</v>
       </c>
       <c r="B93" s="8">
-        <v>46125.43316075232</v>
+        <v>46125.59982741898</v>
       </c>
       <c r="C93" s="8">
-        <v>46196.60133528935</v>
+        <v>46196.76800195602</v>
       </c>
       <c r="D93" s="8">
-        <v>46223.44041752315</v>
+        <v>46223.60708418982</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>199</v>
@@ -7224,13 +7224,13 @@
         <v>285</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.43322416667</v>
+        <v>46125.599890833335</v>
       </c>
       <c r="C94" s="5">
-        <v>46196.601356354164</v>
+        <v>46196.768023020835</v>
       </c>
       <c r="D94" s="5">
-        <v>46223.44041325232</v>
+        <v>46223.60707991898</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>199</v>
@@ -7279,13 +7279,13 @@
         <v>287</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.43326467593</v>
+        <v>46125.59993134259</v>
       </c>
       <c r="C95" s="8">
-        <v>46196.601348275464</v>
+        <v>46196.76801494213</v>
       </c>
       <c r="D95" s="8">
-        <v>46223.440409166666</v>
+        <v>46223.60707583334</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>199</v>
@@ -7334,13 +7334,13 @@
         <v>288</v>
       </c>
       <c r="B96" s="5">
-        <v>46125.433302627316</v>
+        <v>46125.59996929398</v>
       </c>
       <c r="C96" s="5">
-        <v>46196.60138443287</v>
+        <v>46196.76805109954</v>
       </c>
       <c r="D96" s="5">
-        <v>46223.440405393514</v>
+        <v>46223.607072060186</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>199</v>
@@ -7389,13 +7389,13 @@
         <v>289</v>
       </c>
       <c r="B97" s="8">
-        <v>46125.43334484954</v>
+        <v>46125.6000115162</v>
       </c>
       <c r="C97" s="8">
-        <v>46196.60139039352</v>
+        <v>46196.76805706018</v>
       </c>
       <c r="D97" s="8">
-        <v>46223.44039952546</v>
+        <v>46223.607066192126</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>199</v>
@@ -7444,13 +7444,13 @@
         <v>290</v>
       </c>
       <c r="B98" s="5">
-        <v>46122.38497746528</v>
+        <v>46122.55164413195</v>
       </c>
       <c r="C98" s="5">
-        <v>46196.601731574076</v>
+        <v>46196.76839824074</v>
       </c>
       <c r="D98" s="5">
-        <v>46227.94037759259</v>
+        <v>46228.10704425926</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>291</v>
@@ -7509,13 +7509,13 @@
         <v>293</v>
       </c>
       <c r="B99" s="8">
-        <v>46125.43249607639</v>
+        <v>46125.599162743056</v>
       </c>
       <c r="C99" s="8">
-        <v>46196.601522997684</v>
+        <v>46196.76818966435</v>
       </c>
       <c r="D99" s="8">
-        <v>46223.44053969908</v>
+        <v>46223.60720636574</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>199</v>
@@ -7564,13 +7564,13 @@
         <v>296</v>
       </c>
       <c r="B100" s="5">
-        <v>46125.4326358449</v>
+        <v>46125.599302511575</v>
       </c>
       <c r="C100" s="5">
-        <v>46196.601537546296</v>
+        <v>46196.76820421296</v>
       </c>
       <c r="D100" s="5">
-        <v>46223.44053581019</v>
+        <v>46223.60720247685</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>199</v>
@@ -7619,13 +7619,13 @@
         <v>297</v>
       </c>
       <c r="B101" s="8">
-        <v>46125.43267978009</v>
+        <v>46125.59934644676</v>
       </c>
       <c r="C101" s="8">
-        <v>46196.601709282404</v>
+        <v>46196.768375949076</v>
       </c>
       <c r="D101" s="8">
-        <v>46223.440531527776</v>
+        <v>46223.60719819444</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>199</v>
@@ -7674,13 +7674,13 @@
         <v>298</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.43272190972</v>
+        <v>46125.59938857639</v>
       </c>
       <c r="C102" s="5">
-        <v>46196.60171030092</v>
+        <v>46196.76837696759</v>
       </c>
       <c r="D102" s="5">
-        <v>46223.44052751157</v>
+        <v>46223.60719417824</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>199</v>
@@ -7729,13 +7729,13 @@
         <v>299</v>
       </c>
       <c r="B103" s="8">
-        <v>46125.43276428241</v>
+        <v>46125.59943094908</v>
       </c>
       <c r="C103" s="8">
-        <v>46196.60171123843</v>
+        <v>46196.76837790509</v>
       </c>
       <c r="D103" s="8">
-        <v>46223.44052174769</v>
+        <v>46223.60718841435</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>199</v>
@@ -7784,13 +7784,13 @@
         <v>300</v>
       </c>
       <c r="B104" s="5">
-        <v>46122.3849843287</v>
+        <v>46122.551650995374</v>
       </c>
       <c r="C104" s="5">
-        <v>46196.601881215276</v>
+        <v>46196.76854788195</v>
       </c>
       <c r="D104" s="5">
-        <v>46237.36827594908</v>
+        <v>46237.53494261574</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>301</v>
@@ -7849,13 +7849,13 @@
         <v>302</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.43286347222</v>
+        <v>46125.59953013889</v>
       </c>
       <c r="C105" s="8">
-        <v>46196.60186116898</v>
+        <v>46196.76852783565</v>
       </c>
       <c r="D105" s="8">
-        <v>46223.44064487268</v>
+        <v>46223.60731153935</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>199</v>
@@ -7904,13 +7904,13 @@
         <v>304</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.43294756944</v>
+        <v>46125.59961423611</v>
       </c>
       <c r="C106" s="5">
-        <v>46196.60179663195</v>
+        <v>46196.76846329861</v>
       </c>
       <c r="D106" s="5">
-        <v>46223.440641168985</v>
+        <v>46223.60730783565</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>199</v>
@@ -7959,13 +7959,13 @@
         <v>305</v>
       </c>
       <c r="B107" s="8">
-        <v>46125.43298765046</v>
+        <v>46125.599654317135</v>
       </c>
       <c r="C107" s="8">
-        <v>46196.601862129624</v>
+        <v>46196.768528796296</v>
       </c>
       <c r="D107" s="8">
-        <v>46223.44063728009</v>
+        <v>46223.60730394676</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>199</v>
@@ -8014,13 +8014,13 @@
         <v>306</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.43290399306</v>
+        <v>46125.59957065972</v>
       </c>
       <c r="C108" s="5">
-        <v>46196.601862881944</v>
+        <v>46196.768529548615</v>
       </c>
       <c r="D108" s="5">
-        <v>46223.44063300926</v>
+        <v>46223.607299675925</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>199</v>
@@ -8069,13 +8069,13 @@
         <v>307</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.433030451386</v>
+        <v>46125.59969711806</v>
       </c>
       <c r="C109" s="8">
-        <v>46196.601863738426</v>
+        <v>46196.7685304051</v>
       </c>
       <c r="D109" s="8">
-        <v>46223.44062707176</v>
+        <v>46223.60729373843</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>199</v>
@@ -8124,13 +8124,13 @@
         <v>308</v>
       </c>
       <c r="B110" s="5">
-        <v>46122.38497059028</v>
+        <v>46122.55163725694</v>
       </c>
       <c r="C110" s="5">
-        <v>46196.6020008912</v>
+        <v>46196.76866755787</v>
       </c>
       <c r="D110" s="5">
-        <v>46223.44111295139</v>
+        <v>46223.607779618054</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>309</v>
@@ -8189,13 +8189,13 @@
         <v>310</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.431135439816</v>
+        <v>46125.59780210648</v>
       </c>
       <c r="C111" s="8">
-        <v>46196.60198236111</v>
+        <v>46196.76864902778</v>
       </c>
       <c r="D111" s="8">
-        <v>46223.44074164351</v>
+        <v>46223.607408310185</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>199</v>
@@ -8244,13 +8244,13 @@
         <v>313</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.43117026621</v>
+        <v>46125.597836932866</v>
       </c>
       <c r="C112" s="5">
-        <v>46196.601983333334</v>
+        <v>46196.76865</v>
       </c>
       <c r="D112" s="5">
-        <v>46223.4407377662</v>
+        <v>46223.60740443287</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>199</v>
@@ -8299,13 +8299,13 @@
         <v>314</v>
       </c>
       <c r="B113" s="8">
-        <v>46125.43125422453</v>
+        <v>46125.5979208912</v>
       </c>
       <c r="C113" s="8">
-        <v>46196.6019841088</v>
+        <v>46196.76865077546</v>
       </c>
       <c r="D113" s="8">
-        <v>46223.44073386574</v>
+        <v>46223.607400532404</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>199</v>
@@ -8354,13 +8354,13 @@
         <v>315</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.431214212964</v>
+        <v>46125.59788087963</v>
       </c>
       <c r="C114" s="5">
-        <v>46196.60198486111</v>
+        <v>46196.768651527775</v>
       </c>
       <c r="D114" s="5">
-        <v>46223.44073002315</v>
+        <v>46223.60739668981</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>199</v>
@@ -8409,13 +8409,13 @@
         <v>316</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.43129835648</v>
+        <v>46125.597965023146</v>
       </c>
       <c r="C115" s="8">
-        <v>46196.60198564814</v>
+        <v>46196.768652314815</v>
       </c>
       <c r="D115" s="8">
-        <v>46223.440723796295</v>
+        <v>46223.60739046296</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>199</v>
@@ -8464,13 +8464,13 @@
         <v>317</v>
       </c>
       <c r="B116" s="5">
-        <v>46122.38505377315</v>
+        <v>46122.55172043982</v>
       </c>
       <c r="C116" s="5">
-        <v>46196.6021055787</v>
+        <v>46196.76877224537</v>
       </c>
       <c r="D116" s="5">
-        <v>46237.368298009256</v>
+        <v>46237.53496467593</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>318</v>
@@ -8529,13 +8529,13 @@
         <v>319</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.43371586806</v>
+        <v>46125.60038253472</v>
       </c>
       <c r="C117" s="8">
-        <v>46196.602085914354</v>
+        <v>46196.76875258102</v>
       </c>
       <c r="D117" s="8">
-        <v>46223.4409177662</v>
+        <v>46223.60758443287</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>199</v>
@@ -8582,13 +8582,13 @@
         <v>321</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.43376346065</v>
+        <v>46125.60043012731</v>
       </c>
       <c r="C118" s="5">
-        <v>46223.44078604167</v>
+        <v>46223.60745270833</v>
       </c>
       <c r="D118" s="5">
-        <v>46223.440913391205</v>
+        <v>46223.60758005787</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>199</v>
@@ -8635,13 +8635,13 @@
         <v>322</v>
       </c>
       <c r="B119" s="8">
-        <v>46125.43380623843</v>
+        <v>46125.60047290509</v>
       </c>
       <c r="C119" s="8">
-        <v>46196.60208751158</v>
+        <v>46196.768754178236</v>
       </c>
       <c r="D119" s="8">
-        <v>46223.44090908565</v>
+        <v>46223.607575752314</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>199</v>
@@ -8688,13 +8688,13 @@
         <v>323</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.4338474074</v>
+        <v>46125.600514074074</v>
       </c>
       <c r="C120" s="5">
-        <v>46196.602088263884</v>
+        <v>46196.768754930556</v>
       </c>
       <c r="D120" s="5">
-        <v>46223.440904930554</v>
+        <v>46223.607571597226</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>199</v>
@@ -8741,13 +8741,13 @@
         <v>324</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.43389193287</v>
+        <v>46125.60055859954</v>
       </c>
       <c r="C121" s="8">
-        <v>46196.602089224536</v>
+        <v>46196.7687558912</v>
       </c>
       <c r="D121" s="8">
-        <v>46223.44089886574</v>
+        <v>46223.60756553241</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>199</v>
@@ -8794,13 +8794,13 @@
         <v>325</v>
       </c>
       <c r="B122" s="5">
-        <v>46122.385063194444</v>
+        <v>46122.55172986111</v>
       </c>
       <c r="C122" s="5">
-        <v>46196.60250790509</v>
+        <v>46196.76917457176</v>
       </c>
       <c r="D122" s="5">
-        <v>46223.44110321759</v>
+        <v>46223.60776988426</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>326</v>
@@ -8859,13 +8859,13 @@
         <v>328</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.4339775</v>
+        <v>46125.60064416667</v>
       </c>
       <c r="C123" s="8">
-        <v>46196.6024843287</v>
+        <v>46196.76915099537</v>
       </c>
       <c r="D123" s="8">
-        <v>46223.44101393518</v>
+        <v>46223.607680601854</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>199</v>
@@ -8912,13 +8912,13 @@
         <v>330</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.43402074074</v>
+        <v>46125.60068740741</v>
       </c>
       <c r="C124" s="5">
-        <v>46196.60248570602</v>
+        <v>46196.76915237268</v>
       </c>
       <c r="D124" s="5">
-        <v>46223.44101039352</v>
+        <v>46223.60767706019</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>199</v>
@@ -8965,13 +8965,13 @@
         <v>331</v>
       </c>
       <c r="B125" s="8">
-        <v>46125.43407178241</v>
+        <v>46125.60073844907</v>
       </c>
       <c r="C125" s="8">
-        <v>46196.60248674768</v>
+        <v>46196.76915341435</v>
       </c>
       <c r="D125" s="8">
-        <v>46223.44100614583</v>
+        <v>46223.607672812504</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>199</v>
@@ -9018,13 +9018,13 @@
         <v>332</v>
       </c>
       <c r="B126" s="5">
-        <v>46125.434109560185</v>
+        <v>46125.60077622686</v>
       </c>
       <c r="C126" s="5">
-        <v>46196.60248771991</v>
+        <v>46196.76915438657</v>
       </c>
       <c r="D126" s="5">
-        <v>46223.44100177083</v>
+        <v>46223.6076684375</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>199</v>
@@ -9071,13 +9071,13 @@
         <v>333</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.43416247686</v>
+        <v>46125.600829143514</v>
       </c>
       <c r="C127" s="8">
-        <v>46196.60248869213</v>
+        <v>46196.769155358794</v>
       </c>
       <c r="D127" s="8">
-        <v>46223.440996226855</v>
+        <v>46223.60766289352</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>199</v>
@@ -9124,13 +9124,13 @@
         <v>334</v>
       </c>
       <c r="B128" s="5">
-        <v>46122.38506837963</v>
+        <v>46122.5517350463</v>
       </c>
       <c r="C128" s="5">
-        <v>46195.39650850694</v>
+        <v>46195.56317517361</v>
       </c>
       <c r="D128" s="5">
-        <v>46196.60293743055</v>
+        <v>46196.76960409722</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>335</v>
@@ -9177,13 +9177,13 @@
         <v>337</v>
       </c>
       <c r="B129" s="8">
-        <v>46122.38507239583</v>
+        <v>46122.5517390625</v>
       </c>
       <c r="C129" s="8">
-        <v>46196.60269986111</v>
+        <v>46196.76936652778</v>
       </c>
       <c r="D129" s="8">
-        <v>46240.43895601852</v>
+        <v>46240.60562268519</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>338</v>
@@ -9242,13 +9242,13 @@
         <v>342</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.43427064815</v>
+        <v>46125.60093731481</v>
       </c>
       <c r="C130" s="5">
-        <v>46196.602678483796</v>
+        <v>46196.76934515046</v>
       </c>
       <c r="D130" s="5">
-        <v>46196.60268401621</v>
+        <v>46196.769350682865</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>199</v>
@@ -9295,13 +9295,13 @@
         <v>344</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.4347141551</v>
+        <v>46125.601380821754</v>
       </c>
       <c r="C131" s="8">
-        <v>46196.602679641204</v>
+        <v>46196.769346307876</v>
       </c>
       <c r="D131" s="8">
-        <v>46196.60268447916</v>
+        <v>46196.769351145835</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>199</v>
@@ -9348,13 +9348,13 @@
         <v>345</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.43475814815</v>
+        <v>46125.60142481481</v>
       </c>
       <c r="C132" s="5">
-        <v>46196.60268056713</v>
+        <v>46196.7693472338</v>
       </c>
       <c r="D132" s="5">
-        <v>46196.60268488426</v>
+        <v>46196.76935155093</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>199</v>
@@ -9401,13 +9401,13 @@
         <v>346</v>
       </c>
       <c r="B133" s="8">
-        <v>46125.434794189816</v>
+        <v>46125.60146085648</v>
       </c>
       <c r="C133" s="8">
-        <v>46196.60268145833</v>
+        <v>46196.769348125</v>
       </c>
       <c r="D133" s="8">
-        <v>46196.602685254635</v>
+        <v>46196.76935192129</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>199</v>
@@ -9454,13 +9454,13 @@
         <v>347</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.434835416665</v>
+        <v>46125.60150208333</v>
       </c>
       <c r="C134" s="5">
-        <v>46196.60268231481</v>
+        <v>46196.769348981485</v>
       </c>
       <c r="D134" s="5">
-        <v>46196.602685624996</v>
+        <v>46196.76935229167</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>199</v>
@@ -9507,13 +9507,13 @@
         <v>348</v>
       </c>
       <c r="B135" s="8">
-        <v>46122.38507716435</v>
+        <v>46122.55174383102</v>
       </c>
       <c r="C135" s="8">
-        <v>46196.60293025463</v>
+        <v>46196.769596921295</v>
       </c>
       <c r="D135" s="8">
-        <v>46227.94093403935</v>
+        <v>46228.10760070602</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>349</v>
@@ -9570,13 +9570,13 @@
         <v>350</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.4344203125</v>
+        <v>46125.601086979164</v>
       </c>
       <c r="C136" s="5">
-        <v>46196.602804884256</v>
+        <v>46196.76947155093</v>
       </c>
       <c r="D136" s="5">
-        <v>46223.44170403935</v>
+        <v>46223.60837070602</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>199</v>
@@ -9623,13 +9623,13 @@
         <v>352</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.4344865162</v>
+        <v>46125.60115318287</v>
       </c>
       <c r="C137" s="8">
-        <v>46196.60283766204</v>
+        <v>46196.7695043287</v>
       </c>
       <c r="D137" s="8">
-        <v>46223.44169987268</v>
+        <v>46223.60836653935</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>199</v>
@@ -9676,13 +9676,13 @@
         <v>353</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.43453724537</v>
+        <v>46125.60120391204</v>
       </c>
       <c r="C138" s="5">
-        <v>46196.60283883102</v>
+        <v>46196.76950549769</v>
       </c>
       <c r="D138" s="5">
-        <v>46223.4416959375</v>
+        <v>46223.608362604165</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>199</v>
@@ -9729,13 +9729,13 @@
         <v>354</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.434591296296</v>
+        <v>46125.60125796296</v>
       </c>
       <c r="C139" s="8">
-        <v>46196.60283971065</v>
+        <v>46196.76950637731</v>
       </c>
       <c r="D139" s="8">
-        <v>46223.44169238426</v>
+        <v>46223.60835905092</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>199</v>
@@ -9782,13 +9782,13 @@
         <v>355</v>
       </c>
       <c r="B140" s="5">
-        <v>46125.43463761574</v>
+        <v>46125.601304282405</v>
       </c>
       <c r="C140" s="5">
-        <v>46196.60284063657</v>
+        <v>46196.76950730324</v>
       </c>
       <c r="D140" s="5">
-        <v>46223.44168600695</v>
+        <v>46223.60835267361</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>199</v>
@@ -9835,13 +9835,13 @@
         <v>356</v>
       </c>
       <c r="B141" s="8">
-        <v>46122.38508202546</v>
+        <v>46122.55174869213</v>
       </c>
       <c r="C141" s="8">
-        <v>46191.539318634255</v>
+        <v>46191.70598530093</v>
       </c>
       <c r="D141" s="8">
-        <v>46240.438971701384</v>
+        <v>46240.605638368055</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>357</v>
@@ -9898,13 +9898,13 @@
         <v>358</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.434919837964</v>
+        <v>46125.60158650463</v>
       </c>
       <c r="C142" s="5">
-        <v>46196.60301796296</v>
+        <v>46196.76968462963</v>
       </c>
       <c r="D142" s="5">
-        <v>46196.60302322917</v>
+        <v>46196.76968989584</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>199</v>
@@ -9951,13 +9951,13 @@
         <v>360</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.43496466435</v>
+        <v>46125.60163133102</v>
       </c>
       <c r="C143" s="8">
-        <v>46196.60301918982</v>
+        <v>46196.76968585648</v>
       </c>
       <c r="D143" s="8">
-        <v>46196.60302364583</v>
+        <v>46196.7696903125</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>199</v>
@@ -10004,13 +10004,13 @@
         <v>361</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.43500349537</v>
+        <v>46125.60167016204</v>
       </c>
       <c r="C144" s="5">
-        <v>46196.603019988426</v>
+        <v>46196.7696866551</v>
       </c>
       <c r="D144" s="5">
-        <v>46196.60302403935</v>
+        <v>46196.769690706016</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>199</v>
@@ -10057,13 +10057,13 @@
         <v>363</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.43503768518</v>
+        <v>46125.60170435185</v>
       </c>
       <c r="C145" s="8">
-        <v>46196.60302072916</v>
+        <v>46196.769687395834</v>
       </c>
       <c r="D145" s="8">
-        <v>46196.60302447916</v>
+        <v>46196.76969114583</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>199</v>
@@ -10110,13 +10110,13 @@
         <v>364</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.4350728125</v>
+        <v>46125.60173947917</v>
       </c>
       <c r="C146" s="5">
-        <v>46196.60302144676</v>
+        <v>46196.769688113425</v>
       </c>
       <c r="D146" s="5">
-        <v>46196.60302497685</v>
+        <v>46196.76969164352</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>199</v>
@@ -10163,13 +10163,13 @@
         <v>365</v>
       </c>
       <c r="B147" s="8">
-        <v>46122.38508680556</v>
+        <v>46122.551753472224</v>
       </c>
       <c r="C147" s="8">
-        <v>46191.53937342593</v>
+        <v>46191.70604009259</v>
       </c>
       <c r="D147" s="8">
-        <v>46240.4389865625</v>
+        <v>46240.60565322917</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>366</v>
@@ -10226,13 +10226,13 @@
         <v>368</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.43514888889</v>
+        <v>46125.60181555555</v>
       </c>
       <c r="C148" s="5">
-        <v>46196.60312598379</v>
+        <v>46196.76979265046</v>
       </c>
       <c r="D148" s="5">
-        <v>46196.603129027775</v>
+        <v>46196.76979569445</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>199</v>
@@ -10279,13 +10279,13 @@
         <v>369</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.43519024306</v>
+        <v>46125.60185690972</v>
       </c>
       <c r="C149" s="8">
-        <v>46196.603126898146</v>
+        <v>46196.76979356482</v>
       </c>
       <c r="D149" s="8">
-        <v>46196.60312947917</v>
+        <v>46196.76979614583</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>199</v>
@@ -10332,13 +10332,13 @@
         <v>370</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.43523282408</v>
+        <v>46125.601899490735</v>
       </c>
       <c r="C150" s="5">
-        <v>46196.60312755787</v>
+        <v>46196.769794224536</v>
       </c>
       <c r="D150" s="5">
-        <v>46196.603129814815</v>
+        <v>46196.76979648148</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>199</v>
@@ -10385,13 +10385,13 @@
         <v>371</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.43527268519</v>
+        <v>46125.60193935185</v>
       </c>
       <c r="C151" s="8">
-        <v>46196.603098101856</v>
+        <v>46196.76976476852</v>
       </c>
       <c r="D151" s="8">
-        <v>46196.60310020833</v>
+        <v>46196.769766875004</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>199</v>
@@ -10438,13 +10438,13 @@
         <v>372</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.43531043982</v>
+        <v>46125.60197710648</v>
       </c>
       <c r="C152" s="5">
-        <v>46196.603105393515</v>
+        <v>46196.76977206019</v>
       </c>
       <c r="D152" s="5">
-        <v>46196.60310703704</v>
+        <v>46196.76977370371</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>199</v>
@@ -10491,13 +10491,13 @@
         <v>373</v>
       </c>
       <c r="B153" s="8">
-        <v>46122.38509195602</v>
+        <v>46122.551758622685</v>
       </c>
       <c r="C153" s="8">
-        <v>46240.487175752314</v>
+        <v>46240.65384241898</v>
       </c>
       <c r="D153" s="8">
-        <v>46240.48718778935</v>
+        <v>46240.65385445602</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>374</v>
@@ -10544,13 +10544,13 @@
         <v>376</v>
       </c>
       <c r="B154" s="5">
-        <v>46122.38509467593</v>
+        <v>46122.55176134259</v>
       </c>
       <c r="C154" s="5">
-        <v>46240.487151678244</v>
+        <v>46240.65381834491</v>
       </c>
       <c r="D154" s="5">
-        <v>46240.487169479165</v>
+        <v>46240.65383614584</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>377</v>
@@ -10609,13 +10609,13 @@
         <v>380</v>
       </c>
       <c r="B155" s="8">
-        <v>46122.38509943287</v>
+        <v>46122.55176609954</v>
       </c>
       <c r="C155" s="8">
-        <v>46240.487160578705</v>
+        <v>46240.65382724537</v>
       </c>
       <c r="D155" s="8">
-        <v>46240.4871771412</v>
+        <v>46240.65384380787</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>381</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -5999,7 +5999,7 @@
         <v>46181.66878061343</v>
       </c>
       <c r="D73" s="8">
-        <v>46252.20192400463</v>
+        <v>46260.20541972222</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>244</v>
@@ -6043,8 +6043,8 @@
       <c r="R73" s="8">
         <v>46259</v>
       </c>
-      <c r="S73" s="12" t="s">
-        <v>74</v>
+      <c r="S73" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T73" s="9">
         <v>1</v>
@@ -6457,7 +6457,7 @@
         <v>46195.50751318287</v>
       </c>
       <c r="D81" s="8">
-        <v>46195.50753130787</v>
+        <v>46260.18797238426</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>260</v>
@@ -6501,8 +6501,8 @@
       <c r="R81" s="8">
         <v>46267</v>
       </c>
-      <c r="S81" s="11" t="s">
-        <v>107</v>
+      <c r="S81" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -2214,7 +2214,7 @@
         <v>46193.93280347223</v>
       </c>
       <c r="D10" s="5">
-        <v>46223.423621180555</v>
+        <v>46263.5553215625</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -4662,7 +4662,7 @@
         <v>46195.5074512963</v>
       </c>
       <c r="D50" s="5">
-        <v>46195.50756488426</v>
+        <v>46263.75423934028</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -3153,7 +3153,7 @@
         <v>46174.626168703704</v>
       </c>
       <c r="D25" s="8">
-        <v>46258.19630414352</v>
+        <v>46266.17935409722</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -3197,8 +3197,8 @@
       <c r="R25" s="8">
         <v>46265</v>
       </c>
-      <c r="S25" s="12" t="s">
-        <v>74</v>
+      <c r="S25" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T25" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -6457,7 +6457,7 @@
         <v>46195.50751318287</v>
       </c>
       <c r="D81" s="8">
-        <v>46260.18797238426</v>
+        <v>46268.17383480324</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>260</v>
@@ -6501,8 +6501,8 @@
       <c r="R81" s="8">
         <v>46267</v>
       </c>
-      <c r="S81" s="12" t="s">
-        <v>74</v>
+      <c r="S81" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -6770,7 +6770,7 @@
         <v>46195.50768850694</v>
       </c>
       <c r="D86" s="5">
-        <v>46223.60779484954</v>
+        <v>46272.13737606481</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>272</v>
@@ -6814,8 +6814,8 @@
       <c r="R86" s="5">
         <v>46279</v>
       </c>
-      <c r="S86" s="11" t="s">
-        <v>107</v>
+      <c r="S86" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>

--- a/data/50001466 - ZITRON PERU PODEROSA.xlsx
+++ b/data/50001466 - ZITRON PERU PODEROSA.xlsx
@@ -7110,7 +7110,7 @@
         <v>46196.76755512731</v>
       </c>
       <c r="D92" s="5">
-        <v>46237.53492259259</v>
+        <v>46275.15928740741</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>
@@ -7154,8 +7154,8 @@
       <c r="R92" s="5">
         <v>46282</v>
       </c>
-      <c r="S92" s="11" t="s">
-        <v>107</v>
+      <c r="S92" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
